--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4800055C-8A5E-1A49-95E3-C7F361278D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2654F286-6A14-9849-B4CB-492BD3771A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="481">
   <si>
     <t>Surname</t>
   </si>
@@ -788,9 +788,6 @@
     <t>H262222f</t>
   </si>
   <si>
-    <t>Sukuta Mutandwa</t>
-  </si>
-  <si>
     <t>H262905I</t>
   </si>
   <si>
@@ -1422,13 +1419,73 @@
   </si>
   <si>
     <t>H263423S</t>
+  </si>
+  <si>
+    <t>Mutandwa</t>
+  </si>
+  <si>
+    <t>Dhakwa</t>
+  </si>
+  <si>
+    <t>H265870F</t>
+  </si>
+  <si>
+    <t>Jimha</t>
+  </si>
+  <si>
+    <t>H267967T</t>
+  </si>
+  <si>
+    <t>Kupara</t>
+  </si>
+  <si>
+    <t>H267904U</t>
+  </si>
+  <si>
+    <t>Makhiwa</t>
+  </si>
+  <si>
+    <t>H268746K</t>
+  </si>
+  <si>
+    <t>Mhike</t>
+  </si>
+  <si>
+    <t>H269731S</t>
+  </si>
+  <si>
+    <t>Mkanya</t>
+  </si>
+  <si>
+    <t>H268897W</t>
+  </si>
+  <si>
+    <t>H265254X</t>
+  </si>
+  <si>
+    <t>Mutsamwira</t>
+  </si>
+  <si>
+    <t>H266222Y</t>
+  </si>
+  <si>
+    <t>Makoni</t>
+  </si>
+  <si>
+    <t>H250504N</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>H240464X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -1460,6 +1517,12 @@
       <sz val="13"/>
       <color rgb="FF333333"/>
       <name val="Times"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1518,7 +1581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1533,6 +1596,11 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1577,10 +1645,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
-  <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="C1:C228"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M235" totalsRowShown="0">
+  <autoFilter ref="A1:M235" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M235">
+    <sortCondition ref="C1:C235"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -1918,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M228"/>
+  <dimension ref="A1:M235"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2843,10 +2911,10 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>15</v>
@@ -3231,10 +3299,10 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>460</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>461</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>159</v>
@@ -3648,10 +3716,10 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>159</v>
@@ -3822,10 +3890,10 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>159</v>
@@ -3885,10 +3953,10 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>454</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>455</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>159</v>
@@ -3903,10 +3971,10 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B122" s="6" t="s">
         <v>304</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>305</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>245</v>
@@ -3914,6 +3982,9 @@
       <c r="D122" s="6">
         <v>0.87</v>
       </c>
+      <c r="G122">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="J122">
         <v>0.8</v>
       </c>
@@ -3921,10 +3992,10 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B123" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>245</v>
@@ -3932,14 +4003,17 @@
       <c r="D123" s="6">
         <v>0.86</v>
       </c>
+      <c r="G123">
+        <v>0.62</v>
+      </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B124" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>245</v>
@@ -3947,14 +4021,17 @@
       <c r="D124" s="6">
         <v>0.79</v>
       </c>
+      <c r="G124">
+        <v>0.53</v>
+      </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B125" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>335</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>245</v>
@@ -3962,14 +4039,17 @@
       <c r="D125" s="6">
         <v>0.64</v>
       </c>
+      <c r="G125">
+        <v>0.47</v>
+      </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B126" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>245</v>
@@ -3977,14 +4057,17 @@
       <c r="D126" s="6">
         <v>0.79</v>
       </c>
+      <c r="G126">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B127" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>245</v>
@@ -3992,14 +4075,17 @@
       <c r="D127" s="6">
         <v>0.69</v>
       </c>
+      <c r="G127">
+        <v>0.47</v>
+      </c>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B128" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>245</v>
@@ -4007,14 +4093,17 @@
       <c r="D128" s="6">
         <v>0.91</v>
       </c>
+      <c r="G128">
+        <v>0.64</v>
+      </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B129" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>245</v>
@@ -4022,14 +4111,17 @@
       <c r="D129" s="6">
         <v>0.88</v>
       </c>
+      <c r="G129">
+        <v>0.42</v>
+      </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>245</v>
@@ -4037,14 +4129,17 @@
       <c r="D130" s="6">
         <v>0.86</v>
       </c>
+      <c r="G130">
+        <v>0.51</v>
+      </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B131" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>291</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>245</v>
@@ -4052,260 +4147,311 @@
       <c r="D131" s="6">
         <v>0.87</v>
       </c>
+      <c r="G131">
+        <v>0.66</v>
+      </c>
       <c r="J131">
         <v>0.8</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C132" s="6" t="s">
+      <c r="A132" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D132" s="6">
-        <v>0.8</v>
+      <c r="D132" s="5">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>0.6</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.41</v>
+        <v>0.8</v>
+      </c>
+      <c r="G133">
+        <v>0.25</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>285</v>
+        <v>340</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
-        <v>0.81</v>
+        <v>0.41</v>
+      </c>
+      <c r="G134">
+        <v>0.36</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
-        <v>0.71</v>
+        <v>0.81</v>
+      </c>
+      <c r="G135">
+        <v>0.47</v>
       </c>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="6" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D136" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="G136">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M136" s="4"/>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D137" s="6">
         <v>0.86</v>
       </c>
-      <c r="M136" s="4"/>
-    </row>
-    <row r="137" spans="1:13">
-      <c r="A137" s="5" t="s">
+      <c r="G137">
+        <v>0.53</v>
+      </c>
+      <c r="M137" s="4"/>
+    </row>
+    <row r="138" spans="1:13">
+      <c r="A138" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B137" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C137" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D138" s="5">
         <v>0</v>
       </c>
-      <c r="J137">
+      <c r="G138">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J138">
         <v>0.83</v>
-      </c>
-      <c r="M137" s="4"/>
-    </row>
-    <row r="138" spans="1:13">
-      <c r="A138" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D138" s="6">
-        <v>0.87</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.8</v>
+        <v>0.87</v>
+      </c>
+      <c r="G139">
+        <v>0.61</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="C140" s="6" t="s">
+      <c r="A140" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D140" s="6">
-        <v>0.88</v>
+      <c r="D140" s="5">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0.62</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>0.98</v>
+        <v>0.8</v>
+      </c>
+      <c r="G141">
+        <v>0.56999999999999995</v>
       </c>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D142" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
+      </c>
+      <c r="G142">
+        <v>0.51</v>
       </c>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="6" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D143" s="6">
-        <v>0.85</v>
+        <v>0.98</v>
+      </c>
+      <c r="G143">
+        <v>0.45</v>
       </c>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C144" s="6" t="s">
+      <c r="A144" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C144" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D144" s="6">
-        <v>0.88</v>
+      <c r="D144" s="5">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0.53</v>
       </c>
       <c r="M144" s="4"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="6" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D145" s="6">
-        <v>0.71</v>
+        <v>0.75</v>
+      </c>
+      <c r="G145">
+        <v>0.56999999999999995</v>
       </c>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="1:13">
-      <c r="A146" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C146" s="6" t="s">
+      <c r="A146" t="s">
+        <v>479</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C146" t="s">
         <v>245</v>
       </c>
-      <c r="D146" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="M146" s="4"/>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>0.52</v>
+      </c>
+      <c r="M146" s="10"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>1</v>
+        <v>0.85</v>
+      </c>
+      <c r="G147">
+        <v>0.47</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6" t="s">
-        <v>314</v>
+        <v>246</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>245</v>
@@ -4313,98 +4459,116 @@
       <c r="D148" s="6">
         <v>0.88</v>
       </c>
-      <c r="J148">
-        <v>0.83</v>
+      <c r="G148">
+        <v>0.61</v>
       </c>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C149" s="6" t="s">
+      <c r="A149" t="s">
+        <v>468</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C149" t="s">
         <v>245</v>
       </c>
-      <c r="D149" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="M149" s="4"/>
+      <c r="D149" s="2">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0.39</v>
+      </c>
+      <c r="M149" s="10"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="6" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D150" s="6">
-        <v>0.91</v>
+        <v>0.71</v>
+      </c>
+      <c r="G150">
+        <v>0.53</v>
       </c>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
-      <c r="A151" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="C151" s="6" t="s">
+      <c r="A151" t="s">
+        <v>477</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="C151" t="s">
         <v>245</v>
       </c>
-      <c r="D151" s="6">
-        <v>1</v>
-      </c>
-      <c r="M151" s="4"/>
+      <c r="D151" s="2">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>0.45</v>
+      </c>
+      <c r="M151" s="10"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D152" s="6">
-        <v>0.81</v>
+        <v>0.74</v>
+      </c>
+      <c r="G152">
+        <v>0.62</v>
       </c>
       <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
-        <v>0.84</v>
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>0.39</v>
       </c>
       <c r="M153" s="4"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="6" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D154" s="6">
-        <v>0.81</v>
+        <v>0.88</v>
+      </c>
+      <c r="G154">
+        <v>0.75</v>
       </c>
       <c r="J154">
         <v>0.83</v>
@@ -4413,25 +4577,28 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="6" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D155" s="6">
-        <v>0.85</v>
+        <v>0.8</v>
+      </c>
+      <c r="G155">
+        <v>0.71</v>
       </c>
       <c r="M155" s="4"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="6" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>245</v>
@@ -4439,134 +4606,164 @@
       <c r="D156" s="6">
         <v>0.91</v>
       </c>
+      <c r="G156">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M156" s="4"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="6" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D157" s="6">
-        <v>0.86</v>
+        <v>1</v>
+      </c>
+      <c r="G157">
+        <v>0.74</v>
       </c>
       <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
-      <c r="A158" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="C158" s="6" t="s">
+      <c r="A158" t="s">
+        <v>470</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C158" t="s">
         <v>245</v>
       </c>
-      <c r="D158" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="M158" s="4"/>
+      <c r="D158" s="2">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0.71</v>
+      </c>
+      <c r="M158" s="10"/>
     </row>
     <row r="159" spans="1:13">
-      <c r="A159" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C159" s="6" t="s">
+      <c r="A159" t="s">
+        <v>472</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C159" t="s">
         <v>245</v>
       </c>
-      <c r="D159" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="M159" s="4"/>
+      <c r="D159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>0.38</v>
+      </c>
+      <c r="M159" s="10"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
-        <v>0.75</v>
+        <v>0.81</v>
+      </c>
+      <c r="G160">
+        <v>0.44</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C161" s="6" t="s">
+      <c r="A161" t="s">
+        <v>388</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C161" t="s">
         <v>245</v>
       </c>
-      <c r="D161" s="6">
-        <v>0.82</v>
-      </c>
-      <c r="M161" s="4"/>
+      <c r="D161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161">
+        <v>0.51</v>
+      </c>
+      <c r="M161" s="10"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>332</v>
+        <v>253</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>333</v>
+        <v>254</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
-        <v>0.86</v>
+        <v>0.84</v>
+      </c>
+      <c r="G162">
+        <v>0.49</v>
       </c>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="6" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D163" s="6">
-        <v>0.93</v>
+        <v>0.81</v>
+      </c>
+      <c r="G163">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J163">
+        <v>0.83</v>
       </c>
       <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D164" s="6">
-        <v>1</v>
+        <v>0.85</v>
+      </c>
+      <c r="G164">
+        <v>0.69</v>
       </c>
       <c r="M164" s="4"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="6" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>245</v>
@@ -4574,32 +4771,35 @@
       <c r="D165" s="6">
         <v>0.91</v>
       </c>
-      <c r="J165">
-        <v>0.8</v>
+      <c r="G165">
+        <v>0.65</v>
       </c>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="6" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D166" s="6">
-        <v>0.81</v>
+        <v>0.86</v>
+      </c>
+      <c r="G166">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M166" s="4"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B167" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>245</v>
@@ -4607,149 +4807,170 @@
       <c r="D167" s="6">
         <v>0.93</v>
       </c>
+      <c r="G167">
+        <v>0.62</v>
+      </c>
       <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D168" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="J168">
-        <v>0.83</v>
+        <v>0.79</v>
+      </c>
+      <c r="G168">
+        <v>0.48</v>
       </c>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D169" s="6">
-        <v>0.8</v>
+        <v>0.86</v>
+      </c>
+      <c r="G169">
+        <v>0.61</v>
       </c>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D170" s="6">
-        <v>0.85</v>
+        <v>0.75</v>
+      </c>
+      <c r="G170">
+        <v>0.36</v>
       </c>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
-      <c r="A171" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="C171" s="6" t="s">
+      <c r="A171" t="s">
+        <v>475</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C171" t="s">
         <v>245</v>
       </c>
-      <c r="D171" s="6">
-        <v>0.89</v>
-      </c>
-      <c r="M171" s="4"/>
+      <c r="D171" s="2">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0.68</v>
+      </c>
+      <c r="M171" s="10"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>349</v>
+        <v>248</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>350</v>
+        <v>249</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D172" s="6">
-        <v>0.77</v>
-      </c>
-      <c r="J172">
-        <v>0.8</v>
+        <v>0.82</v>
+      </c>
+      <c r="G172">
+        <v>0.4</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>393</v>
+        <v>331</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>394</v>
+        <v>332</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D173" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="J173">
-        <v>0.85</v>
+        <v>0.86</v>
+      </c>
+      <c r="G173">
+        <v>0.38</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>431</v>
+        <v>291</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>432</v>
+        <v>292</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D174" s="6">
-        <v>0.74</v>
+        <v>0.93</v>
+      </c>
+      <c r="G174">
+        <v>0.66</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>366</v>
+        <v>278</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D175" s="6">
-        <v>0.82</v>
+        <v>1</v>
+      </c>
+      <c r="G175">
+        <v>0.66</v>
       </c>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="6" t="s">
-        <v>351</v>
+        <v>255</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D176" s="6">
-        <v>0.85</v>
+        <v>0.91</v>
+      </c>
+      <c r="G176">
+        <v>0.53</v>
       </c>
       <c r="J176">
         <v>0.8</v>
@@ -4758,795 +4979,951 @@
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="6" t="s">
-        <v>373</v>
+        <v>275</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>374</v>
+        <v>276</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D177" s="6">
-        <v>0.98</v>
+        <v>0.81</v>
+      </c>
+      <c r="G177">
+        <v>0.32</v>
       </c>
       <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>435</v>
+        <v>319</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>436</v>
+        <v>320</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D178" s="6">
-        <v>0.93</v>
+        <v>0.81</v>
+      </c>
+      <c r="G178">
+        <v>0.82</v>
+      </c>
+      <c r="J178">
+        <v>0.83</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>437</v>
+        <v>281</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>438</v>
+        <v>282</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D179" s="6">
-        <v>0.67</v>
+        <v>0.8</v>
+      </c>
+      <c r="G179">
+        <v>0.73</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>419</v>
+        <v>321</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>420</v>
+        <v>322</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D180" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
+      </c>
+      <c r="G180">
+        <v>0.43</v>
       </c>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>414</v>
+        <v>318</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D181" s="6">
-        <v>0.92</v>
+        <v>0.89</v>
+      </c>
+      <c r="G181">
+        <v>0.51</v>
       </c>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D182" s="6">
-        <v>0.84</v>
+        <v>0.77</v>
+      </c>
+      <c r="J182">
+        <v>0.8</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D183" s="6">
-        <v>0.63</v>
+        <v>0.8</v>
+      </c>
+      <c r="J183">
+        <v>0.85</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D184" s="6">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D185" s="6">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>416</v>
+        <v>351</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D186" s="6">
-        <v>0.75</v>
+        <v>0.85</v>
+      </c>
+      <c r="J186">
+        <v>0.8</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D187" s="6">
-        <v>0.96</v>
-      </c>
-      <c r="J187">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D188" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>367</v>
+        <v>436</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>368</v>
+        <v>437</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D189" s="6">
-        <v>0.81</v>
+        <v>0.67</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D190" s="6">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D191" s="6">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="B192" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C192" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C192" s="6" t="s">
-        <v>344</v>
-      </c>
       <c r="D192" s="6">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D193" s="6">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D194" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="J194">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D195" s="6">
-        <v>0.81</v>
+        <v>0.93</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>369</v>
+        <v>414</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D196" s="6">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>412</v>
+        <v>361</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D197" s="6">
         <v>0.96</v>
       </c>
+      <c r="J197">
+        <v>0.8</v>
+      </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>346</v>
+        <v>427</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D198" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="J198">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D199" s="6">
-        <v>0.96</v>
+        <v>0.81</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D200" s="6">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D201" s="6">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>409</v>
+        <v>341</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>410</v>
+        <v>342</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D202" s="6">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D203" s="6">
-        <v>1</v>
-      </c>
-      <c r="J203">
         <v>0.93</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>433</v>
+        <v>370</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>434</v>
+        <v>371</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D204" s="6">
-        <v>0.91</v>
+        <v>0.79</v>
+      </c>
+      <c r="J204">
+        <v>0.85</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="6" t="s">
-        <v>357</v>
+        <v>446</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>358</v>
+        <v>447</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D205" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.81</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>417</v>
+        <v>368</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>418</v>
+        <v>369</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D206" s="6">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="6" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="C207" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D207" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="M207" s="4"/>
+    </row>
+    <row r="208" spans="1:13">
+      <c r="A208" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="D207" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="J207">
-        <v>0.85</v>
-      </c>
-      <c r="M207" s="4"/>
-    </row>
-    <row r="208" spans="1:13">
-      <c r="A208" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B208" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="D208" s="5">
-        <v>0</v>
+      <c r="B208" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D208" s="6">
+        <v>0.81</v>
       </c>
       <c r="J208">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D209" s="6">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D210" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D211" s="6">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D212" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="J212">
         <v>0.93</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D213" s="6">
-        <v>0.88</v>
+        <v>1</v>
+      </c>
+      <c r="J213">
+        <v>0.93</v>
       </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D214" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="J214">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D215" s="6">
-        <v>0.96</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D216" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="J216">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>392</v>
+        <v>439</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D217" s="6">
-        <v>0.76</v>
+        <v>0.98</v>
+      </c>
+      <c r="J217">
+        <v>0.85</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="A218" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D218" s="6">
-        <v>0.41</v>
+      <c r="A218" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D218" s="5">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0.93</v>
       </c>
       <c r="M218" s="4"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="6" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D219" s="6">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="6" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D220" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="6" t="s">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D221" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="6" t="s">
-        <v>359</v>
+        <v>424</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D222" s="6">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
       <c r="J222">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="M222" s="4"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="6" t="s">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>386</v>
+        <v>441</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D223" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="J223">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="M223" s="4"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="6" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>356</v>
+        <v>445</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D224" s="6">
-        <v>0.97</v>
+        <v>0.78</v>
+      </c>
+      <c r="J224">
+        <v>0.93</v>
       </c>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D225" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="M225" s="4"/>
+    </row>
+    <row r="226" spans="1:13">
+      <c r="A226" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D226" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="J226">
+        <v>0.8</v>
+      </c>
+      <c r="M226" s="4"/>
+    </row>
+    <row r="227" spans="1:13">
+      <c r="A227" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D227" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="M227" s="4"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D228" s="6">
+        <v>0.41</v>
+      </c>
+      <c r="M228" s="4"/>
+    </row>
+    <row r="229" spans="1:13">
+      <c r="A229" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D229" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="M229" s="11"/>
+    </row>
+    <row r="230" spans="1:13">
+      <c r="A230" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D230" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="M230" s="11"/>
+    </row>
+    <row r="231" spans="1:13">
+      <c r="A231" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D231" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="M231" s="11"/>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="A232" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D232" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="J232">
+        <v>0.83</v>
+      </c>
+      <c r="M232" s="11"/>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D233" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="J233">
+        <v>0.8</v>
+      </c>
+      <c r="M233" s="11"/>
+    </row>
+    <row r="234" spans="1:13">
+      <c r="A234" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D234" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="M234" s="11"/>
+    </row>
+    <row r="235" spans="1:13">
+      <c r="A235" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B235" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="B225" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="C225" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D225" s="6">
+      <c r="C235" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D235" s="6">
         <v>0.88</v>
       </c>
-      <c r="J225">
+      <c r="J235">
         <v>0.93</v>
       </c>
-      <c r="M225" s="4"/>
-    </row>
-    <row r="226" spans="1:13">
-      <c r="A226" s="5"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
-      <c r="M226" s="4"/>
-    </row>
-    <row r="227" spans="1:13">
-      <c r="A227" s="5"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="5"/>
-      <c r="D227" s="5"/>
-      <c r="M227" s="4"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" s="5"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
-      <c r="M228" s="4"/>
+      <c r="M235" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2654F286-6A14-9849-B4CB-492BD3771A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C68D1E-4458-5D40-92AE-BF8BA2DCF384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="16000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="485">
   <si>
     <t>Surname</t>
   </si>
@@ -1479,6 +1479,18 @@
   </si>
   <si>
     <t>H240464X</t>
+  </si>
+  <si>
+    <t>Chigumbura</t>
+  </si>
+  <si>
+    <t>H265396A</t>
+  </si>
+  <si>
+    <t>Madyise</t>
+  </si>
+  <si>
+    <t>H264395O</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1611,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1645,8 +1657,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M235" totalsRowShown="0">
-  <autoFilter ref="A1:M235" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M237" totalsRowShown="0">
+  <autoFilter ref="A1:M237" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M235">
     <sortCondition ref="C1:C235"/>
   </sortState>
@@ -1986,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M237"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2048,6 +2060,9 @@
       <c r="D2" s="6">
         <v>0.73</v>
       </c>
+      <c r="E2">
+        <v>0.88</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="J2">
         <v>0.72</v>
@@ -2067,6 +2082,9 @@
       <c r="D3" s="6">
         <v>0.79</v>
       </c>
+      <c r="E3">
+        <v>0.98</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="J3">
         <v>0.72</v>
@@ -2086,6 +2104,9 @@
       <c r="D4" s="6">
         <v>0.89</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="M4" s="7"/>
     </row>
@@ -2102,6 +2123,9 @@
       <c r="D5" s="6">
         <v>0.87</v>
       </c>
+      <c r="E5">
+        <v>0.98</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="M5" s="7"/>
     </row>
@@ -2118,6 +2142,9 @@
       <c r="D6" s="6">
         <v>0.92</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13">
@@ -2133,6 +2160,9 @@
       <c r="D7" s="6">
         <v>0.88</v>
       </c>
+      <c r="E7">
+        <v>0.93</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="M7" s="4"/>
     </row>
@@ -2149,6 +2179,9 @@
       <c r="D8" s="6">
         <v>0.79</v>
       </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="M8" s="4"/>
     </row>
@@ -2165,6 +2198,9 @@
       <c r="D9" s="6">
         <v>0.7</v>
       </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="M9" s="4"/>
     </row>
@@ -2181,6 +2217,9 @@
       <c r="D10" s="6">
         <v>0.76</v>
       </c>
+      <c r="E10">
+        <v>0.93</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="M10" s="4"/>
     </row>
@@ -2197,6 +2236,9 @@
       <c r="D11" s="6">
         <v>0.88</v>
       </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="M11" s="4"/>
     </row>
@@ -2213,6 +2255,9 @@
       <c r="D12" s="6">
         <v>0.75</v>
       </c>
+      <c r="E12">
+        <v>0.98</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="M12" s="4"/>
     </row>
@@ -2229,6 +2274,9 @@
       <c r="D13" s="6">
         <v>0.8</v>
       </c>
+      <c r="E13">
+        <v>0.98</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="M13" s="4"/>
     </row>
@@ -2245,6 +2293,9 @@
       <c r="D14" s="6">
         <v>0.92</v>
       </c>
+      <c r="E14">
+        <v>0.95</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="M14" s="4"/>
     </row>
@@ -2261,6 +2312,9 @@
       <c r="D15" s="6">
         <v>0.84</v>
       </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="M15" s="4"/>
     </row>
@@ -2277,6 +2331,9 @@
       <c r="D16" s="6">
         <v>0.8</v>
       </c>
+      <c r="E16">
+        <v>0.98</v>
+      </c>
       <c r="H16" s="3"/>
       <c r="M16" s="4"/>
     </row>
@@ -2293,6 +2350,9 @@
       <c r="D17" s="6">
         <v>0.7</v>
       </c>
+      <c r="E17">
+        <v>0.95</v>
+      </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13">
@@ -2308,6 +2368,9 @@
       <c r="D18" s="6">
         <v>0.74</v>
       </c>
+      <c r="E18">
+        <v>0.93</v>
+      </c>
       <c r="H18" s="3"/>
       <c r="M18" s="4"/>
     </row>
@@ -2324,6 +2387,9 @@
       <c r="D19" s="6">
         <v>0.86</v>
       </c>
+      <c r="E19">
+        <v>0.95</v>
+      </c>
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13">
@@ -2339,6 +2405,9 @@
       <c r="D20" s="6">
         <v>0.93</v>
       </c>
+      <c r="E20">
+        <v>0.98</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="M20" s="4"/>
     </row>
@@ -2355,6 +2424,9 @@
       <c r="D21" s="6">
         <v>0.92</v>
       </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="M21" s="4"/>
     </row>
@@ -2371,6 +2443,9 @@
       <c r="D22" s="6">
         <v>0.89</v>
       </c>
+      <c r="E22">
+        <v>0.98</v>
+      </c>
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13">
@@ -2386,6 +2461,9 @@
       <c r="D23" s="6">
         <v>0.85</v>
       </c>
+      <c r="E23">
+        <v>0.93</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="M23" s="4"/>
     </row>
@@ -2402,6 +2480,9 @@
       <c r="D24" s="6">
         <v>0.81</v>
       </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
       <c r="H24" s="3"/>
       <c r="M24" s="4"/>
     </row>
@@ -2418,6 +2499,9 @@
       <c r="D25" s="6">
         <v>0.82</v>
       </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
       <c r="H25" s="3"/>
       <c r="M25" s="4"/>
     </row>
@@ -2434,6 +2518,9 @@
       <c r="D26" s="6">
         <v>0.9</v>
       </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="1:13">
@@ -2449,6 +2536,9 @@
       <c r="D27" s="6">
         <v>0.9</v>
       </c>
+      <c r="E27">
+        <v>0.7</v>
+      </c>
       <c r="H27" s="3"/>
       <c r="M27" s="8"/>
     </row>
@@ -2465,6 +2555,9 @@
       <c r="D28" s="6">
         <v>0.96</v>
       </c>
+      <c r="E28">
+        <v>0.86</v>
+      </c>
       <c r="H28" s="3"/>
       <c r="M28" s="4"/>
     </row>
@@ -2481,6 +2574,9 @@
       <c r="D29" s="6">
         <v>0.77</v>
       </c>
+      <c r="E29">
+        <v>0.93</v>
+      </c>
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="1:13">
@@ -2496,6 +2592,9 @@
       <c r="D30" s="6">
         <v>0.81</v>
       </c>
+      <c r="E30">
+        <v>0.93</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="M30" s="4"/>
     </row>
@@ -2512,6 +2611,9 @@
       <c r="D31" s="6">
         <v>0.91</v>
       </c>
+      <c r="E31">
+        <v>0.81</v>
+      </c>
       <c r="H31" s="3"/>
       <c r="M31" s="4"/>
     </row>
@@ -2528,6 +2630,9 @@
       <c r="D32" s="6">
         <v>0.95</v>
       </c>
+      <c r="E32">
+        <v>0.77</v>
+      </c>
       <c r="J32">
         <v>0.78</v>
       </c>
@@ -2546,6 +2651,9 @@
       <c r="D33" s="6">
         <v>0.84</v>
       </c>
+      <c r="E33">
+        <v>0.91</v>
+      </c>
       <c r="H33" s="3"/>
       <c r="M33" s="8"/>
     </row>
@@ -2562,6 +2670,9 @@
       <c r="D34" s="6">
         <v>0.88</v>
       </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
       <c r="H34" s="3"/>
       <c r="M34" s="4"/>
     </row>
@@ -2578,6 +2689,9 @@
       <c r="D35" s="6">
         <v>0.55000000000000004</v>
       </c>
+      <c r="E35">
+        <v>0.93</v>
+      </c>
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="1:13">
@@ -2593,6 +2707,9 @@
       <c r="D36" s="6">
         <v>0.85</v>
       </c>
+      <c r="E36">
+        <v>0.98</v>
+      </c>
       <c r="H36" s="3"/>
       <c r="J36">
         <v>0.7</v>
@@ -2612,6 +2729,9 @@
       <c r="D37" s="6">
         <v>0.95</v>
       </c>
+      <c r="E37">
+        <v>0.93</v>
+      </c>
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13">
@@ -2627,6 +2747,9 @@
       <c r="D38" s="6">
         <v>0.57999999999999996</v>
       </c>
+      <c r="E38">
+        <v>0.98</v>
+      </c>
       <c r="H38" s="3"/>
       <c r="M38" s="4"/>
     </row>
@@ -2643,6 +2766,9 @@
       <c r="D39" s="6">
         <v>0.86</v>
       </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
       <c r="H39" s="3"/>
       <c r="J39">
         <v>0.7</v>
@@ -2662,6 +2788,9 @@
       <c r="D40" s="6">
         <v>0.78</v>
       </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
       <c r="H40" s="3"/>
       <c r="M40" s="4"/>
     </row>
@@ -2678,6 +2807,9 @@
       <c r="D41" s="6">
         <v>0.93</v>
       </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="J41">
         <v>0.84</v>
@@ -2697,6 +2829,9 @@
       <c r="D42" s="6">
         <v>0.92</v>
       </c>
+      <c r="E42">
+        <v>0.98</v>
+      </c>
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="1:13">
@@ -2712,6 +2847,9 @@
       <c r="D43" s="6">
         <v>0.93</v>
       </c>
+      <c r="E43">
+        <v>0.79</v>
+      </c>
       <c r="H43" s="3"/>
       <c r="M43" s="8"/>
     </row>
@@ -2728,6 +2866,9 @@
       <c r="D44" s="6">
         <v>0.8</v>
       </c>
+      <c r="E44">
+        <v>0.98</v>
+      </c>
       <c r="H44" s="3"/>
       <c r="M44" s="8"/>
     </row>
@@ -2744,6 +2885,9 @@
       <c r="D45" s="6">
         <v>0.93</v>
       </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
       <c r="H45" s="3"/>
       <c r="M45" s="4"/>
     </row>
@@ -2760,6 +2904,9 @@
       <c r="D46" s="6">
         <v>0.79</v>
       </c>
+      <c r="E46">
+        <v>0.93</v>
+      </c>
       <c r="H46" s="3"/>
       <c r="M46" s="4"/>
     </row>
@@ -2776,6 +2923,9 @@
       <c r="D47" s="6">
         <v>0.89</v>
       </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
       <c r="H47" s="3"/>
       <c r="M47" s="4"/>
     </row>
@@ -2792,6 +2942,9 @@
       <c r="D48" s="6">
         <v>0.79</v>
       </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
       <c r="J48">
         <v>0.84</v>
       </c>
@@ -2810,6 +2963,9 @@
       <c r="D49" s="6">
         <v>0.78</v>
       </c>
+      <c r="E49">
+        <v>0.95</v>
+      </c>
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="1:13">
@@ -2825,6 +2981,9 @@
       <c r="D50" s="6">
         <v>0.81</v>
       </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13">
@@ -2840,6 +2999,9 @@
       <c r="D51" s="6">
         <v>0.9</v>
       </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
       <c r="H51" s="3"/>
       <c r="M51" s="4"/>
     </row>
@@ -2856,6 +3018,9 @@
       <c r="D52" s="6">
         <v>0.86</v>
       </c>
+      <c r="E52">
+        <v>0.95</v>
+      </c>
       <c r="H52" s="3"/>
       <c r="M52" s="4"/>
     </row>
@@ -2872,6 +3037,9 @@
       <c r="D53" s="6">
         <v>0.86</v>
       </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
       <c r="H53" s="3"/>
       <c r="M53" s="4"/>
     </row>
@@ -2888,6 +3056,9 @@
       <c r="D54" s="6">
         <v>0.96</v>
       </c>
+      <c r="E54">
+        <v>0.98</v>
+      </c>
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="1:13">
@@ -2903,6 +3074,9 @@
       <c r="D55" s="6">
         <v>0.88</v>
       </c>
+      <c r="E55">
+        <v>0.98</v>
+      </c>
       <c r="H55" s="3"/>
       <c r="J55">
         <v>0.72</v>
@@ -2922,6 +3096,9 @@
       <c r="D56" s="5">
         <v>0</v>
       </c>
+      <c r="E56">
+        <v>0.98</v>
+      </c>
       <c r="J56">
         <v>0.84</v>
       </c>
@@ -2940,6 +3117,9 @@
       <c r="D57" s="6">
         <v>0.87</v>
       </c>
+      <c r="E57">
+        <v>0.98</v>
+      </c>
       <c r="H57" s="3"/>
       <c r="M57" s="4"/>
     </row>
@@ -2956,6 +3136,9 @@
       <c r="D58" s="6">
         <v>0.82</v>
       </c>
+      <c r="E58">
+        <v>0.98</v>
+      </c>
       <c r="J58">
         <v>0.78</v>
       </c>
@@ -2974,6 +3157,9 @@
       <c r="D59" s="6">
         <v>0.9</v>
       </c>
+      <c r="E59">
+        <v>0.98</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="J59">
         <v>0.7</v>
@@ -2993,6 +3179,9 @@
       <c r="D60" s="6">
         <v>0.86</v>
       </c>
+      <c r="E60">
+        <v>0.98</v>
+      </c>
       <c r="H60" s="3"/>
       <c r="M60" s="4"/>
     </row>
@@ -3009,6 +3198,9 @@
       <c r="D61" s="6">
         <v>0.96</v>
       </c>
+      <c r="E61">
+        <v>0.95</v>
+      </c>
       <c r="H61" s="3"/>
       <c r="M61" s="4"/>
     </row>
@@ -3025,6 +3217,9 @@
       <c r="D62" s="6">
         <v>0.78</v>
       </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
       <c r="M62" s="4"/>
     </row>
     <row r="63" spans="1:13">
@@ -3040,6 +3235,9 @@
       <c r="D63" s="6">
         <v>0.95</v>
       </c>
+      <c r="E63">
+        <v>0.95</v>
+      </c>
       <c r="H63" s="3"/>
       <c r="M63" s="4"/>
     </row>
@@ -3056,6 +3254,9 @@
       <c r="D64" s="6">
         <v>0.9</v>
       </c>
+      <c r="E64">
+        <v>0.98</v>
+      </c>
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="1:13">
@@ -3071,6 +3272,9 @@
       <c r="D65" s="6">
         <v>0.75</v>
       </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
       <c r="J65">
         <v>0.78</v>
       </c>
@@ -3089,6 +3293,9 @@
       <c r="D66" s="6">
         <v>0.56999999999999995</v>
       </c>
+      <c r="E66">
+        <v>0.98</v>
+      </c>
       <c r="M66" s="4"/>
     </row>
     <row r="67" spans="1:13">
@@ -3104,6 +3311,9 @@
       <c r="D67" s="6">
         <v>0.75</v>
       </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
       <c r="H67" s="3"/>
       <c r="J67">
         <v>0.72</v>
@@ -3123,6 +3333,9 @@
       <c r="D68" s="6">
         <v>0.77</v>
       </c>
+      <c r="E68">
+        <v>0.88</v>
+      </c>
       <c r="H68" s="3"/>
       <c r="J68">
         <v>0.72</v>
@@ -3142,6 +3355,9 @@
       <c r="D69" s="6">
         <v>0.88</v>
       </c>
+      <c r="E69">
+        <v>0.98</v>
+      </c>
       <c r="H69" s="3"/>
       <c r="J69">
         <v>0.78</v>
@@ -3161,6 +3377,9 @@
       <c r="D70" s="6">
         <v>0.86</v>
       </c>
+      <c r="E70">
+        <v>0.98</v>
+      </c>
       <c r="H70" s="3"/>
       <c r="J70">
         <v>0.73</v>
@@ -3180,6 +3399,9 @@
       <c r="D71" s="6">
         <v>0.88</v>
       </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="1:13">
@@ -3195,6 +3417,9 @@
       <c r="D72" s="6">
         <v>0.79</v>
       </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
       <c r="J72">
         <v>0.7</v>
       </c>
@@ -3213,6 +3438,9 @@
       <c r="D73" s="6">
         <v>0.88</v>
       </c>
+      <c r="E73">
+        <v>0.95</v>
+      </c>
       <c r="J73">
         <v>0.78</v>
       </c>
@@ -3231,6 +3459,9 @@
       <c r="D74" s="6">
         <v>0.98</v>
       </c>
+      <c r="E74">
+        <v>0.95</v>
+      </c>
       <c r="H74" s="3"/>
       <c r="M74" s="4"/>
     </row>
@@ -5924,6 +6155,40 @@
         <v>0.93</v>
       </c>
       <c r="M235" s="11"/>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" t="s">
+        <v>481</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="C236" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236" s="2">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" t="s">
+        <v>483</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="C237" t="s">
+        <v>15</v>
+      </c>
+      <c r="D237" s="2">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0.98</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C68D1E-4458-5D40-92AE-BF8BA2DCF384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C271594-C650-EC42-AFA1-7D18AE906B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="16000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="491">
   <si>
     <t>Surname</t>
   </si>
@@ -1491,6 +1491,24 @@
   </si>
   <si>
     <t>H264395O</t>
+  </si>
+  <si>
+    <t>Mapara</t>
+  </si>
+  <si>
+    <t>H261856N</t>
+  </si>
+  <si>
+    <t>Masuka</t>
+  </si>
+  <si>
+    <t>H268594Z</t>
+  </si>
+  <si>
+    <t>Munhuweyi</t>
+  </si>
+  <si>
+    <t>H261401R</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1614,6 +1632,10 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1657,10 +1679,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M237" totalsRowShown="0">
-  <autoFilter ref="A1:M237" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M235">
-    <sortCondition ref="C1:C235"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M240" totalsRowShown="0">
+  <autoFilter ref="A1:M240" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M240">
+    <sortCondition ref="C1:C240"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -1998,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M237"/>
+  <dimension ref="A1:M240"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2092,111 +2114,110 @@
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0.89</v>
+      <c r="A4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="M4" s="7"/>
+        <v>0.98</v>
+      </c>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="6" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="6">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="E5">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="6" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="6">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="H6" s="3"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="6">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="E7">
-        <v>0.93</v>
-      </c>
-      <c r="H7" s="3"/>
+        <v>0</v>
+      </c>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="6">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H8" s="3"/>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="6">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2206,73 +2227,73 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="6">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="E10">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="6">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H11" s="3"/>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="E12">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3"/>
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="6">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E13">
         <v>0.98</v>
@@ -2282,452 +2303,449 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="6">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="E14">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H14" s="3"/>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="6">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H15" s="3"/>
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="6">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="E16">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3"/>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="6" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="6">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E17">
-        <v>0.95</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="H17" s="3"/>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="6" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="6">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="E18">
-        <v>0.93</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>0.95</v>
+      </c>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="6" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="6">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="E19">
-        <v>0.95</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="H19" s="3"/>
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="6" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="6">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E20">
-        <v>0.98</v>
-      </c>
-      <c r="H20" s="3"/>
+        <v>0.95</v>
+      </c>
       <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H21" s="3"/>
       <c r="M21" s="4"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="6" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="6">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>483</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>0.98</v>
       </c>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="E23">
-        <v>0.93</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="M23" s="4"/>
+      <c r="M23" s="10"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="6">
-        <v>0.81</v>
+        <v>0.89</v>
       </c>
       <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3"/>
+        <v>0.98</v>
+      </c>
       <c r="M24" s="4"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="6" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="6">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H25" s="3"/>
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="6">
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
+      <c r="H26" s="3"/>
       <c r="M26" s="4"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="6" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="6">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="E27">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="M27" s="8"/>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="6" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="6">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="E28">
-        <v>0.86</v>
-      </c>
-      <c r="H28" s="3"/>
+        <v>1</v>
+      </c>
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="6" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D29" s="6">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="E29">
-        <v>0.93</v>
-      </c>
-      <c r="M29" s="4"/>
+        <v>0.7</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="M29" s="8"/>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="6" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="6">
-        <v>0.81</v>
+        <v>0.96</v>
       </c>
       <c r="E30">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="H30" s="3"/>
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="6" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="6">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="E31">
-        <v>0.81</v>
-      </c>
-      <c r="H31" s="3"/>
+        <v>0.93</v>
+      </c>
       <c r="M31" s="4"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="6" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="6">
-        <v>0.95</v>
+        <v>0.81</v>
       </c>
       <c r="E32">
-        <v>0.77</v>
-      </c>
-      <c r="J32">
-        <v>0.78</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="H32" s="3"/>
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="6" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="6">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="E33">
-        <v>0.91</v>
+        <v>0.81</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="M33" s="8"/>
+      <c r="M33" s="4"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="6" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="6">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3"/>
+        <v>0.77</v>
+      </c>
+      <c r="J34">
+        <v>0.78</v>
+      </c>
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="6" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.84</v>
       </c>
       <c r="E35">
-        <v>0.93</v>
-      </c>
-      <c r="M35" s="4"/>
+        <v>0.91</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="6" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="6">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="E36">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="J36">
-        <v>0.7</v>
-      </c>
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="6" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="6">
-        <v>0.95</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E37">
         <v>0.93</v>
@@ -2736,110 +2754,110 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="6" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="6">
-        <v>0.57999999999999996</v>
+        <v>0.85</v>
       </c>
       <c r="E38">
         <v>0.98</v>
       </c>
       <c r="H38" s="3"/>
+      <c r="J38">
+        <v>0.7</v>
+      </c>
       <c r="M38" s="4"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="6" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="6">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="J39">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="6" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="6">
-        <v>0.78</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H40" s="3"/>
       <c r="M40" s="4"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="6" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D41" s="6">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="H41" s="3"/>
       <c r="J41">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="6" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="6">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="E42">
-        <v>0.98</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H42" s="3"/>
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="6" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>15</v>
@@ -2848,36 +2866,38 @@
         <v>0.93</v>
       </c>
       <c r="E43">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3"/>
-      <c r="M43" s="8"/>
+      <c r="J43">
+        <v>0.84</v>
+      </c>
+      <c r="M43" s="4"/>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="6" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="6">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="E44">
         <v>0.98</v>
       </c>
-      <c r="H44" s="3"/>
-      <c r="M44" s="8"/>
+      <c r="M44" s="4"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="6" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>15</v>
@@ -2886,42 +2906,42 @@
         <v>0.93</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="H45" s="3"/>
-      <c r="M45" s="4"/>
+      <c r="M45" s="8"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D46" s="6">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="E46">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="H46" s="3"/>
-      <c r="M46" s="4"/>
+      <c r="M46" s="8"/>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="6" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="6">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -2931,10 +2951,10 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="6" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>15</v>
@@ -2943,99 +2963,99 @@
         <v>0.79</v>
       </c>
       <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="J48">
-        <v>0.84</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="H48" s="3"/>
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="6" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="6">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="E49">
-        <v>0.95</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H49" s="3"/>
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="6" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="6">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E50">
         <v>1</v>
+      </c>
+      <c r="J50">
+        <v>0.84</v>
       </c>
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="6" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="6">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3"/>
+        <v>0.95</v>
+      </c>
       <c r="M51" s="4"/>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="6" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="6">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="E52">
-        <v>0.95</v>
-      </c>
-      <c r="H52" s="3"/>
+        <v>1</v>
+      </c>
       <c r="M52" s="4"/>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="6">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3045,195 +3065,196 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="6" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="6">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="E54">
-        <v>0.98</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="H54" s="3"/>
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="6" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D55" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E55">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="J55">
-        <v>0.72</v>
-      </c>
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="5">
-        <v>0</v>
+      <c r="A56" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="6">
+        <v>0.96</v>
       </c>
       <c r="E56">
         <v>0.98</v>
       </c>
-      <c r="J56">
-        <v>0.84</v>
-      </c>
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="6">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="E57">
         <v>0.98</v>
       </c>
       <c r="H57" s="3"/>
+      <c r="J57">
+        <v>0.72</v>
+      </c>
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="6">
-        <v>0.82</v>
+      <c r="A58" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="5">
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0.98</v>
       </c>
       <c r="J58">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="6" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="6">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="E59">
         <v>0.98</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="J59">
-        <v>0.7</v>
-      </c>
       <c r="M59" s="4"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="6" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="6">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="E60">
         <v>0.98</v>
       </c>
-      <c r="H60" s="3"/>
+      <c r="J60">
+        <v>0.78</v>
+      </c>
       <c r="M60" s="4"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="6" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="6">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="E61">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H61" s="3"/>
+      <c r="J61">
+        <v>0.7</v>
+      </c>
       <c r="M61" s="4"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="6" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="6">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="E62">
-        <v>1</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="H62" s="3"/>
       <c r="M62" s="4"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="6" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="6">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="E63">
         <v>0.95</v>
@@ -3243,55 +3264,53 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="6">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="E64">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="6" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="6">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="J65">
-        <v>0.78</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="H65" s="3"/>
       <c r="M65" s="4"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="6" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="6">
-        <v>0.56999999999999995</v>
+        <v>0.9</v>
       </c>
       <c r="E66">
         <v>0.98</v>
@@ -3300,10 +3319,10 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="6" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>15</v>
@@ -3314,84 +3333,79 @@
       <c r="E67">
         <v>1</v>
       </c>
-      <c r="H67" s="3"/>
       <c r="J67">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="M67" s="4"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="6" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="6">
-        <v>0.77</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E68">
-        <v>0.88</v>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="J68">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="M68" s="4"/>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="6" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="6">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="E69">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H69" s="3"/>
       <c r="J69">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="M69" s="4"/>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="6" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D70" s="6">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="E70">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H70" s="3"/>
       <c r="J70">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="M70" s="4"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="6" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>15</v>
@@ -3400,37 +3414,42 @@
         <v>0.88</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="H71" s="3"/>
+      <c r="J71">
+        <v>0.78</v>
       </c>
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="6" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="E72">
-        <v>1</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="H72" s="3"/>
       <c r="J72">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="6" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>15</v>
@@ -3439,44 +3458,46 @@
         <v>0.88</v>
       </c>
       <c r="E73">
-        <v>0.95</v>
-      </c>
-      <c r="J73">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="M73" s="4"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="6" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="6">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="E74">
-        <v>0.95</v>
-      </c>
-      <c r="H74" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>0.7</v>
+      </c>
       <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="6" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>213</v>
+        <v>122</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="D75" s="6">
-        <v>0.93</v>
+        <v>0.88</v>
+      </c>
+      <c r="E75">
+        <v>0.95</v>
       </c>
       <c r="J75">
         <v>0.78</v>
@@ -3485,556 +3506,665 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="6" t="s">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>211</v>
+        <v>51</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="D76" s="6">
-        <v>0.73</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="E76">
+        <v>0.95</v>
+      </c>
+      <c r="H76" s="3"/>
       <c r="M76" s="4"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="6" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D77" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>0.78</v>
       </c>
       <c r="M77" s="4"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="6" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D78" s="6">
-        <v>0.88</v>
+        <v>0.73</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
       </c>
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C79" s="5" t="s">
+      <c r="A79" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="5">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>0.78</v>
+      <c r="D79" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E79">
+        <v>0.98</v>
       </c>
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D80" s="6">
-        <v>0.85</v>
+        <v>0.88</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
       </c>
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C81" s="6" t="s">
+      <c r="A81" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D81" s="6">
-        <v>0.96</v>
+      <c r="D81" s="5">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0.77</v>
+      </c>
+      <c r="J81">
+        <v>0.78</v>
       </c>
       <c r="M81" s="4"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="6" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D82" s="6">
-        <v>0.82</v>
-      </c>
-      <c r="J82">
-        <v>0.78</v>
+        <v>0.85</v>
+      </c>
+      <c r="E82">
+        <v>0.98</v>
       </c>
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="6" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D83" s="6">
-        <v>0.84</v>
+        <v>0.96</v>
+      </c>
+      <c r="E83">
+        <v>0.98</v>
       </c>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="6" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D84" s="6">
-        <v>0.88</v>
+        <v>0.82</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>0.78</v>
       </c>
       <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="6" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D85" s="6">
-        <v>0.53</v>
+        <v>0.84</v>
+      </c>
+      <c r="E85">
+        <v>0.98</v>
       </c>
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D86" s="6">
-        <v>0.78</v>
+        <v>0.88</v>
+      </c>
+      <c r="E86">
+        <v>0.98</v>
       </c>
       <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D87" s="6">
-        <v>0.91</v>
+        <v>0.53</v>
+      </c>
+      <c r="E87">
+        <v>0.95</v>
       </c>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="6" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D88" s="6">
-        <v>0.81</v>
+        <v>0.78</v>
+      </c>
+      <c r="E88">
+        <v>0.95</v>
       </c>
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D89" s="6">
-        <v>0.8</v>
+        <v>0.91</v>
+      </c>
+      <c r="E89">
+        <v>0.93</v>
       </c>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="6" t="s">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D90" s="6">
-        <v>0.78</v>
+        <v>0.81</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
       </c>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="6" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D91" s="6">
-        <v>0.85</v>
+        <v>0.8</v>
+      </c>
+      <c r="E91">
+        <v>0.93</v>
       </c>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="6" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D92" s="6">
-        <v>0.8</v>
+        <v>0.78</v>
+      </c>
+      <c r="E92">
+        <v>0.51</v>
       </c>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="6" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D93" s="6">
-        <v>0.92</v>
+        <v>0.85</v>
+      </c>
+      <c r="E93">
+        <v>0.98</v>
       </c>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="6" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D94" s="6">
-        <v>0.78</v>
+        <v>0.8</v>
+      </c>
+      <c r="E94">
+        <v>0.74</v>
       </c>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="6" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D95" s="6">
-        <v>0.73</v>
+        <v>0.92</v>
+      </c>
+      <c r="E95">
+        <v>0.95</v>
       </c>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="6" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D96" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="E96">
         <v>0.93</v>
-      </c>
-      <c r="J96">
-        <v>0.78</v>
       </c>
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="6" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D97" s="6">
-        <v>0.92</v>
+        <v>0.73</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
       </c>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C98" s="6" t="s">
+      <c r="A98" t="s">
+        <v>485</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="C98" t="s">
         <v>159</v>
       </c>
-      <c r="D98" s="6">
-        <v>0.69</v>
-      </c>
-      <c r="M98" s="4"/>
+      <c r="D98" s="2">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0.86</v>
+      </c>
+      <c r="M98" s="10"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="6" t="s">
-        <v>13</v>
+        <v>216</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D99" s="6">
-        <v>0.74</v>
+        <v>0.93</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>0.78</v>
       </c>
       <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C100" s="6" t="s">
+      <c r="A100" t="s">
+        <v>487</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C100" t="s">
         <v>159</v>
       </c>
-      <c r="D100" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="M100" s="4"/>
+      <c r="D100" s="2">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="M100" s="10"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="6" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D101" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="J101">
-        <v>0.86</v>
+        <v>0.92</v>
+      </c>
+      <c r="E101">
+        <v>0.91</v>
       </c>
       <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="6" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D102" s="6">
-        <v>0.63</v>
+        <v>0.69</v>
+      </c>
+      <c r="E102">
+        <v>0.93</v>
       </c>
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="6" t="s">
-        <v>162</v>
+        <v>13</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D103" s="6">
-        <v>0.98</v>
+        <v>0.74</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
       </c>
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="6" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D104" s="6">
-        <v>0.73</v>
+        <v>0.81</v>
+      </c>
+      <c r="E104">
+        <v>0.86</v>
       </c>
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D105" s="6">
-        <v>0.91</v>
+        <v>0.74</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0.86</v>
       </c>
       <c r="M105" s="4"/>
     </row>
     <row r="106" spans="1:13">
-      <c r="A106" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C106" s="5" t="s">
+      <c r="A106" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="E106">
+        <v>0.98</v>
+      </c>
+      <c r="M106" s="4"/>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" t="s">
+        <v>489</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C107" t="s">
+        <v>159</v>
+      </c>
+      <c r="D107" s="2">
         <v>0</v>
       </c>
-      <c r="J106">
-        <v>0.86</v>
-      </c>
-      <c r="M106" s="4"/>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="A107" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D107" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="M107" s="4"/>
+      <c r="E107">
+        <v>0.95</v>
+      </c>
+      <c r="M107" s="10"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D108" s="6">
-        <v>0.86</v>
+        <v>0.98</v>
+      </c>
+      <c r="E108">
+        <v>0.95</v>
       </c>
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D109" s="6">
-        <v>0.87</v>
+        <v>0.73</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
       </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D110" s="6">
-        <v>0.89</v>
+        <v>0.91</v>
+      </c>
+      <c r="E110">
+        <v>0.91</v>
       </c>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C111" s="6" t="s">
+      <c r="A111" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D111" s="6">
-        <v>0.86</v>
+      <c r="D111" s="5">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0.91</v>
       </c>
       <c r="J111">
         <v>0.86</v>
@@ -4043,700 +4173,805 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="6" t="s">
-        <v>174</v>
+        <v>231</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D112" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="J112">
-        <v>0.78</v>
+        <v>0.86</v>
+      </c>
+      <c r="E112">
+        <v>0.98</v>
       </c>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D113" s="6">
-        <v>0.75</v>
+        <v>0.86</v>
+      </c>
+      <c r="E113">
+        <v>0.95</v>
       </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D114" s="6">
-        <v>0.96</v>
+        <v>0.87</v>
+      </c>
+      <c r="E114">
+        <v>0.86</v>
       </c>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="6" t="s">
-        <v>237</v>
+        <v>180</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D115" s="6">
-        <v>0.91</v>
+        <v>0.89</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
       </c>
       <c r="M115" s="4"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="6" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D116" s="6">
-        <v>0.73</v>
+        <v>0.86</v>
+      </c>
+      <c r="E116">
+        <v>0.98</v>
+      </c>
+      <c r="J116">
+        <v>0.86</v>
       </c>
       <c r="M116" s="4"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C117" s="5" t="s">
+      <c r="A117" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D117" s="5">
-        <v>0</v>
+      <c r="D117" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E117">
+        <v>0.93</v>
       </c>
       <c r="J117">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D118" s="6">
-        <v>0.69</v>
+        <v>0.75</v>
+      </c>
+      <c r="E118">
+        <v>0.93</v>
       </c>
       <c r="M118" s="4"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D119" s="6">
-        <v>0.77</v>
+        <v>0.96</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
       </c>
       <c r="M119" s="4"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="6" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D120" s="6">
-        <v>0.68</v>
+        <v>0.91</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
       </c>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
-      <c r="A121" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C121" s="5" t="s">
+      <c r="A121" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="E121">
+        <v>0.95</v>
+      </c>
+      <c r="M121" s="4"/>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D122" s="5">
         <v>0</v>
       </c>
-      <c r="J121">
+      <c r="E122">
+        <v>0.88</v>
+      </c>
+      <c r="J122">
         <v>0.86</v>
-      </c>
-      <c r="M121" s="4"/>
-    </row>
-    <row r="122" spans="1:13">
-      <c r="A122" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D122" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="G122">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J122">
-        <v>0.8</v>
       </c>
       <c r="M122" s="4"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="6" t="s">
-        <v>269</v>
+        <v>184</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>270</v>
+        <v>185</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D123" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="G123">
-        <v>0.62</v>
+        <v>0.69</v>
+      </c>
+      <c r="E123">
+        <v>0.95</v>
       </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
-        <v>311</v>
+        <v>198</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>312</v>
+        <v>199</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D124" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="G124">
-        <v>0.53</v>
+        <v>0.77</v>
+      </c>
+      <c r="E124">
+        <v>0.98</v>
       </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
-        <v>333</v>
+        <v>220</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>334</v>
+        <v>221</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D125" s="6">
-        <v>0.64</v>
-      </c>
-      <c r="G125">
-        <v>0.47</v>
+        <v>0.68</v>
+      </c>
+      <c r="E125">
+        <v>0.93</v>
       </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
-      <c r="A126" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D126" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="G126">
-        <v>0.55000000000000004</v>
+      <c r="A126" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D126" s="5">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>0.86</v>
       </c>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="6" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D127" s="6">
-        <v>0.69</v>
+        <v>0.87</v>
+      </c>
+      <c r="E127">
+        <v>0.93</v>
       </c>
       <c r="G127">
-        <v>0.47</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J127">
+        <v>0.8</v>
       </c>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D128" s="6">
-        <v>0.91</v>
+        <v>0.86</v>
+      </c>
+      <c r="E128">
+        <v>0.95</v>
       </c>
       <c r="G128">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D129" s="6">
-        <v>0.88</v>
+        <v>0.79</v>
+      </c>
+      <c r="E129">
+        <v>0.91</v>
       </c>
       <c r="G129">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D130" s="6">
-        <v>0.86</v>
+        <v>0.64</v>
+      </c>
+      <c r="E130">
+        <v>0.79</v>
       </c>
       <c r="G130">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D131" s="6">
-        <v>0.87</v>
+        <v>0.79</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
       </c>
       <c r="G131">
-        <v>0.66</v>
-      </c>
-      <c r="J131">
-        <v>0.8</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C132" s="5" t="s">
+      <c r="A132" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D132" s="5">
-        <v>0</v>
+      <c r="D132" s="6">
+        <v>0.69</v>
+      </c>
+      <c r="E132">
+        <v>0.88</v>
       </c>
       <c r="G132">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>326</v>
+        <v>258</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.8</v>
+        <v>0.91</v>
+      </c>
+      <c r="E133">
+        <v>0.86</v>
       </c>
       <c r="G133">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>339</v>
+        <v>265</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>340</v>
+        <v>266</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
-        <v>0.41</v>
+        <v>0.88</v>
+      </c>
+      <c r="E134">
+        <v>0.93</v>
       </c>
       <c r="G134">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
-        <v>0.81</v>
+        <v>0.86</v>
+      </c>
+      <c r="E135">
+        <v>0.98</v>
       </c>
       <c r="G135">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="6" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D136" s="6">
-        <v>0.71</v>
+        <v>0.87</v>
+      </c>
+      <c r="E136">
+        <v>1</v>
       </c>
       <c r="G136">
-        <v>0.55000000000000004</v>
+        <v>0.66</v>
+      </c>
+      <c r="J136">
+        <v>0.8</v>
       </c>
       <c r="M136" s="4"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C137" s="6" t="s">
+      <c r="A137" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D137" s="6">
-        <v>0.86</v>
+      <c r="D137" s="5">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0.88</v>
       </c>
       <c r="G137">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="M137" s="4"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C138" s="5" t="s">
+      <c r="A138" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="5">
-        <v>0</v>
+      <c r="D138" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E138">
+        <v>0.91</v>
       </c>
       <c r="G138">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J138">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.87</v>
+        <v>0.41</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>0.61</v>
+        <v>0.36</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C140" s="5" t="s">
+      <c r="A140" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140" s="6">
+        <v>0.81</v>
+      </c>
+      <c r="E140">
         <v>0</v>
       </c>
       <c r="G140">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>0.8</v>
+        <v>0.71</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
       </c>
       <c r="G141">
-        <v>0.56999999999999995</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D142" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
       </c>
       <c r="G142">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
-      <c r="A143" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C143" s="6" t="s">
+      <c r="A143" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C143" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D143" s="6">
-        <v>0.98</v>
+      <c r="D143" s="5">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0.86</v>
       </c>
       <c r="G143">
-        <v>0.45</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J143">
+        <v>0.83</v>
       </c>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="C144" s="5" t="s">
+      <c r="A144" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>0.61</v>
+      </c>
+      <c r="M144" s="4"/>
+    </row>
+    <row r="145" spans="1:13">
+      <c r="A145" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D145" s="5">
         <v>0</v>
       </c>
-      <c r="G144">
-        <v>0.53</v>
-      </c>
-      <c r="M144" s="4"/>
-    </row>
-    <row r="145" spans="1:13">
-      <c r="A145" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C145" s="6" t="s">
+      <c r="E145">
+        <v>0.6</v>
+      </c>
+      <c r="G145">
+        <v>0.62</v>
+      </c>
+      <c r="M145" s="4"/>
+    </row>
+    <row r="146" spans="1:13">
+      <c r="A146" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D145" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="G145">
+      <c r="D146" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+      <c r="G146">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M145" s="4"/>
-    </row>
-    <row r="146" spans="1:13">
-      <c r="A146" t="s">
-        <v>479</v>
-      </c>
-      <c r="B146" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="C146" t="s">
-        <v>245</v>
-      </c>
-      <c r="D146" s="2">
-        <v>0</v>
-      </c>
-      <c r="G146">
-        <v>0.52</v>
-      </c>
-      <c r="M146" s="10"/>
+      <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>0.85</v>
+        <v>0.88</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6" t="s">
-        <v>246</v>
+        <v>337</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>247</v>
+        <v>338</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D148" s="6">
-        <v>0.88</v>
+        <v>0.98</v>
+      </c>
+      <c r="E148">
+        <v>0.98</v>
       </c>
       <c r="G148">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" t="s">
-        <v>468</v>
-      </c>
-      <c r="B149" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="A149" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="5">
         <v>0</v>
       </c>
+      <c r="E149">
+        <v>0.93</v>
+      </c>
       <c r="G149">
-        <v>0.39</v>
-      </c>
-      <c r="M149" s="10"/>
+        <v>0.53</v>
+      </c>
+      <c r="M149" s="4"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="6" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D150" s="6">
-        <v>0.71</v>
+        <v>0.75</v>
+      </c>
+      <c r="E150">
+        <v>0.98</v>
       </c>
       <c r="G150">
-        <v>0.53</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C151" t="s">
         <v>245</v>
@@ -4744,1139 +4979,1352 @@
       <c r="D151" s="2">
         <v>0</v>
       </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
       <c r="G151">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="M151" s="10"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="6" t="s">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D152" s="6">
-        <v>0.74</v>
+        <v>0.85</v>
+      </c>
+      <c r="E152">
+        <v>0.93</v>
       </c>
       <c r="G152">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
-        <v>1</v>
+        <v>0.88</v>
+      </c>
+      <c r="E153">
+        <v>0.98</v>
       </c>
       <c r="G153">
+        <v>0.61</v>
+      </c>
+      <c r="M153" s="4"/>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" t="s">
+        <v>468</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C154" t="s">
+        <v>245</v>
+      </c>
+      <c r="D154" s="2">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+      <c r="G154">
         <v>0.39</v>
       </c>
-      <c r="M153" s="4"/>
-    </row>
-    <row r="154" spans="1:13">
-      <c r="A154" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D154" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="G154">
-        <v>0.75</v>
-      </c>
-      <c r="J154">
-        <v>0.83</v>
-      </c>
-      <c r="M154" s="4"/>
+      <c r="M154" s="10"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="6" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D155" s="6">
-        <v>0.8</v>
+        <v>0.71</v>
+      </c>
+      <c r="E155">
+        <v>0.88</v>
       </c>
       <c r="G155">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="M155" s="4"/>
     </row>
     <row r="156" spans="1:13">
-      <c r="A156" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="C156" s="6" t="s">
+      <c r="A156" t="s">
+        <v>477</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="C156" t="s">
         <v>245</v>
       </c>
-      <c r="D156" s="6">
-        <v>0.91</v>
+      <c r="D156" s="2">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="M156" s="4"/>
+        <v>0.45</v>
+      </c>
+      <c r="M156" s="10"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="6" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D157" s="6">
-        <v>1</v>
+        <v>0.74</v>
+      </c>
+      <c r="E157">
+        <v>0.98</v>
       </c>
       <c r="G157">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
-      <c r="A158" t="s">
-        <v>470</v>
-      </c>
-      <c r="B158" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="C158" t="s">
+      <c r="A158" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C158" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D158" s="2">
-        <v>0</v>
+      <c r="D158" s="6">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
       </c>
       <c r="G158">
-        <v>0.71</v>
-      </c>
-      <c r="M158" s="10"/>
+        <v>0.39</v>
+      </c>
+      <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
-      <c r="A159" t="s">
-        <v>472</v>
-      </c>
-      <c r="B159" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="C159" t="s">
+      <c r="A159" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C159" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D159" s="2">
-        <v>0</v>
+      <c r="D159" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E159">
+        <v>0.84</v>
       </c>
       <c r="G159">
-        <v>0.38</v>
-      </c>
-      <c r="M159" s="10"/>
+        <v>0.75</v>
+      </c>
+      <c r="J159">
+        <v>0.83</v>
+      </c>
+      <c r="M159" s="4"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
-        <v>0.81</v>
+        <v>0.8</v>
+      </c>
+      <c r="E160">
+        <v>0.84</v>
       </c>
       <c r="G160">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" t="s">
-        <v>388</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="A161" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C161" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D161" s="2">
-        <v>0</v>
+      <c r="D161" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E161">
+        <v>0.84</v>
       </c>
       <c r="G161">
-        <v>0.51</v>
-      </c>
-      <c r="M161" s="10"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M161" s="4"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
-        <v>0.84</v>
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
       </c>
       <c r="G162">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
-      <c r="A163" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="C163" s="6" t="s">
+      <c r="A163" t="s">
+        <v>470</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C163" t="s">
         <v>245</v>
       </c>
-      <c r="D163" s="6">
-        <v>0.81</v>
+      <c r="D163" s="2">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0.91</v>
       </c>
       <c r="G163">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J163">
-        <v>0.83</v>
-      </c>
-      <c r="M163" s="4"/>
+        <v>0.71</v>
+      </c>
+      <c r="M163" s="10"/>
     </row>
     <row r="164" spans="1:13">
-      <c r="A164" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C164" s="6" t="s">
+      <c r="A164" t="s">
+        <v>472</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C164" t="s">
         <v>245</v>
       </c>
-      <c r="D164" s="6">
-        <v>0.85</v>
+      <c r="D164" s="2">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>0.98</v>
       </c>
       <c r="G164">
-        <v>0.69</v>
-      </c>
-      <c r="M164" s="4"/>
+        <v>0.38</v>
+      </c>
+      <c r="M164" s="10"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="6" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D165" s="6">
-        <v>0.91</v>
+        <v>0.81</v>
+      </c>
+      <c r="E165">
+        <v>0.95</v>
       </c>
       <c r="G165">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
-      <c r="A166" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C166" s="6" t="s">
+      <c r="A166" t="s">
+        <v>388</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C166" t="s">
         <v>245</v>
       </c>
-      <c r="D166" s="6">
-        <v>0.86</v>
+      <c r="D166" s="2">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
       </c>
       <c r="G166">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M166" s="4"/>
+        <v>0.51</v>
+      </c>
+      <c r="M166" s="10"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="6" t="s">
-        <v>461</v>
+        <v>253</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D167" s="6">
-        <v>0.93</v>
+        <v>0.84</v>
+      </c>
+      <c r="E167">
+        <v>0.98</v>
       </c>
       <c r="G167">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D168" s="6">
-        <v>0.79</v>
+        <v>0.81</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>0.48</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J168">
+        <v>0.83</v>
       </c>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D169" s="6">
-        <v>0.86</v>
+        <v>0.85</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
       </c>
       <c r="G169">
-        <v>0.61</v>
+        <v>0.69</v>
       </c>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D170" s="6">
-        <v>0.75</v>
+        <v>0.91</v>
+      </c>
+      <c r="E170">
+        <v>0.98</v>
       </c>
       <c r="G170">
-        <v>0.36</v>
+        <v>0.65</v>
       </c>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
-      <c r="A171" t="s">
-        <v>475</v>
-      </c>
-      <c r="B171" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="A171" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C171" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D171" s="2">
-        <v>0</v>
+      <c r="D171" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="E171">
+        <v>0.81</v>
       </c>
       <c r="G171">
-        <v>0.68</v>
-      </c>
-      <c r="M171" s="10"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M171" s="4"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>248</v>
+        <v>461</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D172" s="6">
-        <v>0.82</v>
+        <v>0.93</v>
+      </c>
+      <c r="E172">
+        <v>0.88</v>
       </c>
       <c r="G172">
-        <v>0.4</v>
+        <v>0.62</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D173" s="6">
-        <v>0.86</v>
+        <v>0.79</v>
+      </c>
+      <c r="E173">
+        <v>0.98</v>
       </c>
       <c r="G173">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D174" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="E174">
         <v>0.93</v>
       </c>
       <c r="G174">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D175" s="6">
-        <v>1</v>
+        <v>0.75</v>
+      </c>
+      <c r="E175">
+        <v>0.93</v>
       </c>
       <c r="G175">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
-      <c r="A176" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C176" s="6" t="s">
+      <c r="A176" t="s">
+        <v>475</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C176" t="s">
         <v>245</v>
       </c>
-      <c r="D176" s="6">
-        <v>0.91</v>
+      <c r="D176" s="2">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>0.98</v>
       </c>
       <c r="G176">
-        <v>0.53</v>
-      </c>
-      <c r="J176">
-        <v>0.8</v>
-      </c>
-      <c r="M176" s="4"/>
+        <v>0.68</v>
+      </c>
+      <c r="M176" s="10"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="6" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D177" s="6">
-        <v>0.81</v>
+        <v>0.82</v>
+      </c>
+      <c r="E177">
+        <v>0.98</v>
       </c>
       <c r="G177">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D178" s="6">
-        <v>0.81</v>
+        <v>0.86</v>
+      </c>
+      <c r="E178">
+        <v>0.98</v>
       </c>
       <c r="G178">
-        <v>0.82</v>
-      </c>
-      <c r="J178">
-        <v>0.83</v>
+        <v>0.38</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D179" s="6">
-        <v>0.8</v>
+        <v>0.93</v>
+      </c>
+      <c r="E179">
+        <v>0.95</v>
       </c>
       <c r="G179">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D180" s="6">
-        <v>0.85</v>
+        <v>1</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
       </c>
       <c r="G180">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6" t="s">
-        <v>317</v>
+        <v>255</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>318</v>
+        <v>256</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D181" s="6">
-        <v>0.89</v>
+        <v>0.91</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
       </c>
       <c r="G181">
-        <v>0.51</v>
+        <v>0.53</v>
+      </c>
+      <c r="J181">
+        <v>0.8</v>
       </c>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>349</v>
+        <v>276</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D182" s="6">
-        <v>0.77</v>
-      </c>
-      <c r="J182">
-        <v>0.8</v>
+        <v>0.81</v>
+      </c>
+      <c r="E182">
+        <v>0.65</v>
+      </c>
+      <c r="G182">
+        <v>0.32</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>392</v>
+        <v>319</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>393</v>
+        <v>320</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D183" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
+      </c>
+      <c r="E183">
+        <v>0.95</v>
+      </c>
+      <c r="G183">
+        <v>0.82</v>
       </c>
       <c r="J183">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>430</v>
+        <v>281</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>431</v>
+        <v>282</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D184" s="6">
-        <v>0.74</v>
+        <v>0.8</v>
+      </c>
+      <c r="E184">
+        <v>0.91</v>
+      </c>
+      <c r="G184">
+        <v>0.73</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D185" s="6">
-        <v>0.82</v>
+        <v>0.85</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>0.43</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D186" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="J186">
-        <v>0.8</v>
+        <v>0.89</v>
+      </c>
+      <c r="E186">
+        <v>0.93</v>
+      </c>
+      <c r="G186">
+        <v>0.51</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D187" s="6">
-        <v>0.98</v>
+        <v>0.77</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>0.8</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>434</v>
+        <v>392</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>435</v>
+        <v>393</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D188" s="6">
-        <v>0.93</v>
+        <v>0.8</v>
+      </c>
+      <c r="E188">
+        <v>0.95</v>
+      </c>
+      <c r="J188">
+        <v>0.85</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D189" s="6">
-        <v>0.67</v>
+        <v>0.74</v>
+      </c>
+      <c r="E189">
+        <v>0.91</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>418</v>
+        <v>364</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D190" s="6">
-        <v>0.96</v>
+        <v>0.82</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>412</v>
+        <v>350</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D191" s="6">
-        <v>0.92</v>
+        <v>0.85</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="J191">
+        <v>0.8</v>
       </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D192" s="6">
-        <v>0.84</v>
+        <v>0.98</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
       </c>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>394</v>
+        <v>434</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>395</v>
+        <v>435</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D193" s="6">
-        <v>0.63</v>
+        <v>0.93</v>
+      </c>
+      <c r="E193">
+        <v>0.86</v>
       </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D194" s="6">
-        <v>0.82</v>
+        <v>0.67</v>
+      </c>
+      <c r="E194">
+        <v>0.91</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D195" s="6">
-        <v>0.93</v>
+        <v>0.96</v>
+      </c>
+      <c r="E195">
+        <v>0.91</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D196" s="6">
-        <v>0.75</v>
+        <v>0.92</v>
+      </c>
+      <c r="E196">
+        <v>0.91</v>
       </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D197" s="6">
-        <v>0.96</v>
-      </c>
-      <c r="J197">
-        <v>0.8</v>
+        <v>0.84</v>
+      </c>
+      <c r="E197">
+        <v>0.95</v>
       </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D198" s="6">
-        <v>0.92</v>
+        <v>0.63</v>
+      </c>
+      <c r="E198">
+        <v>0.42</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D199" s="6">
-        <v>0.81</v>
+        <v>0.82</v>
+      </c>
+      <c r="E199">
+        <v>0.95</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D200" s="6">
-        <v>0.9</v>
+        <v>0.93</v>
+      </c>
+      <c r="E200">
+        <v>0.98</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D201" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
+      </c>
+      <c r="E201">
+        <v>0.98</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D202" s="6">
-        <v>0.76</v>
+        <v>0.96</v>
+      </c>
+      <c r="E202">
+        <v>0.91</v>
+      </c>
+      <c r="J202">
+        <v>0.8</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D203" s="6">
-        <v>0.93</v>
+        <v>0.92</v>
+      </c>
+      <c r="E203">
+        <v>1</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D204" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="J204">
-        <v>0.85</v>
+        <v>0.81</v>
+      </c>
+      <c r="E204">
+        <v>0.88</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="6" t="s">
-        <v>446</v>
+        <v>380</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D205" s="6">
-        <v>0.81</v>
+        <v>0.9</v>
+      </c>
+      <c r="E205">
+        <v>0.98</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D206" s="6">
-        <v>0.85</v>
+        <v>0.96</v>
+      </c>
+      <c r="E206">
+        <v>0.91</v>
       </c>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="6" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>411</v>
+        <v>342</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D207" s="6">
-        <v>0.96</v>
+        <v>0.76</v>
+      </c>
+      <c r="E207">
+        <v>0.88</v>
       </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="6" t="s">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D208" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="J208">
-        <v>0.79</v>
+        <v>0.93</v>
+      </c>
+      <c r="E208">
+        <v>0.95</v>
       </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D209" s="6">
-        <v>0.96</v>
+        <v>0.79</v>
+      </c>
+      <c r="E209">
+        <v>0.91</v>
+      </c>
+      <c r="J209">
+        <v>0.85</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>374</v>
+        <v>446</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>375</v>
+        <v>447</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D210" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
       </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D211" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
+      </c>
+      <c r="E211">
+        <v>0.98</v>
       </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D212" s="6">
-        <v>0.93</v>
+        <v>0.96</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>420</v>
+        <v>344</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>421</v>
+        <v>345</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D213" s="6">
-        <v>1</v>
+        <v>0.81</v>
+      </c>
+      <c r="E213">
+        <v>0.95</v>
       </c>
       <c r="J213">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D214" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
+      </c>
+      <c r="E214">
+        <v>0.98</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D215" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.85</v>
+      </c>
+      <c r="E215">
+        <v>0.86</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>417</v>
+        <v>389</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D216" s="6">
-        <v>0.89</v>
+        <v>0.77</v>
+      </c>
+      <c r="E216">
+        <v>0.98</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D217" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="J217">
-        <v>0.85</v>
+        <v>0.93</v>
+      </c>
+      <c r="E217">
+        <v>1</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="A218" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C218" s="5" t="s">
+      <c r="A218" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="C218" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="D218" s="5">
-        <v>0</v>
+      <c r="D218" s="6">
+        <v>1</v>
+      </c>
+      <c r="E218">
+        <v>0.88</v>
       </c>
       <c r="J218">
         <v>0.93</v>
@@ -5885,106 +6333,124 @@
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="6" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>387</v>
+        <v>433</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D219" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E219">
         <v>0.98</v>
       </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="6" t="s">
-        <v>402</v>
+        <v>356</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>403</v>
+        <v>357</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D220" s="6">
-        <v>0.96</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
       </c>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="6" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D221" s="6">
-        <v>0.96</v>
+        <v>0.89</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
       </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="6" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D222" s="6">
-        <v>0.42</v>
+        <v>0.98</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
       </c>
       <c r="J222">
+        <v>0.85</v>
+      </c>
+      <c r="M222" s="4"/>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D223" s="5">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
+      <c r="J223">
         <v>0.93</v>
-      </c>
-      <c r="M222" s="4"/>
-    </row>
-    <row r="223" spans="1:13">
-      <c r="A223" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="D223" s="6">
-        <v>0.88</v>
       </c>
       <c r="M223" s="4"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="6" t="s">
-        <v>444</v>
+        <v>386</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>445</v>
+        <v>387</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D224" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="J224">
-        <v>0.93</v>
+        <v>0.98</v>
+      </c>
+      <c r="E224">
+        <v>0.95</v>
       </c>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="6" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>343</v>
@@ -5992,203 +6458,298 @@
       <c r="D225" s="6">
         <v>0.96</v>
       </c>
+      <c r="E225">
+        <v>0.98</v>
+      </c>
       <c r="M225" s="4"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="6" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D226" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="J226">
-        <v>0.8</v>
+        <v>0.96</v>
+      </c>
+      <c r="E226">
+        <v>0.95</v>
       </c>
       <c r="M226" s="4"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="6" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D227" s="6">
-        <v>0.76</v>
+        <v>0.42</v>
+      </c>
+      <c r="E227">
+        <v>0.77</v>
+      </c>
+      <c r="J227">
+        <v>0.93</v>
       </c>
       <c r="M227" s="4"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="6" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D228" s="6">
-        <v>0.41</v>
+        <v>0.88</v>
+      </c>
+      <c r="E228">
+        <v>1</v>
       </c>
       <c r="M228" s="4"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="6" t="s">
-        <v>346</v>
+        <v>444</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>347</v>
+        <v>445</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D229" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="M229" s="11"/>
+        <v>0.78</v>
+      </c>
+      <c r="E229">
+        <v>0.95</v>
+      </c>
+      <c r="J229">
+        <v>0.93</v>
+      </c>
+      <c r="M229" s="12"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="6" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D230" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="M230" s="11"/>
+        <v>0.96</v>
+      </c>
+      <c r="E230">
+        <v>0.93</v>
+      </c>
+      <c r="M230" s="12"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="6" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D231" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="M231" s="11"/>
+        <v>0.68</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="J231">
+        <v>0.8</v>
+      </c>
+      <c r="M231" s="12"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="6" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="C232" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D232" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="J232">
-        <v>0.83</v>
-      </c>
-      <c r="M232" s="11"/>
+        <v>0.76</v>
+      </c>
+      <c r="E232">
+        <v>0.98</v>
+      </c>
+      <c r="M232" s="12"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="6" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D233" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="J233">
-        <v>0.8</v>
-      </c>
-      <c r="M233" s="11"/>
+        <v>0.41</v>
+      </c>
+      <c r="E233">
+        <v>0.63</v>
+      </c>
+      <c r="M233" s="12"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="6" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D234" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="M234" s="11"/>
+        <v>0.8</v>
+      </c>
+      <c r="E234">
+        <v>0.88</v>
+      </c>
+      <c r="M234" s="12"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="6" t="s">
-        <v>442</v>
+        <v>378</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>443</v>
+        <v>379</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D235" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="M235" s="12"/>
+    </row>
+    <row r="236" spans="1:13">
+      <c r="A236" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D236" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="M236" s="12"/>
+    </row>
+    <row r="237" spans="1:13">
+      <c r="A237" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D237" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="E237">
         <v>0.88</v>
       </c>
-      <c r="J235">
+      <c r="J237">
+        <v>0.83</v>
+      </c>
+      <c r="M237" s="12"/>
+    </row>
+    <row r="238" spans="1:13">
+      <c r="A238" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D238" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="E238">
+        <v>0.98</v>
+      </c>
+      <c r="J238">
+        <v>0.8</v>
+      </c>
+      <c r="M238" s="12"/>
+    </row>
+    <row r="239" spans="1:13">
+      <c r="A239" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D239" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="E239">
         <v>0.93</v>
       </c>
-      <c r="M235" s="11"/>
-    </row>
-    <row r="236" spans="1:13">
-      <c r="A236" t="s">
-        <v>481</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="C236" t="s">
-        <v>15</v>
-      </c>
-      <c r="D236" s="2">
-        <v>0</v>
-      </c>
-      <c r="E236">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13">
-      <c r="A237" t="s">
-        <v>483</v>
-      </c>
-      <c r="B237" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="C237" t="s">
-        <v>15</v>
-      </c>
-      <c r="D237" s="2">
-        <v>0</v>
-      </c>
-      <c r="E237">
-        <v>0.98</v>
-      </c>
+      <c r="M239" s="11"/>
+    </row>
+    <row r="240" spans="1:13">
+      <c r="A240" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D240" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E240">
+        <v>0.95</v>
+      </c>
+      <c r="J240">
+        <v>0.93</v>
+      </c>
+      <c r="M240" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C271594-C650-EC42-AFA1-7D18AE906B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8785FEE2-8D6A-1349-9AB9-9DECE47D2211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="16000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1611,7 +1611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1630,9 +1630,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -2129,7 +2126,7 @@
       <c r="E4">
         <v>0.98</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="6" t="s">
@@ -4110,7 +4107,7 @@
         <v>0.98</v>
       </c>
       <c r="E108">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="M108" s="4"/>
     </row>
@@ -6539,7 +6536,7 @@
       <c r="J229">
         <v>0.93</v>
       </c>
-      <c r="M229" s="12"/>
+      <c r="M229" s="11"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="6" t="s">
@@ -6557,7 +6554,7 @@
       <c r="E230">
         <v>0.93</v>
       </c>
-      <c r="M230" s="12"/>
+      <c r="M230" s="11"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="6" t="s">
@@ -6578,7 +6575,7 @@
       <c r="J231">
         <v>0.8</v>
       </c>
-      <c r="M231" s="12"/>
+      <c r="M231" s="11"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="6" t="s">
@@ -6596,7 +6593,7 @@
       <c r="E232">
         <v>0.98</v>
       </c>
-      <c r="M232" s="12"/>
+      <c r="M232" s="11"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="6" t="s">
@@ -6614,7 +6611,7 @@
       <c r="E233">
         <v>0.63</v>
       </c>
-      <c r="M233" s="12"/>
+      <c r="M233" s="11"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="6" t="s">
@@ -6632,7 +6629,7 @@
       <c r="E234">
         <v>0.88</v>
       </c>
-      <c r="M234" s="12"/>
+      <c r="M234" s="11"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="6" t="s">
@@ -6650,7 +6647,7 @@
       <c r="E235">
         <v>0</v>
       </c>
-      <c r="M235" s="12"/>
+      <c r="M235" s="11"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="6" t="s">
@@ -6668,7 +6665,7 @@
       <c r="E236">
         <v>0</v>
       </c>
-      <c r="M236" s="12"/>
+      <c r="M236" s="11"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="6" t="s">
@@ -6689,7 +6686,7 @@
       <c r="J237">
         <v>0.83</v>
       </c>
-      <c r="M237" s="12"/>
+      <c r="M237" s="11"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="6" t="s">
@@ -6710,7 +6707,7 @@
       <c r="J238">
         <v>0.8</v>
       </c>
-      <c r="M238" s="12"/>
+      <c r="M238" s="11"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="6" t="s">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8785FEE2-8D6A-1349-9AB9-9DECE47D2211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA0FEFC-A7D7-2E4B-AAFF-B73FCDEFC63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="16000" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1020" yWindow="620" windowWidth="20220" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5747,6 +5747,9 @@
       <c r="E187">
         <v>1</v>
       </c>
+      <c r="G187">
+        <v>0.69</v>
+      </c>
       <c r="J187">
         <v>0.8</v>
       </c>
@@ -5768,6 +5771,9 @@
       <c r="E188">
         <v>0.95</v>
       </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
       <c r="J188">
         <v>0.85</v>
       </c>
@@ -5789,6 +5795,9 @@
       <c r="E189">
         <v>0.91</v>
       </c>
+      <c r="G189">
+        <v>0.45</v>
+      </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
@@ -5807,6 +5816,9 @@
       <c r="E190">
         <v>1</v>
       </c>
+      <c r="G190">
+        <v>0.61</v>
+      </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
@@ -5825,6 +5837,9 @@
       <c r="E191">
         <v>1</v>
       </c>
+      <c r="G191">
+        <v>0.61</v>
+      </c>
       <c r="J191">
         <v>0.8</v>
       </c>
@@ -5846,6 +5861,9 @@
       <c r="E192">
         <v>1</v>
       </c>
+      <c r="G192">
+        <v>0.64</v>
+      </c>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
@@ -5864,6 +5882,9 @@
       <c r="E193">
         <v>0.86</v>
       </c>
+      <c r="G193">
+        <v>0.64</v>
+      </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
@@ -5882,6 +5903,9 @@
       <c r="E194">
         <v>0.91</v>
       </c>
+      <c r="G194">
+        <v>0.65</v>
+      </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
@@ -5900,6 +5924,9 @@
       <c r="E195">
         <v>0.91</v>
       </c>
+      <c r="G195">
+        <v>0.69</v>
+      </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
@@ -5918,6 +5945,9 @@
       <c r="E196">
         <v>0.91</v>
       </c>
+      <c r="G196">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
@@ -5936,6 +5966,9 @@
       <c r="E197">
         <v>0.95</v>
       </c>
+      <c r="G197">
+        <v>0.74</v>
+      </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
@@ -5954,6 +5987,9 @@
       <c r="E198">
         <v>0.42</v>
       </c>
+      <c r="G198">
+        <v>0.64</v>
+      </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
@@ -5972,6 +6008,9 @@
       <c r="E199">
         <v>0.95</v>
       </c>
+      <c r="G199">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
@@ -5990,6 +6029,9 @@
       <c r="E200">
         <v>0.98</v>
       </c>
+      <c r="G200">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
@@ -6008,6 +6050,9 @@
       <c r="E201">
         <v>0.98</v>
       </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
@@ -6026,6 +6071,9 @@
       <c r="E202">
         <v>0.91</v>
       </c>
+      <c r="G202">
+        <v>0.82</v>
+      </c>
       <c r="J202">
         <v>0.8</v>
       </c>
@@ -6047,6 +6095,9 @@
       <c r="E203">
         <v>1</v>
       </c>
+      <c r="G203">
+        <v>0.64</v>
+      </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
@@ -6065,6 +6116,9 @@
       <c r="E204">
         <v>0.88</v>
       </c>
+      <c r="G204">
+        <v>0.7</v>
+      </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
@@ -6083,6 +6137,9 @@
       <c r="E205">
         <v>0.98</v>
       </c>
+      <c r="G205">
+        <v>0.53</v>
+      </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
@@ -6101,6 +6158,9 @@
       <c r="E206">
         <v>0.91</v>
       </c>
+      <c r="G206">
+        <v>0.81</v>
+      </c>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
@@ -6119,6 +6179,9 @@
       <c r="E207">
         <v>0.88</v>
       </c>
+      <c r="G207">
+        <v>0.71</v>
+      </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
@@ -6137,6 +6200,9 @@
       <c r="E208">
         <v>0.95</v>
       </c>
+      <c r="G208">
+        <v>0.49</v>
+      </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
@@ -6155,6 +6221,9 @@
       <c r="E209">
         <v>0.91</v>
       </c>
+      <c r="G209">
+        <v>0.6</v>
+      </c>
       <c r="J209">
         <v>0.85</v>
       </c>
@@ -6176,6 +6245,9 @@
       <c r="E210">
         <v>1</v>
       </c>
+      <c r="G210">
+        <v>0.75</v>
+      </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
@@ -6194,6 +6266,9 @@
       <c r="E211">
         <v>0.98</v>
       </c>
+      <c r="G211">
+        <v>0.69</v>
+      </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
@@ -6212,6 +6287,9 @@
       <c r="E212">
         <v>1</v>
       </c>
+      <c r="G212">
+        <v>0.73</v>
+      </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
@@ -6230,6 +6308,9 @@
       <c r="E213">
         <v>0.95</v>
       </c>
+      <c r="G213">
+        <v>0.73</v>
+      </c>
       <c r="J213">
         <v>0.79</v>
       </c>
@@ -6251,6 +6332,9 @@
       <c r="E214">
         <v>0.98</v>
       </c>
+      <c r="G214">
+        <v>0.65</v>
+      </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
@@ -6269,6 +6353,9 @@
       <c r="E215">
         <v>0.86</v>
       </c>
+      <c r="G215">
+        <v>0.83</v>
+      </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
@@ -6287,6 +6374,9 @@
       <c r="E216">
         <v>0.98</v>
       </c>
+      <c r="G216">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
@@ -6305,6 +6395,9 @@
       <c r="E217">
         <v>1</v>
       </c>
+      <c r="G217">
+        <v>0.77</v>
+      </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
@@ -6323,6 +6416,9 @@
       <c r="E218">
         <v>0.88</v>
       </c>
+      <c r="G218">
+        <v>0.77</v>
+      </c>
       <c r="J218">
         <v>0.93</v>
       </c>
@@ -6344,6 +6440,9 @@
       <c r="E219">
         <v>0.98</v>
       </c>
+      <c r="G219">
+        <v>0.7</v>
+      </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
@@ -6362,6 +6461,9 @@
       <c r="E220">
         <v>0</v>
       </c>
+      <c r="G220">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
@@ -6380,6 +6482,9 @@
       <c r="E221">
         <v>1</v>
       </c>
+      <c r="G221">
+        <v>0.35</v>
+      </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
@@ -6398,6 +6503,9 @@
       <c r="E222">
         <v>0</v>
       </c>
+      <c r="G222">
+        <v>0.88</v>
+      </c>
       <c r="J222">
         <v>0.85</v>
       </c>
@@ -6419,6 +6527,9 @@
       <c r="E223">
         <v>1</v>
       </c>
+      <c r="G223">
+        <v>0.6</v>
+      </c>
       <c r="J223">
         <v>0.93</v>
       </c>
@@ -6440,6 +6551,9 @@
       <c r="E224">
         <v>0.95</v>
       </c>
+      <c r="G224">
+        <v>0.81</v>
+      </c>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">
@@ -6458,6 +6572,9 @@
       <c r="E225">
         <v>0.98</v>
       </c>
+      <c r="G225">
+        <v>0.7</v>
+      </c>
       <c r="M225" s="4"/>
     </row>
     <row r="226" spans="1:13">
@@ -6476,6 +6593,9 @@
       <c r="E226">
         <v>0.95</v>
       </c>
+      <c r="G226">
+        <v>0.77</v>
+      </c>
       <c r="M226" s="4"/>
     </row>
     <row r="227" spans="1:13">
@@ -6494,6 +6614,9 @@
       <c r="E227">
         <v>0.77</v>
       </c>
+      <c r="G227">
+        <v>0.53</v>
+      </c>
       <c r="J227">
         <v>0.93</v>
       </c>
@@ -6515,6 +6638,9 @@
       <c r="E228">
         <v>1</v>
       </c>
+      <c r="G228">
+        <v>0.69</v>
+      </c>
       <c r="M228" s="4"/>
     </row>
     <row r="229" spans="1:13">
@@ -6533,6 +6659,9 @@
       <c r="E229">
         <v>0.95</v>
       </c>
+      <c r="G229">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J229">
         <v>0.93</v>
       </c>
@@ -6554,6 +6683,9 @@
       <c r="E230">
         <v>0.93</v>
       </c>
+      <c r="G230">
+        <v>0.64</v>
+      </c>
       <c r="M230" s="11"/>
     </row>
     <row r="231" spans="1:13">
@@ -6572,6 +6704,9 @@
       <c r="E231">
         <v>1</v>
       </c>
+      <c r="G231">
+        <v>0.78</v>
+      </c>
       <c r="J231">
         <v>0.8</v>
       </c>
@@ -6593,6 +6728,9 @@
       <c r="E232">
         <v>0.98</v>
       </c>
+      <c r="G232">
+        <v>0.68</v>
+      </c>
       <c r="M232" s="11"/>
     </row>
     <row r="233" spans="1:13">
@@ -6611,6 +6749,9 @@
       <c r="E233">
         <v>0.63</v>
       </c>
+      <c r="G233">
+        <v>0.43</v>
+      </c>
       <c r="M233" s="11"/>
     </row>
     <row r="234" spans="1:13">
@@ -6629,6 +6770,9 @@
       <c r="E234">
         <v>0.88</v>
       </c>
+      <c r="G234">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M234" s="11"/>
     </row>
     <row r="235" spans="1:13">
@@ -6647,6 +6791,9 @@
       <c r="E235">
         <v>0</v>
       </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
       <c r="M235" s="11"/>
     </row>
     <row r="236" spans="1:13">
@@ -6665,6 +6812,9 @@
       <c r="E236">
         <v>0</v>
       </c>
+      <c r="G236">
+        <v>0.77</v>
+      </c>
       <c r="M236" s="11"/>
     </row>
     <row r="237" spans="1:13">
@@ -6683,6 +6833,9 @@
       <c r="E237">
         <v>0.88</v>
       </c>
+      <c r="G237">
+        <v>0.51</v>
+      </c>
       <c r="J237">
         <v>0.83</v>
       </c>
@@ -6704,6 +6857,9 @@
       <c r="E238">
         <v>0.98</v>
       </c>
+      <c r="G238">
+        <v>0.74</v>
+      </c>
       <c r="J238">
         <v>0.8</v>
       </c>
@@ -6725,6 +6881,9 @@
       <c r="E239">
         <v>0.93</v>
       </c>
+      <c r="G239">
+        <v>0.65</v>
+      </c>
       <c r="M239" s="11"/>
     </row>
     <row r="240" spans="1:13">
@@ -6742,6 +6901,9 @@
       </c>
       <c r="E240">
         <v>0.95</v>
+      </c>
+      <c r="G240">
+        <v>0.71</v>
       </c>
       <c r="J240">
         <v>0.93</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA0FEFC-A7D7-2E4B-AAFF-B73FCDEFC63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556CF55F-563C-5F47-8FF6-976E62B5740A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="620" windowWidth="20220" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="492">
   <si>
     <t>Surname</t>
   </si>
@@ -1509,6 +1509,9 @@
   </si>
   <si>
     <t>H261401R</t>
+  </si>
+  <si>
+    <t>H265070B</t>
   </si>
 </sst>
 </file>
@@ -1676,8 +1679,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M240" totalsRowShown="0">
-  <autoFilter ref="A1:M240" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M241" totalsRowShown="0">
+  <autoFilter ref="A1:M241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M240">
     <sortCondition ref="C1:C240"/>
   </sortState>
@@ -2017,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M240"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -3536,6 +3539,9 @@
       <c r="E77">
         <v>1</v>
       </c>
+      <c r="G77">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="J77">
         <v>0.78</v>
       </c>
@@ -3557,6 +3563,9 @@
       <c r="E78">
         <v>1</v>
       </c>
+      <c r="G78">
+        <v>0.48</v>
+      </c>
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13">
@@ -3575,6 +3584,9 @@
       <c r="E79">
         <v>0.98</v>
       </c>
+      <c r="G79">
+        <v>0.52</v>
+      </c>
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13">
@@ -3593,6 +3605,9 @@
       <c r="E80">
         <v>1</v>
       </c>
+      <c r="G80">
+        <v>0.68</v>
+      </c>
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13">
@@ -3611,6 +3626,9 @@
       <c r="E81">
         <v>0.77</v>
       </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
       <c r="J81">
         <v>0.78</v>
       </c>
@@ -3632,6 +3650,9 @@
       <c r="E82">
         <v>0.98</v>
       </c>
+      <c r="G82">
+        <v>0.69</v>
+      </c>
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13">
@@ -3650,6 +3671,9 @@
       <c r="E83">
         <v>0.98</v>
       </c>
+      <c r="G83">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
@@ -3668,6 +3692,9 @@
       <c r="E84">
         <v>1</v>
       </c>
+      <c r="G84">
+        <v>0.42</v>
+      </c>
       <c r="J84">
         <v>0.78</v>
       </c>
@@ -3689,6 +3716,9 @@
       <c r="E85">
         <v>0.98</v>
       </c>
+      <c r="G85">
+        <v>0.51</v>
+      </c>
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
@@ -3707,6 +3737,9 @@
       <c r="E86">
         <v>0.98</v>
       </c>
+      <c r="G86">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13">
@@ -3725,6 +3758,9 @@
       <c r="E87">
         <v>0.95</v>
       </c>
+      <c r="G87">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
@@ -3743,6 +3779,9 @@
       <c r="E88">
         <v>0.95</v>
       </c>
+      <c r="G88">
+        <v>0.62</v>
+      </c>
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13">
@@ -3761,6 +3800,9 @@
       <c r="E89">
         <v>0.93</v>
       </c>
+      <c r="G89">
+        <v>0.61</v>
+      </c>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
@@ -3779,6 +3821,9 @@
       <c r="E90">
         <v>0</v>
       </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
@@ -3797,6 +3842,9 @@
       <c r="E91">
         <v>0.93</v>
       </c>
+      <c r="G91">
+        <v>0.65</v>
+      </c>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
@@ -3815,6 +3863,9 @@
       <c r="E92">
         <v>0.51</v>
       </c>
+      <c r="G92">
+        <v>0.52</v>
+      </c>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
@@ -3833,6 +3884,9 @@
       <c r="E93">
         <v>0.98</v>
       </c>
+      <c r="G93">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
@@ -3851,6 +3905,9 @@
       <c r="E94">
         <v>0.74</v>
       </c>
+      <c r="G94">
+        <v>0.77</v>
+      </c>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
@@ -3869,6 +3926,9 @@
       <c r="E95">
         <v>0.95</v>
       </c>
+      <c r="G95">
+        <v>0.73</v>
+      </c>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
@@ -3887,6 +3947,9 @@
       <c r="E96">
         <v>0.93</v>
       </c>
+      <c r="G96">
+        <v>0.52</v>
+      </c>
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13">
@@ -3905,6 +3968,9 @@
       <c r="E97">
         <v>1</v>
       </c>
+      <c r="G97">
+        <v>0.65</v>
+      </c>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="1:13">
@@ -3923,6 +3989,9 @@
       <c r="E98">
         <v>0.86</v>
       </c>
+      <c r="G98">
+        <v>0.6</v>
+      </c>
       <c r="M98" s="10"/>
     </row>
     <row r="99" spans="1:13">
@@ -3941,6 +4010,9 @@
       <c r="E99">
         <v>1</v>
       </c>
+      <c r="G99">
+        <v>0.6</v>
+      </c>
       <c r="J99">
         <v>0.78</v>
       </c>
@@ -3962,6 +4034,9 @@
       <c r="E100">
         <v>1</v>
       </c>
+      <c r="G100">
+        <v>0.81</v>
+      </c>
       <c r="M100" s="10"/>
     </row>
     <row r="101" spans="1:13">
@@ -3980,6 +4055,9 @@
       <c r="E101">
         <v>0.91</v>
       </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
       <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13">
@@ -3998,6 +4076,9 @@
       <c r="E102">
         <v>0.93</v>
       </c>
+      <c r="G102">
+        <v>0.53</v>
+      </c>
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13">
@@ -4016,6 +4097,9 @@
       <c r="E103">
         <v>1</v>
       </c>
+      <c r="G103">
+        <v>0.64</v>
+      </c>
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13">
@@ -4034,6 +4118,9 @@
       <c r="E104">
         <v>0.86</v>
       </c>
+      <c r="G104">
+        <v>0.51</v>
+      </c>
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13">
@@ -4052,6 +4139,9 @@
       <c r="E105">
         <v>1</v>
       </c>
+      <c r="G105">
+        <v>0.61</v>
+      </c>
       <c r="J105">
         <v>0.86</v>
       </c>
@@ -4073,6 +4163,9 @@
       <c r="E106">
         <v>0.98</v>
       </c>
+      <c r="G106">
+        <v>0.36</v>
+      </c>
       <c r="M106" s="4"/>
     </row>
     <row r="107" spans="1:13">
@@ -4091,6 +4184,9 @@
       <c r="E107">
         <v>0.95</v>
       </c>
+      <c r="G107">
+        <v>0.66</v>
+      </c>
       <c r="M107" s="10"/>
     </row>
     <row r="108" spans="1:13">
@@ -4109,6 +4205,9 @@
       <c r="E108">
         <v>1</v>
       </c>
+      <c r="G108">
+        <v>0.68</v>
+      </c>
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
@@ -4127,6 +4226,9 @@
       <c r="E109">
         <v>1</v>
       </c>
+      <c r="G109">
+        <v>0.79</v>
+      </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
@@ -4145,6 +4247,9 @@
       <c r="E110">
         <v>0.91</v>
       </c>
+      <c r="G110">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
@@ -4163,6 +4268,9 @@
       <c r="E111">
         <v>0.91</v>
       </c>
+      <c r="G111">
+        <v>0.6</v>
+      </c>
       <c r="J111">
         <v>0.86</v>
       </c>
@@ -4184,6 +4292,9 @@
       <c r="E112">
         <v>0.98</v>
       </c>
+      <c r="G112">
+        <v>0.52</v>
+      </c>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
@@ -4202,6 +4313,9 @@
       <c r="E113">
         <v>0.95</v>
       </c>
+      <c r="G113">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
@@ -4220,6 +4334,9 @@
       <c r="E114">
         <v>0.86</v>
       </c>
+      <c r="G114">
+        <v>0.39</v>
+      </c>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
@@ -4238,6 +4355,9 @@
       <c r="E115">
         <v>1</v>
       </c>
+      <c r="G115">
+        <v>0.71</v>
+      </c>
       <c r="M115" s="4"/>
     </row>
     <row r="116" spans="1:13">
@@ -4256,6 +4376,9 @@
       <c r="E116">
         <v>0.98</v>
       </c>
+      <c r="G116">
+        <v>0.36</v>
+      </c>
       <c r="J116">
         <v>0.86</v>
       </c>
@@ -4277,6 +4400,9 @@
       <c r="E117">
         <v>0.93</v>
       </c>
+      <c r="G117">
+        <v>0.42</v>
+      </c>
       <c r="J117">
         <v>0.78</v>
       </c>
@@ -4298,6 +4424,9 @@
       <c r="E118">
         <v>0.93</v>
       </c>
+      <c r="G118">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M118" s="4"/>
     </row>
     <row r="119" spans="1:13">
@@ -4316,6 +4445,9 @@
       <c r="E119">
         <v>0</v>
       </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
       <c r="M119" s="4"/>
     </row>
     <row r="120" spans="1:13">
@@ -4334,6 +4466,9 @@
       <c r="E120">
         <v>1</v>
       </c>
+      <c r="G120">
+        <v>0.52</v>
+      </c>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
@@ -4352,6 +4487,9 @@
       <c r="E121">
         <v>0.95</v>
       </c>
+      <c r="G121">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M121" s="4"/>
     </row>
     <row r="122" spans="1:13">
@@ -4370,6 +4508,9 @@
       <c r="E122">
         <v>0.88</v>
       </c>
+      <c r="G122">
+        <v>0.71</v>
+      </c>
       <c r="J122">
         <v>0.86</v>
       </c>
@@ -4391,6 +4532,9 @@
       <c r="E123">
         <v>0.95</v>
       </c>
+      <c r="G123">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
@@ -4409,6 +4553,9 @@
       <c r="E124">
         <v>0.98</v>
       </c>
+      <c r="G124">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
@@ -4427,6 +4574,9 @@
       <c r="E125">
         <v>0.93</v>
       </c>
+      <c r="G125">
+        <v>0.78</v>
+      </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
@@ -4445,6 +4595,9 @@
       <c r="E126">
         <v>1</v>
       </c>
+      <c r="G126">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="J126">
         <v>0.86</v>
       </c>
@@ -6909,6 +7062,21 @@
         <v>0.93</v>
       </c>
       <c r="M240" s="11"/>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" t="s">
+        <v>462</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="C241" t="s">
+        <v>159</v>
+      </c>
+      <c r="D241" s="2"/>
+      <c r="G241">
+        <v>0.53</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{556CF55F-563C-5F47-8FF6-976E62B5740A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BD463B-EDE1-7F43-BF1D-A8C71F6F79FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="620" windowWidth="20220" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1160" yWindow="620" windowWidth="16740" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2085,6 +2085,9 @@
       <c r="E2">
         <v>0.88</v>
       </c>
+      <c r="G2">
+        <v>0.42</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="J2">
         <v>0.72</v>
@@ -2107,6 +2110,9 @@
       <c r="E3">
         <v>0.98</v>
       </c>
+      <c r="G3">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="J3">
         <v>0.72</v>
@@ -2129,6 +2135,9 @@
       <c r="E4">
         <v>0.98</v>
       </c>
+      <c r="G4">
+        <v>0.68</v>
+      </c>
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:13">
@@ -2147,6 +2156,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="G5">
+        <v>0.77</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="M5" s="7"/>
     </row>
@@ -2166,6 +2178,9 @@
       <c r="E6">
         <v>0.98</v>
       </c>
+      <c r="G6">
+        <v>0.68</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="M6" s="4"/>
     </row>
@@ -2185,6 +2200,9 @@
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="G7">
+        <v>0.81</v>
+      </c>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13">
@@ -2203,6 +2221,9 @@
       <c r="E8">
         <v>0.93</v>
       </c>
+      <c r="G8">
+        <v>0.6</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="M8" s="4"/>
     </row>
@@ -2222,6 +2243,9 @@
       <c r="E9">
         <v>1</v>
       </c>
+      <c r="G9">
+        <v>0.51</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="M9" s="4"/>
     </row>
@@ -2241,6 +2265,9 @@
       <c r="E10">
         <v>1</v>
       </c>
+      <c r="G10">
+        <v>0.53</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="M10" s="4"/>
     </row>
@@ -2260,6 +2287,9 @@
       <c r="E11">
         <v>0.93</v>
       </c>
+      <c r="G11">
+        <v>0.66</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="M11" s="4"/>
     </row>
@@ -2279,6 +2309,9 @@
       <c r="E12">
         <v>1</v>
       </c>
+      <c r="G12">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="M12" s="4"/>
     </row>
@@ -2298,6 +2331,9 @@
       <c r="E13">
         <v>0.98</v>
       </c>
+      <c r="G13">
+        <v>0.75</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="M13" s="4"/>
     </row>
@@ -2317,6 +2353,9 @@
       <c r="E14">
         <v>0.98</v>
       </c>
+      <c r="G14">
+        <v>0.51</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="M14" s="4"/>
     </row>
@@ -2336,6 +2375,9 @@
       <c r="E15">
         <v>0.95</v>
       </c>
+      <c r="G15">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H15" s="3"/>
       <c r="M15" s="4"/>
     </row>
@@ -2355,6 +2397,9 @@
       <c r="E16">
         <v>1</v>
       </c>
+      <c r="G16">
+        <v>0.52</v>
+      </c>
       <c r="H16" s="3"/>
       <c r="M16" s="4"/>
     </row>
@@ -2374,6 +2419,9 @@
       <c r="E17">
         <v>0.98</v>
       </c>
+      <c r="G17">
+        <v>0.47</v>
+      </c>
       <c r="H17" s="3"/>
       <c r="M17" s="4"/>
     </row>
@@ -2393,6 +2441,9 @@
       <c r="E18">
         <v>0.95</v>
       </c>
+      <c r="G18">
+        <v>0.65</v>
+      </c>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13">
@@ -2411,6 +2462,9 @@
       <c r="E19">
         <v>0.93</v>
       </c>
+      <c r="G19">
+        <v>0.73</v>
+      </c>
       <c r="H19" s="3"/>
       <c r="M19" s="4"/>
     </row>
@@ -2430,6 +2484,9 @@
       <c r="E20">
         <v>0.95</v>
       </c>
+      <c r="G20">
+        <v>0.62</v>
+      </c>
       <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13">
@@ -2448,6 +2505,9 @@
       <c r="E21">
         <v>0.98</v>
       </c>
+      <c r="G21">
+        <v>0.66</v>
+      </c>
       <c r="H21" s="3"/>
       <c r="M21" s="4"/>
     </row>
@@ -2467,6 +2527,9 @@
       <c r="E22">
         <v>1</v>
       </c>
+      <c r="G22">
+        <v>0.78</v>
+      </c>
       <c r="H22" s="3"/>
       <c r="M22" s="4"/>
     </row>
@@ -2486,6 +2549,9 @@
       <c r="E23">
         <v>0.98</v>
       </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
       <c r="M23" s="10"/>
     </row>
     <row r="24" spans="1:13">
@@ -2504,6 +2570,9 @@
       <c r="E24">
         <v>0.98</v>
       </c>
+      <c r="G24">
+        <v>0.62</v>
+      </c>
       <c r="M24" s="4"/>
     </row>
     <row r="25" spans="1:13">
@@ -2522,6 +2591,9 @@
       <c r="E25">
         <v>0.93</v>
       </c>
+      <c r="G25">
+        <v>0.61</v>
+      </c>
       <c r="H25" s="3"/>
       <c r="M25" s="4"/>
     </row>
@@ -2541,6 +2613,9 @@
       <c r="E26">
         <v>1</v>
       </c>
+      <c r="G26">
+        <v>0.4</v>
+      </c>
       <c r="H26" s="3"/>
       <c r="M26" s="4"/>
     </row>
@@ -2560,6 +2635,9 @@
       <c r="E27">
         <v>1</v>
       </c>
+      <c r="G27">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H27" s="3"/>
       <c r="M27" s="4"/>
     </row>
@@ -2579,6 +2657,9 @@
       <c r="E28">
         <v>1</v>
       </c>
+      <c r="G28">
+        <v>0.77</v>
+      </c>
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13">
@@ -2597,6 +2678,9 @@
       <c r="E29">
         <v>0.7</v>
       </c>
+      <c r="G29">
+        <v>0.34</v>
+      </c>
       <c r="H29" s="3"/>
       <c r="M29" s="8"/>
     </row>
@@ -2616,6 +2700,9 @@
       <c r="E30">
         <v>0.86</v>
       </c>
+      <c r="G30">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="M30" s="4"/>
     </row>
@@ -2635,6 +2722,9 @@
       <c r="E31">
         <v>0.93</v>
       </c>
+      <c r="G31">
+        <v>0.73</v>
+      </c>
       <c r="M31" s="4"/>
     </row>
     <row r="32" spans="1:13">
@@ -2653,6 +2743,9 @@
       <c r="E32">
         <v>0.93</v>
       </c>
+      <c r="G32">
+        <v>0.4</v>
+      </c>
       <c r="H32" s="3"/>
       <c r="M32" s="4"/>
     </row>
@@ -2672,6 +2765,9 @@
       <c r="E33">
         <v>0.81</v>
       </c>
+      <c r="G33">
+        <v>0.7</v>
+      </c>
       <c r="H33" s="3"/>
       <c r="M33" s="4"/>
     </row>
@@ -2691,6 +2787,9 @@
       <c r="E34">
         <v>0.77</v>
       </c>
+      <c r="G34">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="J34">
         <v>0.78</v>
       </c>
@@ -2712,6 +2811,9 @@
       <c r="E35">
         <v>0.91</v>
       </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
       <c r="H35" s="3"/>
       <c r="M35" s="8"/>
     </row>
@@ -2731,6 +2833,9 @@
       <c r="E36">
         <v>1</v>
       </c>
+      <c r="G36">
+        <v>0.27</v>
+      </c>
       <c r="H36" s="3"/>
       <c r="M36" s="4"/>
     </row>
@@ -2750,6 +2855,9 @@
       <c r="E37">
         <v>0.93</v>
       </c>
+      <c r="G37">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13">
@@ -2768,6 +2876,9 @@
       <c r="E38">
         <v>0.98</v>
       </c>
+      <c r="G38">
+        <v>0.65</v>
+      </c>
       <c r="H38" s="3"/>
       <c r="J38">
         <v>0.7</v>
@@ -2790,6 +2901,9 @@
       <c r="E39">
         <v>0.93</v>
       </c>
+      <c r="G39">
+        <v>0.66</v>
+      </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
@@ -2808,6 +2922,9 @@
       <c r="E40">
         <v>0.98</v>
       </c>
+      <c r="G40">
+        <v>0.48</v>
+      </c>
       <c r="H40" s="3"/>
       <c r="M40" s="4"/>
     </row>
@@ -2827,6 +2944,9 @@
       <c r="E41">
         <v>1</v>
       </c>
+      <c r="G41">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="J41">
         <v>0.7</v>
@@ -2849,6 +2969,9 @@
       <c r="E42">
         <v>1</v>
       </c>
+      <c r="G42">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H42" s="3"/>
       <c r="M42" s="4"/>
     </row>
@@ -2868,6 +2991,9 @@
       <c r="E43">
         <v>1</v>
       </c>
+      <c r="G43">
+        <v>0.79</v>
+      </c>
       <c r="H43" s="3"/>
       <c r="J43">
         <v>0.84</v>
@@ -2890,6 +3016,9 @@
       <c r="E44">
         <v>0.98</v>
       </c>
+      <c r="G44">
+        <v>0.69</v>
+      </c>
       <c r="M44" s="4"/>
     </row>
     <row r="45" spans="1:13">
@@ -2908,6 +3037,9 @@
       <c r="E45">
         <v>0.79</v>
       </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
       <c r="H45" s="3"/>
       <c r="M45" s="8"/>
     </row>
@@ -2927,6 +3059,9 @@
       <c r="E46">
         <v>0.98</v>
       </c>
+      <c r="G46">
+        <v>0.66</v>
+      </c>
       <c r="H46" s="3"/>
       <c r="M46" s="8"/>
     </row>
@@ -2946,6 +3081,9 @@
       <c r="E47">
         <v>1</v>
       </c>
+      <c r="G47">
+        <v>0.74</v>
+      </c>
       <c r="H47" s="3"/>
       <c r="M47" s="4"/>
     </row>
@@ -2965,6 +3103,9 @@
       <c r="E48">
         <v>0.93</v>
       </c>
+      <c r="G48">
+        <v>0.18</v>
+      </c>
       <c r="H48" s="3"/>
       <c r="M48" s="4"/>
     </row>
@@ -2984,6 +3125,9 @@
       <c r="E49">
         <v>1</v>
       </c>
+      <c r="G49">
+        <v>0.18</v>
+      </c>
       <c r="H49" s="3"/>
       <c r="M49" s="4"/>
     </row>
@@ -3003,6 +3147,9 @@
       <c r="E50">
         <v>1</v>
       </c>
+      <c r="G50">
+        <v>0.52</v>
+      </c>
       <c r="J50">
         <v>0.84</v>
       </c>
@@ -3024,6 +3171,9 @@
       <c r="E51">
         <v>0.95</v>
       </c>
+      <c r="G51">
+        <v>0.53</v>
+      </c>
       <c r="M51" s="4"/>
     </row>
     <row r="52" spans="1:13">
@@ -3042,6 +3192,9 @@
       <c r="E52">
         <v>1</v>
       </c>
+      <c r="G52">
+        <v>0.62</v>
+      </c>
       <c r="M52" s="4"/>
     </row>
     <row r="53" spans="1:13">
@@ -3060,6 +3213,9 @@
       <c r="E53">
         <v>1</v>
       </c>
+      <c r="G53">
+        <v>0.36</v>
+      </c>
       <c r="H53" s="3"/>
       <c r="M53" s="4"/>
     </row>
@@ -3079,6 +3235,9 @@
       <c r="E54">
         <v>0.95</v>
       </c>
+      <c r="G54">
+        <v>0.65</v>
+      </c>
       <c r="H54" s="3"/>
       <c r="M54" s="4"/>
     </row>
@@ -3098,6 +3257,9 @@
       <c r="E55">
         <v>1</v>
       </c>
+      <c r="G55">
+        <v>0.68</v>
+      </c>
       <c r="H55" s="3"/>
       <c r="M55" s="4"/>
     </row>
@@ -3117,6 +3279,9 @@
       <c r="E56">
         <v>0.98</v>
       </c>
+      <c r="G56">
+        <v>0.68</v>
+      </c>
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="1:13">
@@ -3135,6 +3300,9 @@
       <c r="E57">
         <v>0.98</v>
       </c>
+      <c r="G57">
+        <v>0.65</v>
+      </c>
       <c r="H57" s="3"/>
       <c r="J57">
         <v>0.72</v>
@@ -3157,6 +3325,9 @@
       <c r="E58">
         <v>0.98</v>
       </c>
+      <c r="G58">
+        <v>0.34</v>
+      </c>
       <c r="J58">
         <v>0.84</v>
       </c>
@@ -3178,6 +3349,9 @@
       <c r="E59">
         <v>0.98</v>
       </c>
+      <c r="G59">
+        <v>0.53</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="M59" s="4"/>
     </row>
@@ -3197,6 +3371,9 @@
       <c r="E60">
         <v>0.98</v>
       </c>
+      <c r="G60">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J60">
         <v>0.78</v>
       </c>
@@ -3218,6 +3395,9 @@
       <c r="E61">
         <v>0.98</v>
       </c>
+      <c r="G61">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="H61" s="3"/>
       <c r="J61">
         <v>0.7</v>
@@ -3240,6 +3420,9 @@
       <c r="E62">
         <v>0.98</v>
       </c>
+      <c r="G62">
+        <v>0.73</v>
+      </c>
       <c r="H62" s="3"/>
       <c r="M62" s="4"/>
     </row>
@@ -3259,6 +3442,9 @@
       <c r="E63">
         <v>0.95</v>
       </c>
+      <c r="G63">
+        <v>0.69</v>
+      </c>
       <c r="H63" s="3"/>
       <c r="M63" s="4"/>
     </row>
@@ -3278,6 +3464,9 @@
       <c r="E64">
         <v>1</v>
       </c>
+      <c r="G64">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="1:13">
@@ -3296,6 +3485,9 @@
       <c r="E65">
         <v>0.95</v>
       </c>
+      <c r="G65">
+        <v>0.6</v>
+      </c>
       <c r="H65" s="3"/>
       <c r="M65" s="4"/>
     </row>
@@ -3315,6 +3507,9 @@
       <c r="E66">
         <v>0.98</v>
       </c>
+      <c r="G66">
+        <v>0.49</v>
+      </c>
       <c r="M66" s="4"/>
     </row>
     <row r="67" spans="1:13">
@@ -3333,6 +3528,9 @@
       <c r="E67">
         <v>1</v>
       </c>
+      <c r="G67">
+        <v>0.7</v>
+      </c>
       <c r="J67">
         <v>0.78</v>
       </c>
@@ -3354,6 +3552,9 @@
       <c r="E68">
         <v>0.98</v>
       </c>
+      <c r="G68">
+        <v>0.62</v>
+      </c>
       <c r="M68" s="4"/>
     </row>
     <row r="69" spans="1:13">
@@ -3372,6 +3573,9 @@
       <c r="E69">
         <v>1</v>
       </c>
+      <c r="G69">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="H69" s="3"/>
       <c r="J69">
         <v>0.72</v>
@@ -3394,6 +3598,9 @@
       <c r="E70">
         <v>0.88</v>
       </c>
+      <c r="G70">
+        <v>0.68</v>
+      </c>
       <c r="H70" s="3"/>
       <c r="J70">
         <v>0.72</v>
@@ -3416,6 +3623,9 @@
       <c r="E71">
         <v>0.98</v>
       </c>
+      <c r="G71">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="H71" s="3"/>
       <c r="J71">
         <v>0.78</v>
@@ -3438,6 +3648,9 @@
       <c r="E72">
         <v>0.98</v>
       </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
       <c r="H72" s="3"/>
       <c r="J72">
         <v>0.73</v>
@@ -3460,6 +3673,9 @@
       <c r="E73">
         <v>1</v>
       </c>
+      <c r="G73">
+        <v>0.66</v>
+      </c>
       <c r="M73" s="4"/>
     </row>
     <row r="74" spans="1:13">
@@ -3478,6 +3694,9 @@
       <c r="E74">
         <v>1</v>
       </c>
+      <c r="G74">
+        <v>0.48</v>
+      </c>
       <c r="J74">
         <v>0.7</v>
       </c>
@@ -3499,6 +3718,9 @@
       <c r="E75">
         <v>0.95</v>
       </c>
+      <c r="G75">
+        <v>0.62</v>
+      </c>
       <c r="J75">
         <v>0.78</v>
       </c>
@@ -3519,6 +3741,9 @@
       </c>
       <c r="E76">
         <v>0.95</v>
+      </c>
+      <c r="G76">
+        <v>0.71</v>
       </c>
       <c r="H76" s="3"/>
       <c r="M76" s="4"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BD463B-EDE1-7F43-BF1D-A8C71F6F79FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867CDA02-622A-1F4C-A5F2-8001F818F451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="620" windowWidth="16740" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1614,7 +1614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1636,6 +1636,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1681,8 +1684,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M241" totalsRowShown="0">
   <autoFilter ref="A1:M241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M240">
-    <sortCondition ref="C1:C240"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M241">
+    <sortCondition ref="C1:C241"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -3947,587 +3950,587 @@
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C86" s="6" t="s">
+      <c r="A86" t="s">
+        <v>462</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="C86" t="s">
         <v>159</v>
       </c>
-      <c r="D86" s="6">
-        <v>0.88</v>
+      <c r="D86" s="2">
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G86">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="M86" s="4"/>
+        <v>0.53</v>
+      </c>
+      <c r="M86" s="10"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="6" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D87" s="6">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="E87">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G87">
-        <v>0.56000000000000005</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="6" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D88" s="6">
-        <v>0.78</v>
+        <v>0.53</v>
       </c>
       <c r="E88">
         <v>0.95</v>
       </c>
       <c r="G88">
-        <v>0.62</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="6" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D89" s="6">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="E89">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G89">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="6" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D90" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="6" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D91" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="E91">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="6" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D92" s="6">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="E92">
-        <v>0.51</v>
+        <v>0.93</v>
       </c>
       <c r="G92">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="6" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D93" s="6">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="E93">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
       <c r="G93">
-        <v>0.57999999999999996</v>
+        <v>0.52</v>
       </c>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D94" s="6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E94">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="G94">
-        <v>0.77</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="6" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D95" s="6">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="E95">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="G95">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="6" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D96" s="6">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="E96">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G96">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="6" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D97" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="E97">
+        <v>0.93</v>
+      </c>
+      <c r="G97">
+        <v>0.52</v>
+      </c>
+      <c r="M97" s="4"/>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="A98" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D98" s="6">
         <v>0.73</v>
       </c>
-      <c r="E97">
+      <c r="E98">
         <v>1</v>
       </c>
-      <c r="G97">
+      <c r="G98">
         <v>0.65</v>
       </c>
-      <c r="M97" s="4"/>
-    </row>
-    <row r="98" spans="1:13">
-      <c r="A98" t="s">
+      <c r="M98" s="4"/>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="A99" t="s">
         <v>485</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B99" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C99" t="s">
         <v>159</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D99" s="2">
         <v>0</v>
       </c>
-      <c r="E98">
+      <c r="E99">
         <v>0.86</v>
-      </c>
-      <c r="G98">
-        <v>0.6</v>
-      </c>
-      <c r="M98" s="10"/>
-    </row>
-    <row r="99" spans="1:13">
-      <c r="A99" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D99" s="6">
-        <v>0.93</v>
-      </c>
-      <c r="E99">
-        <v>1</v>
       </c>
       <c r="G99">
         <v>0.6</v>
       </c>
-      <c r="J99">
-        <v>0.78</v>
-      </c>
-      <c r="M99" s="4"/>
+      <c r="M99" s="10"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" t="s">
-        <v>487</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="A100" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D100" s="2">
-        <v>0</v>
+      <c r="D100" s="6">
+        <v>0.93</v>
       </c>
       <c r="E100">
         <v>1</v>
       </c>
       <c r="G100">
+        <v>0.6</v>
+      </c>
+      <c r="J100">
+        <v>0.78</v>
+      </c>
+      <c r="M100" s="4"/>
+    </row>
+    <row r="101" spans="1:13">
+      <c r="A101" t="s">
+        <v>487</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C101" t="s">
+        <v>159</v>
+      </c>
+      <c r="D101" s="2">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="G101">
         <v>0.81</v>
       </c>
-      <c r="M100" s="10"/>
-    </row>
-    <row r="101" spans="1:13">
-      <c r="A101" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D101" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="E101">
-        <v>0.91</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="M101" s="4"/>
+      <c r="M101" s="10"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="6" t="s">
-        <v>241</v>
+        <v>166</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D102" s="6">
-        <v>0.69</v>
+        <v>0.92</v>
       </c>
       <c r="E102">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="G102">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="6" t="s">
-        <v>13</v>
+        <v>241</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D103" s="6">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G103">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="6" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D104" s="6">
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
       <c r="E104">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G104">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D105" s="6">
-        <v>0.74</v>
+        <v>0.81</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G105">
-        <v>0.61</v>
-      </c>
-      <c r="J105">
-        <v>0.86</v>
+        <v>0.51</v>
       </c>
       <c r="M105" s="4"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="6" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D106" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="G106">
+        <v>0.61</v>
+      </c>
+      <c r="J106">
+        <v>0.86</v>
+      </c>
+      <c r="M106" s="4"/>
+    </row>
+    <row r="107" spans="1:13">
+      <c r="A107" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D107" s="6">
         <v>0.63</v>
       </c>
-      <c r="E106">
+      <c r="E107">
         <v>0.98</v>
       </c>
-      <c r="G106">
+      <c r="G107">
         <v>0.36</v>
       </c>
-      <c r="M106" s="4"/>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="A107" t="s">
+      <c r="M107" s="4"/>
+    </row>
+    <row r="108" spans="1:13">
+      <c r="A108" t="s">
         <v>489</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B108" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C108" t="s">
         <v>159</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D108" s="2">
         <v>0</v>
       </c>
-      <c r="E107">
+      <c r="E108">
         <v>0.95</v>
       </c>
-      <c r="G107">
+      <c r="G108">
         <v>0.66</v>
       </c>
-      <c r="M107" s="10"/>
-    </row>
-    <row r="108" spans="1:13">
-      <c r="A108" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D108" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E108">
-        <v>1</v>
-      </c>
-      <c r="G108">
-        <v>0.68</v>
-      </c>
-      <c r="M108" s="4"/>
+      <c r="M108" s="10"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D109" s="6">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="E109">
         <v>1</v>
       </c>
       <c r="G109">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D110" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>0.79</v>
+      </c>
+      <c r="M110" s="4"/>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="A111" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D111" s="6">
         <v>0.91</v>
-      </c>
-      <c r="E110">
-        <v>0.91</v>
-      </c>
-      <c r="G110">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="M110" s="4"/>
-    </row>
-    <row r="111" spans="1:13">
-      <c r="A111" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D111" s="5">
-        <v>0</v>
       </c>
       <c r="E111">
         <v>0.91</v>
       </c>
       <c r="G111">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M111" s="4"/>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D112" s="5">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0.91</v>
+      </c>
+      <c r="G112">
         <v>0.6</v>
       </c>
-      <c r="J111">
+      <c r="J112">
         <v>0.86</v>
-      </c>
-      <c r="M111" s="4"/>
-    </row>
-    <row r="112" spans="1:13">
-      <c r="A112" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D112" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="E112">
-        <v>0.98</v>
-      </c>
-      <c r="G112">
-        <v>0.52</v>
       </c>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>159</v>
@@ -4536,1093 +4539,1093 @@
         <v>0.86</v>
       </c>
       <c r="E113">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G113">
-        <v>0.56999999999999995</v>
+        <v>0.52</v>
       </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D114" s="6">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="E114">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="G114">
-        <v>0.39</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D115" s="6">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="E115">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G115">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="M115" s="4"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="6" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D116" s="6">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="E116">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G116">
-        <v>0.36</v>
-      </c>
-      <c r="J116">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="M116" s="4"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="6" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D117" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E117">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G117">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="J117">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D118" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="E118">
         <v>0.93</v>
       </c>
       <c r="G118">
-        <v>0.57999999999999996</v>
+        <v>0.42</v>
+      </c>
+      <c r="J118">
+        <v>0.78</v>
       </c>
       <c r="M118" s="4"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D119" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M119" s="4"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="6" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D120" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D121" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>0.52</v>
+      </c>
+      <c r="M121" s="4"/>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D122" s="6">
         <v>0.73</v>
       </c>
-      <c r="E121">
+      <c r="E122">
         <v>0.95</v>
       </c>
-      <c r="G121">
+      <c r="G122">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M121" s="4"/>
-    </row>
-    <row r="122" spans="1:13">
-      <c r="A122" s="5" t="s">
+      <c r="M122" s="4"/>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B123" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D123" s="5">
         <v>0</v>
       </c>
-      <c r="E122">
+      <c r="E123">
         <v>0.88</v>
       </c>
-      <c r="G122">
+      <c r="G123">
         <v>0.71</v>
       </c>
-      <c r="J122">
+      <c r="J123">
         <v>0.86</v>
-      </c>
-      <c r="M122" s="4"/>
-    </row>
-    <row r="123" spans="1:13">
-      <c r="A123" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D123" s="6">
-        <v>0.69</v>
-      </c>
-      <c r="E123">
-        <v>0.95</v>
-      </c>
-      <c r="G123">
-        <v>0.28999999999999998</v>
       </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D124" s="6">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="E124">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G124">
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D125" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="E125">
+        <v>0.98</v>
+      </c>
+      <c r="G125">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M125" s="4"/>
+    </row>
+    <row r="126" spans="1:13">
+      <c r="A126" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D126" s="6">
         <v>0.68</v>
       </c>
-      <c r="E125">
+      <c r="E126">
         <v>0.93</v>
       </c>
-      <c r="G125">
+      <c r="G126">
         <v>0.78</v>
       </c>
-      <c r="M125" s="4"/>
-    </row>
-    <row r="126" spans="1:13">
-      <c r="A126" s="5" t="s">
+      <c r="M126" s="4"/>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B127" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C127" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D127" s="5">
         <v>0</v>
       </c>
-      <c r="E126">
+      <c r="E127">
         <v>1</v>
-      </c>
-      <c r="G126">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J126">
-        <v>0.86</v>
-      </c>
-      <c r="M126" s="4"/>
-    </row>
-    <row r="127" spans="1:13">
-      <c r="A127" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D127" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="E127">
-        <v>0.93</v>
       </c>
       <c r="G127">
         <v>0.56999999999999995</v>
       </c>
       <c r="J127">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D128" s="6">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="E128">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="G128">
-        <v>0.62</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J128">
+        <v>0.8</v>
       </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D129" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="E129">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G129">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D130" s="6">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="E130">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="G130">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D131" s="6">
+        <v>0.64</v>
+      </c>
+      <c r="E131">
         <v>0.79</v>
       </c>
-      <c r="E131">
-        <v>1</v>
-      </c>
       <c r="G131">
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="6" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D132" s="6">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="E132">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G132">
-        <v>0.47</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.91</v>
+        <v>0.69</v>
       </c>
       <c r="E133">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G133">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="E134">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="G134">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="E135">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="G135">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="6" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D136" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="E136">
+        <v>0.98</v>
+      </c>
+      <c r="G136">
+        <v>0.51</v>
+      </c>
+      <c r="M136" s="4"/>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D137" s="6">
         <v>0.87</v>
       </c>
-      <c r="E136">
+      <c r="E137">
         <v>1</v>
       </c>
-      <c r="G136">
+      <c r="G137">
         <v>0.66</v>
       </c>
-      <c r="J136">
+      <c r="J137">
         <v>0.8</v>
       </c>
-      <c r="M136" s="4"/>
-    </row>
-    <row r="137" spans="1:13">
-      <c r="A137" s="5" t="s">
+      <c r="M137" s="4"/>
+    </row>
+    <row r="138" spans="1:13">
+      <c r="A138" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B138" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D138" s="5">
         <v>0</v>
       </c>
-      <c r="E137">
+      <c r="E138">
         <v>0.88</v>
       </c>
-      <c r="G137">
+      <c r="G138">
         <v>0.6</v>
-      </c>
-      <c r="M137" s="4"/>
-    </row>
-    <row r="138" spans="1:13">
-      <c r="A138" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D138" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E138">
-        <v>0.91</v>
-      </c>
-      <c r="G138">
-        <v>0.25</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="G139">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="6" t="s">
-        <v>283</v>
+        <v>339</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D140" s="6">
-        <v>0.81</v>
+        <v>0.41</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="G140">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D142" s="6">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="E142">
         <v>1</v>
       </c>
       <c r="G142">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M142" s="4"/>
+    </row>
+    <row r="143" spans="1:13">
+      <c r="A143" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D143" s="6">
+        <v>0.86</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+      <c r="G143">
         <v>0.53</v>
       </c>
-      <c r="M142" s="4"/>
-    </row>
-    <row r="143" spans="1:13">
-      <c r="A143" s="5" t="s">
+      <c r="M143" s="4"/>
+    </row>
+    <row r="144" spans="1:13">
+      <c r="A144" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B144" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="C143" s="5" t="s">
+      <c r="C144" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D143" s="5">
+      <c r="D144" s="5">
         <v>0</v>
       </c>
-      <c r="E143">
+      <c r="E144">
         <v>0.86</v>
       </c>
-      <c r="G143">
+      <c r="G144">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J143">
+      <c r="J144">
         <v>0.83</v>
       </c>
-      <c r="M143" s="4"/>
-    </row>
-    <row r="144" spans="1:13">
-      <c r="A144" s="6" t="s">
+      <c r="M144" s="4"/>
+    </row>
+    <row r="145" spans="1:13">
+      <c r="A145" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B145" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C145" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D145" s="6">
         <v>0.87</v>
       </c>
-      <c r="E144">
+      <c r="E145">
         <v>1</v>
       </c>
-      <c r="G144">
+      <c r="G145">
         <v>0.61</v>
       </c>
-      <c r="M144" s="4"/>
-    </row>
-    <row r="145" spans="1:13">
-      <c r="A145" s="5" t="s">
+      <c r="M145" s="4"/>
+    </row>
+    <row r="146" spans="1:13">
+      <c r="A146" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B146" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="C145" s="5" t="s">
+      <c r="C146" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D146" s="5">
         <v>0</v>
       </c>
-      <c r="E145">
+      <c r="E146">
         <v>0.6</v>
       </c>
-      <c r="G145">
+      <c r="G146">
         <v>0.62</v>
-      </c>
-      <c r="M145" s="4"/>
-    </row>
-    <row r="146" spans="1:13">
-      <c r="A146" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D146" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E146">
-        <v>1</v>
-      </c>
-      <c r="G146">
-        <v>0.56999999999999995</v>
       </c>
       <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>0.51</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D148" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0.51</v>
+      </c>
+      <c r="M148" s="4"/>
+    </row>
+    <row r="149" spans="1:13">
+      <c r="A149" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D149" s="6">
         <v>0.98</v>
       </c>
-      <c r="E148">
+      <c r="E149">
         <v>0.98</v>
       </c>
-      <c r="G148">
+      <c r="G149">
         <v>0.45</v>
       </c>
-      <c r="M148" s="4"/>
-    </row>
-    <row r="149" spans="1:13">
-      <c r="A149" s="5" t="s">
+      <c r="M149" s="4"/>
+    </row>
+    <row r="150" spans="1:13">
+      <c r="A150" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B150" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="C149" s="5" t="s">
+      <c r="C150" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D150" s="5">
         <v>0</v>
       </c>
-      <c r="E149">
+      <c r="E150">
         <v>0.93</v>
       </c>
-      <c r="G149">
+      <c r="G150">
         <v>0.53</v>
       </c>
-      <c r="M149" s="4"/>
-    </row>
-    <row r="150" spans="1:13">
-      <c r="A150" s="6" t="s">
+      <c r="M150" s="4"/>
+    </row>
+    <row r="151" spans="1:13">
+      <c r="A151" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B151" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C150" s="6" t="s">
+      <c r="C151" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D150" s="6">
+      <c r="D151" s="6">
         <v>0.75</v>
       </c>
-      <c r="E150">
+      <c r="E151">
         <v>0.98</v>
       </c>
-      <c r="G150">
+      <c r="G151">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M150" s="4"/>
-    </row>
-    <row r="151" spans="1:13">
-      <c r="A151" t="s">
+      <c r="M151" s="4"/>
+    </row>
+    <row r="152" spans="1:13">
+      <c r="A152" t="s">
         <v>479</v>
       </c>
-      <c r="B151" s="9" t="s">
+      <c r="B152" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C152" t="s">
         <v>245</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D152" s="2">
         <v>0</v>
       </c>
-      <c r="E151">
+      <c r="E152">
         <v>1</v>
       </c>
-      <c r="G151">
+      <c r="G152">
         <v>0.52</v>
       </c>
-      <c r="M151" s="10"/>
-    </row>
-    <row r="152" spans="1:13">
-      <c r="A152" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D152" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="E152">
-        <v>0.93</v>
-      </c>
-      <c r="G152">
-        <v>0.47</v>
-      </c>
-      <c r="M152" s="4"/>
+      <c r="M152" s="10"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>246</v>
+        <v>329</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="E153">
+        <v>0.93</v>
+      </c>
+      <c r="G153">
+        <v>0.47</v>
+      </c>
+      <c r="M153" s="4"/>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D154" s="6">
         <v>0.88</v>
       </c>
-      <c r="E153">
+      <c r="E154">
         <v>0.98</v>
       </c>
-      <c r="G153">
+      <c r="G154">
         <v>0.61</v>
       </c>
-      <c r="M153" s="4"/>
-    </row>
-    <row r="154" spans="1:13">
-      <c r="A154" t="s">
+      <c r="M154" s="4"/>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="A155" t="s">
         <v>468</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="B155" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C155" t="s">
         <v>245</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D155" s="2">
         <v>0</v>
       </c>
-      <c r="E154">
+      <c r="E155">
         <v>1</v>
       </c>
-      <c r="G154">
+      <c r="G155">
         <v>0.39</v>
       </c>
-      <c r="M154" s="10"/>
-    </row>
-    <row r="155" spans="1:13">
-      <c r="A155" s="6" t="s">
+      <c r="M155" s="10"/>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="A156" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B156" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C156" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D156" s="6">
         <v>0.71</v>
       </c>
-      <c r="E155">
+      <c r="E156">
         <v>0.88</v>
       </c>
-      <c r="G155">
+      <c r="G156">
         <v>0.53</v>
       </c>
-      <c r="M155" s="4"/>
-    </row>
-    <row r="156" spans="1:13">
-      <c r="A156" t="s">
+      <c r="M156" s="4"/>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="A157" t="s">
         <v>477</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B157" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>245</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D157" s="2">
         <v>0</v>
       </c>
-      <c r="E156">
+      <c r="E157">
         <v>0</v>
       </c>
-      <c r="G156">
+      <c r="G157">
         <v>0.45</v>
       </c>
-      <c r="M156" s="10"/>
-    </row>
-    <row r="157" spans="1:13">
-      <c r="A157" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D157" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="E157">
-        <v>0.98</v>
-      </c>
-      <c r="G157">
-        <v>0.62</v>
-      </c>
-      <c r="M157" s="4"/>
+      <c r="M157" s="10"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="6" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D158" s="6">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G158">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="6" t="s">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D159" s="6">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="E159">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="G159">
-        <v>0.75</v>
-      </c>
-      <c r="J159">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
       <c r="M159" s="4"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E160">
         <v>0.84</v>
       </c>
       <c r="G160">
-        <v>0.71</v>
+        <v>0.75</v>
+      </c>
+      <c r="J160">
+        <v>0.83</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="6" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D161" s="6">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="E161">
         <v>0.84</v>
       </c>
       <c r="G161">
-        <v>0.57999999999999996</v>
+        <v>0.71</v>
       </c>
       <c r="M161" s="4"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E162">
+        <v>0.84</v>
+      </c>
+      <c r="G162">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M162" s="4"/>
+    </row>
+    <row r="163" spans="1:13">
+      <c r="A163" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D163" s="6">
         <v>1</v>
       </c>
-      <c r="E162">
+      <c r="E163">
         <v>1</v>
       </c>
-      <c r="G162">
+      <c r="G163">
         <v>0.74</v>
       </c>
-      <c r="M162" s="4"/>
-    </row>
-    <row r="163" spans="1:13">
-      <c r="A163" t="s">
-        <v>470</v>
-      </c>
-      <c r="B163" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="C163" t="s">
-        <v>245</v>
-      </c>
-      <c r="D163" s="2">
-        <v>0</v>
-      </c>
-      <c r="E163">
-        <v>0.91</v>
-      </c>
-      <c r="G163">
-        <v>0.71</v>
-      </c>
-      <c r="M163" s="10"/>
+      <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C164" t="s">
         <v>245</v>
@@ -5631,346 +5634,346 @@
         <v>0</v>
       </c>
       <c r="E164">
+        <v>0.91</v>
+      </c>
+      <c r="G164">
+        <v>0.71</v>
+      </c>
+      <c r="M164" s="10"/>
+    </row>
+    <row r="165" spans="1:13">
+      <c r="A165" t="s">
+        <v>472</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C165" t="s">
+        <v>245</v>
+      </c>
+      <c r="D165" s="2">
+        <v>0</v>
+      </c>
+      <c r="E165">
         <v>0.98</v>
       </c>
-      <c r="G164">
+      <c r="G165">
         <v>0.38</v>
       </c>
-      <c r="M164" s="10"/>
-    </row>
-    <row r="165" spans="1:13">
-      <c r="A165" s="6" t="s">
+      <c r="M165" s="10"/>
+    </row>
+    <row r="166" spans="1:13">
+      <c r="A166" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B165" s="6" t="s">
+      <c r="B166" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C166" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D165" s="6">
+      <c r="D166" s="6">
         <v>0.81</v>
       </c>
-      <c r="E165">
+      <c r="E166">
         <v>0.95</v>
       </c>
-      <c r="G165">
+      <c r="G166">
         <v>0.44</v>
       </c>
-      <c r="M165" s="4"/>
-    </row>
-    <row r="166" spans="1:13">
-      <c r="A166" t="s">
+      <c r="M166" s="4"/>
+    </row>
+    <row r="167" spans="1:13">
+      <c r="A167" t="s">
         <v>388</v>
       </c>
-      <c r="B166" s="9" t="s">
+      <c r="B167" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C167" t="s">
         <v>245</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D167" s="2">
         <v>0</v>
       </c>
-      <c r="E166">
+      <c r="E167">
         <v>1</v>
       </c>
-      <c r="G166">
+      <c r="G167">
         <v>0.51</v>
       </c>
-      <c r="M166" s="10"/>
-    </row>
-    <row r="167" spans="1:13">
-      <c r="A167" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D167" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="E167">
-        <v>0.98</v>
-      </c>
-      <c r="G167">
-        <v>0.49</v>
-      </c>
-      <c r="M167" s="4"/>
+      <c r="M167" s="10"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D168" s="6">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="G168">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J168">
-        <v>0.83</v>
+        <v>0.49</v>
       </c>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D169" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="E169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>0.69</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J169">
+        <v>0.83</v>
       </c>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D170" s="6">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="E170">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G170">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D171" s="6">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="E171">
-        <v>0.81</v>
+        <v>0.98</v>
       </c>
       <c r="G171">
-        <v>0.56000000000000005</v>
+        <v>0.65</v>
       </c>
       <c r="M171" s="4"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>461</v>
+        <v>295</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D172" s="6">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E172">
-        <v>0.88</v>
+        <v>0.81</v>
       </c>
       <c r="G172">
-        <v>0.62</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>301</v>
+        <v>461</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D173" s="6">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="E173">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="G173">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>244</v>
+        <v>302</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D174" s="6">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="E174">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G174">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D175" s="6">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="E175">
         <v>0.93</v>
       </c>
       <c r="G175">
+        <v>0.61</v>
+      </c>
+      <c r="M175" s="4"/>
+    </row>
+    <row r="176" spans="1:13">
+      <c r="A176" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D176" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="E176">
+        <v>0.93</v>
+      </c>
+      <c r="G176">
         <v>0.36</v>
       </c>
-      <c r="M175" s="4"/>
-    </row>
-    <row r="176" spans="1:13">
-      <c r="A176" t="s">
+      <c r="M176" s="4"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" t="s">
         <v>475</v>
       </c>
-      <c r="B176" s="9" t="s">
+      <c r="B177" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C177" t="s">
         <v>245</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D177" s="2">
         <v>0</v>
-      </c>
-      <c r="E176">
-        <v>0.98</v>
-      </c>
-      <c r="G176">
-        <v>0.68</v>
-      </c>
-      <c r="M176" s="10"/>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D177" s="6">
-        <v>0.82</v>
       </c>
       <c r="E177">
         <v>0.98</v>
       </c>
       <c r="G177">
-        <v>0.4</v>
-      </c>
-      <c r="M177" s="4"/>
+        <v>0.68</v>
+      </c>
+      <c r="M177" s="10"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>331</v>
+        <v>248</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D178" s="6">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="E178">
         <v>0.98</v>
       </c>
       <c r="G178">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D179" s="6">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E179">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G179">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D180" s="6">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E180">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G180">
         <v>0.66</v>
@@ -5979,55 +5982,55 @@
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D181" s="6">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="E181">
         <v>1</v>
       </c>
       <c r="G181">
-        <v>0.53</v>
-      </c>
-      <c r="J181">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D182" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="E182">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="G182">
-        <v>0.32</v>
+        <v>0.53</v>
+      </c>
+      <c r="J182">
+        <v>0.8</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>245</v>
@@ -6036,181 +6039,181 @@
         <v>0.81</v>
       </c>
       <c r="E183">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="G183">
-        <v>0.82</v>
-      </c>
-      <c r="J183">
-        <v>0.83</v>
+        <v>0.32</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D184" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="E184">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G184">
-        <v>0.73</v>
+        <v>0.82</v>
+      </c>
+      <c r="J184">
+        <v>0.83</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D185" s="6">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E185">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G185">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D186" s="6">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="E186">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G186">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D187" s="6">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G187">
-        <v>0.69</v>
-      </c>
-      <c r="J187">
-        <v>0.8</v>
+        <v>0.51</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D188" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>0.69</v>
+      </c>
+      <c r="J188">
         <v>0.8</v>
-      </c>
-      <c r="E188">
-        <v>0.95</v>
-      </c>
-      <c r="G188">
-        <v>0</v>
-      </c>
-      <c r="J188">
-        <v>0.85</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>430</v>
+        <v>392</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D189" s="6">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="E189">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G189">
-        <v>0.45</v>
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0.85</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D190" s="6">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G190">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D191" s="6">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -6218,47 +6221,47 @@
       <c r="G191">
         <v>0.61</v>
       </c>
-      <c r="J191">
-        <v>0.8</v>
-      </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D192" s="6">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="E192">
         <v>1</v>
       </c>
       <c r="G192">
-        <v>0.64</v>
+        <v>0.61</v>
+      </c>
+      <c r="J192">
+        <v>0.8</v>
       </c>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D193" s="6">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="E193">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G193">
         <v>0.64</v>
@@ -6267,700 +6270,700 @@
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D194" s="6">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="E194">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="G194">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D195" s="6">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="E195">
         <v>0.91</v>
       </c>
       <c r="G195">
-        <v>0.69</v>
+        <v>0.65</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D196" s="6">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="E196">
         <v>0.91</v>
       </c>
       <c r="G196">
-        <v>0.56999999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D197" s="6">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="E197">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="G197">
-        <v>0.74</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D198" s="6">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="E198">
-        <v>0.42</v>
+        <v>0.95</v>
       </c>
       <c r="G198">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D199" s="6">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="E199">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
       <c r="G199">
-        <v>0.56999999999999995</v>
+        <v>0.64</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D200" s="6">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="E200">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G200">
-        <v>0.55000000000000004</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D201" s="6">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="E201">
         <v>0.98</v>
       </c>
       <c r="G201">
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D202" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="E202">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="G202">
-        <v>0.82</v>
-      </c>
-      <c r="J202">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D203" s="6">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="E203">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G203">
-        <v>0.64</v>
+        <v>0.82</v>
+      </c>
+      <c r="J203">
+        <v>0.8</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D204" s="6">
-        <v>0.81</v>
+        <v>0.92</v>
       </c>
       <c r="E204">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G204">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="6" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D205" s="6">
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
       <c r="E205">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="G205">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D206" s="6">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="E206">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="G206">
-        <v>0.81</v>
+        <v>0.53</v>
       </c>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="6" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D207" s="6">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="E207">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G207">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="6" t="s">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>407</v>
+        <v>342</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D208" s="6">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="E208">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="G208">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D209" s="6">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="E209">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G209">
-        <v>0.6</v>
-      </c>
-      <c r="J209">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>446</v>
+        <v>370</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D210" s="6">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E210">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G210">
-        <v>0.75</v>
+        <v>0.6</v>
+      </c>
+      <c r="J210">
+        <v>0.85</v>
       </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>368</v>
+        <v>446</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>369</v>
+        <v>447</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D211" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="E211">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G211">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D212" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G212">
-        <v>0.73</v>
+        <v>0.69</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>344</v>
+        <v>410</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D213" s="6">
-        <v>0.81</v>
+        <v>0.96</v>
       </c>
       <c r="E213">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G213">
         <v>0.73</v>
       </c>
-      <c r="J213">
-        <v>0.79</v>
-      </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D214" s="6">
-        <v>0.96</v>
+        <v>0.81</v>
       </c>
       <c r="E214">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G214">
-        <v>0.65</v>
+        <v>0.73</v>
+      </c>
+      <c r="J214">
+        <v>0.79</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D215" s="6">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="E215">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="G215">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D216" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="E216">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="G216">
-        <v>0.56999999999999995</v>
+        <v>0.83</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D217" s="6">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G217">
-        <v>0.77</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="6" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D218" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="E218">
         <v>1</v>
-      </c>
-      <c r="E218">
-        <v>0.88</v>
       </c>
       <c r="G218">
         <v>0.77</v>
       </c>
-      <c r="J218">
-        <v>0.93</v>
-      </c>
       <c r="M218" s="4"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="6" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D219" s="6">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="E219">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="G219">
-        <v>0.7</v>
+        <v>0.77</v>
+      </c>
+      <c r="J219">
+        <v>0.93</v>
       </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="6" t="s">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>357</v>
+        <v>433</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D220" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.91</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="G220">
-        <v>0.57999999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="6" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D221" s="6">
-        <v>0.89</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>0.35</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="6" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D222" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
+      <c r="G222">
+        <v>0.35</v>
+      </c>
+      <c r="M222" s="4"/>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D223" s="6">
         <v>0.98</v>
       </c>
-      <c r="E222">
+      <c r="E223">
         <v>0</v>
       </c>
-      <c r="G222">
+      <c r="G223">
         <v>0.88</v>
       </c>
-      <c r="J222">
+      <c r="J223">
         <v>0.85</v>
       </c>
-      <c r="M222" s="4"/>
-    </row>
-    <row r="223" spans="1:13">
-      <c r="A223" s="5" t="s">
+      <c r="M223" s="4"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="B223" s="5" t="s">
+      <c r="B224" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="C223" s="5" t="s">
+      <c r="C224" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D223" s="5">
+      <c r="D224" s="5">
         <v>0</v>
       </c>
-      <c r="E223">
+      <c r="E224">
         <v>1</v>
       </c>
-      <c r="G223">
+      <c r="G224">
         <v>0.6</v>
       </c>
-      <c r="J223">
+      <c r="J224">
         <v>0.93</v>
-      </c>
-      <c r="M223" s="4"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="D224" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E224">
-        <v>0.95</v>
-      </c>
-      <c r="G224">
-        <v>0.81</v>
       </c>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="6" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D225" s="6">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="E225">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G225">
-        <v>0.7</v>
+        <v>0.81</v>
       </c>
       <c r="M225" s="4"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="6" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>343</v>
@@ -6969,217 +6972,217 @@
         <v>0.96</v>
       </c>
       <c r="E226">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G226">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="M226" s="4"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="6" t="s">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D227" s="6">
-        <v>0.42</v>
+        <v>0.96</v>
       </c>
       <c r="E227">
+        <v>0.95</v>
+      </c>
+      <c r="G227">
         <v>0.77</v>
-      </c>
-      <c r="G227">
-        <v>0.53</v>
-      </c>
-      <c r="J227">
-        <v>0.93</v>
       </c>
       <c r="M227" s="4"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="6" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D228" s="6">
-        <v>0.88</v>
+        <v>0.42</v>
       </c>
       <c r="E228">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="G228">
-        <v>0.69</v>
+        <v>0.53</v>
+      </c>
+      <c r="J228">
+        <v>0.93</v>
       </c>
       <c r="M228" s="4"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="6" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D229" s="6">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="E229">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G229">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J229">
-        <v>0.93</v>
-      </c>
-      <c r="M229" s="11"/>
+        <v>0.69</v>
+      </c>
+      <c r="M229" s="13"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="6" t="s">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>363</v>
+        <v>445</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D230" s="6">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="E230">
+        <v>0.95</v>
+      </c>
+      <c r="G230">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J230">
         <v>0.93</v>
       </c>
-      <c r="G230">
-        <v>0.64</v>
-      </c>
-      <c r="M230" s="11"/>
+      <c r="M230" s="13"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="6" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D231" s="6">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G231">
-        <v>0.78</v>
-      </c>
-      <c r="J231">
-        <v>0.8</v>
-      </c>
-      <c r="M231" s="11"/>
+        <v>0.64</v>
+      </c>
+      <c r="M231" s="13"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="6" t="s">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="C232" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D232" s="6">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="E232">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G232">
-        <v>0.68</v>
-      </c>
-      <c r="M232" s="11"/>
+        <v>0.78</v>
+      </c>
+      <c r="J232">
+        <v>0.8</v>
+      </c>
+      <c r="M232" s="13"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="6" t="s">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>429</v>
+        <v>391</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D233" s="6">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="E233">
-        <v>0.63</v>
+        <v>0.98</v>
       </c>
       <c r="G233">
-        <v>0.43</v>
-      </c>
-      <c r="M233" s="11"/>
+        <v>0.68</v>
+      </c>
+      <c r="M233" s="13"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="6" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D234" s="6">
-        <v>0.8</v>
+        <v>0.41</v>
       </c>
       <c r="E234">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
       <c r="G234">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="M234" s="11"/>
+        <v>0.43</v>
+      </c>
+      <c r="M234" s="13"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="6" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D235" s="6">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="G235">
-        <v>0</v>
-      </c>
-      <c r="M235" s="11"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M235" s="13"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="6" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>423</v>
+        <v>379</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>343</v>
@@ -7191,64 +7194,61 @@
         <v>0</v>
       </c>
       <c r="G236">
-        <v>0.77</v>
-      </c>
-      <c r="M236" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="M236" s="13"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="6" t="s">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D237" s="6">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="E237">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>0.51</v>
-      </c>
-      <c r="J237">
-        <v>0.83</v>
-      </c>
-      <c r="M237" s="11"/>
+        <v>0.77</v>
+      </c>
+      <c r="M237" s="13"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="6" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D238" s="6">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="E238">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="G238">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="J238">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M238" s="11"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="6" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>343</v>
@@ -7257,51 +7257,60 @@
         <v>0.97</v>
       </c>
       <c r="E239">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G239">
-        <v>0.65</v>
+        <v>0.74</v>
+      </c>
+      <c r="J239">
+        <v>0.8</v>
       </c>
       <c r="M239" s="11"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="6" t="s">
-        <v>442</v>
+        <v>354</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D240" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="E240">
+        <v>0.93</v>
+      </c>
+      <c r="G240">
+        <v>0.65</v>
+      </c>
+      <c r="M240" s="11"/>
+    </row>
+    <row r="241" spans="1:13">
+      <c r="A241" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D241" s="6">
         <v>0.88</v>
       </c>
-      <c r="E240">
+      <c r="E241">
         <v>0.95</v>
       </c>
-      <c r="G240">
+      <c r="G241">
         <v>0.71</v>
       </c>
-      <c r="J240">
+      <c r="J241">
         <v>0.93</v>
       </c>
-      <c r="M240" s="11"/>
-    </row>
-    <row r="241" spans="1:7">
-      <c r="A241" t="s">
-        <v>462</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="C241" t="s">
-        <v>159</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="G241">
-        <v>0.53</v>
-      </c>
+      <c r="M241" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867CDA02-622A-1F4C-A5F2-8001F818F451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3EED19-0610-544F-93DB-7897CB9D0A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="620" windowWidth="16740" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1160" yWindow="620" windowWidth="23560" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="505">
   <si>
     <t>Surname</t>
   </si>
@@ -1512,6 +1512,45 @@
   </si>
   <si>
     <t>H265070B</t>
+  </si>
+  <si>
+    <t>Ngavaseke</t>
+  </si>
+  <si>
+    <t>H260328C</t>
+  </si>
+  <si>
+    <t>Tangayi</t>
+  </si>
+  <si>
+    <t>H263009N</t>
+  </si>
+  <si>
+    <t>Tsasha</t>
+  </si>
+  <si>
+    <t>Chidumira</t>
+  </si>
+  <si>
+    <t>H250615P</t>
+  </si>
+  <si>
+    <t>Chipere</t>
+  </si>
+  <si>
+    <t>H260886R</t>
+  </si>
+  <si>
+    <t>Japani</t>
+  </si>
+  <si>
+    <t>H261839W</t>
+  </si>
+  <si>
+    <t>Kafura</t>
+  </si>
+  <si>
+    <t>H265349W</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1639,6 +1678,7 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1682,10 +1722,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M241" totalsRowShown="0">
-  <autoFilter ref="A1:M241" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M241">
-    <sortCondition ref="C1:C241"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M248" totalsRowShown="0">
+  <autoFilter ref="A1:M248" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M248">
+    <sortCondition ref="C1:C248"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -2023,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M241"/>
+  <dimension ref="A1:M248"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -3839,782 +3879,782 @@
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" s="5" t="s">
+      <c r="A81" t="s">
+        <v>497</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="C81" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="2">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0.6</v>
+      </c>
+      <c r="M81" s="10"/>
+    </row>
+    <row r="82" spans="1:13">
+      <c r="A82" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B82" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D82" s="5">
         <v>0</v>
       </c>
-      <c r="E81">
+      <c r="E82">
         <v>0.77</v>
       </c>
-      <c r="G81">
+      <c r="G82">
         <v>0</v>
       </c>
-      <c r="J81">
+      <c r="J82">
         <v>0.78</v>
-      </c>
-      <c r="M81" s="4"/>
-    </row>
-    <row r="82" spans="1:13">
-      <c r="A82" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D82" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="E82">
-        <v>0.98</v>
-      </c>
-      <c r="G82">
-        <v>0.69</v>
       </c>
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="6" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D83" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="E83">
         <v>0.98</v>
       </c>
       <c r="G83">
-        <v>0.56999999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
-      <c r="A84" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C84" s="6" t="s">
+      <c r="A84" t="s">
+        <v>499</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="C84" t="s">
         <v>159</v>
       </c>
-      <c r="D84" s="6">
-        <v>0.82</v>
+      <c r="D84" s="2">
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>0.42</v>
-      </c>
-      <c r="J84">
-        <v>0.78</v>
-      </c>
-      <c r="M84" s="4"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M84" s="10"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="6" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D85" s="6">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="E85">
         <v>0.98</v>
       </c>
       <c r="G85">
-        <v>0.51</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" t="s">
-        <v>462</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="A86" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D86" s="2">
-        <v>0</v>
+      <c r="D86" s="6">
+        <v>0.82</v>
       </c>
       <c r="E86">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G86">
-        <v>0.53</v>
-      </c>
-      <c r="M86" s="10"/>
+        <v>0.42</v>
+      </c>
+      <c r="J86">
+        <v>0.78</v>
+      </c>
+      <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D87" s="6">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E87">
         <v>0.98</v>
       </c>
       <c r="G87">
-        <v>0.56999999999999995</v>
+        <v>0.51</v>
       </c>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C88" s="6" t="s">
+      <c r="A88" t="s">
+        <v>462</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="C88" t="s">
         <v>159</v>
       </c>
-      <c r="D88" s="6">
-        <v>0.53</v>
+      <c r="D88" s="2">
+        <v>0</v>
       </c>
       <c r="E88">
         <v>0.95</v>
       </c>
       <c r="G88">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M88" s="4"/>
+        <v>0.53</v>
+      </c>
+      <c r="M88" s="10"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="6" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D89" s="6">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="E89">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G89">
-        <v>0.62</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D90" s="6">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="E90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G90">
-        <v>0.61</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="6" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D91" s="6">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D92" s="6">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="E92">
         <v>0.93</v>
       </c>
       <c r="G92">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="6" t="s">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D93" s="6">
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
       <c r="E93">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="6" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D94" s="6">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E94">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="G94">
-        <v>0.57999999999999996</v>
+        <v>0.65</v>
       </c>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="6" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D95" s="6">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="E95">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="G95">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C96" s="6" t="s">
+      <c r="A96" t="s">
+        <v>501</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="C96" t="s">
         <v>159</v>
       </c>
-      <c r="D96" s="6">
-        <v>0.92</v>
+      <c r="D96" s="2">
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>0.73</v>
-      </c>
-      <c r="M96" s="4"/>
+        <v>0.69</v>
+      </c>
+      <c r="M96" s="10"/>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C97" s="6" t="s">
+      <c r="A97" t="s">
+        <v>503</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="C97" t="s">
         <v>159</v>
       </c>
-      <c r="D97" s="6">
-        <v>0.78</v>
+      <c r="D97" s="2">
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>0.52</v>
-      </c>
-      <c r="M97" s="4"/>
+        <v>0.71</v>
+      </c>
+      <c r="M97" s="10"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="6" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D98" s="6">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G98">
-        <v>0.65</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" t="s">
-        <v>485</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="A99" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D99" s="2">
-        <v>0</v>
+      <c r="D99" s="6">
+        <v>0.8</v>
       </c>
       <c r="E99">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="G99">
-        <v>0.6</v>
-      </c>
-      <c r="M99" s="10"/>
+        <v>0.77</v>
+      </c>
+      <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="6" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D100" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="E100">
+        <v>0.95</v>
+      </c>
+      <c r="G100">
+        <v>0.73</v>
+      </c>
+      <c r="M100" s="4"/>
+    </row>
+    <row r="101" spans="1:13">
+      <c r="A101" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D101" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="E101">
         <v>0.93</v>
       </c>
-      <c r="E100">
-        <v>1</v>
-      </c>
-      <c r="G100">
-        <v>0.6</v>
-      </c>
-      <c r="J100">
-        <v>0.78</v>
-      </c>
-      <c r="M100" s="4"/>
-    </row>
-    <row r="101" spans="1:13">
-      <c r="A101" t="s">
-        <v>487</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="C101" t="s">
-        <v>159</v>
-      </c>
-      <c r="D101" s="2">
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <v>1</v>
-      </c>
       <c r="G101">
-        <v>0.81</v>
-      </c>
-      <c r="M101" s="10"/>
+        <v>0.52</v>
+      </c>
+      <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="6" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D102" s="6">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="E102">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G102">
+        <v>0.65</v>
+      </c>
+      <c r="M102" s="4"/>
+    </row>
+    <row r="103" spans="1:13">
+      <c r="A103" t="s">
+        <v>485</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="C103" t="s">
+        <v>159</v>
+      </c>
+      <c r="D103" s="2">
         <v>0</v>
       </c>
-      <c r="M102" s="4"/>
-    </row>
-    <row r="103" spans="1:13">
-      <c r="A103" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D103" s="6">
-        <v>0.69</v>
-      </c>
       <c r="E103">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="G103">
-        <v>0.53</v>
-      </c>
-      <c r="M103" s="4"/>
+        <v>0.6</v>
+      </c>
+      <c r="M103" s="10"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="6" t="s">
-        <v>13</v>
+        <v>216</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D104" s="6">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
       <c r="G104">
-        <v>0.64</v>
+        <v>0.6</v>
+      </c>
+      <c r="J104">
+        <v>0.78</v>
       </c>
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C105" s="6" t="s">
+      <c r="A105" t="s">
+        <v>487</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C105" t="s">
         <v>159</v>
       </c>
-      <c r="D105" s="6">
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="G105">
         <v>0.81</v>
       </c>
-      <c r="E105">
-        <v>0.86</v>
-      </c>
-      <c r="G105">
-        <v>0.51</v>
-      </c>
-      <c r="M105" s="4"/>
+      <c r="M105" s="10"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="6" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D106" s="6">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="E106">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G106">
-        <v>0.61</v>
-      </c>
-      <c r="J106">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="M106" s="4"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="6" t="s">
-        <v>157</v>
+        <v>241</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D107" s="6">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="E107">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="G107">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="M107" s="4"/>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" t="s">
-        <v>489</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="A108" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D108" s="2">
-        <v>0</v>
+      <c r="D108" s="6">
+        <v>0.74</v>
       </c>
       <c r="E108">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G108">
-        <v>0.66</v>
-      </c>
-      <c r="M108" s="10"/>
+        <v>0.64</v>
+      </c>
+      <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D109" s="6">
-        <v>0.98</v>
+        <v>0.81</v>
       </c>
       <c r="E109">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G109">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D110" s="6">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="G110">
-        <v>0.79</v>
+        <v>0.61</v>
+      </c>
+      <c r="J110">
+        <v>0.86</v>
       </c>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="6" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D111" s="6">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="E111">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="G111">
-        <v>0.56999999999999995</v>
+        <v>0.36</v>
       </c>
       <c r="M111" s="4"/>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C112" s="5" t="s">
+      <c r="A112" t="s">
+        <v>489</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C112" t="s">
         <v>159</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="2">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G112">
-        <v>0.6</v>
-      </c>
-      <c r="J112">
-        <v>0.86</v>
-      </c>
-      <c r="M112" s="4"/>
+        <v>0.66</v>
+      </c>
+      <c r="M112" s="10"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>232</v>
+        <v>163</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D113" s="6">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="E113">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G113">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D114" s="6">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="E114">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G114">
-        <v>0.56999999999999995</v>
+        <v>0.79</v>
       </c>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="6" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D115" s="6">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="E115">
+        <v>0.91</v>
+      </c>
+      <c r="G115">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M115" s="4"/>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D116" s="5">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0.91</v>
+      </c>
+      <c r="G116">
+        <v>0.6</v>
+      </c>
+      <c r="J116">
         <v>0.86</v>
-      </c>
-      <c r="G115">
-        <v>0.39</v>
-      </c>
-      <c r="M115" s="4"/>
-    </row>
-    <row r="116" spans="1:13">
-      <c r="A116" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D116" s="6">
-        <v>0.89</v>
-      </c>
-      <c r="E116">
-        <v>1</v>
-      </c>
-      <c r="G116">
-        <v>0.71</v>
       </c>
       <c r="M116" s="4"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>159</v>
@@ -4626,214 +4666,211 @@
         <v>0.98</v>
       </c>
       <c r="G117">
-        <v>0.36</v>
-      </c>
-      <c r="J117">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D118" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="E118">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G118">
-        <v>0.42</v>
-      </c>
-      <c r="J118">
-        <v>0.78</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M118" s="4"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="6" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D119" s="6">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="E119">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="G119">
-        <v>0.57999999999999996</v>
+        <v>0.39</v>
       </c>
       <c r="M119" s="4"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="6" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D120" s="6">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D121" s="6">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="E121">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G121">
-        <v>0.52</v>
+        <v>0.36</v>
+      </c>
+      <c r="J121">
+        <v>0.86</v>
       </c>
       <c r="M121" s="4"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="6" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D122" s="6">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="E122">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="G122">
-        <v>0.56000000000000005</v>
+        <v>0.42</v>
+      </c>
+      <c r="J122">
+        <v>0.78</v>
       </c>
       <c r="M122" s="4"/>
     </row>
     <row r="123" spans="1:13">
-      <c r="A123" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C123" s="5" t="s">
+      <c r="A123" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C123" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D123" s="5">
-        <v>0</v>
+      <c r="D123" s="6">
+        <v>0.75</v>
       </c>
       <c r="E123">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="G123">
-        <v>0.71</v>
-      </c>
-      <c r="J123">
-        <v>0.86</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D124" s="6">
-        <v>0.69</v>
+        <v>0.96</v>
       </c>
       <c r="E124">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D125" s="6">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="E125">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G125">
-        <v>0.56000000000000005</v>
+        <v>0.52</v>
       </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D126" s="6">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="E126">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G126">
-        <v>0.78</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="5" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>159</v>
@@ -4842,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G127">
-        <v>0.56999999999999995</v>
+        <v>0.71</v>
       </c>
       <c r="J127">
         <v>0.86</v>
@@ -4854,481 +4891,484 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>303</v>
+        <v>184</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>304</v>
+        <v>185</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D128" s="6">
-        <v>0.87</v>
+        <v>0.69</v>
       </c>
       <c r="E128">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G128">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J128">
-        <v>0.8</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>269</v>
+        <v>198</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>270</v>
+        <v>199</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D129" s="6">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="E129">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G129">
-        <v>0.62</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>311</v>
+        <v>220</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>312</v>
+        <v>221</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D130" s="6">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="E130">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="G130">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D131" s="6">
-        <v>0.64</v>
+      <c r="A131" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D131" s="5">
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="G131">
-        <v>0.47</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J131">
+        <v>0.86</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="6" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D132" s="6">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G132">
-        <v>0.55000000000000004</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J132">
+        <v>0.8</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>335</v>
+        <v>269</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="E133">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="G133">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
+        <v>0.79</v>
+      </c>
+      <c r="E134">
         <v>0.91</v>
       </c>
-      <c r="E134">
-        <v>0.86</v>
-      </c>
       <c r="G134">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>265</v>
+        <v>333</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="E135">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G135">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="6" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D136" s="6">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="E136">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G136">
-        <v>0.51</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M136" s="4"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="6" t="s">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D137" s="6">
-        <v>0.87</v>
+        <v>0.69</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G137">
-        <v>0.66</v>
-      </c>
-      <c r="J137">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="M137" s="4"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C138" s="5" t="s">
+      <c r="A138" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="5">
-        <v>0</v>
+      <c r="D138" s="6">
+        <v>0.91</v>
       </c>
       <c r="E138">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="G138">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E139">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="G139">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="6" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D140" s="6">
-        <v>0.41</v>
+        <v>0.86</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="G140">
-        <v>0.36</v>
+        <v>0.51</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>0.66</v>
+      </c>
+      <c r="J141">
+        <v>0.8</v>
+      </c>
+      <c r="M141" s="4"/>
+    </row>
+    <row r="142" spans="1:13">
+      <c r="A142" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D142" s="5">
         <v>0</v>
       </c>
-      <c r="G141">
-        <v>0.47</v>
-      </c>
-      <c r="M141" s="4"/>
-    </row>
-    <row r="142" spans="1:13">
-      <c r="A142" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D142" s="6">
-        <v>0.71</v>
-      </c>
       <c r="E142">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G142">
-        <v>0.55000000000000004</v>
+        <v>0.6</v>
       </c>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="6" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D143" s="6">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G143">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C144" s="5" t="s">
+      <c r="A144" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="6">
+        <v>0.41</v>
+      </c>
+      <c r="E144">
         <v>0</v>
       </c>
-      <c r="E144">
-        <v>0.86</v>
-      </c>
       <c r="G144">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J144">
-        <v>0.83</v>
+        <v>0.36</v>
       </c>
       <c r="M144" s="4"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="6" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D145" s="6">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
       <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0.47</v>
+      </c>
+      <c r="M145" s="4"/>
+    </row>
+    <row r="146" spans="1:13">
+      <c r="A146" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D146" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="E146">
         <v>1</v>
       </c>
-      <c r="G145">
-        <v>0.61</v>
-      </c>
-      <c r="M145" s="4"/>
-    </row>
-    <row r="146" spans="1:13">
-      <c r="A146" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D146" s="5">
-        <v>0</v>
-      </c>
-      <c r="E146">
-        <v>0.6</v>
-      </c>
       <c r="G146">
-        <v>0.62</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="E147">
         <v>1</v>
       </c>
       <c r="G147">
-        <v>0.56999999999999995</v>
+        <v>0.53</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
-      <c r="A148" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C148" s="6" t="s">
+      <c r="A148" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D148" s="6">
-        <v>0.88</v>
+      <c r="D148" s="5">
+        <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="G148">
-        <v>0.51</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J148">
+        <v>0.83</v>
       </c>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="6" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D149" s="6">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="E149">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G149">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="M149" s="4"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>245</v>
@@ -5337,28 +5377,28 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="G150">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D151" s="6">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E151">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G151">
         <v>0.56999999999999995</v>
@@ -5366,164 +5406,164 @@
       <c r="M151" s="4"/>
     </row>
     <row r="152" spans="1:13">
-      <c r="A152" t="s">
-        <v>479</v>
-      </c>
-      <c r="B152" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="C152" t="s">
+      <c r="A152" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C152" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E152">
         <v>0</v>
       </c>
-      <c r="E152">
-        <v>1</v>
-      </c>
       <c r="G152">
-        <v>0.52</v>
-      </c>
-      <c r="M152" s="10"/>
+        <v>0.51</v>
+      </c>
+      <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
+        <v>0.98</v>
+      </c>
+      <c r="E153">
+        <v>0.98</v>
+      </c>
+      <c r="G153">
+        <v>0.45</v>
+      </c>
+      <c r="M153" s="4"/>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D154" s="5">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>0.93</v>
+      </c>
+      <c r="G154">
+        <v>0.53</v>
+      </c>
+      <c r="M154" s="4"/>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="A155" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D155" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="E155">
+        <v>0.98</v>
+      </c>
+      <c r="G155">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M155" s="4"/>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="A156" t="s">
+        <v>479</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="C156" t="s">
+        <v>245</v>
+      </c>
+      <c r="D156" s="2">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>0.52</v>
+      </c>
+      <c r="M156" s="10"/>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="A157" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D157" s="6">
         <v>0.85</v>
       </c>
-      <c r="E153">
+      <c r="E157">
         <v>0.93</v>
       </c>
-      <c r="G153">
+      <c r="G157">
         <v>0.47</v>
       </c>
-      <c r="M153" s="4"/>
-    </row>
-    <row r="154" spans="1:13">
-      <c r="A154" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D154" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="E154">
-        <v>0.98</v>
-      </c>
-      <c r="G154">
-        <v>0.61</v>
-      </c>
-      <c r="M154" s="4"/>
-    </row>
-    <row r="155" spans="1:13">
-      <c r="A155" t="s">
-        <v>468</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="C155" t="s">
-        <v>245</v>
-      </c>
-      <c r="D155" s="2">
-        <v>0</v>
-      </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-      <c r="G155">
-        <v>0.39</v>
-      </c>
-      <c r="M155" s="10"/>
-    </row>
-    <row r="156" spans="1:13">
-      <c r="A156" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D156" s="6">
-        <v>0.71</v>
-      </c>
-      <c r="E156">
-        <v>0.88</v>
-      </c>
-      <c r="G156">
-        <v>0.53</v>
-      </c>
-      <c r="M156" s="4"/>
-    </row>
-    <row r="157" spans="1:13">
-      <c r="A157" t="s">
-        <v>477</v>
-      </c>
-      <c r="B157" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="C157" t="s">
-        <v>245</v>
-      </c>
-      <c r="D157" s="2">
-        <v>0</v>
-      </c>
-      <c r="E157">
-        <v>0</v>
-      </c>
-      <c r="G157">
-        <v>0.45</v>
-      </c>
-      <c r="M157" s="10"/>
+      <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="6" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D158" s="6">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="E158">
         <v>0.98</v>
       </c>
       <c r="G158">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
-      <c r="A159" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C159" s="6" t="s">
+      <c r="A159" t="s">
+        <v>468</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C159" t="s">
         <v>245</v>
       </c>
-      <c r="D159" s="6">
-        <v>1</v>
+      <c r="D159" s="2">
+        <v>0</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -5531,80 +5571,77 @@
       <c r="G159">
         <v>0.39</v>
       </c>
-      <c r="M159" s="4"/>
+      <c r="M159" s="10"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="E160">
         <v>0.88</v>
       </c>
-      <c r="E160">
-        <v>0.84</v>
-      </c>
       <c r="G160">
-        <v>0.75</v>
-      </c>
-      <c r="J160">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C161" s="6" t="s">
+      <c r="A161" t="s">
+        <v>477</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="C161" t="s">
         <v>245</v>
       </c>
-      <c r="D161" s="6">
-        <v>0.8</v>
+      <c r="D161" s="2">
+        <v>0</v>
       </c>
       <c r="E161">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>0.71</v>
-      </c>
-      <c r="M161" s="4"/>
+        <v>0.45</v>
+      </c>
+      <c r="M161" s="10"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="E162">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="G162">
-        <v>0.57999999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>245</v>
@@ -5616,334 +5653,337 @@
         <v>1</v>
       </c>
       <c r="G163">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
-      <c r="A164" t="s">
-        <v>470</v>
-      </c>
-      <c r="B164" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="A164" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C164" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D164" s="2">
-        <v>0</v>
+      <c r="D164" s="6">
+        <v>0.88</v>
       </c>
       <c r="E164">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G164">
+        <v>0.75</v>
+      </c>
+      <c r="J164">
+        <v>0.83</v>
+      </c>
+      <c r="M164" s="4"/>
+    </row>
+    <row r="165" spans="1:13">
+      <c r="A165" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D165" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E165">
+        <v>0.84</v>
+      </c>
+      <c r="G165">
         <v>0.71</v>
       </c>
-      <c r="M164" s="10"/>
-    </row>
-    <row r="165" spans="1:13">
-      <c r="A165" t="s">
-        <v>472</v>
-      </c>
-      <c r="B165" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="C165" t="s">
-        <v>245</v>
-      </c>
-      <c r="D165" s="2">
-        <v>0</v>
-      </c>
-      <c r="E165">
-        <v>0.98</v>
-      </c>
-      <c r="G165">
-        <v>0.38</v>
-      </c>
-      <c r="M165" s="10"/>
+      <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D166" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="E166">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="G166">
-        <v>0.44</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M166" s="4"/>
     </row>
     <row r="167" spans="1:13">
-      <c r="A167" t="s">
-        <v>388</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="A167" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C167" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D167" s="2">
-        <v>0</v>
+      <c r="D167" s="6">
+        <v>1</v>
       </c>
       <c r="E167">
         <v>1</v>
       </c>
       <c r="G167">
-        <v>0.51</v>
-      </c>
-      <c r="M167" s="10"/>
+        <v>0.74</v>
+      </c>
+      <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
-      <c r="A168" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C168" s="6" t="s">
+      <c r="A168" t="s">
+        <v>470</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C168" t="s">
         <v>245</v>
       </c>
-      <c r="D168" s="6">
-        <v>0.84</v>
+      <c r="D168" s="2">
+        <v>0</v>
       </c>
       <c r="E168">
+        <v>0.91</v>
+      </c>
+      <c r="G168">
+        <v>0.71</v>
+      </c>
+      <c r="M168" s="10"/>
+    </row>
+    <row r="169" spans="1:13">
+      <c r="A169" t="s">
+        <v>472</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C169" t="s">
+        <v>245</v>
+      </c>
+      <c r="D169" s="2">
+        <v>0</v>
+      </c>
+      <c r="E169">
         <v>0.98</v>
       </c>
-      <c r="G168">
-        <v>0.49</v>
-      </c>
-      <c r="M168" s="4"/>
-    </row>
-    <row r="169" spans="1:13">
-      <c r="A169" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="C169" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D169" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="E169">
-        <v>0</v>
-      </c>
       <c r="G169">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J169">
-        <v>0.83</v>
-      </c>
-      <c r="M169" s="4"/>
+        <v>0.38</v>
+      </c>
+      <c r="M169" s="10"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D170" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="E170">
+        <v>0.95</v>
+      </c>
+      <c r="G170">
+        <v>0.44</v>
+      </c>
+      <c r="M170" s="4"/>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" t="s">
+        <v>388</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C171" t="s">
+        <v>245</v>
+      </c>
+      <c r="D171" s="2">
+        <v>0</v>
+      </c>
+      <c r="E171">
         <v>1</v>
       </c>
-      <c r="G170">
-        <v>0.69</v>
-      </c>
-      <c r="M170" s="4"/>
-    </row>
-    <row r="171" spans="1:13">
-      <c r="A171" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D171" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="E171">
-        <v>0.98</v>
-      </c>
       <c r="G171">
-        <v>0.65</v>
-      </c>
-      <c r="M171" s="4"/>
+        <v>0.51</v>
+      </c>
+      <c r="M171" s="10"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D172" s="6">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="E172">
-        <v>0.81</v>
+        <v>0.98</v>
       </c>
       <c r="G172">
-        <v>0.56000000000000005</v>
+        <v>0.49</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>461</v>
+        <v>285</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D173" s="6">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="E173">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>0.62</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J173">
+        <v>0.83</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>302</v>
+        <v>252</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D174" s="6">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="E174">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G174">
-        <v>0.48</v>
+        <v>0.69</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D175" s="6">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="E175">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G175">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="6" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D176" s="6">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="E176">
+        <v>0.81</v>
+      </c>
+      <c r="G176">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M176" s="4"/>
+    </row>
+    <row r="177" spans="1:13">
+      <c r="A177" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D177" s="6">
         <v>0.93</v>
       </c>
-      <c r="G176">
-        <v>0.36</v>
-      </c>
-      <c r="M176" s="4"/>
-    </row>
-    <row r="177" spans="1:13">
-      <c r="A177" t="s">
-        <v>475</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="C177" t="s">
-        <v>245</v>
-      </c>
-      <c r="D177" s="2">
-        <v>0</v>
-      </c>
       <c r="E177">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="G177">
-        <v>0.68</v>
-      </c>
-      <c r="M177" s="10"/>
+        <v>0.62</v>
+      </c>
+      <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D178" s="6">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="E178">
         <v>0.98</v>
       </c>
       <c r="G178">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>331</v>
+        <v>243</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>332</v>
+        <v>244</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>245</v>
@@ -5952,295 +5992,289 @@
         <v>0.86</v>
       </c>
       <c r="E179">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="G179">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D180" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="E180">
         <v>0.93</v>
       </c>
-      <c r="E180">
-        <v>0.95</v>
-      </c>
       <c r="G180">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
-      <c r="A181" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="C181" s="6" t="s">
+      <c r="A181" t="s">
+        <v>475</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="C181" t="s">
         <v>245</v>
       </c>
-      <c r="D181" s="6">
-        <v>1</v>
+      <c r="D181" s="2">
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G181">
-        <v>0.66</v>
-      </c>
-      <c r="M181" s="4"/>
+        <v>0.68</v>
+      </c>
+      <c r="M181" s="10"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D182" s="6">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="E182">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G182">
-        <v>0.53</v>
-      </c>
-      <c r="J182">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D183" s="6">
-        <v>0.81</v>
+        <v>0.86</v>
       </c>
       <c r="E183">
-        <v>0.65</v>
+        <v>0.98</v>
       </c>
       <c r="G183">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>320</v>
+        <v>292</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D184" s="6">
-        <v>0.81</v>
+        <v>0.93</v>
       </c>
       <c r="E184">
         <v>0.95</v>
       </c>
       <c r="G184">
-        <v>0.82</v>
-      </c>
-      <c r="J184">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D185" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E185">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G185">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>321</v>
+        <v>255</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>322</v>
+        <v>256</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D186" s="6">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="E186">
         <v>1</v>
       </c>
       <c r="G186">
-        <v>0.43</v>
+        <v>0.53</v>
+      </c>
+      <c r="J186">
+        <v>0.8</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D187" s="6">
-        <v>0.89</v>
+        <v>0.81</v>
       </c>
       <c r="E187">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="G187">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D188" s="6">
-        <v>0.77</v>
+        <v>0.81</v>
       </c>
       <c r="E188">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G188">
-        <v>0.69</v>
+        <v>0.82</v>
       </c>
       <c r="J188">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>392</v>
+        <v>281</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>393</v>
+        <v>282</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D189" s="6">
         <v>0.8</v>
       </c>
       <c r="E189">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="G189">
-        <v>0</v>
-      </c>
-      <c r="J189">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>430</v>
+        <v>321</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>431</v>
+        <v>322</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D190" s="6">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="E190">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G190">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>364</v>
+        <v>317</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>365</v>
+        <v>318</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D191" s="6">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G191">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D192" s="6">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="E192">
         <v>1</v>
       </c>
       <c r="G192">
-        <v>0.61</v>
+        <v>0.69</v>
       </c>
       <c r="J192">
         <v>0.8</v>
@@ -6249,307 +6283,310 @@
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D193" s="6">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G193">
-        <v>0.64</v>
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0.85</v>
       </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D194" s="6">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="E194">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="G194">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>437</v>
+        <v>365</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D195" s="6">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="E195">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G195">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>418</v>
+        <v>350</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>419</v>
+        <v>351</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D196" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="E196">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G196">
-        <v>0.69</v>
+        <v>0.61</v>
+      </c>
+      <c r="J196">
+        <v>0.8</v>
       </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>413</v>
+        <v>373</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D197" s="6">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="E197">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G197">
-        <v>0.56999999999999995</v>
+        <v>0.64</v>
       </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>376</v>
+        <v>434</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>377</v>
+        <v>435</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D198" s="6">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="E198">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="G198">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>394</v>
+        <v>436</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>395</v>
+        <v>437</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D199" s="6">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="E199">
-        <v>0.42</v>
+        <v>0.91</v>
       </c>
       <c r="G199">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D200" s="6">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="E200">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="G200">
-        <v>0.56999999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D201" s="6">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="E201">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="G201">
-        <v>0.55000000000000004</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>414</v>
+        <v>376</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D202" s="6">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="E202">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D203" s="6">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="E203">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="G203">
-        <v>0.82</v>
-      </c>
-      <c r="J203">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D204" s="6">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="E204">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G204">
-        <v>0.64</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="6" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D205" s="6">
-        <v>0.81</v>
+        <v>0.93</v>
       </c>
       <c r="E205">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="G205">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D206" s="6">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="E206">
         <v>0.98</v>
       </c>
       <c r="G206">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="6" t="s">
-        <v>404</v>
+        <v>360</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>405</v>
+        <v>361</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>343</v>
@@ -6561,190 +6598,190 @@
         <v>0.91</v>
       </c>
       <c r="G207">
-        <v>0.81</v>
+        <v>0.82</v>
+      </c>
+      <c r="J207">
+        <v>0.8</v>
       </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="6" t="s">
-        <v>341</v>
+        <v>426</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>342</v>
+        <v>427</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D208" s="6">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="E208">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G208">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D209" s="6">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="E209">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="G209">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D210" s="6">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="E210">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="G210">
-        <v>0.6</v>
-      </c>
-      <c r="J210">
-        <v>0.85</v>
+        <v>0.53</v>
       </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D211" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="E211">
+        <v>0.91</v>
+      </c>
+      <c r="G211">
         <v>0.81</v>
-      </c>
-      <c r="E211">
-        <v>1</v>
-      </c>
-      <c r="G211">
-        <v>0.75</v>
       </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D212" s="6">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="E212">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="G212">
-        <v>0.69</v>
+        <v>0.71</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D213" s="6">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="E213">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G213">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D214" s="6">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E214">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="G214">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="J214">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>399</v>
+        <v>447</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D215" s="6">
-        <v>0.96</v>
+        <v>0.81</v>
       </c>
       <c r="E215">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G215">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>343</v>
@@ -6753,271 +6790,271 @@
         <v>0.85</v>
       </c>
       <c r="E216">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="G216">
-        <v>0.83</v>
+        <v>0.69</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D217" s="6">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="E217">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G217">
-        <v>0.56999999999999995</v>
+        <v>0.73</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="6" t="s">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>409</v>
+        <v>345</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D218" s="6">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="E218">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G218">
-        <v>0.77</v>
+        <v>0.73</v>
+      </c>
+      <c r="J218">
+        <v>0.79</v>
       </c>
       <c r="M218" s="4"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="6" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D219" s="6">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="E219">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="G219">
-        <v>0.77</v>
-      </c>
-      <c r="J219">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="6" t="s">
-        <v>432</v>
+        <v>374</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D220" s="6">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="E220">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="G220">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="6" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D221" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.77</v>
       </c>
       <c r="E221">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="G221">
-        <v>0.57999999999999996</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="6" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D222" s="6">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="E222">
         <v>1</v>
       </c>
       <c r="G222">
-        <v>0.35</v>
+        <v>0.77</v>
       </c>
       <c r="M222" s="4"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D223" s="6">
+        <v>1</v>
+      </c>
+      <c r="E223">
+        <v>0.88</v>
+      </c>
+      <c r="G223">
+        <v>0.77</v>
+      </c>
+      <c r="J223">
+        <v>0.93</v>
+      </c>
+      <c r="M223" s="4"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D224" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E224">
         <v>0.98</v>
       </c>
-      <c r="E223">
-        <v>0</v>
-      </c>
-      <c r="G223">
-        <v>0.88</v>
-      </c>
-      <c r="J223">
-        <v>0.85</v>
-      </c>
-      <c r="M223" s="4"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="B224" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="D224" s="5">
-        <v>0</v>
-      </c>
-      <c r="E224">
-        <v>1</v>
-      </c>
       <c r="G224">
-        <v>0.6</v>
-      </c>
-      <c r="J224">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="6" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D225" s="6">
-        <v>0.98</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E225">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="G225">
-        <v>0.81</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M225" s="4"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="6" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D226" s="6">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="E226">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G226">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="M226" s="4"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="6" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>383</v>
+        <v>439</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D227" s="6">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="E227">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>0.77</v>
+        <v>0.88</v>
+      </c>
+      <c r="J227">
+        <v>0.85</v>
       </c>
       <c r="M227" s="4"/>
     </row>
     <row r="228" spans="1:13">
-      <c r="A228" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="C228" s="6" t="s">
+      <c r="A228" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C228" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D228" s="6">
-        <v>0.42</v>
+      <c r="D228" s="5">
+        <v>0</v>
       </c>
       <c r="E228">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="G228">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="J228">
         <v>0.93</v>
@@ -7026,55 +7063,52 @@
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="6" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D229" s="6">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="E229">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G229">
-        <v>0.69</v>
+        <v>0.81</v>
       </c>
       <c r="M229" s="13"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="6" t="s">
-        <v>444</v>
+        <v>402</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D230" s="6">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="E230">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G230">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J230">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="M230" s="13"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="6" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>343</v>
@@ -7083,234 +7117,385 @@
         <v>0.96</v>
       </c>
       <c r="E231">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G231">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="M231" s="13"/>
     </row>
     <row r="232" spans="1:13">
-      <c r="A232" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="C232" s="6" t="s">
+      <c r="A232" t="s">
+        <v>492</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C232" t="s">
         <v>343</v>
       </c>
-      <c r="D232" s="6">
-        <v>0.68</v>
+      <c r="D232" s="2">
+        <v>0</v>
       </c>
       <c r="E232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232">
-        <v>0.78</v>
-      </c>
-      <c r="J232">
-        <v>0.8</v>
-      </c>
-      <c r="M232" s="13"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M232" s="14"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="6" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D233" s="6">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="E233">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="G233">
-        <v>0.68</v>
+        <v>0.53</v>
+      </c>
+      <c r="J233">
+        <v>0.93</v>
       </c>
       <c r="M233" s="13"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="6" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D234" s="6">
-        <v>0.41</v>
+        <v>0.88</v>
       </c>
       <c r="E234">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="G234">
-        <v>0.43</v>
+        <v>0.69</v>
       </c>
       <c r="M234" s="13"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="6" t="s">
-        <v>346</v>
+        <v>444</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>347</v>
+        <v>445</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D235" s="6">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="E235">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="G235">
         <v>0.57999999999999996</v>
       </c>
+      <c r="J235">
+        <v>0.93</v>
+      </c>
       <c r="M235" s="13"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="6" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D236" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="E236">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="M236" s="13"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="6" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D237" s="6">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="E237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237">
-        <v>0.77</v>
+        <v>0.78</v>
+      </c>
+      <c r="J237">
+        <v>0.8</v>
       </c>
       <c r="M237" s="13"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="6" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D238" s="6">
-        <v>0.95</v>
+        <v>0.76</v>
       </c>
       <c r="E238">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="G238">
-        <v>0.51</v>
-      </c>
-      <c r="J238">
-        <v>0.83</v>
-      </c>
-      <c r="M238" s="11"/>
+        <v>0.68</v>
+      </c>
+      <c r="M238" s="13"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="6" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D239" s="6">
-        <v>0.97</v>
+        <v>0.41</v>
       </c>
       <c r="E239">
-        <v>0.98</v>
+        <v>0.63</v>
       </c>
       <c r="G239">
-        <v>0.74</v>
-      </c>
-      <c r="J239">
-        <v>0.8</v>
-      </c>
-      <c r="M239" s="11"/>
+        <v>0.43</v>
+      </c>
+      <c r="M239" s="13"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="6" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>343</v>
       </c>
       <c r="D240" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E240">
+        <v>0.88</v>
+      </c>
+      <c r="G240">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="M240" s="13"/>
+    </row>
+    <row r="241" spans="1:13">
+      <c r="A241" t="s">
+        <v>494</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C241" t="s">
+        <v>343</v>
+      </c>
+      <c r="D241" s="2">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="G241">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13">
+      <c r="A242" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D242" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="G242">
+        <v>0</v>
+      </c>
+      <c r="M242" s="11"/>
+    </row>
+    <row r="243" spans="1:13">
+      <c r="A243" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D243" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="G243">
+        <v>0.77</v>
+      </c>
+      <c r="M243" s="11"/>
+    </row>
+    <row r="244" spans="1:13">
+      <c r="A244" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D244" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="E244">
+        <v>0.88</v>
+      </c>
+      <c r="G244">
+        <v>0.51</v>
+      </c>
+      <c r="J244">
+        <v>0.83</v>
+      </c>
+      <c r="M244" s="11"/>
+    </row>
+    <row r="245" spans="1:13">
+      <c r="A245" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D245" s="6">
         <v>0.97</v>
       </c>
-      <c r="E240">
+      <c r="E245">
+        <v>0.98</v>
+      </c>
+      <c r="G245">
+        <v>0.74</v>
+      </c>
+      <c r="J245">
+        <v>0.8</v>
+      </c>
+      <c r="M245" s="11"/>
+    </row>
+    <row r="246" spans="1:13">
+      <c r="A246" t="s">
+        <v>496</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C246" t="s">
+        <v>343</v>
+      </c>
+      <c r="D246" s="2">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+      <c r="G246">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13">
+      <c r="A247" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D247" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="E247">
         <v>0.93</v>
       </c>
-      <c r="G240">
+      <c r="G247">
         <v>0.65</v>
       </c>
-      <c r="M240" s="11"/>
-    </row>
-    <row r="241" spans="1:13">
-      <c r="A241" s="6" t="s">
+      <c r="M247" s="11"/>
+    </row>
+    <row r="248" spans="1:13">
+      <c r="A248" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="B241" s="6" t="s">
+      <c r="B248" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="C241" s="6" t="s">
+      <c r="C248" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="D241" s="6">
+      <c r="D248" s="6">
         <v>0.88</v>
       </c>
-      <c r="E241">
+      <c r="E248">
         <v>0.95</v>
       </c>
-      <c r="G241">
+      <c r="G248">
         <v>0.71</v>
       </c>
-      <c r="J241">
+      <c r="J248">
         <v>0.93</v>
       </c>
-      <c r="M241" s="11"/>
+      <c r="M248" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3EED19-0610-544F-93DB-7897CB9D0A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A99DA-F186-5E41-9D27-C17BC17A1487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="620" windowWidth="23560" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1653,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1675,10 +1675,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2179,7 +2175,7 @@
         <v>0.98</v>
       </c>
       <c r="G4">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="M4" s="12"/>
     </row>
@@ -2375,7 +2371,7 @@
         <v>0.98</v>
       </c>
       <c r="G13">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="3"/>
       <c r="M13" s="4"/>
@@ -2571,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H22" s="3"/>
       <c r="M22" s="4"/>
@@ -2593,7 +2589,7 @@
         <v>0.98</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M23" s="10"/>
     </row>
@@ -2614,7 +2610,7 @@
         <v>0.98</v>
       </c>
       <c r="G24">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="M24" s="4"/>
     </row>
@@ -2701,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="M28" s="4"/>
     </row>
@@ -2945,7 +2941,7 @@
         <v>0.93</v>
       </c>
       <c r="G39">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="M39" s="4"/>
     </row>
@@ -3035,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="G43">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H43" s="3"/>
       <c r="J43">
@@ -3060,7 +3056,7 @@
         <v>0.98</v>
       </c>
       <c r="G44">
-        <v>0.69</v>
+        <v>0.77</v>
       </c>
       <c r="M44" s="4"/>
     </row>
@@ -3125,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="H47" s="3"/>
       <c r="M47" s="4"/>
@@ -3464,7 +3460,7 @@
         <v>0.98</v>
       </c>
       <c r="G62">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="H62" s="3"/>
       <c r="M62" s="4"/>
@@ -3786,7 +3782,7 @@
         <v>0.95</v>
       </c>
       <c r="G76">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H76" s="3"/>
       <c r="M76" s="4"/>
@@ -3808,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="G77">
-        <v>0.56999999999999995</v>
+        <v>0.61</v>
       </c>
       <c r="J77">
         <v>0.78</v>
@@ -3940,7 +3936,7 @@
         <v>0.98</v>
       </c>
       <c r="G83">
-        <v>0.69</v>
+        <v>0.78</v>
       </c>
       <c r="M83" s="4"/>
     </row>
@@ -4384,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="G104">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="J104">
         <v>0.78</v>
@@ -4408,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="G105">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="M105" s="10"/>
     </row>
@@ -4600,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="G114">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="M114" s="4"/>
     </row>
@@ -4840,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="G125">
-        <v>0.52</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M125" s="4"/>
     </row>
@@ -4882,7 +4878,7 @@
         <v>0.88</v>
       </c>
       <c r="G127">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="J127">
         <v>0.86</v>
@@ -5059,7 +5055,7 @@
         <v>0.79</v>
       </c>
       <c r="G135">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="M135" s="4"/>
     </row>
@@ -5422,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="G152">
-        <v>0.51</v>
+        <v>0.71</v>
       </c>
       <c r="M152" s="4"/>
     </row>
@@ -5719,7 +5715,7 @@
         <v>0.84</v>
       </c>
       <c r="G166">
-        <v>0.57999999999999996</v>
+        <v>0.81</v>
       </c>
       <c r="M166" s="4"/>
     </row>
@@ -6121,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="G185">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="M185" s="4"/>
     </row>
@@ -6274,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="G192">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="J192">
         <v>0.8</v>
@@ -6298,7 +6294,7 @@
         <v>0.95</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="J193">
         <v>0.85</v>
@@ -6364,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="G196">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="J196">
         <v>0.8</v>
@@ -6493,7 +6489,7 @@
         <v>0.95</v>
       </c>
       <c r="G202">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="M202" s="4"/>
     </row>
@@ -6577,7 +6573,7 @@
         <v>0.98</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="M206" s="4"/>
     </row>
@@ -6664,7 +6660,7 @@
         <v>0.98</v>
       </c>
       <c r="G210">
-        <v>0.53</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M210" s="4"/>
     </row>
@@ -6859,7 +6855,7 @@
         <v>0.98</v>
       </c>
       <c r="G219">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="M219" s="4"/>
     </row>
@@ -6967,7 +6963,7 @@
         <v>0.98</v>
       </c>
       <c r="G224">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="M224" s="4"/>
     </row>
@@ -7080,7 +7076,7 @@
       <c r="G229">
         <v>0.81</v>
       </c>
-      <c r="M229" s="13"/>
+      <c r="M229" s="11"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="6" t="s">
@@ -7101,7 +7097,7 @@
       <c r="G230">
         <v>0.7</v>
       </c>
-      <c r="M230" s="13"/>
+      <c r="M230" s="11"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="6" t="s">
@@ -7122,7 +7118,7 @@
       <c r="G231">
         <v>0.77</v>
       </c>
-      <c r="M231" s="13"/>
+      <c r="M231" s="11"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" t="s">
@@ -7143,7 +7139,6 @@
       <c r="G232">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M232" s="14"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="6" t="s">
@@ -7167,7 +7162,7 @@
       <c r="J233">
         <v>0.93</v>
       </c>
-      <c r="M233" s="13"/>
+      <c r="M233" s="11"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="6" t="s">
@@ -7188,7 +7183,7 @@
       <c r="G234">
         <v>0.69</v>
       </c>
-      <c r="M234" s="13"/>
+      <c r="M234" s="11"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="6" t="s">
@@ -7212,7 +7207,7 @@
       <c r="J235">
         <v>0.93</v>
       </c>
-      <c r="M235" s="13"/>
+      <c r="M235" s="11"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="6" t="s">
@@ -7233,7 +7228,7 @@
       <c r="G236">
         <v>0.64</v>
       </c>
-      <c r="M236" s="13"/>
+      <c r="M236" s="11"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="6" t="s">
@@ -7252,12 +7247,12 @@
         <v>1</v>
       </c>
       <c r="G237">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="J237">
         <v>0.8</v>
       </c>
-      <c r="M237" s="13"/>
+      <c r="M237" s="11"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="6" t="s">
@@ -7278,7 +7273,7 @@
       <c r="G238">
         <v>0.68</v>
       </c>
-      <c r="M238" s="13"/>
+      <c r="M238" s="11"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="6" t="s">
@@ -7299,7 +7294,7 @@
       <c r="G239">
         <v>0.43</v>
       </c>
-      <c r="M239" s="13"/>
+      <c r="M239" s="11"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="6" t="s">
@@ -7320,7 +7315,7 @@
       <c r="G240">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M240" s="13"/>
+      <c r="M240" s="11"/>
     </row>
     <row r="241" spans="1:13">
       <c r="A241" t="s">
@@ -7425,7 +7420,7 @@
         <v>0.98</v>
       </c>
       <c r="G245">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="J245">
         <v>0.8</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A99DA-F186-5E41-9D27-C17BC17A1487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA1E54F-881F-4643-AAF1-F5270F2DC5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="620" windowWidth="23560" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA1E54F-881F-4643-AAF1-F5270F2DC5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDCF09A-4F99-2A4E-B913-9249DA4ADE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="620" windowWidth="23560" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2124,6 +2124,9 @@
       <c r="E2">
         <v>0.88</v>
       </c>
+      <c r="F2">
+        <v>0.98</v>
+      </c>
       <c r="G2">
         <v>0.42</v>
       </c>
@@ -2149,6 +2152,9 @@
       <c r="E3">
         <v>0.98</v>
       </c>
+      <c r="F3">
+        <v>0.93</v>
+      </c>
       <c r="G3">
         <v>0.57999999999999996</v>
       </c>
@@ -2174,6 +2180,9 @@
       <c r="E4">
         <v>0.98</v>
       </c>
+      <c r="F4">
+        <v>0.92</v>
+      </c>
       <c r="G4">
         <v>0.75</v>
       </c>
@@ -2195,6 +2204,9 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="G5">
         <v>0.77</v>
       </c>
@@ -2217,6 +2229,9 @@
       <c r="E6">
         <v>0.98</v>
       </c>
+      <c r="F6">
+        <v>0.89</v>
+      </c>
       <c r="G6">
         <v>0.68</v>
       </c>
@@ -2239,6 +2254,9 @@
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7">
+        <v>0.94</v>
+      </c>
       <c r="G7">
         <v>0.81</v>
       </c>
@@ -2260,6 +2278,9 @@
       <c r="E8">
         <v>0.93</v>
       </c>
+      <c r="F8">
+        <v>0.95</v>
+      </c>
       <c r="G8">
         <v>0.6</v>
       </c>
@@ -2282,6 +2303,9 @@
       <c r="E9">
         <v>1</v>
       </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
       <c r="G9">
         <v>0.51</v>
       </c>
@@ -2304,6 +2328,9 @@
       <c r="E10">
         <v>1</v>
       </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
       <c r="G10">
         <v>0.53</v>
       </c>
@@ -2326,6 +2353,9 @@
       <c r="E11">
         <v>0.93</v>
       </c>
+      <c r="F11">
+        <v>0.89</v>
+      </c>
       <c r="G11">
         <v>0.66</v>
       </c>
@@ -2348,6 +2378,9 @@
       <c r="E12">
         <v>1</v>
       </c>
+      <c r="F12">
+        <v>0.98</v>
+      </c>
       <c r="G12">
         <v>0.55000000000000004</v>
       </c>
@@ -2370,6 +2403,9 @@
       <c r="E13">
         <v>0.98</v>
       </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
       <c r="G13">
         <v>0.9</v>
       </c>
@@ -2392,6 +2428,9 @@
       <c r="E14">
         <v>0.98</v>
       </c>
+      <c r="F14">
+        <v>0.95</v>
+      </c>
       <c r="G14">
         <v>0.51</v>
       </c>
@@ -2414,6 +2453,9 @@
       <c r="E15">
         <v>0.95</v>
       </c>
+      <c r="F15">
+        <v>0.93</v>
+      </c>
       <c r="G15">
         <v>0.57999999999999996</v>
       </c>
@@ -2436,6 +2478,9 @@
       <c r="E16">
         <v>1</v>
       </c>
+      <c r="F16">
+        <v>0.69</v>
+      </c>
       <c r="G16">
         <v>0.52</v>
       </c>
@@ -2458,6 +2503,9 @@
       <c r="E17">
         <v>0.98</v>
       </c>
+      <c r="F17">
+        <v>0.94</v>
+      </c>
       <c r="G17">
         <v>0.47</v>
       </c>
@@ -2480,6 +2528,9 @@
       <c r="E18">
         <v>0.95</v>
       </c>
+      <c r="F18">
+        <v>0.95</v>
+      </c>
       <c r="G18">
         <v>0.65</v>
       </c>
@@ -2501,6 +2552,9 @@
       <c r="E19">
         <v>0.93</v>
       </c>
+      <c r="F19">
+        <v>0.95</v>
+      </c>
       <c r="G19">
         <v>0.73</v>
       </c>
@@ -2523,6 +2577,9 @@
       <c r="E20">
         <v>0.95</v>
       </c>
+      <c r="F20">
+        <v>0.88</v>
+      </c>
       <c r="G20">
         <v>0.62</v>
       </c>
@@ -2544,6 +2601,9 @@
       <c r="E21">
         <v>0.98</v>
       </c>
+      <c r="F21">
+        <v>0.98</v>
+      </c>
       <c r="G21">
         <v>0.66</v>
       </c>
@@ -2566,6 +2626,9 @@
       <c r="E22">
         <v>1</v>
       </c>
+      <c r="F22">
+        <v>0.88</v>
+      </c>
       <c r="G22">
         <v>0.82</v>
       </c>
@@ -2588,6 +2651,9 @@
       <c r="E23">
         <v>0.98</v>
       </c>
+      <c r="F23">
+        <v>0.9</v>
+      </c>
       <c r="G23">
         <v>0.38</v>
       </c>
@@ -2609,6 +2675,9 @@
       <c r="E24">
         <v>0.98</v>
       </c>
+      <c r="F24">
+        <v>0.98</v>
+      </c>
       <c r="G24">
         <v>0.74</v>
       </c>
@@ -2630,6 +2699,9 @@
       <c r="E25">
         <v>0.93</v>
       </c>
+      <c r="F25">
+        <v>0.86</v>
+      </c>
       <c r="G25">
         <v>0.61</v>
       </c>
@@ -2652,6 +2724,9 @@
       <c r="E26">
         <v>1</v>
       </c>
+      <c r="F26">
+        <v>0.92</v>
+      </c>
       <c r="G26">
         <v>0.4</v>
       </c>
@@ -2674,6 +2749,9 @@
       <c r="E27">
         <v>1</v>
       </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
       <c r="G27">
         <v>0.57999999999999996</v>
       </c>
@@ -2696,6 +2774,9 @@
       <c r="E28">
         <v>1</v>
       </c>
+      <c r="F28">
+        <v>0.93</v>
+      </c>
       <c r="G28">
         <v>0.78</v>
       </c>
@@ -2717,6 +2798,9 @@
       <c r="E29">
         <v>0.7</v>
       </c>
+      <c r="F29">
+        <v>0.95</v>
+      </c>
       <c r="G29">
         <v>0.34</v>
       </c>
@@ -2739,6 +2823,9 @@
       <c r="E30">
         <v>0.86</v>
       </c>
+      <c r="F30">
+        <v>0.87</v>
+      </c>
       <c r="G30">
         <v>0.56999999999999995</v>
       </c>
@@ -2761,6 +2848,9 @@
       <c r="E31">
         <v>0.93</v>
       </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
       <c r="G31">
         <v>0.73</v>
       </c>
@@ -2782,6 +2872,9 @@
       <c r="E32">
         <v>0.93</v>
       </c>
+      <c r="F32">
+        <v>0.8</v>
+      </c>
       <c r="G32">
         <v>0.4</v>
       </c>
@@ -2804,6 +2897,9 @@
       <c r="E33">
         <v>0.81</v>
       </c>
+      <c r="F33">
+        <v>0.98</v>
+      </c>
       <c r="G33">
         <v>0.7</v>
       </c>
@@ -2826,6 +2922,9 @@
       <c r="E34">
         <v>0.77</v>
       </c>
+      <c r="F34">
+        <v>0.77</v>
+      </c>
       <c r="G34">
         <v>0.55000000000000004</v>
       </c>
@@ -2850,6 +2949,9 @@
       <c r="E35">
         <v>0.91</v>
       </c>
+      <c r="F35">
+        <v>0.93</v>
+      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -2872,6 +2974,9 @@
       <c r="E36">
         <v>1</v>
       </c>
+      <c r="F36">
+        <v>0.89</v>
+      </c>
       <c r="G36">
         <v>0.27</v>
       </c>
@@ -2894,6 +2999,9 @@
       <c r="E37">
         <v>0.93</v>
       </c>
+      <c r="F37">
+        <v>0.88</v>
+      </c>
       <c r="G37">
         <v>0.57999999999999996</v>
       </c>
@@ -2915,6 +3023,9 @@
       <c r="E38">
         <v>0.98</v>
       </c>
+      <c r="F38">
+        <v>0.89</v>
+      </c>
       <c r="G38">
         <v>0.65</v>
       </c>
@@ -2940,6 +3051,9 @@
       <c r="E39">
         <v>0.93</v>
       </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
       <c r="G39">
         <v>0.75</v>
       </c>
@@ -2961,6 +3075,9 @@
       <c r="E40">
         <v>0.98</v>
       </c>
+      <c r="F40">
+        <v>0.88</v>
+      </c>
       <c r="G40">
         <v>0.48</v>
       </c>
@@ -2983,6 +3100,9 @@
       <c r="E41">
         <v>1</v>
       </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
       <c r="G41">
         <v>0.55000000000000004</v>
       </c>
@@ -3008,6 +3128,9 @@
       <c r="E42">
         <v>1</v>
       </c>
+      <c r="F42">
+        <v>0.92</v>
+      </c>
       <c r="G42">
         <v>0.56000000000000005</v>
       </c>
@@ -3030,6 +3153,9 @@
       <c r="E43">
         <v>1</v>
       </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
       <c r="G43">
         <v>0.92</v>
       </c>
@@ -3055,6 +3181,9 @@
       <c r="E44">
         <v>0.98</v>
       </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
       <c r="G44">
         <v>0.77</v>
       </c>
@@ -3076,6 +3205,9 @@
       <c r="E45">
         <v>0.79</v>
       </c>
+      <c r="F45">
+        <v>0.86</v>
+      </c>
       <c r="G45">
         <v>0</v>
       </c>
@@ -3098,6 +3230,9 @@
       <c r="E46">
         <v>0.98</v>
       </c>
+      <c r="F46">
+        <v>0.98</v>
+      </c>
       <c r="G46">
         <v>0.66</v>
       </c>
@@ -3120,6 +3255,9 @@
       <c r="E47">
         <v>1</v>
       </c>
+      <c r="F47">
+        <v>0.95</v>
+      </c>
       <c r="G47">
         <v>0.83</v>
       </c>
@@ -3142,6 +3280,9 @@
       <c r="E48">
         <v>0.93</v>
       </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
       <c r="G48">
         <v>0.18</v>
       </c>
@@ -3164,6 +3305,9 @@
       <c r="E49">
         <v>1</v>
       </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
       <c r="G49">
         <v>0.18</v>
       </c>
@@ -3186,6 +3330,9 @@
       <c r="E50">
         <v>1</v>
       </c>
+      <c r="F50">
+        <v>0.98</v>
+      </c>
       <c r="G50">
         <v>0.52</v>
       </c>
@@ -3210,6 +3357,9 @@
       <c r="E51">
         <v>0.95</v>
       </c>
+      <c r="F51">
+        <v>0.88</v>
+      </c>
       <c r="G51">
         <v>0.53</v>
       </c>
@@ -3231,6 +3381,9 @@
       <c r="E52">
         <v>1</v>
       </c>
+      <c r="F52">
+        <v>0.98</v>
+      </c>
       <c r="G52">
         <v>0.62</v>
       </c>
@@ -3252,6 +3405,9 @@
       <c r="E53">
         <v>1</v>
       </c>
+      <c r="F53">
+        <v>0.98</v>
+      </c>
       <c r="G53">
         <v>0.36</v>
       </c>
@@ -3274,6 +3430,9 @@
       <c r="E54">
         <v>0.95</v>
       </c>
+      <c r="F54">
+        <v>0.94</v>
+      </c>
       <c r="G54">
         <v>0.65</v>
       </c>
@@ -3296,6 +3455,9 @@
       <c r="E55">
         <v>1</v>
       </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
       <c r="G55">
         <v>0.68</v>
       </c>
@@ -3318,6 +3480,9 @@
       <c r="E56">
         <v>0.98</v>
       </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
       <c r="G56">
         <v>0.68</v>
       </c>
@@ -3339,6 +3504,9 @@
       <c r="E57">
         <v>0.98</v>
       </c>
+      <c r="F57">
+        <v>0.98</v>
+      </c>
       <c r="G57">
         <v>0.65</v>
       </c>
@@ -3364,6 +3532,9 @@
       <c r="E58">
         <v>0.98</v>
       </c>
+      <c r="F58">
+        <v>0.84</v>
+      </c>
       <c r="G58">
         <v>0.34</v>
       </c>
@@ -3388,6 +3559,9 @@
       <c r="E59">
         <v>0.98</v>
       </c>
+      <c r="F59">
+        <v>0.95</v>
+      </c>
       <c r="G59">
         <v>0.53</v>
       </c>
@@ -3410,6 +3584,9 @@
       <c r="E60">
         <v>0.98</v>
       </c>
+      <c r="F60">
+        <v>0.95</v>
+      </c>
       <c r="G60">
         <v>0.56000000000000005</v>
       </c>
@@ -3434,6 +3611,9 @@
       <c r="E61">
         <v>0.98</v>
       </c>
+      <c r="F61">
+        <v>0.92</v>
+      </c>
       <c r="G61">
         <v>0.56000000000000005</v>
       </c>
@@ -3459,6 +3639,9 @@
       <c r="E62">
         <v>0.98</v>
       </c>
+      <c r="F62">
+        <v>0.98</v>
+      </c>
       <c r="G62">
         <v>0.78</v>
       </c>
@@ -3481,6 +3664,9 @@
       <c r="E63">
         <v>0.95</v>
       </c>
+      <c r="F63">
+        <v>0.94</v>
+      </c>
       <c r="G63">
         <v>0.69</v>
       </c>
@@ -3503,6 +3689,9 @@
       <c r="E64">
         <v>1</v>
       </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
       <c r="G64">
         <v>0.56999999999999995</v>
       </c>
@@ -3524,6 +3713,9 @@
       <c r="E65">
         <v>0.95</v>
       </c>
+      <c r="F65">
+        <v>0.92</v>
+      </c>
       <c r="G65">
         <v>0.6</v>
       </c>
@@ -3546,6 +3738,9 @@
       <c r="E66">
         <v>0.98</v>
       </c>
+      <c r="F66">
+        <v>0.98</v>
+      </c>
       <c r="G66">
         <v>0.49</v>
       </c>
@@ -3567,6 +3762,9 @@
       <c r="E67">
         <v>1</v>
       </c>
+      <c r="F67">
+        <v>0.98</v>
+      </c>
       <c r="G67">
         <v>0.7</v>
       </c>
@@ -3591,6 +3789,9 @@
       <c r="E68">
         <v>0.98</v>
       </c>
+      <c r="F68">
+        <v>0.89</v>
+      </c>
       <c r="G68">
         <v>0.62</v>
       </c>
@@ -3612,6 +3813,9 @@
       <c r="E69">
         <v>1</v>
       </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
       <c r="G69">
         <v>0.55000000000000004</v>
       </c>
@@ -3637,6 +3841,9 @@
       <c r="E70">
         <v>0.88</v>
       </c>
+      <c r="F70">
+        <v>0.98</v>
+      </c>
       <c r="G70">
         <v>0.68</v>
       </c>
@@ -3662,6 +3869,9 @@
       <c r="E71">
         <v>0.98</v>
       </c>
+      <c r="F71">
+        <v>0.98</v>
+      </c>
       <c r="G71">
         <v>0.57999999999999996</v>
       </c>
@@ -3687,6 +3897,9 @@
       <c r="E72">
         <v>0.98</v>
       </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
       <c r="G72">
         <v>0</v>
       </c>
@@ -3712,6 +3925,9 @@
       <c r="E73">
         <v>1</v>
       </c>
+      <c r="F73">
+        <v>0.82</v>
+      </c>
       <c r="G73">
         <v>0.66</v>
       </c>
@@ -3733,6 +3949,9 @@
       <c r="E74">
         <v>1</v>
       </c>
+      <c r="F74">
+        <v>0.92</v>
+      </c>
       <c r="G74">
         <v>0.48</v>
       </c>
@@ -3757,6 +3976,9 @@
       <c r="E75">
         <v>0.95</v>
       </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
       <c r="G75">
         <v>0.62</v>
       </c>
@@ -3780,6 +4002,9 @@
       </c>
       <c r="E76">
         <v>0.95</v>
+      </c>
+      <c r="F76">
+        <v>0.9</v>
       </c>
       <c r="G76">
         <v>0.79</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDCF09A-4F99-2A4E-B913-9249DA4ADE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103D5426-2658-9240-80EC-C566E575507C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="620" windowWidth="23560" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="60" yWindow="620" windowWidth="30760" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1653,11 +1653,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1675,16 +1673,48 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1703,6 +1733,9 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1725,15 +1758,15 @@
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
-    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept"/>
-    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2"/>
-    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3"/>
-    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1"/>
-    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="0"/>
-    <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 "/>
-    <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1"/>
+    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 " dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 "/>
     <tableColumn id="12" xr3:uid="{912F9A7A-D63B-9A42-91A4-38F3D4DCB1F9}" name="AS_3"/>
     <tableColumn id="13" xr3:uid="{C1D2D2AB-5806-CA4E-9587-399F7BCCF779}" name="CW"/>
@@ -2064,7 +2097,14 @@
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="2"/>
+    <col min="3" max="3" width="10.140625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="11"/>
+    <col min="6" max="6" width="7.42578125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="11"/>
+    <col min="10" max="10" width="7" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2074,28 +2114,28 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="K1" t="s">
@@ -2109,5613 +2149,5805 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="12">
         <v>0.73</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="11">
         <v>0.88</v>
       </c>
-      <c r="F2">
-        <v>0.98</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G2" s="11">
         <v>0.42</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="J2">
+      <c r="H2" s="15"/>
+      <c r="J2" s="11">
         <v>0.72</v>
       </c>
-      <c r="M2" s="7"/>
+      <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="12">
         <v>0.79</v>
       </c>
-      <c r="E3">
-        <v>0.98</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F3" s="11">
         <v>0.93</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="J3">
+      <c r="H3" s="15"/>
+      <c r="J3" s="11">
         <v>0.72</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>481</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="14">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>0.98</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F4" s="11">
         <v>0.92</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="11">
         <v>0.75</v>
       </c>
-      <c r="M4" s="12"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="12">
         <v>0.89</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
+      <c r="E5" s="11">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11">
         <v>0.77</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="M5" s="7"/>
+      <c r="H5" s="15"/>
+      <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="12">
         <v>0.87</v>
       </c>
-      <c r="E6">
-        <v>0.98</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F6" s="11">
         <v>0.89</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="11">
         <v>0.68</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="M6" s="4"/>
+      <c r="H6" s="15"/>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="12">
         <v>0.92</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="11">
         <v>0</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="11">
         <v>0.94</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="11">
         <v>0.81</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="12">
         <v>0.88</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="11">
         <v>0.93</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="11">
         <v>0.95</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="11">
         <v>0.6</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="M8" s="4"/>
+      <c r="H8" s="15"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="12">
         <v>0.79</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
         <v>0.51</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="M9" s="4"/>
+      <c r="H9" s="15"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="12">
         <v>0.7</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
+      <c r="E10" s="11">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11">
         <v>0.53</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="M10" s="4"/>
+      <c r="H10" s="15"/>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="12">
         <v>0.76</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="11">
         <v>0.93</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="11">
         <v>0.89</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="11">
         <v>0.66</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="M11" s="4"/>
+      <c r="H11" s="15"/>
+      <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="12">
         <v>0.88</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0.98</v>
-      </c>
-      <c r="G12">
+      <c r="E12" s="11">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G12" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="M12" s="4"/>
+      <c r="H12" s="15"/>
+      <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="12">
         <v>0.75</v>
       </c>
-      <c r="E13">
-        <v>0.98</v>
-      </c>
-      <c r="F13">
+      <c r="E13" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F13" s="11">
         <v>0</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="11">
         <v>0.9</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="M13" s="4"/>
+      <c r="H13" s="15"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="12">
         <v>0.8</v>
       </c>
-      <c r="E14">
-        <v>0.98</v>
-      </c>
-      <c r="F14">
+      <c r="E14" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F14" s="11">
         <v>0.95</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="11">
         <v>0.51</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="M14" s="4"/>
+      <c r="H14" s="15"/>
+      <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="12">
         <v>0.92</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="11">
         <v>0.95</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="11">
         <v>0.93</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="M15" s="4"/>
+      <c r="H15" s="15"/>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="12">
         <v>0.84</v>
       </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
         <v>0.69</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="11">
         <v>0.52</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="M16" s="4"/>
+      <c r="H16" s="15"/>
+      <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="12">
         <v>0.8</v>
       </c>
-      <c r="E17">
-        <v>0.98</v>
-      </c>
-      <c r="F17">
+      <c r="E17" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F17" s="11">
         <v>0.94</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="11">
         <v>0.47</v>
       </c>
-      <c r="H17" s="3"/>
-      <c r="M17" s="4"/>
+      <c r="H17" s="15"/>
+      <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="12">
         <v>0.7</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="11">
         <v>0.95</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="11">
         <v>0.95</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="11">
         <v>0.65</v>
       </c>
-      <c r="M18" s="4"/>
+      <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="12">
         <v>0.74</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="11">
         <v>0.93</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="11">
         <v>0.95</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="11">
         <v>0.73</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="M19" s="4"/>
+      <c r="H19" s="15"/>
+      <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="12">
         <v>0.86</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="11">
         <v>0.95</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="11">
         <v>0.88</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="11">
         <v>0.62</v>
       </c>
-      <c r="M20" s="4"/>
+      <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="12">
         <v>0.93</v>
       </c>
-      <c r="E21">
-        <v>0.98</v>
-      </c>
-      <c r="F21">
-        <v>0.98</v>
-      </c>
-      <c r="G21">
+      <c r="E21" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G21" s="11">
         <v>0.66</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="M21" s="4"/>
+      <c r="H21" s="15"/>
+      <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="12">
         <v>0.92</v>
       </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
+      <c r="E22" s="11">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11">
         <v>0.88</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="11">
         <v>0.82</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="M22" s="4"/>
+      <c r="H22" s="15"/>
+      <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>483</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="14">
         <v>0</v>
       </c>
-      <c r="E23">
-        <v>0.98</v>
-      </c>
-      <c r="F23">
+      <c r="E23" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F23" s="11">
         <v>0.9</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="11">
         <v>0.38</v>
       </c>
-      <c r="M23" s="10"/>
+      <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="12">
         <v>0.89</v>
       </c>
-      <c r="E24">
-        <v>0.98</v>
-      </c>
-      <c r="F24">
-        <v>0.98</v>
-      </c>
-      <c r="G24">
+      <c r="E24" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G24" s="11">
         <v>0.74</v>
       </c>
-      <c r="M24" s="4"/>
+      <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="12">
         <v>0.85</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="11">
         <v>0.93</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="11">
         <v>0.86</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="11">
         <v>0.61</v>
       </c>
-      <c r="H25" s="3"/>
-      <c r="M25" s="4"/>
+      <c r="H25" s="15"/>
+      <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="12">
         <v>0.81</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
+      <c r="E26" s="11">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11">
         <v>0.92</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="11">
         <v>0.4</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="M26" s="4"/>
+      <c r="H26" s="15"/>
+      <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="12">
         <v>0.82</v>
       </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
+      <c r="E27" s="11">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11">
+        <v>1</v>
+      </c>
+      <c r="G27" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H27" s="3"/>
-      <c r="M27" s="4"/>
+      <c r="H27" s="15"/>
+      <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="12">
         <v>0.9</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28">
+      <c r="E28" s="11">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11">
         <v>0.93</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="11">
         <v>0.78</v>
       </c>
-      <c r="M28" s="4"/>
+      <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="12">
         <v>0.9</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="11">
         <v>0.7</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="11">
         <v>0.95</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="11">
         <v>0.34</v>
       </c>
-      <c r="H29" s="3"/>
-      <c r="M29" s="8"/>
+      <c r="H29" s="15"/>
+      <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="12">
         <v>0.96</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="11">
         <v>0.86</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="11">
         <v>0.87</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H30" s="3"/>
-      <c r="M30" s="4"/>
+      <c r="H30" s="15"/>
+      <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="12">
         <v>0.77</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="11">
         <v>0.93</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="11">
         <v>0</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="11">
         <v>0.73</v>
       </c>
-      <c r="M31" s="4"/>
+      <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="12">
         <v>0.81</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="11">
         <v>0.93</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="11">
         <v>0.8</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="11">
         <v>0.4</v>
       </c>
-      <c r="H32" s="3"/>
-      <c r="M32" s="4"/>
+      <c r="H32" s="15"/>
+      <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="12">
         <v>0.91</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="11">
         <v>0.81</v>
       </c>
-      <c r="F33">
-        <v>0.98</v>
-      </c>
-      <c r="G33">
+      <c r="F33" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G33" s="11">
         <v>0.7</v>
       </c>
-      <c r="H33" s="3"/>
-      <c r="M33" s="4"/>
+      <c r="H33" s="15"/>
+      <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="12">
         <v>0.95</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="11">
         <v>0.77</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="11">
         <v>0.77</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="11">
         <v>0.78</v>
       </c>
-      <c r="M34" s="4"/>
+      <c r="M34" s="2"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="12">
         <v>0.84</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="11">
         <v>0.91</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="11">
         <v>0.93</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="11">
         <v>0</v>
       </c>
-      <c r="H35" s="3"/>
-      <c r="M35" s="8"/>
+      <c r="H35" s="15"/>
+      <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="12">
         <v>0.88</v>
       </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36">
+      <c r="E36" s="11">
+        <v>1</v>
+      </c>
+      <c r="F36" s="11">
         <v>0.89</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="11">
         <v>0.27</v>
       </c>
-      <c r="H36" s="3"/>
-      <c r="M36" s="4"/>
+      <c r="H36" s="15"/>
+      <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="11">
         <v>0.93</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="11">
         <v>0.88</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M37" s="4"/>
+      <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="12">
         <v>0.85</v>
       </c>
-      <c r="E38">
-        <v>0.98</v>
-      </c>
-      <c r="F38">
+      <c r="E38" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F38" s="11">
         <v>0.89</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="11">
         <v>0.65</v>
       </c>
-      <c r="H38" s="3"/>
-      <c r="J38">
+      <c r="H38" s="15"/>
+      <c r="J38" s="11">
         <v>0.7</v>
       </c>
-      <c r="M38" s="4"/>
+      <c r="M38" s="2"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="12">
         <v>0.95</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="11">
         <v>0.93</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="11">
         <v>0</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="11">
         <v>0.75</v>
       </c>
-      <c r="M39" s="4"/>
+      <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="12">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E40">
-        <v>0.98</v>
-      </c>
-      <c r="F40">
+      <c r="E40" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F40" s="11">
         <v>0.88</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="11">
         <v>0.48</v>
       </c>
-      <c r="H40" s="3"/>
-      <c r="M40" s="4"/>
+      <c r="H40" s="15"/>
+      <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="12">
         <v>0.86</v>
       </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
+      <c r="E41" s="11">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11">
         <v>0</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H41" s="3"/>
-      <c r="J41">
+      <c r="H41" s="15"/>
+      <c r="J41" s="11">
         <v>0.7</v>
       </c>
-      <c r="M41" s="4"/>
+      <c r="M41" s="2"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="12">
         <v>0.78</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
+      <c r="E42" s="11">
+        <v>1</v>
+      </c>
+      <c r="F42" s="11">
         <v>0.92</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H42" s="3"/>
-      <c r="M42" s="4"/>
+      <c r="H42" s="15"/>
+      <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="12">
         <v>0.93</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
+      <c r="E43" s="11">
+        <v>1</v>
+      </c>
+      <c r="F43" s="11">
+        <v>1</v>
+      </c>
+      <c r="G43" s="11">
         <v>0.92</v>
       </c>
-      <c r="H43" s="3"/>
-      <c r="J43">
+      <c r="H43" s="15"/>
+      <c r="J43" s="11">
         <v>0.84</v>
       </c>
-      <c r="M43" s="4"/>
+      <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="12">
         <v>0.92</v>
       </c>
-      <c r="E44">
-        <v>0.98</v>
-      </c>
-      <c r="F44">
+      <c r="E44" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F44" s="11">
         <v>0</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="11">
         <v>0.77</v>
       </c>
-      <c r="M44" s="4"/>
+      <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="12">
         <v>0.93</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="11">
         <v>0.79</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="11">
         <v>0.86</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="11">
         <v>0</v>
       </c>
-      <c r="H45" s="3"/>
-      <c r="M45" s="8"/>
+      <c r="H45" s="15"/>
+      <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="12">
         <v>0.8</v>
       </c>
-      <c r="E46">
-        <v>0.98</v>
-      </c>
-      <c r="F46">
-        <v>0.98</v>
-      </c>
-      <c r="G46">
+      <c r="E46" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F46" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G46" s="11">
         <v>0.66</v>
       </c>
-      <c r="H46" s="3"/>
-      <c r="M46" s="8"/>
+      <c r="H46" s="15"/>
+      <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="12">
         <v>0.93</v>
       </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="F47">
+      <c r="E47" s="11">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11">
         <v>0.95</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="11">
         <v>0.83</v>
       </c>
-      <c r="H47" s="3"/>
-      <c r="M47" s="4"/>
+      <c r="H47" s="15"/>
+      <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="12">
         <v>0.79</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="11">
         <v>0.93</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-      <c r="G48">
+      <c r="F48" s="11">
+        <v>1</v>
+      </c>
+      <c r="G48" s="11">
         <v>0.18</v>
       </c>
-      <c r="H48" s="3"/>
-      <c r="M48" s="4"/>
+      <c r="H48" s="15"/>
+      <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="12">
         <v>0.89</v>
       </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
+      <c r="E49" s="11">
+        <v>1</v>
+      </c>
+      <c r="F49" s="11">
+        <v>1</v>
+      </c>
+      <c r="G49" s="11">
         <v>0.18</v>
       </c>
-      <c r="H49" s="3"/>
-      <c r="M49" s="4"/>
+      <c r="H49" s="15"/>
+      <c r="M49" s="2"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="12">
         <v>0.79</v>
       </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>0.98</v>
-      </c>
-      <c r="G50">
+      <c r="E50" s="11">
+        <v>1</v>
+      </c>
+      <c r="F50" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G50" s="11">
         <v>0.52</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="11">
         <v>0.84</v>
       </c>
-      <c r="M50" s="4"/>
+      <c r="M50" s="2"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="12">
         <v>0.78</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="11">
         <v>0.95</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="11">
         <v>0.88</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="11">
         <v>0.53</v>
       </c>
-      <c r="M51" s="4"/>
+      <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="12">
         <v>0.81</v>
       </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52">
-        <v>0.98</v>
-      </c>
-      <c r="G52">
+      <c r="E52" s="11">
+        <v>1</v>
+      </c>
+      <c r="F52" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G52" s="11">
         <v>0.62</v>
       </c>
-      <c r="M52" s="4"/>
+      <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="12">
         <v>0.9</v>
       </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
-        <v>0.98</v>
-      </c>
-      <c r="G53">
+      <c r="E53" s="11">
+        <v>1</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G53" s="11">
         <v>0.36</v>
       </c>
-      <c r="H53" s="3"/>
-      <c r="M53" s="4"/>
+      <c r="H53" s="15"/>
+      <c r="M53" s="2"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="12">
         <v>0.86</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="11">
         <v>0.95</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="11">
         <v>0.94</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="11">
         <v>0.65</v>
       </c>
-      <c r="H54" s="3"/>
-      <c r="M54" s="4"/>
+      <c r="H54" s="15"/>
+      <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="12">
         <v>0.86</v>
       </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
+      <c r="E55" s="11">
+        <v>1</v>
+      </c>
+      <c r="F55" s="11">
         <v>0</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="11">
         <v>0.68</v>
       </c>
-      <c r="H55" s="3"/>
-      <c r="M55" s="4"/>
+      <c r="H55" s="15"/>
+      <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="12">
         <v>0.96</v>
       </c>
-      <c r="E56">
-        <v>0.98</v>
-      </c>
-      <c r="F56">
+      <c r="E56" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F56" s="11">
         <v>0</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="11">
         <v>0.68</v>
       </c>
-      <c r="M56" s="4"/>
+      <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="12">
         <v>0.88</v>
       </c>
-      <c r="E57">
-        <v>0.98</v>
-      </c>
-      <c r="F57">
-        <v>0.98</v>
-      </c>
-      <c r="G57">
+      <c r="E57" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F57" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G57" s="11">
         <v>0.65</v>
       </c>
-      <c r="H57" s="3"/>
-      <c r="J57">
+      <c r="H57" s="15"/>
+      <c r="J57" s="11">
         <v>0.72</v>
       </c>
-      <c r="M57" s="4"/>
+      <c r="M57" s="2"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="13">
         <v>0</v>
       </c>
-      <c r="E58">
-        <v>0.98</v>
-      </c>
-      <c r="F58">
+      <c r="E58" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F58" s="11">
         <v>0.84</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="11">
         <v>0.34</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="11">
         <v>0.84</v>
       </c>
-      <c r="M58" s="4"/>
+      <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="12">
         <v>0.87</v>
       </c>
-      <c r="E59">
-        <v>0.98</v>
-      </c>
-      <c r="F59">
+      <c r="E59" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F59" s="11">
         <v>0.95</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="11">
         <v>0.53</v>
       </c>
-      <c r="H59" s="3"/>
-      <c r="M59" s="4"/>
+      <c r="H59" s="15"/>
+      <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="12">
         <v>0.82</v>
       </c>
-      <c r="E60">
-        <v>0.98</v>
-      </c>
-      <c r="F60">
+      <c r="E60" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F60" s="11">
         <v>0.95</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="11">
         <v>0.78</v>
       </c>
-      <c r="M60" s="4"/>
+      <c r="M60" s="2"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="12">
         <v>0.9</v>
       </c>
-      <c r="E61">
-        <v>0.98</v>
-      </c>
-      <c r="F61">
+      <c r="E61" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F61" s="11">
         <v>0.92</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H61" s="3"/>
-      <c r="J61">
+      <c r="H61" s="15"/>
+      <c r="J61" s="11">
         <v>0.7</v>
       </c>
-      <c r="M61" s="4"/>
+      <c r="M61" s="2"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="12">
         <v>0.86</v>
       </c>
-      <c r="E62">
-        <v>0.98</v>
-      </c>
-      <c r="F62">
-        <v>0.98</v>
-      </c>
-      <c r="G62">
+      <c r="E62" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F62" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G62" s="11">
         <v>0.78</v>
       </c>
-      <c r="H62" s="3"/>
-      <c r="M62" s="4"/>
+      <c r="H62" s="15"/>
+      <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="12">
         <v>0.96</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="11">
         <v>0.95</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="11">
         <v>0.94</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="11">
         <v>0.69</v>
       </c>
-      <c r="H63" s="3"/>
-      <c r="M63" s="4"/>
+      <c r="H63" s="15"/>
+      <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="12">
         <v>0.78</v>
       </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
+      <c r="E64" s="11">
+        <v>1</v>
+      </c>
+      <c r="F64" s="11">
         <v>0</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M64" s="4"/>
+      <c r="M64" s="2"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="12">
         <v>0.95</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="11">
         <v>0.95</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="11">
         <v>0.92</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="11">
         <v>0.6</v>
       </c>
-      <c r="H65" s="3"/>
-      <c r="M65" s="4"/>
+      <c r="H65" s="15"/>
+      <c r="M65" s="2"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="12">
         <v>0.9</v>
       </c>
-      <c r="E66">
-        <v>0.98</v>
-      </c>
-      <c r="F66">
-        <v>0.98</v>
-      </c>
-      <c r="G66">
+      <c r="E66" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F66" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G66" s="11">
         <v>0.49</v>
       </c>
-      <c r="M66" s="4"/>
+      <c r="M66" s="2"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="12">
         <v>0.75</v>
       </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>0.98</v>
-      </c>
-      <c r="G67">
+      <c r="E67" s="11">
+        <v>1</v>
+      </c>
+      <c r="F67" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G67" s="11">
         <v>0.7</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="11">
         <v>0.78</v>
       </c>
-      <c r="M67" s="4"/>
+      <c r="M67" s="2"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="12">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E68">
-        <v>0.98</v>
-      </c>
-      <c r="F68">
+      <c r="E68" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F68" s="11">
         <v>0.89</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="11">
         <v>0.62</v>
       </c>
-      <c r="M68" s="4"/>
+      <c r="M68" s="2"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="12">
         <v>0.75</v>
       </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69">
+      <c r="E69" s="11">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11">
         <v>0</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H69" s="3"/>
-      <c r="J69">
+      <c r="H69" s="15"/>
+      <c r="J69" s="11">
         <v>0.72</v>
       </c>
-      <c r="M69" s="4"/>
+      <c r="M69" s="2"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="12">
         <v>0.77</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="11">
         <v>0.88</v>
       </c>
-      <c r="F70">
-        <v>0.98</v>
-      </c>
-      <c r="G70">
+      <c r="F70" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G70" s="11">
         <v>0.68</v>
       </c>
-      <c r="H70" s="3"/>
-      <c r="J70">
+      <c r="H70" s="15"/>
+      <c r="J70" s="11">
         <v>0.72</v>
       </c>
-      <c r="M70" s="4"/>
+      <c r="M70" s="2"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="12">
         <v>0.88</v>
       </c>
-      <c r="E71">
-        <v>0.98</v>
-      </c>
-      <c r="F71">
-        <v>0.98</v>
-      </c>
-      <c r="G71">
+      <c r="E71" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F71" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G71" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H71" s="3"/>
-      <c r="J71">
+      <c r="H71" s="15"/>
+      <c r="J71" s="11">
         <v>0.78</v>
       </c>
-      <c r="M71" s="4"/>
+      <c r="M71" s="2"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="12">
         <v>0.86</v>
       </c>
-      <c r="E72">
-        <v>0.98</v>
-      </c>
-      <c r="F72">
+      <c r="E72" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F72" s="11">
         <v>0</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="11">
         <v>0</v>
       </c>
-      <c r="H72" s="3"/>
-      <c r="J72">
+      <c r="H72" s="15"/>
+      <c r="J72" s="11">
         <v>0.73</v>
       </c>
-      <c r="M72" s="4"/>
+      <c r="M72" s="2"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="12">
         <v>0.88</v>
       </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73">
+      <c r="E73" s="11">
+        <v>1</v>
+      </c>
+      <c r="F73" s="11">
         <v>0.82</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="11">
         <v>0.66</v>
       </c>
-      <c r="M73" s="4"/>
+      <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="12">
         <v>0.79</v>
       </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74">
+      <c r="E74" s="11">
+        <v>1</v>
+      </c>
+      <c r="F74" s="11">
         <v>0.92</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="11">
         <v>0.48</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="11">
         <v>0.7</v>
       </c>
-      <c r="M74" s="4"/>
+      <c r="M74" s="2"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D75" s="6">
+      <c r="D75" s="12">
         <v>0.88</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="11">
         <v>0.95</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="11">
         <v>0</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="11">
         <v>0.62</v>
       </c>
-      <c r="J75">
+      <c r="J75" s="11">
         <v>0.78</v>
       </c>
-      <c r="M75" s="4"/>
+      <c r="M75" s="2"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D76" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E76">
+      <c r="D76" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E76" s="11">
         <v>0.95</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="11">
         <v>0.9</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="11">
         <v>0.79</v>
       </c>
-      <c r="H76" s="3"/>
-      <c r="M76" s="4"/>
+      <c r="H76" s="15"/>
+      <c r="M76" s="2"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D77" s="6">
+      <c r="D77" s="12">
         <v>0.93</v>
       </c>
-      <c r="E77">
-        <v>1</v>
-      </c>
-      <c r="G77">
+      <c r="E77" s="11">
+        <v>1</v>
+      </c>
+      <c r="F77" s="11">
+        <v>1</v>
+      </c>
+      <c r="G77" s="11">
         <v>0.61</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="11">
         <v>0.78</v>
       </c>
-      <c r="M77" s="4"/>
+      <c r="M77" s="2"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D78" s="6">
+      <c r="D78" s="12">
         <v>0.73</v>
       </c>
-      <c r="E78">
-        <v>1</v>
-      </c>
-      <c r="G78">
+      <c r="E78" s="11">
+        <v>1</v>
+      </c>
+      <c r="F78" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G78" s="11">
         <v>0.48</v>
       </c>
-      <c r="M78" s="4"/>
+      <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="6">
+      <c r="D79" s="12">
         <v>0.91</v>
       </c>
-      <c r="E79">
-        <v>0.98</v>
-      </c>
-      <c r="G79">
+      <c r="E79" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F79" s="11">
+        <v>1</v>
+      </c>
+      <c r="G79" s="11">
         <v>0.52</v>
       </c>
-      <c r="M79" s="4"/>
+      <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D80" s="6">
+      <c r="D80" s="12">
         <v>0.88</v>
       </c>
-      <c r="E80">
-        <v>1</v>
-      </c>
-      <c r="G80">
+      <c r="E80" s="11">
+        <v>1</v>
+      </c>
+      <c r="F80" s="11">
+        <v>0</v>
+      </c>
+      <c r="G80" s="11">
         <v>0.68</v>
       </c>
-      <c r="M80" s="4"/>
+      <c r="M80" s="2"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
         <v>497</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="14">
         <v>0</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="11">
         <v>0</v>
       </c>
-      <c r="G81">
+      <c r="F81" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G81" s="11">
         <v>0.6</v>
       </c>
-      <c r="M81" s="10"/>
+      <c r="M81" s="8"/>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="13">
         <v>0</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="11">
         <v>0.77</v>
       </c>
-      <c r="G82">
+      <c r="F82" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="G82" s="11">
         <v>0</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="11">
         <v>0.78</v>
       </c>
-      <c r="M82" s="4"/>
+      <c r="M82" s="2"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="12">
         <v>0.85</v>
       </c>
-      <c r="E83">
-        <v>0.98</v>
-      </c>
-      <c r="G83">
+      <c r="E83" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F83" s="11">
+        <v>0.86</v>
+      </c>
+      <c r="G83" s="11">
         <v>0.78</v>
       </c>
-      <c r="M83" s="4"/>
+      <c r="M83" s="2"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
         <v>499</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="14">
         <v>0</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="11">
         <v>0</v>
       </c>
-      <c r="G84">
+      <c r="F84" s="11">
+        <v>0</v>
+      </c>
+      <c r="G84" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M84" s="10"/>
+      <c r="M84" s="8"/>
     </row>
     <row r="85" spans="1:13">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="12">
         <v>0.96</v>
       </c>
-      <c r="E85">
-        <v>0.98</v>
-      </c>
-      <c r="G85">
+      <c r="E85" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F85" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G85" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M85" s="4"/>
+      <c r="M85" s="2"/>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="12">
         <v>0.82</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="G86">
+      <c r="E86" s="11">
+        <v>1</v>
+      </c>
+      <c r="F86" s="11">
+        <v>0.78</v>
+      </c>
+      <c r="G86" s="11">
         <v>0.42</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="11">
         <v>0.78</v>
       </c>
-      <c r="M86" s="4"/>
+      <c r="M86" s="2"/>
     </row>
     <row r="87" spans="1:13">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="12">
         <v>0.84</v>
       </c>
-      <c r="E87">
-        <v>0.98</v>
-      </c>
-      <c r="G87">
+      <c r="E87" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F87" s="11">
+        <v>0</v>
+      </c>
+      <c r="G87" s="11">
         <v>0.51</v>
       </c>
-      <c r="M87" s="4"/>
+      <c r="M87" s="2"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
         <v>462</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="14">
         <v>0</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="11">
         <v>0.95</v>
       </c>
-      <c r="G88">
+      <c r="F88" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="G88" s="11">
         <v>0.53</v>
       </c>
-      <c r="M88" s="10"/>
+      <c r="M88" s="8"/>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="12">
         <v>0.88</v>
       </c>
-      <c r="E89">
-        <v>0.98</v>
-      </c>
-      <c r="G89">
+      <c r="E89" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F89" s="11">
+        <v>1</v>
+      </c>
+      <c r="G89" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M89" s="4"/>
+      <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="12">
         <v>0.53</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="11">
         <v>0.95</v>
       </c>
-      <c r="G90">
+      <c r="F90" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="G90" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M90" s="4"/>
+      <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="12">
         <v>0.78</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="11">
         <v>0.95</v>
       </c>
-      <c r="G91">
+      <c r="F91" s="11">
+        <v>1</v>
+      </c>
+      <c r="G91" s="11">
         <v>0.62</v>
       </c>
-      <c r="M91" s="4"/>
+      <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D92" s="12">
         <v>0.91</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="11">
         <v>0.93</v>
       </c>
-      <c r="G92">
+      <c r="F92" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="G92" s="11">
         <v>0.61</v>
       </c>
-      <c r="M92" s="4"/>
+      <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="12">
         <v>0.81</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="11">
         <v>0</v>
       </c>
-      <c r="G93">
+      <c r="F93" s="11">
         <v>0</v>
       </c>
-      <c r="M93" s="4"/>
+      <c r="G93" s="11">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="12">
         <v>0.8</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="11">
         <v>0.93</v>
       </c>
-      <c r="G94">
+      <c r="F94" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G94" s="11">
         <v>0.65</v>
       </c>
-      <c r="M94" s="4"/>
+      <c r="M94" s="2"/>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C95" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="12">
         <v>0.78</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="11">
         <v>0.51</v>
       </c>
-      <c r="G95">
+      <c r="F95" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G95" s="11">
         <v>0.52</v>
       </c>
-      <c r="M95" s="4"/>
+      <c r="M95" s="2"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
         <v>501</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="14">
         <v>0</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="11">
         <v>0</v>
       </c>
-      <c r="G96">
+      <c r="F96" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G96" s="11">
         <v>0.69</v>
       </c>
-      <c r="M96" s="10"/>
+      <c r="M96" s="8"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
         <v>503</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="14">
         <v>0</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="11">
         <v>0</v>
       </c>
-      <c r="G97">
+      <c r="F97" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="G97" s="11">
         <v>0.71</v>
       </c>
-      <c r="M97" s="10"/>
+      <c r="M97" s="8"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="12">
         <v>0.85</v>
       </c>
-      <c r="E98">
-        <v>0.98</v>
-      </c>
-      <c r="G98">
+      <c r="E98" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F98" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G98" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M98" s="4"/>
+      <c r="M98" s="2"/>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="12">
         <v>0.8</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="11">
         <v>0.74</v>
       </c>
-      <c r="G99">
+      <c r="F99" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G99" s="11">
         <v>0.77</v>
       </c>
-      <c r="M99" s="4"/>
+      <c r="M99" s="2"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="12">
         <v>0.92</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="11">
         <v>0.95</v>
       </c>
-      <c r="G100">
+      <c r="F100" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G100" s="11">
         <v>0.73</v>
       </c>
-      <c r="M100" s="4"/>
+      <c r="M100" s="2"/>
     </row>
     <row r="101" spans="1:13">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="12">
         <v>0.78</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="11">
         <v>0.93</v>
       </c>
-      <c r="G101">
+      <c r="F101" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="G101" s="11">
         <v>0.52</v>
       </c>
-      <c r="M101" s="4"/>
+      <c r="M101" s="2"/>
     </row>
     <row r="102" spans="1:13">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D102" s="6">
+      <c r="D102" s="12">
         <v>0.73</v>
       </c>
-      <c r="E102">
-        <v>1</v>
-      </c>
-      <c r="G102">
+      <c r="E102" s="11">
+        <v>1</v>
+      </c>
+      <c r="F102" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="G102" s="11">
         <v>0.65</v>
       </c>
-      <c r="M102" s="4"/>
+      <c r="M102" s="2"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
         <v>485</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="14">
         <v>0</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="11">
         <v>0.86</v>
       </c>
-      <c r="G103">
+      <c r="F103" s="11">
+        <v>1</v>
+      </c>
+      <c r="G103" s="11">
         <v>0.6</v>
       </c>
-      <c r="M103" s="10"/>
+      <c r="M103" s="8"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D104" s="12">
         <v>0.93</v>
       </c>
-      <c r="E104">
-        <v>1</v>
-      </c>
-      <c r="G104">
+      <c r="E104" s="11">
+        <v>1</v>
+      </c>
+      <c r="F104" s="11">
+        <v>1</v>
+      </c>
+      <c r="G104" s="11">
         <v>0.64</v>
       </c>
-      <c r="J104">
+      <c r="J104" s="11">
         <v>0.78</v>
       </c>
-      <c r="M104" s="4"/>
+      <c r="M104" s="2"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
         <v>487</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="14">
         <v>0</v>
       </c>
-      <c r="E105">
-        <v>1</v>
-      </c>
-      <c r="G105">
+      <c r="E105" s="11">
+        <v>1</v>
+      </c>
+      <c r="F105" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="G105" s="11">
         <v>0.85</v>
       </c>
-      <c r="M105" s="10"/>
+      <c r="M105" s="8"/>
     </row>
     <row r="106" spans="1:13">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D106" s="6">
+      <c r="D106" s="12">
         <v>0.92</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="11">
         <v>0.91</v>
       </c>
-      <c r="G106">
+      <c r="F106" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="G106" s="11">
         <v>0</v>
       </c>
-      <c r="M106" s="4"/>
+      <c r="M106" s="2"/>
     </row>
     <row r="107" spans="1:13">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D107" s="6">
+      <c r="D107" s="12">
         <v>0.69</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="11">
         <v>0.93</v>
       </c>
-      <c r="G107">
+      <c r="F107" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G107" s="11">
         <v>0.53</v>
       </c>
-      <c r="M107" s="4"/>
+      <c r="M107" s="2"/>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D108" s="6">
+      <c r="D108" s="12">
         <v>0.74</v>
       </c>
-      <c r="E108">
-        <v>1</v>
-      </c>
-      <c r="G108">
+      <c r="E108" s="11">
+        <v>1</v>
+      </c>
+      <c r="F108" s="11">
+        <v>1</v>
+      </c>
+      <c r="G108" s="11">
         <v>0.64</v>
       </c>
-      <c r="M108" s="4"/>
+      <c r="M108" s="2"/>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D109" s="6">
+      <c r="D109" s="12">
         <v>0.81</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="11">
         <v>0.86</v>
       </c>
-      <c r="G109">
+      <c r="F109" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="G109" s="11">
         <v>0.51</v>
       </c>
-      <c r="M109" s="4"/>
+      <c r="M109" s="2"/>
     </row>
     <row r="110" spans="1:13">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D110" s="6">
+      <c r="D110" s="12">
         <v>0.74</v>
       </c>
-      <c r="E110">
-        <v>1</v>
-      </c>
-      <c r="G110">
+      <c r="E110" s="11">
+        <v>1</v>
+      </c>
+      <c r="F110" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="G110" s="11">
         <v>0.61</v>
       </c>
-      <c r="J110">
+      <c r="J110" s="11">
         <v>0.86</v>
       </c>
-      <c r="M110" s="4"/>
+      <c r="M110" s="2"/>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D111" s="6">
+      <c r="D111" s="12">
         <v>0.63</v>
       </c>
-      <c r="E111">
-        <v>0.98</v>
-      </c>
-      <c r="G111">
+      <c r="E111" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F111" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="G111" s="11">
         <v>0.36</v>
       </c>
-      <c r="M111" s="4"/>
+      <c r="M111" s="2"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
         <v>489</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="14">
         <v>0</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="11">
         <v>0.95</v>
       </c>
-      <c r="G112">
+      <c r="F112" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="G112" s="11">
         <v>0.66</v>
       </c>
-      <c r="M112" s="10"/>
+      <c r="M112" s="8"/>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D113" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E113">
-        <v>1</v>
-      </c>
-      <c r="G113">
+      <c r="D113" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E113" s="11">
+        <v>1</v>
+      </c>
+      <c r="F113" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G113" s="11">
         <v>0.68</v>
       </c>
-      <c r="M113" s="4"/>
+      <c r="M113" s="2"/>
     </row>
     <row r="114" spans="1:13">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D114" s="6">
+      <c r="D114" s="12">
         <v>0.73</v>
       </c>
-      <c r="E114">
-        <v>1</v>
-      </c>
-      <c r="G114">
+      <c r="E114" s="11">
+        <v>1</v>
+      </c>
+      <c r="F114" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G114" s="11">
         <v>0.82</v>
       </c>
-      <c r="M114" s="4"/>
+      <c r="M114" s="2"/>
     </row>
     <row r="115" spans="1:13">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C115" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D115" s="6">
+      <c r="D115" s="12">
         <v>0.91</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="11">
         <v>0.91</v>
       </c>
-      <c r="G115">
+      <c r="F115" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G115" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M115" s="4"/>
+      <c r="M115" s="2"/>
     </row>
     <row r="116" spans="1:13">
-      <c r="A116" s="5" t="s">
+      <c r="A116" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C116" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D116" s="13">
         <v>0</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="11">
         <v>0.91</v>
       </c>
-      <c r="G116">
+      <c r="F116" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="G116" s="11">
         <v>0.6</v>
       </c>
-      <c r="J116">
+      <c r="J116" s="11">
         <v>0.86</v>
       </c>
-      <c r="M116" s="4"/>
+      <c r="M116" s="2"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="6" t="s">
+      <c r="C117" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D117" s="12">
         <v>0.86</v>
       </c>
-      <c r="E117">
-        <v>0.98</v>
-      </c>
-      <c r="G117">
+      <c r="E117" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F117" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G117" s="11">
         <v>0.52</v>
       </c>
-      <c r="M117" s="4"/>
+      <c r="M117" s="2"/>
     </row>
     <row r="118" spans="1:13">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D118" s="6">
+      <c r="D118" s="12">
         <v>0.86</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="11">
         <v>0.95</v>
       </c>
-      <c r="G118">
+      <c r="F118" s="11">
+        <v>0.86</v>
+      </c>
+      <c r="G118" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M118" s="4"/>
+      <c r="M118" s="2"/>
     </row>
     <row r="119" spans="1:13">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D119" s="6">
+      <c r="D119" s="12">
         <v>0.87</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="11">
         <v>0.86</v>
       </c>
-      <c r="G119">
+      <c r="F119" s="11">
+        <v>1</v>
+      </c>
+      <c r="G119" s="11">
         <v>0.39</v>
       </c>
-      <c r="M119" s="4"/>
+      <c r="M119" s="2"/>
     </row>
     <row r="120" spans="1:13">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B120" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C120" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D120" s="6">
+      <c r="D120" s="12">
         <v>0.89</v>
       </c>
-      <c r="E120">
-        <v>1</v>
-      </c>
-      <c r="G120">
+      <c r="E120" s="11">
+        <v>1</v>
+      </c>
+      <c r="F120" s="11">
+        <v>0.92</v>
+      </c>
+      <c r="G120" s="11">
         <v>0.71</v>
       </c>
-      <c r="M120" s="4"/>
+      <c r="M120" s="2"/>
     </row>
     <row r="121" spans="1:13">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D121" s="6">
+      <c r="D121" s="12">
         <v>0.86</v>
       </c>
-      <c r="E121">
-        <v>0.98</v>
-      </c>
-      <c r="G121">
+      <c r="E121" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F121" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="G121" s="11">
         <v>0.36</v>
       </c>
-      <c r="J121">
+      <c r="J121" s="11">
         <v>0.86</v>
       </c>
-      <c r="M121" s="4"/>
+      <c r="M121" s="2"/>
     </row>
     <row r="122" spans="1:13">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B122" s="6" t="s">
+      <c r="B122" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D122" s="12">
         <v>0.88</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="11">
         <v>0.93</v>
       </c>
-      <c r="G122">
+      <c r="F122" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="G122" s="11">
         <v>0.42</v>
       </c>
-      <c r="J122">
+      <c r="J122" s="11">
         <v>0.78</v>
       </c>
-      <c r="M122" s="4"/>
+      <c r="M122" s="2"/>
     </row>
     <row r="123" spans="1:13">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B123" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C123" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D123" s="12">
         <v>0.75</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="11">
         <v>0.93</v>
       </c>
-      <c r="G123">
+      <c r="F123" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G123" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M123" s="4"/>
+      <c r="M123" s="2"/>
     </row>
     <row r="124" spans="1:13">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B124" s="6" t="s">
+      <c r="B124" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D124" s="12">
         <v>0.96</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="11">
         <v>0</v>
       </c>
-      <c r="G124">
+      <c r="F124" s="11">
         <v>0</v>
       </c>
-      <c r="M124" s="4"/>
+      <c r="G124" s="11">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2"/>
     </row>
     <row r="125" spans="1:13">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B125" s="6" t="s">
+      <c r="B125" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C125" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="12">
         <v>0.91</v>
       </c>
-      <c r="E125">
-        <v>1</v>
-      </c>
-      <c r="G125">
+      <c r="E125" s="11">
+        <v>1</v>
+      </c>
+      <c r="F125" s="11">
+        <v>1</v>
+      </c>
+      <c r="G125" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M125" s="4"/>
+      <c r="M125" s="2"/>
     </row>
     <row r="126" spans="1:13">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B126" s="6" t="s">
+      <c r="B126" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="12">
         <v>0.73</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="11">
         <v>0.95</v>
       </c>
-      <c r="G126">
+      <c r="F126" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G126" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M126" s="4"/>
+      <c r="M126" s="2"/>
     </row>
     <row r="127" spans="1:13">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C127" s="5" t="s">
+      <c r="C127" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="13">
         <v>0</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="11">
         <v>0.88</v>
       </c>
-      <c r="G127">
+      <c r="F127" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G127" s="11">
         <v>0.79</v>
       </c>
-      <c r="J127">
+      <c r="J127" s="11">
         <v>0.86</v>
       </c>
-      <c r="M127" s="4"/>
+      <c r="M127" s="2"/>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B128" s="6" t="s">
+      <c r="B128" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="C128" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D128" s="12">
         <v>0.69</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="11">
         <v>0.95</v>
       </c>
-      <c r="G128">
+      <c r="F128" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G128" s="11">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M128" s="4"/>
+      <c r="M128" s="2"/>
     </row>
     <row r="129" spans="1:13">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="12">
         <v>0.77</v>
       </c>
-      <c r="E129">
-        <v>0.98</v>
-      </c>
-      <c r="G129">
+      <c r="E129" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F129" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G129" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M129" s="4"/>
+      <c r="M129" s="2"/>
     </row>
     <row r="130" spans="1:13">
-      <c r="A130" s="6" t="s">
+      <c r="A130" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="C130" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="D130" s="6">
+      <c r="D130" s="12">
         <v>0.68</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="11">
         <v>0.93</v>
       </c>
-      <c r="G130">
+      <c r="F130" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G130" s="11">
         <v>0.78</v>
       </c>
-      <c r="M130" s="4"/>
+      <c r="M130" s="2"/>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B131" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C131" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="D131" s="5">
+      <c r="D131" s="13">
         <v>0</v>
       </c>
-      <c r="E131">
-        <v>1</v>
-      </c>
-      <c r="G131">
+      <c r="E131" s="11">
+        <v>1</v>
+      </c>
+      <c r="F131" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G131" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J131">
+      <c r="J131" s="11">
         <v>0.86</v>
       </c>
-      <c r="M131" s="4"/>
+      <c r="M131" s="2"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D132" s="6">
+      <c r="D132" s="12">
         <v>0.87</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="11">
         <v>0.93</v>
       </c>
-      <c r="G132">
+      <c r="G132" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="J132">
+      <c r="J132" s="11">
         <v>0.8</v>
       </c>
-      <c r="M132" s="4"/>
+      <c r="M132" s="2"/>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="12">
         <v>0.86</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="11">
         <v>0.95</v>
       </c>
-      <c r="G133">
+      <c r="G133" s="11">
         <v>0.62</v>
       </c>
-      <c r="M133" s="4"/>
+      <c r="J133" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M133" s="2"/>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C134" s="6" t="s">
+      <c r="C134" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="12">
         <v>0.79</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="11">
         <v>0.91</v>
       </c>
-      <c r="G134">
+      <c r="G134" s="11">
         <v>0.53</v>
       </c>
-      <c r="M134" s="4"/>
+      <c r="M134" s="2"/>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B135" s="6" t="s">
+      <c r="B135" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C135" s="6" t="s">
+      <c r="C135" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="12">
         <v>0.64</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="11">
         <v>0.79</v>
       </c>
-      <c r="G135">
+      <c r="G135" s="11">
         <v>0.52</v>
       </c>
-      <c r="M135" s="4"/>
+      <c r="M135" s="2"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B136" s="6" t="s">
+      <c r="B136" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="12">
         <v>0.79</v>
       </c>
-      <c r="E136">
-        <v>1</v>
-      </c>
-      <c r="G136">
+      <c r="E136" s="11">
+        <v>1</v>
+      </c>
+      <c r="G136" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M136" s="4"/>
+      <c r="M136" s="2"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="C137" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D137" s="6">
+      <c r="D137" s="12">
         <v>0.69</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="11">
         <v>0.88</v>
       </c>
-      <c r="G137">
+      <c r="G137" s="11">
         <v>0.47</v>
       </c>
-      <c r="M137" s="4"/>
+      <c r="M137" s="2"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C138" s="6" t="s">
+      <c r="C138" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="12">
         <v>0.91</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="11">
         <v>0.86</v>
       </c>
-      <c r="G138">
+      <c r="G138" s="11">
         <v>0.64</v>
       </c>
-      <c r="M138" s="4"/>
+      <c r="M138" s="2"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B139" s="6" t="s">
+      <c r="B139" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C139" s="6" t="s">
+      <c r="C139" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="12">
         <v>0.88</v>
       </c>
-      <c r="E139">
+      <c r="E139" s="11">
         <v>0.93</v>
       </c>
-      <c r="G139">
+      <c r="G139" s="11">
         <v>0.42</v>
       </c>
-      <c r="M139" s="4"/>
+      <c r="M139" s="2"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B140" s="6" t="s">
+      <c r="B140" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C140" s="6" t="s">
+      <c r="C140" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="12">
         <v>0.86</v>
       </c>
-      <c r="E140">
-        <v>0.98</v>
-      </c>
-      <c r="G140">
+      <c r="E140" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G140" s="11">
         <v>0.51</v>
       </c>
-      <c r="M140" s="4"/>
+      <c r="M140" s="2"/>
     </row>
     <row r="141" spans="1:13">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="12">
         <v>0.87</v>
       </c>
-      <c r="E141">
-        <v>1</v>
-      </c>
-      <c r="G141">
+      <c r="E141" s="11">
+        <v>1</v>
+      </c>
+      <c r="G141" s="11">
         <v>0.66</v>
       </c>
-      <c r="J141">
+      <c r="J141" s="11">
         <v>0.8</v>
       </c>
-      <c r="M141" s="4"/>
+      <c r="M141" s="2"/>
     </row>
     <row r="142" spans="1:13">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142" s="13">
         <v>0</v>
       </c>
-      <c r="E142">
+      <c r="E142" s="11">
         <v>0.88</v>
       </c>
-      <c r="G142">
+      <c r="G142" s="11">
         <v>0.6</v>
       </c>
-      <c r="M142" s="4"/>
+      <c r="M142" s="2"/>
     </row>
     <row r="143" spans="1:13">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="12">
         <v>0.8</v>
       </c>
-      <c r="E143">
+      <c r="E143" s="11">
         <v>0.91</v>
       </c>
-      <c r="G143">
+      <c r="G143" s="11">
         <v>0.25</v>
       </c>
-      <c r="M143" s="4"/>
+      <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B144" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C144" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D144" s="12">
         <v>0.41</v>
       </c>
-      <c r="E144">
+      <c r="E144" s="11">
         <v>0</v>
       </c>
-      <c r="G144">
+      <c r="G144" s="11">
         <v>0.36</v>
       </c>
-      <c r="M144" s="4"/>
+      <c r="M144" s="2"/>
     </row>
     <row r="145" spans="1:13">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B145" s="6" t="s">
+      <c r="B145" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C145" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D145" s="6">
+      <c r="D145" s="12">
         <v>0.81</v>
       </c>
-      <c r="E145">
+      <c r="E145" s="11">
         <v>0</v>
       </c>
-      <c r="G145">
+      <c r="G145" s="11">
         <v>0.47</v>
       </c>
-      <c r="M145" s="4"/>
+      <c r="M145" s="2"/>
     </row>
     <row r="146" spans="1:13">
-      <c r="A146" s="6" t="s">
+      <c r="A146" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B146" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C146" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D146" s="12">
         <v>0.71</v>
       </c>
-      <c r="E146">
-        <v>1</v>
-      </c>
-      <c r="G146">
+      <c r="E146" s="11">
+        <v>1</v>
+      </c>
+      <c r="G146" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M146" s="4"/>
+      <c r="J146" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M146" s="2"/>
     </row>
     <row r="147" spans="1:13">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B147" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C147" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D147" s="6">
+      <c r="D147" s="12">
         <v>0.86</v>
       </c>
-      <c r="E147">
-        <v>1</v>
-      </c>
-      <c r="G147">
+      <c r="E147" s="11">
+        <v>1</v>
+      </c>
+      <c r="G147" s="11">
         <v>0.53</v>
       </c>
-      <c r="M147" s="4"/>
+      <c r="J147" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M147" s="2"/>
     </row>
     <row r="148" spans="1:13">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="C148" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D148" s="5">
+      <c r="D148" s="13">
         <v>0</v>
       </c>
-      <c r="E148">
+      <c r="E148" s="11">
         <v>0.86</v>
       </c>
-      <c r="G148">
+      <c r="G148" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J148">
+      <c r="J148" s="11">
         <v>0.83</v>
       </c>
-      <c r="M148" s="4"/>
+      <c r="M148" s="2"/>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B149" s="6" t="s">
+      <c r="B149" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C149" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D149" s="6">
+      <c r="D149" s="12">
         <v>0.87</v>
       </c>
-      <c r="E149">
-        <v>1</v>
-      </c>
-      <c r="G149">
+      <c r="E149" s="11">
+        <v>1</v>
+      </c>
+      <c r="G149" s="11">
         <v>0.61</v>
       </c>
-      <c r="M149" s="4"/>
+      <c r="M149" s="2"/>
     </row>
     <row r="150" spans="1:13">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="C150" s="5" t="s">
+      <c r="C150" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D150" s="13">
         <v>0</v>
       </c>
-      <c r="E150">
+      <c r="E150" s="11">
         <v>0.6</v>
       </c>
-      <c r="G150">
+      <c r="G150" s="11">
         <v>0.62</v>
       </c>
-      <c r="M150" s="4"/>
+      <c r="M150" s="2"/>
     </row>
     <row r="151" spans="1:13">
-      <c r="A151" s="6" t="s">
+      <c r="A151" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B151" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C151" s="6" t="s">
+      <c r="C151" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D151" s="6">
+      <c r="D151" s="12">
         <v>0.8</v>
       </c>
-      <c r="E151">
-        <v>1</v>
-      </c>
-      <c r="G151">
+      <c r="E151" s="11">
+        <v>1</v>
+      </c>
+      <c r="G151" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M151" s="4"/>
+      <c r="M151" s="2"/>
     </row>
     <row r="152" spans="1:13">
-      <c r="A152" s="6" t="s">
+      <c r="A152" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B152" s="6" t="s">
+      <c r="B152" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C152" s="6" t="s">
+      <c r="C152" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D152" s="6">
+      <c r="D152" s="12">
         <v>0.88</v>
       </c>
-      <c r="E152">
+      <c r="E152" s="11">
         <v>0</v>
       </c>
-      <c r="G152">
+      <c r="G152" s="11">
         <v>0.71</v>
       </c>
-      <c r="M152" s="4"/>
+      <c r="M152" s="2"/>
     </row>
     <row r="153" spans="1:13">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B153" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D153" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E153">
-        <v>0.98</v>
-      </c>
-      <c r="G153">
+      <c r="D153" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E153" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G153" s="11">
         <v>0.45</v>
       </c>
-      <c r="M153" s="4"/>
+      <c r="J153" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M153" s="2"/>
     </row>
     <row r="154" spans="1:13">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C154" s="5" t="s">
+      <c r="C154" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154" s="13">
         <v>0</v>
       </c>
-      <c r="E154">
+      <c r="E154" s="11">
         <v>0.93</v>
       </c>
-      <c r="G154">
+      <c r="G154" s="11">
         <v>0.53</v>
       </c>
-      <c r="M154" s="4"/>
+      <c r="M154" s="2"/>
     </row>
     <row r="155" spans="1:13">
-      <c r="A155" s="6" t="s">
+      <c r="A155" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B155" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C155" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="12">
         <v>0.75</v>
       </c>
-      <c r="E155">
-        <v>0.98</v>
-      </c>
-      <c r="G155">
+      <c r="E155" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G155" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M155" s="4"/>
+      <c r="M155" s="2"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" t="s">
         <v>479</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C156" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="14">
         <v>0</v>
       </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
-      <c r="G156">
+      <c r="E156" s="11">
+        <v>1</v>
+      </c>
+      <c r="G156" s="11">
         <v>0.52</v>
       </c>
-      <c r="M156" s="10"/>
+      <c r="M156" s="8"/>
     </row>
     <row r="157" spans="1:13">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B157" s="6" t="s">
+      <c r="B157" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C157" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D157" s="6">
+      <c r="D157" s="12">
         <v>0.85</v>
       </c>
-      <c r="E157">
+      <c r="E157" s="11">
         <v>0.93</v>
       </c>
-      <c r="G157">
+      <c r="G157" s="11">
         <v>0.47</v>
       </c>
-      <c r="M157" s="4"/>
+      <c r="M157" s="2"/>
     </row>
     <row r="158" spans="1:13">
-      <c r="A158" s="6" t="s">
+      <c r="A158" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B158" s="6" t="s">
+      <c r="B158" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D158" s="6">
+      <c r="D158" s="12">
         <v>0.88</v>
       </c>
-      <c r="E158">
-        <v>0.98</v>
-      </c>
-      <c r="G158">
+      <c r="E158" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G158" s="11">
         <v>0.61</v>
       </c>
-      <c r="M158" s="4"/>
+      <c r="M158" s="2"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" t="s">
         <v>468</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B159" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C159" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="14">
         <v>0</v>
       </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-      <c r="G159">
+      <c r="E159" s="11">
+        <v>1</v>
+      </c>
+      <c r="G159" s="11">
         <v>0.39</v>
       </c>
-      <c r="M159" s="10"/>
+      <c r="M159" s="8"/>
     </row>
     <row r="160" spans="1:13">
-      <c r="A160" s="6" t="s">
+      <c r="A160" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="B160" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C160" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D160" s="6">
+      <c r="D160" s="12">
         <v>0.71</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="11">
         <v>0.88</v>
       </c>
-      <c r="G160">
+      <c r="G160" s="11">
         <v>0.53</v>
       </c>
-      <c r="M160" s="4"/>
+      <c r="M160" s="2"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" t="s">
         <v>477</v>
       </c>
-      <c r="B161" s="9" t="s">
+      <c r="B161" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C161" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="14">
         <v>0</v>
       </c>
-      <c r="E161">
+      <c r="E161" s="11">
         <v>0</v>
       </c>
-      <c r="G161">
+      <c r="G161" s="11">
         <v>0.45</v>
       </c>
-      <c r="M161" s="10"/>
+      <c r="M161" s="8"/>
     </row>
     <row r="162" spans="1:13">
-      <c r="A162" s="6" t="s">
+      <c r="A162" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="B162" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C162" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D162" s="6">
+      <c r="D162" s="12">
         <v>0.74</v>
       </c>
-      <c r="E162">
-        <v>0.98</v>
-      </c>
-      <c r="G162">
+      <c r="E162" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G162" s="11">
         <v>0.62</v>
       </c>
-      <c r="M162" s="4"/>
+      <c r="M162" s="2"/>
     </row>
     <row r="163" spans="1:13">
-      <c r="A163" s="6" t="s">
+      <c r="A163" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B163" s="6" t="s">
+      <c r="B163" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C163" s="6" t="s">
+      <c r="C163" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D163" s="6">
-        <v>1</v>
-      </c>
-      <c r="E163">
-        <v>1</v>
-      </c>
-      <c r="G163">
+      <c r="D163" s="12">
+        <v>1</v>
+      </c>
+      <c r="E163" s="11">
+        <v>1</v>
+      </c>
+      <c r="G163" s="11">
         <v>0.39</v>
       </c>
-      <c r="M163" s="4"/>
+      <c r="M163" s="2"/>
     </row>
     <row r="164" spans="1:13">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B164" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C164" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D164" s="6">
+      <c r="D164" s="12">
         <v>0.88</v>
       </c>
-      <c r="E164">
+      <c r="E164" s="11">
         <v>0.84</v>
       </c>
-      <c r="G164">
+      <c r="G164" s="11">
         <v>0.75</v>
       </c>
-      <c r="J164">
+      <c r="J164" s="11">
         <v>0.83</v>
       </c>
-      <c r="M164" s="4"/>
+      <c r="M164" s="2"/>
     </row>
     <row r="165" spans="1:13">
-      <c r="A165" s="6" t="s">
+      <c r="A165" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B165" s="6" t="s">
+      <c r="B165" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C165" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D165" s="6">
+      <c r="D165" s="12">
         <v>0.8</v>
       </c>
-      <c r="E165">
+      <c r="E165" s="11">
         <v>0.84</v>
       </c>
-      <c r="G165">
+      <c r="G165" s="11">
         <v>0.71</v>
       </c>
-      <c r="M165" s="4"/>
+      <c r="M165" s="2"/>
     </row>
     <row r="166" spans="1:13">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B166" s="6" t="s">
+      <c r="B166" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C166" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D166" s="6">
+      <c r="D166" s="12">
         <v>0.91</v>
       </c>
-      <c r="E166">
+      <c r="E166" s="11">
         <v>0.84</v>
       </c>
-      <c r="G166">
+      <c r="G166" s="11">
         <v>0.81</v>
       </c>
-      <c r="M166" s="4"/>
+      <c r="M166" s="2"/>
     </row>
     <row r="167" spans="1:13">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B167" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C167" s="6" t="s">
+      <c r="C167" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D167" s="6">
-        <v>1</v>
-      </c>
-      <c r="E167">
-        <v>1</v>
-      </c>
-      <c r="G167">
+      <c r="D167" s="12">
+        <v>1</v>
+      </c>
+      <c r="E167" s="11">
+        <v>1</v>
+      </c>
+      <c r="G167" s="11">
         <v>0.74</v>
       </c>
-      <c r="M167" s="4"/>
+      <c r="M167" s="2"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" t="s">
         <v>470</v>
       </c>
-      <c r="B168" s="9" t="s">
+      <c r="B168" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="14">
         <v>0</v>
       </c>
-      <c r="E168">
+      <c r="E168" s="11">
         <v>0.91</v>
       </c>
-      <c r="G168">
+      <c r="G168" s="11">
         <v>0.71</v>
       </c>
-      <c r="M168" s="10"/>
+      <c r="M168" s="8"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
         <v>472</v>
       </c>
-      <c r="B169" s="9" t="s">
+      <c r="B169" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C169" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="14">
         <v>0</v>
       </c>
-      <c r="E169">
-        <v>0.98</v>
-      </c>
-      <c r="G169">
+      <c r="E169" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G169" s="11">
         <v>0.38</v>
       </c>
-      <c r="M169" s="10"/>
+      <c r="M169" s="8"/>
     </row>
     <row r="170" spans="1:13">
-      <c r="A170" s="6" t="s">
+      <c r="A170" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B170" s="6" t="s">
+      <c r="B170" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C170" s="6" t="s">
+      <c r="C170" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D170" s="6">
+      <c r="D170" s="12">
         <v>0.81</v>
       </c>
-      <c r="E170">
+      <c r="E170" s="11">
         <v>0.95</v>
       </c>
-      <c r="G170">
+      <c r="G170" s="11">
         <v>0.44</v>
       </c>
-      <c r="M170" s="4"/>
+      <c r="M170" s="2"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" t="s">
         <v>388</v>
       </c>
-      <c r="B171" s="9" t="s">
+      <c r="B171" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="14">
         <v>0</v>
       </c>
-      <c r="E171">
-        <v>1</v>
-      </c>
-      <c r="G171">
+      <c r="E171" s="11">
+        <v>1</v>
+      </c>
+      <c r="G171" s="11">
         <v>0.51</v>
       </c>
-      <c r="M171" s="10"/>
+      <c r="M171" s="8"/>
     </row>
     <row r="172" spans="1:13">
-      <c r="A172" s="6" t="s">
+      <c r="A172" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C172" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D172" s="6">
+      <c r="D172" s="12">
         <v>0.84</v>
       </c>
-      <c r="E172">
-        <v>0.98</v>
-      </c>
-      <c r="G172">
+      <c r="E172" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G172" s="11">
         <v>0.49</v>
       </c>
-      <c r="M172" s="4"/>
+      <c r="M172" s="2"/>
     </row>
     <row r="173" spans="1:13">
-      <c r="A173" s="6" t="s">
+      <c r="A173" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B173" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C173" s="6" t="s">
+      <c r="C173" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D173" s="6">
+      <c r="D173" s="12">
         <v>0.81</v>
       </c>
-      <c r="E173">
+      <c r="E173" s="11">
         <v>0</v>
       </c>
-      <c r="G173">
+      <c r="G173" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J173">
+      <c r="J173" s="11">
         <v>0.83</v>
       </c>
-      <c r="M173" s="4"/>
+      <c r="M173" s="2"/>
     </row>
     <row r="174" spans="1:13">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B174" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C174" s="6" t="s">
+      <c r="C174" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D174" s="6">
+      <c r="D174" s="12">
         <v>0.85</v>
       </c>
-      <c r="E174">
-        <v>1</v>
-      </c>
-      <c r="G174">
+      <c r="E174" s="11">
+        <v>1</v>
+      </c>
+      <c r="G174" s="11">
         <v>0.69</v>
       </c>
-      <c r="M174" s="4"/>
+      <c r="M174" s="2"/>
     </row>
     <row r="175" spans="1:13">
-      <c r="A175" s="6" t="s">
+      <c r="A175" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B175" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C175" s="6" t="s">
+      <c r="C175" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D175" s="6">
+      <c r="D175" s="12">
         <v>0.91</v>
       </c>
-      <c r="E175">
-        <v>0.98</v>
-      </c>
-      <c r="G175">
+      <c r="E175" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G175" s="11">
         <v>0.65</v>
       </c>
-      <c r="M175" s="4"/>
+      <c r="M175" s="2"/>
     </row>
     <row r="176" spans="1:13">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B176" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C176" s="6" t="s">
+      <c r="C176" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D176" s="6">
+      <c r="D176" s="12">
         <v>0.86</v>
       </c>
-      <c r="E176">
+      <c r="E176" s="11">
         <v>0.81</v>
       </c>
-      <c r="G176">
+      <c r="G176" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M176" s="4"/>
+      <c r="M176" s="2"/>
     </row>
     <row r="177" spans="1:13">
-      <c r="A177" s="6" t="s">
+      <c r="A177" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B177" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C177" s="6" t="s">
+      <c r="C177" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D177" s="6">
+      <c r="D177" s="12">
         <v>0.93</v>
       </c>
-      <c r="E177">
+      <c r="E177" s="11">
         <v>0.88</v>
       </c>
-      <c r="G177">
+      <c r="G177" s="11">
         <v>0.62</v>
       </c>
-      <c r="M177" s="4"/>
+      <c r="M177" s="2"/>
     </row>
     <row r="178" spans="1:13">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B178" s="6" t="s">
+      <c r="B178" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C178" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D178" s="6">
+      <c r="D178" s="12">
         <v>0.79</v>
       </c>
-      <c r="E178">
-        <v>0.98</v>
-      </c>
-      <c r="G178">
+      <c r="E178" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G178" s="11">
         <v>0.48</v>
       </c>
-      <c r="M178" s="4"/>
+      <c r="M178" s="2"/>
     </row>
     <row r="179" spans="1:13">
-      <c r="A179" s="6" t="s">
+      <c r="A179" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B179" s="6" t="s">
+      <c r="B179" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C179" s="6" t="s">
+      <c r="C179" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D179" s="6">
+      <c r="D179" s="12">
         <v>0.86</v>
       </c>
-      <c r="E179">
+      <c r="E179" s="11">
         <v>0.93</v>
       </c>
-      <c r="G179">
+      <c r="G179" s="11">
         <v>0.61</v>
       </c>
-      <c r="M179" s="4"/>
+      <c r="M179" s="2"/>
     </row>
     <row r="180" spans="1:13">
-      <c r="A180" s="6" t="s">
+      <c r="A180" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B180" s="6" t="s">
+      <c r="B180" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C180" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D180" s="6">
+      <c r="D180" s="12">
         <v>0.75</v>
       </c>
-      <c r="E180">
+      <c r="E180" s="11">
         <v>0.93</v>
       </c>
-      <c r="G180">
+      <c r="G180" s="11">
         <v>0.36</v>
       </c>
-      <c r="M180" s="4"/>
+      <c r="M180" s="2"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" t="s">
         <v>475</v>
       </c>
-      <c r="B181" s="9" t="s">
+      <c r="B181" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181" s="14">
         <v>0</v>
       </c>
-      <c r="E181">
-        <v>0.98</v>
-      </c>
-      <c r="G181">
+      <c r="E181" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G181" s="11">
         <v>0.68</v>
       </c>
-      <c r="M181" s="10"/>
+      <c r="M181" s="8"/>
     </row>
     <row r="182" spans="1:13">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B182" s="6" t="s">
+      <c r="B182" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C182" s="6" t="s">
+      <c r="C182" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D182" s="6">
+      <c r="D182" s="12">
         <v>0.82</v>
       </c>
-      <c r="E182">
-        <v>0.98</v>
-      </c>
-      <c r="G182">
+      <c r="E182" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G182" s="11">
         <v>0.4</v>
       </c>
-      <c r="M182" s="4"/>
+      <c r="M182" s="2"/>
     </row>
     <row r="183" spans="1:13">
-      <c r="A183" s="6" t="s">
+      <c r="A183" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B183" s="6" t="s">
+      <c r="B183" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C183" s="6" t="s">
+      <c r="C183" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D183" s="6">
+      <c r="D183" s="12">
         <v>0.86</v>
       </c>
-      <c r="E183">
-        <v>0.98</v>
-      </c>
-      <c r="G183">
+      <c r="E183" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G183" s="11">
         <v>0.38</v>
       </c>
-      <c r="M183" s="4"/>
+      <c r="M183" s="2"/>
     </row>
     <row r="184" spans="1:13">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B184" s="6" t="s">
+      <c r="B184" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C184" s="6" t="s">
+      <c r="C184" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D184" s="6">
+      <c r="D184" s="12">
         <v>0.93</v>
       </c>
-      <c r="E184">
+      <c r="E184" s="11">
         <v>0.95</v>
       </c>
-      <c r="G184">
+      <c r="G184" s="11">
         <v>0.66</v>
       </c>
-      <c r="M184" s="4"/>
+      <c r="M184" s="2"/>
     </row>
     <row r="185" spans="1:13">
-      <c r="A185" s="6" t="s">
+      <c r="A185" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B185" s="6" t="s">
+      <c r="B185" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C185" s="6" t="s">
+      <c r="C185" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D185" s="6">
-        <v>1</v>
-      </c>
-      <c r="E185">
-        <v>1</v>
-      </c>
-      <c r="G185">
+      <c r="D185" s="12">
+        <v>1</v>
+      </c>
+      <c r="E185" s="11">
+        <v>1</v>
+      </c>
+      <c r="G185" s="11">
         <v>0.73</v>
       </c>
-      <c r="M185" s="4"/>
+      <c r="M185" s="2"/>
     </row>
     <row r="186" spans="1:13">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B186" s="6" t="s">
+      <c r="B186" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C186" s="6" t="s">
+      <c r="C186" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D186" s="6">
+      <c r="D186" s="12">
         <v>0.91</v>
       </c>
-      <c r="E186">
-        <v>1</v>
-      </c>
-      <c r="G186">
+      <c r="E186" s="11">
+        <v>1</v>
+      </c>
+      <c r="G186" s="11">
         <v>0.53</v>
       </c>
-      <c r="J186">
+      <c r="J186" s="11">
         <v>0.8</v>
       </c>
-      <c r="M186" s="4"/>
+      <c r="M186" s="2"/>
     </row>
     <row r="187" spans="1:13">
-      <c r="A187" s="6" t="s">
+      <c r="A187" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B187" s="6" t="s">
+      <c r="B187" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C187" s="6" t="s">
+      <c r="C187" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D187" s="6">
+      <c r="D187" s="12">
         <v>0.81</v>
       </c>
-      <c r="E187">
+      <c r="E187" s="11">
         <v>0.65</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="11">
         <v>0.32</v>
       </c>
-      <c r="M187" s="4"/>
+      <c r="M187" s="2"/>
     </row>
     <row r="188" spans="1:13">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B188" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C188" s="6" t="s">
+      <c r="C188" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D188" s="6">
+      <c r="D188" s="12">
         <v>0.81</v>
       </c>
-      <c r="E188">
+      <c r="E188" s="11">
         <v>0.95</v>
       </c>
-      <c r="G188">
+      <c r="G188" s="11">
         <v>0.82</v>
       </c>
-      <c r="J188">
+      <c r="J188" s="11">
         <v>0.83</v>
       </c>
-      <c r="M188" s="4"/>
+      <c r="M188" s="2"/>
     </row>
     <row r="189" spans="1:13">
-      <c r="A189" s="6" t="s">
+      <c r="A189" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B189" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C189" s="6" t="s">
+      <c r="C189" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D189" s="6">
+      <c r="D189" s="12">
         <v>0.8</v>
       </c>
-      <c r="E189">
+      <c r="E189" s="11">
         <v>0.91</v>
       </c>
-      <c r="G189">
+      <c r="G189" s="11">
         <v>0.73</v>
       </c>
-      <c r="M189" s="4"/>
+      <c r="M189" s="2"/>
     </row>
     <row r="190" spans="1:13">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B190" s="6" t="s">
+      <c r="B190" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C190" s="6" t="s">
+      <c r="C190" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D190" s="6">
+      <c r="D190" s="12">
         <v>0.85</v>
       </c>
-      <c r="E190">
-        <v>1</v>
-      </c>
-      <c r="G190">
+      <c r="E190" s="11">
+        <v>1</v>
+      </c>
+      <c r="G190" s="11">
         <v>0.43</v>
       </c>
-      <c r="M190" s="4"/>
+      <c r="M190" s="2"/>
     </row>
     <row r="191" spans="1:13">
-      <c r="A191" s="6" t="s">
+      <c r="A191" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B191" s="6" t="s">
+      <c r="B191" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C191" s="6" t="s">
+      <c r="C191" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D191" s="6">
+      <c r="D191" s="12">
         <v>0.89</v>
       </c>
-      <c r="E191">
+      <c r="E191" s="11">
         <v>0.93</v>
       </c>
-      <c r="G191">
+      <c r="G191" s="11">
         <v>0.51</v>
       </c>
-      <c r="M191" s="4"/>
+      <c r="M191" s="2"/>
     </row>
     <row r="192" spans="1:13">
-      <c r="A192" s="6" t="s">
+      <c r="A192" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B192" s="6" t="s">
+      <c r="B192" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="C192" s="6" t="s">
+      <c r="C192" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D192" s="6">
+      <c r="D192" s="12">
         <v>0.77</v>
       </c>
-      <c r="E192">
-        <v>1</v>
-      </c>
-      <c r="G192">
+      <c r="E192" s="11">
+        <v>1</v>
+      </c>
+      <c r="G192" s="11">
         <v>0.75</v>
       </c>
-      <c r="J192">
+      <c r="J192" s="11">
         <v>0.8</v>
       </c>
-      <c r="M192" s="4"/>
+      <c r="M192" s="2"/>
     </row>
     <row r="193" spans="1:13">
-      <c r="A193" s="6" t="s">
+      <c r="A193" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B193" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="C193" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D193" s="6">
+      <c r="D193" s="12">
         <v>0.8</v>
       </c>
-      <c r="E193">
+      <c r="E193" s="11">
         <v>0.95</v>
       </c>
-      <c r="G193">
+      <c r="G193" s="11">
         <v>0.64</v>
       </c>
-      <c r="J193">
+      <c r="J193" s="11">
         <v>0.85</v>
       </c>
-      <c r="M193" s="4"/>
+      <c r="M193" s="2"/>
     </row>
     <row r="194" spans="1:13">
-      <c r="A194" s="6" t="s">
+      <c r="A194" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B194" s="6" t="s">
+      <c r="B194" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="C194" s="6" t="s">
+      <c r="C194" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D194" s="6">
+      <c r="D194" s="12">
         <v>0.74</v>
       </c>
-      <c r="E194">
+      <c r="E194" s="11">
         <v>0.91</v>
       </c>
-      <c r="G194">
+      <c r="G194" s="11">
         <v>0.45</v>
       </c>
-      <c r="M194" s="4"/>
+      <c r="J194" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="M194" s="2"/>
     </row>
     <row r="195" spans="1:13">
-      <c r="A195" s="6" t="s">
+      <c r="A195" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="B195" s="6" t="s">
+      <c r="B195" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C195" s="6" t="s">
+      <c r="C195" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D195" s="6">
+      <c r="D195" s="12">
         <v>0.82</v>
       </c>
-      <c r="E195">
-        <v>1</v>
-      </c>
-      <c r="G195">
+      <c r="E195" s="11">
+        <v>1</v>
+      </c>
+      <c r="G195" s="11">
         <v>0.61</v>
       </c>
-      <c r="M195" s="4"/>
+      <c r="J195" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M195" s="2"/>
     </row>
     <row r="196" spans="1:13">
-      <c r="A196" s="6" t="s">
+      <c r="A196" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="B196" s="6" t="s">
+      <c r="B196" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="C196" s="6" t="s">
+      <c r="C196" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D196" s="6">
+      <c r="D196" s="12">
         <v>0.85</v>
       </c>
-      <c r="E196">
-        <v>1</v>
-      </c>
-      <c r="G196">
+      <c r="E196" s="11">
+        <v>1</v>
+      </c>
+      <c r="G196" s="11">
         <v>0.7</v>
       </c>
-      <c r="J196">
+      <c r="J196" s="11">
         <v>0.8</v>
       </c>
-      <c r="M196" s="4"/>
+      <c r="M196" s="2"/>
     </row>
     <row r="197" spans="1:13">
-      <c r="A197" s="6" t="s">
+      <c r="A197" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="B197" s="6" t="s">
+      <c r="B197" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="C197" s="6" t="s">
+      <c r="C197" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D197" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E197">
-        <v>1</v>
-      </c>
-      <c r="G197">
+      <c r="D197" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E197" s="11">
+        <v>1</v>
+      </c>
+      <c r="G197" s="11">
         <v>0.64</v>
       </c>
-      <c r="M197" s="4"/>
+      <c r="M197" s="2"/>
     </row>
     <row r="198" spans="1:13">
-      <c r="A198" s="6" t="s">
+      <c r="A198" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B198" s="6" t="s">
+      <c r="B198" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C198" s="6" t="s">
+      <c r="C198" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D198" s="6">
+      <c r="D198" s="12">
         <v>0.93</v>
       </c>
-      <c r="E198">
+      <c r="E198" s="11">
         <v>0.86</v>
       </c>
-      <c r="G198">
+      <c r="G198" s="11">
         <v>0.64</v>
       </c>
-      <c r="M198" s="4"/>
+      <c r="M198" s="2"/>
     </row>
     <row r="199" spans="1:13">
-      <c r="A199" s="6" t="s">
+      <c r="A199" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="B199" s="6" t="s">
+      <c r="B199" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C199" s="6" t="s">
+      <c r="C199" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D199" s="6">
+      <c r="D199" s="12">
         <v>0.67</v>
       </c>
-      <c r="E199">
+      <c r="E199" s="11">
         <v>0.91</v>
       </c>
-      <c r="G199">
+      <c r="G199" s="11">
         <v>0.65</v>
       </c>
-      <c r="M199" s="4"/>
+      <c r="J199" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="M199" s="2"/>
     </row>
     <row r="200" spans="1:13">
-      <c r="A200" s="6" t="s">
+      <c r="A200" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B200" s="6" t="s">
+      <c r="B200" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="C200" s="6" t="s">
+      <c r="C200" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D200" s="6">
+      <c r="D200" s="12">
         <v>0.96</v>
       </c>
-      <c r="E200">
+      <c r="E200" s="11">
         <v>0.91</v>
       </c>
-      <c r="G200">
+      <c r="G200" s="11">
         <v>0.69</v>
       </c>
-      <c r="M200" s="4"/>
+      <c r="M200" s="2"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" s="6" t="s">
+      <c r="A201" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="B201" s="6" t="s">
+      <c r="B201" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C201" s="6" t="s">
+      <c r="C201" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D201" s="6">
+      <c r="D201" s="12">
         <v>0.92</v>
       </c>
-      <c r="E201">
+      <c r="E201" s="11">
         <v>0.91</v>
       </c>
-      <c r="G201">
+      <c r="G201" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M201" s="4"/>
+      <c r="M201" s="2"/>
     </row>
     <row r="202" spans="1:13">
-      <c r="A202" s="6" t="s">
+      <c r="A202" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="B202" s="6" t="s">
+      <c r="B202" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C202" s="6" t="s">
+      <c r="C202" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D202" s="6">
+      <c r="D202" s="12">
         <v>0.84</v>
       </c>
-      <c r="E202">
+      <c r="E202" s="11">
         <v>0.95</v>
       </c>
-      <c r="G202">
+      <c r="G202" s="11">
         <v>0.78</v>
       </c>
-      <c r="M202" s="4"/>
+      <c r="M202" s="2"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="6" t="s">
+      <c r="A203" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B203" s="6" t="s">
+      <c r="B203" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C203" s="6" t="s">
+      <c r="C203" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D203" s="6">
+      <c r="D203" s="12">
         <v>0.63</v>
       </c>
-      <c r="E203">
+      <c r="E203" s="11">
         <v>0.42</v>
       </c>
-      <c r="G203">
+      <c r="G203" s="11">
         <v>0.64</v>
       </c>
-      <c r="M203" s="4"/>
+      <c r="M203" s="2"/>
     </row>
     <row r="204" spans="1:13">
-      <c r="A204" s="6" t="s">
+      <c r="A204" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B204" s="6" t="s">
+      <c r="B204" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C204" s="6" t="s">
+      <c r="C204" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D204" s="6">
+      <c r="D204" s="12">
         <v>0.82</v>
       </c>
-      <c r="E204">
+      <c r="E204" s="11">
         <v>0.95</v>
       </c>
-      <c r="G204">
+      <c r="G204" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M204" s="4"/>
+      <c r="J204" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M204" s="2"/>
     </row>
     <row r="205" spans="1:13">
-      <c r="A205" s="6" t="s">
+      <c r="A205" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="B205" s="6" t="s">
+      <c r="B205" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C205" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D205" s="6">
+      <c r="D205" s="12">
         <v>0.93</v>
       </c>
-      <c r="E205">
-        <v>0.98</v>
-      </c>
-      <c r="G205">
+      <c r="E205" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G205" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M205" s="4"/>
+      <c r="M205" s="2"/>
     </row>
     <row r="206" spans="1:13">
-      <c r="A206" s="6" t="s">
+      <c r="A206" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B206" s="6" t="s">
+      <c r="B206" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="C206" s="6" t="s">
+      <c r="C206" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D206" s="6">
+      <c r="D206" s="12">
         <v>0.75</v>
       </c>
-      <c r="E206">
-        <v>0.98</v>
-      </c>
-      <c r="G206">
+      <c r="E206" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G206" s="11">
         <v>0.73</v>
       </c>
-      <c r="M206" s="4"/>
+      <c r="M206" s="2"/>
     </row>
     <row r="207" spans="1:13">
-      <c r="A207" s="6" t="s">
+      <c r="A207" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="B207" s="6" t="s">
+      <c r="B207" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="C207" s="6" t="s">
+      <c r="C207" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D207" s="6">
+      <c r="D207" s="12">
         <v>0.96</v>
       </c>
-      <c r="E207">
+      <c r="E207" s="11">
         <v>0.91</v>
       </c>
-      <c r="G207">
+      <c r="G207" s="11">
         <v>0.82</v>
       </c>
-      <c r="J207">
+      <c r="J207" s="11">
         <v>0.8</v>
       </c>
-      <c r="M207" s="4"/>
+      <c r="M207" s="2"/>
     </row>
     <row r="208" spans="1:13">
-      <c r="A208" s="6" t="s">
+      <c r="A208" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B208" s="6" t="s">
+      <c r="B208" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="C208" s="6" t="s">
+      <c r="C208" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D208" s="6">
+      <c r="D208" s="12">
         <v>0.92</v>
       </c>
-      <c r="E208">
-        <v>1</v>
-      </c>
-      <c r="G208">
+      <c r="E208" s="11">
+        <v>1</v>
+      </c>
+      <c r="G208" s="11">
         <v>0.64</v>
       </c>
-      <c r="M208" s="4"/>
+      <c r="M208" s="2"/>
     </row>
     <row r="209" spans="1:13">
-      <c r="A209" s="6" t="s">
+      <c r="A209" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="B209" s="6" t="s">
+      <c r="B209" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="C209" s="6" t="s">
+      <c r="C209" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D209" s="6">
+      <c r="D209" s="12">
         <v>0.81</v>
       </c>
-      <c r="E209">
+      <c r="E209" s="11">
         <v>0.88</v>
       </c>
-      <c r="G209">
+      <c r="G209" s="11">
         <v>0.7</v>
       </c>
-      <c r="M209" s="4"/>
+      <c r="M209" s="2"/>
     </row>
     <row r="210" spans="1:13">
-      <c r="A210" s="6" t="s">
+      <c r="A210" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="B210" s="6" t="s">
+      <c r="B210" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="C210" s="6" t="s">
+      <c r="C210" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D210" s="6">
+      <c r="D210" s="12">
         <v>0.9</v>
       </c>
-      <c r="E210">
-        <v>0.98</v>
-      </c>
-      <c r="G210">
+      <c r="E210" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G210" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M210" s="4"/>
+      <c r="M210" s="2"/>
     </row>
     <row r="211" spans="1:13">
-      <c r="A211" s="6" t="s">
+      <c r="A211" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="B211" s="6" t="s">
+      <c r="B211" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="C211" s="6" t="s">
+      <c r="C211" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D211" s="6">
+      <c r="D211" s="12">
         <v>0.96</v>
       </c>
-      <c r="E211">
+      <c r="E211" s="11">
         <v>0.91</v>
       </c>
-      <c r="G211">
+      <c r="G211" s="11">
         <v>0.81</v>
       </c>
-      <c r="M211" s="4"/>
+      <c r="M211" s="2"/>
     </row>
     <row r="212" spans="1:13">
-      <c r="A212" s="6" t="s">
+      <c r="A212" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B212" s="6" t="s">
+      <c r="B212" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C212" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D212" s="6">
+      <c r="D212" s="12">
         <v>0.76</v>
       </c>
-      <c r="E212">
+      <c r="E212" s="11">
         <v>0.88</v>
       </c>
-      <c r="G212">
+      <c r="G212" s="11">
         <v>0.71</v>
       </c>
-      <c r="M212" s="4"/>
+      <c r="J212" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M212" s="2"/>
     </row>
     <row r="213" spans="1:13">
-      <c r="A213" s="6" t="s">
+      <c r="A213" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B213" s="6" t="s">
+      <c r="B213" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="C213" s="6" t="s">
+      <c r="C213" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D213" s="6">
+      <c r="D213" s="12">
         <v>0.93</v>
       </c>
-      <c r="E213">
+      <c r="E213" s="11">
         <v>0.95</v>
       </c>
-      <c r="G213">
+      <c r="G213" s="11">
         <v>0.49</v>
       </c>
-      <c r="M213" s="4"/>
+      <c r="M213" s="2"/>
     </row>
     <row r="214" spans="1:13">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="B214" s="6" t="s">
+      <c r="B214" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C214" s="6" t="s">
+      <c r="C214" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D214" s="6">
+      <c r="D214" s="12">
         <v>0.79</v>
       </c>
-      <c r="E214">
+      <c r="E214" s="11">
         <v>0.91</v>
       </c>
-      <c r="G214">
+      <c r="G214" s="11">
         <v>0.6</v>
       </c>
-      <c r="J214">
+      <c r="J214" s="11">
         <v>0.85</v>
       </c>
-      <c r="M214" s="4"/>
+      <c r="M214" s="2"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="A215" s="6" t="s">
+      <c r="A215" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="B215" s="6" t="s">
+      <c r="B215" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C215" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D215" s="6">
+      <c r="D215" s="12">
         <v>0.81</v>
       </c>
-      <c r="E215">
-        <v>1</v>
-      </c>
-      <c r="G215">
+      <c r="E215" s="11">
+        <v>1</v>
+      </c>
+      <c r="G215" s="11">
         <v>0.75</v>
       </c>
-      <c r="M215" s="4"/>
+      <c r="M215" s="2"/>
     </row>
     <row r="216" spans="1:13">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="B216" s="6" t="s">
+      <c r="B216" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C216" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D216" s="6">
+      <c r="D216" s="12">
         <v>0.85</v>
       </c>
-      <c r="E216">
-        <v>0.98</v>
-      </c>
-      <c r="G216">
+      <c r="E216" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G216" s="11">
         <v>0.69</v>
       </c>
-      <c r="M216" s="4"/>
+      <c r="M216" s="2"/>
     </row>
     <row r="217" spans="1:13">
-      <c r="A217" s="6" t="s">
+      <c r="A217" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B217" s="6" t="s">
+      <c r="B217" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C217" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D217" s="6">
+      <c r="D217" s="12">
         <v>0.96</v>
       </c>
-      <c r="E217">
-        <v>1</v>
-      </c>
-      <c r="G217">
+      <c r="E217" s="11">
+        <v>1</v>
+      </c>
+      <c r="G217" s="11">
         <v>0.73</v>
       </c>
-      <c r="M217" s="4"/>
+      <c r="M217" s="2"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="A218" s="6" t="s">
+      <c r="A218" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B218" s="6" t="s">
+      <c r="B218" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C218" s="6" t="s">
+      <c r="C218" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D218" s="6">
+      <c r="D218" s="12">
         <v>0.81</v>
       </c>
-      <c r="E218">
+      <c r="E218" s="11">
         <v>0.95</v>
       </c>
-      <c r="G218">
+      <c r="G218" s="11">
         <v>0.73</v>
       </c>
-      <c r="J218">
+      <c r="J218" s="11">
         <v>0.79</v>
       </c>
-      <c r="M218" s="4"/>
+      <c r="M218" s="2"/>
     </row>
     <row r="219" spans="1:13">
-      <c r="A219" s="6" t="s">
+      <c r="A219" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B219" s="6" t="s">
+      <c r="B219" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C219" s="6" t="s">
+      <c r="C219" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D219" s="6">
+      <c r="D219" s="12">
         <v>0.96</v>
       </c>
-      <c r="E219">
-        <v>0.98</v>
-      </c>
-      <c r="G219">
+      <c r="E219" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G219" s="11">
         <v>0.69</v>
       </c>
-      <c r="M219" s="4"/>
+      <c r="M219" s="2"/>
     </row>
     <row r="220" spans="1:13">
-      <c r="A220" s="6" t="s">
+      <c r="A220" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="B220" s="6" t="s">
+      <c r="B220" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="C220" s="6" t="s">
+      <c r="C220" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D220" s="6">
+      <c r="D220" s="12">
         <v>0.85</v>
       </c>
-      <c r="E220">
+      <c r="E220" s="11">
         <v>0.86</v>
       </c>
-      <c r="G220">
+      <c r="G220" s="11">
         <v>0.83</v>
       </c>
-      <c r="M220" s="4"/>
+      <c r="M220" s="2"/>
     </row>
     <row r="221" spans="1:13">
-      <c r="A221" s="6" t="s">
+      <c r="A221" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B221" s="6" t="s">
+      <c r="B221" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C221" s="6" t="s">
+      <c r="C221" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D221" s="6">
+      <c r="D221" s="12">
         <v>0.77</v>
       </c>
-      <c r="E221">
-        <v>0.98</v>
-      </c>
-      <c r="G221">
+      <c r="E221" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G221" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M221" s="4"/>
+      <c r="M221" s="2"/>
     </row>
     <row r="222" spans="1:13">
-      <c r="A222" s="6" t="s">
+      <c r="A222" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B222" s="6" t="s">
+      <c r="B222" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="C222" s="6" t="s">
+      <c r="C222" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D222" s="6">
+      <c r="D222" s="12">
         <v>0.93</v>
       </c>
-      <c r="E222">
-        <v>1</v>
-      </c>
-      <c r="G222">
+      <c r="E222" s="11">
+        <v>1</v>
+      </c>
+      <c r="G222" s="11">
         <v>0.77</v>
       </c>
-      <c r="M222" s="4"/>
+      <c r="M222" s="2"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="A223" s="6" t="s">
+      <c r="A223" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B223" s="6" t="s">
+      <c r="B223" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="C223" s="6" t="s">
+      <c r="C223" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D223" s="6">
-        <v>1</v>
-      </c>
-      <c r="E223">
+      <c r="D223" s="12">
+        <v>1</v>
+      </c>
+      <c r="E223" s="11">
         <v>0.88</v>
       </c>
-      <c r="G223">
+      <c r="G223" s="11">
         <v>0.77</v>
       </c>
-      <c r="J223">
+      <c r="J223" s="11">
         <v>0.93</v>
       </c>
-      <c r="M223" s="4"/>
+      <c r="M223" s="2"/>
     </row>
     <row r="224" spans="1:13">
-      <c r="A224" s="6" t="s">
+      <c r="A224" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B224" s="6" t="s">
+      <c r="B224" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C224" s="6" t="s">
+      <c r="C224" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D224" s="6">
+      <c r="D224" s="12">
         <v>0.91</v>
       </c>
-      <c r="E224">
-        <v>0.98</v>
-      </c>
-      <c r="G224">
+      <c r="E224" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G224" s="11">
         <v>0.74</v>
       </c>
-      <c r="M224" s="4"/>
+      <c r="M224" s="2"/>
     </row>
     <row r="225" spans="1:13">
-      <c r="A225" s="6" t="s">
+      <c r="A225" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="B225" s="6" t="s">
+      <c r="B225" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="C225" s="6" t="s">
+      <c r="C225" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D225" s="6">
+      <c r="D225" s="12">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E225">
+      <c r="E225" s="11">
         <v>0</v>
       </c>
-      <c r="G225">
+      <c r="G225" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M225" s="4"/>
+      <c r="M225" s="2"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" s="6" t="s">
+      <c r="A226" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="B226" s="6" t="s">
+      <c r="B226" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="C226" s="6" t="s">
+      <c r="C226" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D226" s="6">
+      <c r="D226" s="12">
         <v>0.89</v>
       </c>
-      <c r="E226">
-        <v>1</v>
-      </c>
-      <c r="G226">
+      <c r="E226" s="11">
+        <v>1</v>
+      </c>
+      <c r="G226" s="11">
         <v>0.35</v>
       </c>
-      <c r="M226" s="4"/>
+      <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13">
-      <c r="A227" s="6" t="s">
+      <c r="A227" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B227" s="6" t="s">
+      <c r="B227" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="C227" s="6" t="s">
+      <c r="C227" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D227" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E227">
+      <c r="D227" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E227" s="11">
         <v>0</v>
       </c>
-      <c r="G227">
+      <c r="G227" s="11">
         <v>0.88</v>
       </c>
-      <c r="J227">
+      <c r="J227" s="11">
         <v>0.85</v>
       </c>
-      <c r="M227" s="4"/>
+      <c r="M227" s="2"/>
     </row>
     <row r="228" spans="1:13">
-      <c r="A228" s="5" t="s">
+      <c r="A228" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C228" s="5" t="s">
+      <c r="C228" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="D228" s="5">
+      <c r="D228" s="13">
         <v>0</v>
       </c>
-      <c r="E228">
-        <v>1</v>
-      </c>
-      <c r="G228">
+      <c r="E228" s="11">
+        <v>1</v>
+      </c>
+      <c r="G228" s="11">
         <v>0.6</v>
       </c>
-      <c r="J228">
+      <c r="J228" s="11">
         <v>0.93</v>
       </c>
-      <c r="M228" s="4"/>
+      <c r="M228" s="2"/>
     </row>
     <row r="229" spans="1:13">
-      <c r="A229" s="6" t="s">
+      <c r="A229" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B229" s="6" t="s">
+      <c r="B229" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="C229" s="6" t="s">
+      <c r="C229" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D229" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E229">
+      <c r="D229" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E229" s="11">
         <v>0.95</v>
       </c>
-      <c r="G229">
+      <c r="G229" s="11">
         <v>0.81</v>
       </c>
-      <c r="M229" s="11"/>
+      <c r="M229" s="9"/>
     </row>
     <row r="230" spans="1:13">
-      <c r="A230" s="6" t="s">
+      <c r="A230" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B230" s="6" t="s">
+      <c r="B230" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="C230" s="6" t="s">
+      <c r="C230" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D230" s="6">
+      <c r="D230" s="12">
         <v>0.96</v>
       </c>
-      <c r="E230">
-        <v>0.98</v>
-      </c>
-      <c r="G230">
+      <c r="E230" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G230" s="11">
         <v>0.7</v>
       </c>
-      <c r="M230" s="11"/>
+      <c r="M230" s="9"/>
     </row>
     <row r="231" spans="1:13">
-      <c r="A231" s="6" t="s">
+      <c r="A231" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B231" s="6" t="s">
+      <c r="B231" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C231" s="6" t="s">
+      <c r="C231" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D231" s="6">
+      <c r="D231" s="12">
         <v>0.96</v>
       </c>
-      <c r="E231">
+      <c r="E231" s="11">
         <v>0.95</v>
       </c>
-      <c r="G231">
+      <c r="G231" s="11">
         <v>0.77</v>
       </c>
-      <c r="M231" s="11"/>
+      <c r="M231" s="9"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" t="s">
         <v>492</v>
       </c>
-      <c r="B232" s="9" t="s">
+      <c r="B232" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="C232" t="s">
+      <c r="C232" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D232" s="2">
+      <c r="D232" s="14">
         <v>0</v>
       </c>
-      <c r="E232">
+      <c r="E232" s="11">
         <v>0</v>
       </c>
-      <c r="G232">
+      <c r="G232" s="11">
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="233" spans="1:13">
-      <c r="A233" s="6" t="s">
+      <c r="A233" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B233" s="6" t="s">
+      <c r="B233" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="C233" s="6" t="s">
+      <c r="C233" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D233" s="6">
+      <c r="D233" s="12">
         <v>0.42</v>
       </c>
-      <c r="E233">
+      <c r="E233" s="11">
         <v>0.77</v>
       </c>
-      <c r="G233">
+      <c r="G233" s="11">
         <v>0.53</v>
       </c>
-      <c r="J233">
+      <c r="J233" s="11">
         <v>0.93</v>
       </c>
-      <c r="M233" s="11"/>
+      <c r="M233" s="9"/>
     </row>
     <row r="234" spans="1:13">
-      <c r="A234" s="6" t="s">
+      <c r="A234" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B234" s="6" t="s">
+      <c r="B234" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="C234" s="6" t="s">
+      <c r="C234" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D234" s="6">
+      <c r="D234" s="12">
         <v>0.88</v>
       </c>
-      <c r="E234">
-        <v>1</v>
-      </c>
-      <c r="G234">
+      <c r="E234" s="11">
+        <v>1</v>
+      </c>
+      <c r="G234" s="11">
         <v>0.69</v>
       </c>
-      <c r="M234" s="11"/>
+      <c r="M234" s="9"/>
     </row>
     <row r="235" spans="1:13">
-      <c r="A235" s="6" t="s">
+      <c r="A235" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="B235" s="6" t="s">
+      <c r="B235" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="C235" s="6" t="s">
+      <c r="C235" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D235" s="6">
+      <c r="D235" s="12">
         <v>0.78</v>
       </c>
-      <c r="E235">
+      <c r="E235" s="11">
         <v>0.95</v>
       </c>
-      <c r="G235">
+      <c r="G235" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="J235">
+      <c r="J235" s="11">
         <v>0.93</v>
       </c>
-      <c r="M235" s="11"/>
+      <c r="M235" s="9"/>
     </row>
     <row r="236" spans="1:13">
-      <c r="A236" s="6" t="s">
+      <c r="A236" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B236" s="6" t="s">
+      <c r="B236" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="C236" s="6" t="s">
+      <c r="C236" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D236" s="6">
+      <c r="D236" s="12">
         <v>0.96</v>
       </c>
-      <c r="E236">
+      <c r="E236" s="11">
         <v>0.93</v>
       </c>
-      <c r="G236">
+      <c r="G236" s="11">
         <v>0.64</v>
       </c>
-      <c r="M236" s="11"/>
+      <c r="M236" s="9"/>
     </row>
     <row r="237" spans="1:13">
-      <c r="A237" s="6" t="s">
+      <c r="A237" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B237" s="6" t="s">
+      <c r="B237" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="C237" s="6" t="s">
+      <c r="C237" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D237" s="6">
+      <c r="D237" s="12">
         <v>0.68</v>
       </c>
-      <c r="E237">
-        <v>1</v>
-      </c>
-      <c r="G237">
+      <c r="E237" s="11">
+        <v>1</v>
+      </c>
+      <c r="G237" s="11">
         <v>0.82</v>
       </c>
-      <c r="J237">
+      <c r="J237" s="11">
         <v>0.8</v>
       </c>
-      <c r="M237" s="11"/>
+      <c r="M237" s="9"/>
     </row>
     <row r="238" spans="1:13">
-      <c r="A238" s="6" t="s">
+      <c r="A238" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="B238" s="6" t="s">
+      <c r="B238" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="C238" s="6" t="s">
+      <c r="C238" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D238" s="6">
+      <c r="D238" s="12">
         <v>0.76</v>
       </c>
-      <c r="E238">
-        <v>0.98</v>
-      </c>
-      <c r="G238">
+      <c r="E238" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G238" s="11">
         <v>0.68</v>
       </c>
-      <c r="M238" s="11"/>
+      <c r="M238" s="9"/>
     </row>
     <row r="239" spans="1:13">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B239" s="6" t="s">
+      <c r="B239" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="C239" s="6" t="s">
+      <c r="C239" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D239" s="6">
+      <c r="D239" s="12">
         <v>0.41</v>
       </c>
-      <c r="E239">
+      <c r="E239" s="11">
         <v>0.63</v>
       </c>
-      <c r="G239">
+      <c r="G239" s="11">
         <v>0.43</v>
       </c>
-      <c r="M239" s="11"/>
+      <c r="M239" s="9"/>
     </row>
     <row r="240" spans="1:13">
-      <c r="A240" s="6" t="s">
+      <c r="A240" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B240" s="6" t="s">
+      <c r="B240" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C240" s="6" t="s">
+      <c r="C240" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D240" s="6">
+      <c r="D240" s="12">
         <v>0.8</v>
       </c>
-      <c r="E240">
+      <c r="E240" s="11">
         <v>0.88</v>
       </c>
-      <c r="G240">
+      <c r="G240" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M240" s="11"/>
+      <c r="M240" s="9"/>
     </row>
     <row r="241" spans="1:13">
       <c r="A241" t="s">
         <v>494</v>
       </c>
-      <c r="B241" s="9" t="s">
+      <c r="B241" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="C241" t="s">
+      <c r="C241" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D241" s="2">
+      <c r="D241" s="14">
         <v>0</v>
       </c>
-      <c r="E241">
+      <c r="E241" s="11">
         <v>0</v>
       </c>
-      <c r="G241">
+      <c r="G241" s="11">
         <v>0.49</v>
       </c>
     </row>
     <row r="242" spans="1:13">
-      <c r="A242" s="6" t="s">
+      <c r="A242" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B242" s="6" t="s">
+      <c r="B242" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C242" s="6" t="s">
+      <c r="C242" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D242" s="6">
+      <c r="D242" s="12">
         <v>0.91</v>
       </c>
-      <c r="E242">
+      <c r="E242" s="11">
         <v>0</v>
       </c>
-      <c r="G242">
+      <c r="G242" s="11">
         <v>0</v>
       </c>
-      <c r="M242" s="11"/>
+      <c r="M242" s="9"/>
     </row>
     <row r="243" spans="1:13">
-      <c r="A243" s="6" t="s">
+      <c r="A243" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B243" s="6" t="s">
+      <c r="B243" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C243" s="6" t="s">
+      <c r="C243" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D243" s="6">
+      <c r="D243" s="12">
         <v>0.91</v>
       </c>
-      <c r="E243">
+      <c r="E243" s="11">
         <v>0</v>
       </c>
-      <c r="G243">
+      <c r="G243" s="11">
         <v>0.77</v>
       </c>
-      <c r="M243" s="11"/>
+      <c r="M243" s="9"/>
     </row>
     <row r="244" spans="1:13">
-      <c r="A244" s="6" t="s">
+      <c r="A244" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B244" s="6" t="s">
+      <c r="B244" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="C244" s="6" t="s">
+      <c r="C244" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D244" s="6">
+      <c r="D244" s="12">
         <v>0.95</v>
       </c>
-      <c r="E244">
+      <c r="E244" s="11">
         <v>0.88</v>
       </c>
-      <c r="G244">
+      <c r="G244" s="11">
         <v>0.51</v>
       </c>
-      <c r="J244">
+      <c r="J244" s="11">
         <v>0.83</v>
       </c>
-      <c r="M244" s="11"/>
+      <c r="M244" s="9"/>
     </row>
     <row r="245" spans="1:13">
-      <c r="A245" s="6" t="s">
+      <c r="A245" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B245" s="6" t="s">
+      <c r="B245" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="C245" s="6" t="s">
+      <c r="C245" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D245" s="6">
+      <c r="D245" s="12">
         <v>0.97</v>
       </c>
-      <c r="E245">
-        <v>0.98</v>
-      </c>
-      <c r="G245">
+      <c r="E245" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G245" s="11">
         <v>0.78</v>
       </c>
-      <c r="J245">
+      <c r="J245" s="11">
         <v>0.8</v>
       </c>
-      <c r="M245" s="11"/>
+      <c r="M245" s="9"/>
     </row>
     <row r="246" spans="1:13">
       <c r="A246" t="s">
         <v>496</v>
       </c>
-      <c r="B246" s="9" t="s">
+      <c r="B246" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C246" t="s">
+      <c r="C246" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="14">
         <v>0</v>
       </c>
-      <c r="E246">
+      <c r="E246" s="11">
         <v>0</v>
       </c>
-      <c r="G246">
+      <c r="G246" s="11">
         <v>0.64</v>
       </c>
     </row>
     <row r="247" spans="1:13">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B247" s="6" t="s">
+      <c r="B247" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C247" s="6" t="s">
+      <c r="C247" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D247" s="6">
+      <c r="D247" s="12">
         <v>0.97</v>
       </c>
-      <c r="E247">
+      <c r="E247" s="11">
         <v>0.93</v>
       </c>
-      <c r="G247">
+      <c r="G247" s="11">
         <v>0.65</v>
       </c>
-      <c r="M247" s="11"/>
+      <c r="M247" s="9"/>
     </row>
     <row r="248" spans="1:13">
-      <c r="A248" s="6" t="s">
+      <c r="A248" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="B248" s="6" t="s">
+      <c r="B248" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="C248" s="6" t="s">
+      <c r="C248" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="D248" s="6">
+      <c r="D248" s="12">
         <v>0.88</v>
       </c>
-      <c r="E248">
+      <c r="E248" s="11">
         <v>0.95</v>
       </c>
-      <c r="G248">
+      <c r="G248" s="11">
         <v>0.71</v>
       </c>
-      <c r="J248">
+      <c r="J248" s="11">
         <v>0.93</v>
       </c>
-      <c r="M248" s="11"/>
+      <c r="M248" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103D5426-2658-9240-80EC-C566E575507C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30DE3FB-A1E7-FD40-9E52-FC57115828ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="620" windowWidth="30760" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1172,12 +1172,6 @@
     <t>H261064Q</t>
   </si>
   <si>
-    <t>Tapiwa</t>
-  </si>
-  <si>
-    <t>H260328</t>
-  </si>
-  <si>
     <t>KONDO</t>
   </si>
   <si>
@@ -1551,6 +1545,12 @@
   </si>
   <si>
     <t>H265349W</t>
+  </si>
+  <si>
+    <t>Chikamhi</t>
+  </si>
+  <si>
+    <t>H260915U</t>
   </si>
 </sst>
 </file>
@@ -1653,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1688,6 +1688,10 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1707,10 +1711,13 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1734,9 +1741,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1758,11 +1762,11 @@
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
-    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 " dataDxfId="1"/>
@@ -2206,10 +2210,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>15</v>
@@ -2677,10 +2681,10 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>15</v>
@@ -3558,10 +3562,10 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>15</v>
@@ -4153,10 +4157,10 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>159</v>
@@ -4177,10 +4181,10 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>159</v>
@@ -4228,10 +4232,10 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>159</v>
@@ -4327,10 +4331,10 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>159</v>
@@ -4519,10 +4523,10 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>159</v>
@@ -4543,10 +4547,10 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>159</v>
@@ -4687,10 +4691,10 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>159</v>
@@ -4738,10 +4742,10 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>159</v>
@@ -4909,10 +4913,10 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>159</v>
@@ -5005,10 +5009,10 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C116" s="13" t="s">
         <v>159</v>
@@ -5278,10 +5282,10 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C127" s="13" t="s">
         <v>159</v>
@@ -5377,10 +5381,10 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C131" s="13" t="s">
         <v>159</v>
@@ -5418,6 +5422,9 @@
       <c r="E132" s="11">
         <v>0.93</v>
       </c>
+      <c r="F132" s="11">
+        <v>0.93</v>
+      </c>
       <c r="G132" s="11">
         <v>0.56999999999999995</v>
       </c>
@@ -5442,6 +5449,9 @@
       <c r="E133" s="11">
         <v>0.95</v>
       </c>
+      <c r="F133" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G133" s="11">
         <v>0.62</v>
       </c>
@@ -5466,6 +5476,9 @@
       <c r="E134" s="11">
         <v>0.91</v>
       </c>
+      <c r="F134" s="11">
+        <v>1</v>
+      </c>
       <c r="G134" s="11">
         <v>0.53</v>
       </c>
@@ -5487,266 +5500,297 @@
       <c r="E135" s="11">
         <v>0.79</v>
       </c>
+      <c r="F135" s="11">
+        <v>0.9</v>
+      </c>
       <c r="G135" s="11">
         <v>0.52</v>
       </c>
       <c r="M135" s="2"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="C136" s="12" t="s">
+      <c r="A136" t="s">
+        <v>503</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="C136" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D136" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="E136" s="11">
-        <v>1</v>
-      </c>
-      <c r="G136" s="11">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="M136" s="2"/>
+      <c r="D136" s="14">
+        <v>0</v>
+      </c>
+      <c r="F136" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="G136" s="11"/>
+      <c r="M136" s="8"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="4" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D137" s="12">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="E137" s="11">
-        <v>0.88</v>
+        <v>1</v>
+      </c>
+      <c r="F137" s="11">
+        <v>1</v>
       </c>
       <c r="G137" s="11">
-        <v>0.47</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M137" s="2"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="4" t="s">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D138" s="12">
-        <v>0.91</v>
+        <v>0.69</v>
       </c>
       <c r="E138" s="11">
-        <v>0.86</v>
+        <v>0.88</v>
+      </c>
+      <c r="F138" s="11">
+        <v>0.92</v>
       </c>
       <c r="G138" s="11">
-        <v>0.64</v>
+        <v>0.47</v>
       </c>
       <c r="M138" s="2"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C139" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="12">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="E139" s="11">
-        <v>0.93</v>
+        <v>0.86</v>
+      </c>
+      <c r="F139" s="11">
+        <v>0.95</v>
       </c>
       <c r="G139" s="11">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
       <c r="M139" s="2"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="4" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D140" s="12">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="E140" s="11">
-        <v>0.98</v>
+        <v>0.93</v>
+      </c>
+      <c r="F140" s="11">
+        <v>0.92</v>
       </c>
       <c r="G140" s="11">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="M140" s="2"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="4" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="12">
+        <v>0.86</v>
+      </c>
+      <c r="E141" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F141" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="G141" s="11">
+        <v>0.51</v>
+      </c>
+      <c r="M141" s="2"/>
+    </row>
+    <row r="142" spans="1:13">
+      <c r="A142" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D142" s="12">
         <v>0.87</v>
       </c>
-      <c r="E141" s="11">
-        <v>1</v>
-      </c>
-      <c r="G141" s="11">
+      <c r="E142" s="11">
+        <v>1</v>
+      </c>
+      <c r="F142" s="11">
+        <v>1</v>
+      </c>
+      <c r="G142" s="11">
         <v>0.66</v>
       </c>
-      <c r="J141" s="11">
+      <c r="J142" s="11">
         <v>0.8</v>
       </c>
-      <c r="M141" s="2"/>
-    </row>
-    <row r="142" spans="1:13">
-      <c r="A142" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C142" s="13" t="s">
+      <c r="M142" s="2"/>
+    </row>
+    <row r="143" spans="1:13">
+      <c r="A143" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C143" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D142" s="13">
+      <c r="D143" s="13">
         <v>0</v>
       </c>
-      <c r="E142" s="11">
+      <c r="E143" s="11">
         <v>0.88</v>
       </c>
-      <c r="G142" s="11">
+      <c r="F143" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="G143" s="11">
         <v>0.6</v>
-      </c>
-      <c r="M142" s="2"/>
-    </row>
-    <row r="143" spans="1:13">
-      <c r="A143" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C143" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D143" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="E143" s="11">
-        <v>0.91</v>
-      </c>
-      <c r="G143" s="11">
-        <v>0.25</v>
       </c>
       <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="4" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D144" s="12">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
       <c r="E144" s="11">
+        <v>0.91</v>
+      </c>
+      <c r="F144" s="11">
         <v>0</v>
       </c>
       <c r="G144" s="11">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="M144" s="2"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="4" t="s">
-        <v>283</v>
+        <v>339</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D145" s="12">
-        <v>0.81</v>
+        <v>0.41</v>
       </c>
       <c r="E145" s="11">
         <v>0</v>
       </c>
+      <c r="F145" s="11">
+        <v>0.89</v>
+      </c>
       <c r="G145" s="11">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="M145" s="2"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="4" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D146" s="12">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="E146" s="11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F146" s="11">
+        <v>0.98</v>
       </c>
       <c r="G146" s="11">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J146" s="11">
-        <v>0.83</v>
+        <v>0.47</v>
       </c>
       <c r="M146" s="2"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="4" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C147" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="12">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="E147" s="11">
         <v>1</v>
       </c>
+      <c r="F147" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G147" s="11">
-        <v>0.53</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J147" s="11">
         <v>0.83</v>
@@ -5754,23 +5798,26 @@
       <c r="M147" s="2"/>
     </row>
     <row r="148" spans="1:13">
-      <c r="A148" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C148" s="13" t="s">
+      <c r="A148" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C148" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D148" s="13">
-        <v>0</v>
+      <c r="D148" s="12">
+        <v>0.86</v>
       </c>
       <c r="E148" s="11">
-        <v>0.86</v>
+        <v>1</v>
+      </c>
+      <c r="F148" s="11">
+        <v>0.95</v>
       </c>
       <c r="G148" s="11">
-        <v>0.56000000000000005</v>
+        <v>0.53</v>
       </c>
       <c r="J148" s="11">
         <v>0.83</v>
@@ -5778,437 +5825,500 @@
       <c r="M148" s="2"/>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C149" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D149" s="13">
+        <v>0</v>
+      </c>
+      <c r="E149" s="11">
+        <v>0.86</v>
+      </c>
+      <c r="F149" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="G149" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J149" s="11">
+        <v>0.83</v>
+      </c>
+      <c r="M149" s="2"/>
+    </row>
+    <row r="150" spans="1:13">
+      <c r="A150" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B150" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C149" s="12" t="s">
+      <c r="C150" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D149" s="12">
+      <c r="D150" s="12">
         <v>0.87</v>
       </c>
-      <c r="E149" s="11">
-        <v>1</v>
-      </c>
-      <c r="G149" s="11">
+      <c r="E150" s="11">
+        <v>1</v>
+      </c>
+      <c r="F150" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G150" s="11">
         <v>0.61</v>
       </c>
-      <c r="M149" s="2"/>
-    </row>
-    <row r="150" spans="1:13">
-      <c r="A150" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C150" s="13" t="s">
+      <c r="M150" s="2"/>
+    </row>
+    <row r="151" spans="1:13">
+      <c r="A151" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C151" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D150" s="13">
+      <c r="D151" s="13">
         <v>0</v>
       </c>
-      <c r="E150" s="11">
+      <c r="E151" s="11">
         <v>0.6</v>
       </c>
-      <c r="G150" s="11">
+      <c r="F151" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G151" s="11">
         <v>0.62</v>
-      </c>
-      <c r="M150" s="2"/>
-    </row>
-    <row r="151" spans="1:13">
-      <c r="A151" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C151" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D151" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="E151" s="11">
-        <v>1</v>
-      </c>
-      <c r="G151" s="11">
-        <v>0.56999999999999995</v>
       </c>
       <c r="M151" s="2"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="4" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D152" s="12">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="E152" s="11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F152" s="11">
+        <v>0.95</v>
       </c>
       <c r="G152" s="11">
-        <v>0.71</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M152" s="2"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="4" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="12">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="E153" s="11">
-        <v>0.98</v>
+        <v>0</v>
+      </c>
+      <c r="F153" s="11">
+        <v>0.95</v>
       </c>
       <c r="G153" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="M153" s="2"/>
+    </row>
+    <row r="154" spans="1:13">
+      <c r="A154" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D154" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E154" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F154" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G154" s="11">
         <v>0.45</v>
       </c>
-      <c r="J153" s="11">
+      <c r="J154" s="11">
         <v>0.83</v>
       </c>
-      <c r="M153" s="2"/>
-    </row>
-    <row r="154" spans="1:13">
-      <c r="A154" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C154" s="13" t="s">
+      <c r="M154" s="2"/>
+    </row>
+    <row r="155" spans="1:13">
+      <c r="A155" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C155" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="D154" s="13">
+      <c r="D155" s="13">
         <v>0</v>
       </c>
-      <c r="E154" s="11">
+      <c r="E155" s="11">
         <v>0.93</v>
       </c>
-      <c r="G154" s="11">
+      <c r="F155" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G155" s="11">
         <v>0.53</v>
       </c>
-      <c r="M154" s="2"/>
-    </row>
-    <row r="155" spans="1:13">
-      <c r="A155" s="4" t="s">
+      <c r="M155" s="2"/>
+    </row>
+    <row r="156" spans="1:13">
+      <c r="A156" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B156" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C155" s="12" t="s">
+      <c r="C156" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D155" s="12">
+      <c r="D156" s="12">
         <v>0.75</v>
       </c>
-      <c r="E155" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G155" s="11">
+      <c r="E156" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F156" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G156" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M155" s="2"/>
-    </row>
-    <row r="156" spans="1:13">
-      <c r="A156" t="s">
-        <v>479</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="C156" s="11" t="s">
+      <c r="M156" s="2"/>
+    </row>
+    <row r="157" spans="1:13">
+      <c r="A157" t="s">
+        <v>477</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="C157" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D156" s="14">
+      <c r="D157" s="14">
         <v>0</v>
       </c>
-      <c r="E156" s="11">
-        <v>1</v>
-      </c>
-      <c r="G156" s="11">
+      <c r="E157" s="11">
+        <v>1</v>
+      </c>
+      <c r="F157" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G157" s="11">
         <v>0.52</v>
       </c>
-      <c r="M156" s="8"/>
-    </row>
-    <row r="157" spans="1:13">
-      <c r="A157" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="C157" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D157" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="E157" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="G157" s="11">
-        <v>0.47</v>
-      </c>
-      <c r="M157" s="2"/>
+      <c r="M157" s="8"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="4" t="s">
-        <v>246</v>
+        <v>329</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D158" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="E158" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="F158" s="11">
+        <v>0.87</v>
+      </c>
+      <c r="G158" s="11">
+        <v>0.47</v>
+      </c>
+      <c r="M158" s="2"/>
+    </row>
+    <row r="159" spans="1:13">
+      <c r="A159" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D159" s="12">
         <v>0.88</v>
       </c>
-      <c r="E158" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G158" s="11">
+      <c r="E159" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F159" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="G159" s="11">
         <v>0.61</v>
       </c>
-      <c r="M158" s="2"/>
-    </row>
-    <row r="159" spans="1:13">
-      <c r="A159" t="s">
-        <v>468</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="C159" s="11" t="s">
+      <c r="M159" s="2"/>
+    </row>
+    <row r="160" spans="1:13">
+      <c r="A160" t="s">
+        <v>466</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C160" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D159" s="14">
+      <c r="D160" s="14">
         <v>0</v>
       </c>
-      <c r="E159" s="11">
-        <v>1</v>
-      </c>
-      <c r="G159" s="11">
+      <c r="E160" s="11">
+        <v>1</v>
+      </c>
+      <c r="F160" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G160" s="11">
         <v>0.39</v>
       </c>
-      <c r="M159" s="8"/>
-    </row>
-    <row r="160" spans="1:13">
-      <c r="A160" s="4" t="s">
+      <c r="M160" s="8"/>
+    </row>
+    <row r="161" spans="1:13">
+      <c r="A161" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B161" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C160" s="12" t="s">
+      <c r="C161" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D160" s="12">
+      <c r="D161" s="12">
         <v>0.71</v>
       </c>
-      <c r="E160" s="11">
+      <c r="E161" s="11">
         <v>0.88</v>
       </c>
-      <c r="G160" s="11">
+      <c r="F161" s="11">
+        <v>0.82</v>
+      </c>
+      <c r="G161" s="11">
         <v>0.53</v>
       </c>
-      <c r="M160" s="2"/>
-    </row>
-    <row r="161" spans="1:13">
-      <c r="A161" t="s">
-        <v>477</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="C161" s="11" t="s">
+      <c r="M161" s="2"/>
+    </row>
+    <row r="162" spans="1:13">
+      <c r="A162" t="s">
+        <v>475</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C162" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D161" s="14">
+      <c r="D162" s="14">
         <v>0</v>
       </c>
-      <c r="E161" s="11">
+      <c r="E162" s="11">
         <v>0</v>
       </c>
-      <c r="G161" s="11">
+      <c r="F162" s="11">
+        <v>0</v>
+      </c>
+      <c r="G162" s="11">
         <v>0.45</v>
       </c>
-      <c r="M161" s="8"/>
-    </row>
-    <row r="162" spans="1:13">
-      <c r="A162" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C162" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D162" s="12">
-        <v>0.74</v>
-      </c>
-      <c r="E162" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G162" s="11">
-        <v>0.62</v>
-      </c>
-      <c r="M162" s="2"/>
+      <c r="M162" s="8"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C163" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D163" s="12">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="E163" s="11">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F163" s="11">
+        <v>0.92</v>
       </c>
       <c r="G163" s="11">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="M163" s="2"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="4" t="s">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D164" s="12">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="E164" s="11">
-        <v>0.84</v>
+        <v>1</v>
+      </c>
+      <c r="F164" s="11">
+        <v>0.95</v>
       </c>
       <c r="G164" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="J164" s="11">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
       <c r="M164" s="2"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="4" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D165" s="12">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E165" s="11">
         <v>0.84</v>
       </c>
+      <c r="F165" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G165" s="11">
-        <v>0.71</v>
+        <v>0.75</v>
+      </c>
+      <c r="J165" s="11">
+        <v>0.83</v>
       </c>
       <c r="M165" s="2"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="4" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D166" s="12">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="E166" s="11">
         <v>0.84</v>
       </c>
+      <c r="F166" s="11">
+        <v>0.76</v>
+      </c>
       <c r="G166" s="11">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="M166" s="2"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D167" s="12">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="E167" s="11">
-        <v>1</v>
+        <v>0.84</v>
+      </c>
+      <c r="F167" s="11">
+        <v>0.82</v>
       </c>
       <c r="G167" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="M167" s="2"/>
+    </row>
+    <row r="168" spans="1:13">
+      <c r="A168" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D168" s="12">
+        <v>1</v>
+      </c>
+      <c r="E168" s="11">
+        <v>1</v>
+      </c>
+      <c r="F168" s="11">
+        <v>0</v>
+      </c>
+      <c r="G168" s="11">
         <v>0.74</v>
       </c>
-      <c r="M167" s="2"/>
-    </row>
-    <row r="168" spans="1:13">
-      <c r="A168" t="s">
-        <v>470</v>
-      </c>
-      <c r="B168" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="C168" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D168" s="14">
-        <v>0</v>
-      </c>
-      <c r="E168" s="11">
-        <v>0.91</v>
-      </c>
-      <c r="G168" s="11">
-        <v>0.71</v>
-      </c>
-      <c r="M168" s="8"/>
+      <c r="M168" s="2"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>245</v>
@@ -6217,403 +6327,460 @@
         <v>0</v>
       </c>
       <c r="E169" s="11">
-        <v>0.98</v>
+        <v>0.91</v>
+      </c>
+      <c r="F169" s="11">
+        <v>0.87</v>
       </c>
       <c r="G169" s="11">
+        <v>0.71</v>
+      </c>
+      <c r="M169" s="8"/>
+    </row>
+    <row r="170" spans="1:13">
+      <c r="A170" t="s">
+        <v>470</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D170" s="14">
+        <v>0</v>
+      </c>
+      <c r="E170" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F170" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G170" s="11">
         <v>0.38</v>
       </c>
-      <c r="M169" s="8"/>
-    </row>
-    <row r="170" spans="1:13">
-      <c r="A170" s="4" t="s">
+      <c r="M170" s="8"/>
+    </row>
+    <row r="171" spans="1:13">
+      <c r="A171" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B171" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C170" s="12" t="s">
+      <c r="C171" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D170" s="12">
+      <c r="D171" s="12">
         <v>0.81</v>
       </c>
-      <c r="E170" s="11">
+      <c r="E171" s="11">
         <v>0.95</v>
       </c>
-      <c r="G170" s="11">
+      <c r="F171" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="G171" s="11">
         <v>0.44</v>
       </c>
-      <c r="M170" s="2"/>
-    </row>
-    <row r="171" spans="1:13">
-      <c r="A171" t="s">
-        <v>388</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="C171" s="11" t="s">
+      <c r="M171" s="2"/>
+    </row>
+    <row r="172" spans="1:13">
+      <c r="A172" t="s">
+        <v>386</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="C172" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D171" s="14">
+      <c r="D172" s="14">
         <v>0</v>
       </c>
-      <c r="E171" s="11">
-        <v>1</v>
-      </c>
-      <c r="G171" s="11">
+      <c r="E172" s="11">
+        <v>1</v>
+      </c>
+      <c r="F172" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G172" s="11">
         <v>0.51</v>
       </c>
-      <c r="M171" s="8"/>
-    </row>
-    <row r="172" spans="1:13">
-      <c r="A172" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="C172" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D172" s="12">
-        <v>0.84</v>
-      </c>
-      <c r="E172" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G172" s="11">
-        <v>0.49</v>
-      </c>
-      <c r="M172" s="2"/>
+      <c r="M172" s="8"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="4" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="C173" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D173" s="12">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="E173" s="11">
-        <v>0</v>
+        <v>0.98</v>
+      </c>
+      <c r="F173" s="11">
+        <v>0.88</v>
       </c>
       <c r="G173" s="11">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J173" s="11">
-        <v>0.83</v>
+        <v>0.49</v>
       </c>
       <c r="M173" s="2"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="4" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D174" s="12">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="E174" s="11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F174" s="11">
+        <v>0.76</v>
       </c>
       <c r="G174" s="11">
-        <v>0.69</v>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J174" s="11">
+        <v>0.83</v>
       </c>
       <c r="M174" s="2"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="4" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="C175" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D175" s="12">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="E175" s="11">
-        <v>0.98</v>
+        <v>1</v>
+      </c>
+      <c r="F175" s="11">
+        <v>0.93</v>
       </c>
       <c r="G175" s="11">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="M175" s="2"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C176" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D176" s="12">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="E176" s="11">
-        <v>0.81</v>
+        <v>0.98</v>
+      </c>
+      <c r="F176" s="11">
+        <v>0.93</v>
       </c>
       <c r="G176" s="11">
-        <v>0.56000000000000005</v>
+        <v>0.65</v>
       </c>
       <c r="M176" s="2"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="4" t="s">
-        <v>461</v>
+        <v>295</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D177" s="12">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E177" s="11">
-        <v>0.88</v>
+        <v>0.81</v>
+      </c>
+      <c r="F177" s="11">
+        <v>0.82</v>
       </c>
       <c r="G177" s="11">
-        <v>0.62</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M177" s="2"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="4" t="s">
-        <v>301</v>
+        <v>459</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D178" s="12">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="E178" s="11">
-        <v>0.98</v>
+        <v>0.88</v>
+      </c>
+      <c r="F178" s="11">
+        <v>0.83</v>
       </c>
       <c r="G178" s="11">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="M178" s="2"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="4" t="s">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>244</v>
+        <v>302</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D179" s="12">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="E179" s="11">
-        <v>0.93</v>
+        <v>0.98</v>
+      </c>
+      <c r="F179" s="11">
+        <v>0.95</v>
       </c>
       <c r="G179" s="11">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="M179" s="2"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="4" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="C180" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D180" s="12">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="E180" s="11">
         <v>0.93</v>
       </c>
+      <c r="F180" s="11">
+        <v>0.92</v>
+      </c>
       <c r="G180" s="11">
+        <v>0.61</v>
+      </c>
+      <c r="M180" s="2"/>
+    </row>
+    <row r="181" spans="1:13">
+      <c r="A181" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D181" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="E181" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="F181" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G181" s="11">
         <v>0.36</v>
       </c>
-      <c r="M180" s="2"/>
-    </row>
-    <row r="181" spans="1:13">
-      <c r="A181" t="s">
-        <v>475</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="C181" s="11" t="s">
+      <c r="M181" s="2"/>
+    </row>
+    <row r="182" spans="1:13">
+      <c r="A182" t="s">
+        <v>473</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C182" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D181" s="14">
+      <c r="D182" s="14">
         <v>0</v>
       </c>
-      <c r="E181" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G181" s="11">
+      <c r="E182" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F182" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="G182" s="11">
         <v>0.68</v>
       </c>
-      <c r="M181" s="8"/>
-    </row>
-    <row r="182" spans="1:13">
-      <c r="A182" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="C182" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D182" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="E182" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G182" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="M182" s="2"/>
+      <c r="M182" s="8"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="4" t="s">
-        <v>331</v>
+        <v>248</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C183" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D183" s="12">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="E183" s="11">
         <v>0.98</v>
       </c>
+      <c r="F183" s="11">
+        <v>0.88</v>
+      </c>
       <c r="G183" s="11">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="M183" s="2"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="4" t="s">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D184" s="12">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E184" s="11">
-        <v>0.95</v>
+        <v>0.98</v>
+      </c>
+      <c r="F184" s="11">
+        <v>0.87</v>
       </c>
       <c r="G184" s="11">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="M184" s="2"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="4" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C185" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D185" s="12">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E185" s="11">
-        <v>1</v>
+        <v>0.95</v>
+      </c>
+      <c r="F185" s="11">
+        <v>0.93</v>
       </c>
       <c r="G185" s="11">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="M185" s="2"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="4" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D186" s="12">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="E186" s="11">
         <v>1</v>
       </c>
+      <c r="F186" s="11">
+        <v>0</v>
+      </c>
       <c r="G186" s="11">
-        <v>0.53</v>
-      </c>
-      <c r="J186" s="11">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M186" s="2"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="4" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C187" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D187" s="12">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="E187" s="11">
-        <v>0.65</v>
+        <v>1</v>
+      </c>
+      <c r="F187" s="11">
+        <v>0.95</v>
       </c>
       <c r="G187" s="11">
-        <v>0.32</v>
+        <v>0.53</v>
+      </c>
+      <c r="J187" s="11">
+        <v>0.8</v>
       </c>
       <c r="M187" s="2"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="4" t="s">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>245</v>
@@ -6622,234 +6789,267 @@
         <v>0.81</v>
       </c>
       <c r="E188" s="11">
-        <v>0.95</v>
+        <v>0.65</v>
+      </c>
+      <c r="F188" s="11">
+        <v>0.88</v>
       </c>
       <c r="G188" s="11">
-        <v>0.82</v>
-      </c>
-      <c r="J188" s="11">
-        <v>0.83</v>
+        <v>0.32</v>
       </c>
       <c r="M188" s="2"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="4" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D189" s="12">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="E189" s="11">
-        <v>0.91</v>
+        <v>0.95</v>
+      </c>
+      <c r="F189" s="11">
+        <v>0.95</v>
       </c>
       <c r="G189" s="11">
-        <v>0.73</v>
+        <v>0.82</v>
+      </c>
+      <c r="J189" s="11">
+        <v>0.83</v>
       </c>
       <c r="M189" s="2"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="4" t="s">
-        <v>321</v>
+        <v>281</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D190" s="12">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E190" s="11">
-        <v>1</v>
+        <v>0.91</v>
+      </c>
+      <c r="F190" s="11">
+        <v>0.95</v>
       </c>
       <c r="G190" s="11">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="M190" s="2"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>245</v>
       </c>
       <c r="D191" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="E191" s="11">
-        <v>0.93</v>
+        <v>1</v>
+      </c>
+      <c r="F191" s="11">
+        <v>1</v>
       </c>
       <c r="G191" s="11">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="M191" s="2"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="4" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="D192" s="12">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="E192" s="11">
-        <v>1</v>
+        <v>0.93</v>
+      </c>
+      <c r="F192" s="11">
+        <v>0.9</v>
       </c>
       <c r="G192" s="11">
-        <v>0.75</v>
-      </c>
-      <c r="J192" s="11">
-        <v>0.8</v>
+        <v>0.51</v>
       </c>
       <c r="M192" s="2"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="4" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D193" s="12">
+        <v>0.77</v>
+      </c>
+      <c r="E193" s="11">
+        <v>1</v>
+      </c>
+      <c r="F193" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="G193" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="J193" s="11">
         <v>0.8</v>
-      </c>
-      <c r="E193" s="11">
-        <v>0.95</v>
-      </c>
-      <c r="G193" s="11">
-        <v>0.64</v>
-      </c>
-      <c r="J193" s="11">
-        <v>0.85</v>
       </c>
       <c r="M193" s="2"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="4" t="s">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>431</v>
+        <v>391</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D194" s="12">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="E194" s="11">
-        <v>0.91</v>
+        <v>0.95</v>
+      </c>
+      <c r="F194" s="11">
+        <v>0.93</v>
       </c>
       <c r="G194" s="11">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="J194" s="11">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="M194" s="2"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="4" t="s">
-        <v>364</v>
+        <v>428</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D195" s="12">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="E195" s="11">
-        <v>1</v>
+        <v>0.91</v>
+      </c>
+      <c r="F195" s="11">
+        <v>0.93</v>
       </c>
       <c r="G195" s="11">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="J195" s="11">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="M195" s="2"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="4" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C196" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D196" s="12">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="E196" s="11">
         <v>1</v>
       </c>
+      <c r="F196" s="11">
+        <v>0.98</v>
+      </c>
       <c r="G196" s="11">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="J196" s="11">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M196" s="2"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="4" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D197" s="12">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="E197" s="11">
         <v>1</v>
       </c>
+      <c r="F197" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G197" s="11">
-        <v>0.64</v>
+        <v>0.7</v>
+      </c>
+      <c r="J197" s="11">
+        <v>0.8</v>
       </c>
       <c r="M197" s="2"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="4" t="s">
-        <v>434</v>
+        <v>372</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D198" s="12">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="E198" s="11">
+        <v>1</v>
+      </c>
+      <c r="F198" s="11">
         <v>0.86</v>
       </c>
       <c r="G198" s="11">
@@ -6859,709 +7059,805 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="4" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D199" s="12">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="E199" s="11">
-        <v>0.91</v>
+        <v>0.86</v>
+      </c>
+      <c r="F199" s="11">
+        <v>0.93</v>
       </c>
       <c r="G199" s="11">
-        <v>0.65</v>
-      </c>
-      <c r="J199" s="11">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="M199" s="2"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="4" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D200" s="12">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="E200" s="11">
         <v>0.91</v>
       </c>
+      <c r="F200" s="11">
+        <v>1</v>
+      </c>
       <c r="G200" s="11">
-        <v>0.69</v>
+        <v>0.65</v>
+      </c>
+      <c r="J200" s="11">
+        <v>0.77</v>
       </c>
       <c r="M200" s="2"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D201" s="12">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="E201" s="11">
         <v>0.91</v>
       </c>
+      <c r="F201" s="11">
+        <v>0.9</v>
+      </c>
       <c r="G201" s="11">
-        <v>0.56999999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="M201" s="2"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="4" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D202" s="12">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="E202" s="11">
-        <v>0.95</v>
+        <v>0.91</v>
+      </c>
+      <c r="F202" s="11">
+        <v>0.98</v>
       </c>
       <c r="G202" s="11">
-        <v>0.78</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M202" s="2"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="4" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C203" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D203" s="12">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="E203" s="11">
-        <v>0.42</v>
+        <v>0.95</v>
+      </c>
+      <c r="F203" s="11">
+        <v>1</v>
       </c>
       <c r="G203" s="11">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="M203" s="2"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D204" s="12">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="E204" s="11">
-        <v>0.95</v>
+        <v>0.42</v>
+      </c>
+      <c r="F204" s="11">
+        <v>0.43</v>
       </c>
       <c r="G204" s="11">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="J204" s="11">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="M204" s="2"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C205" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D205" s="12">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="E205" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="F205" s="11">
         <v>0.98</v>
       </c>
       <c r="G205" s="11">
-        <v>0.55000000000000004</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J205" s="11">
+        <v>0.83</v>
       </c>
       <c r="M205" s="2"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="4" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D206" s="12">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="E206" s="11">
         <v>0.98</v>
       </c>
+      <c r="F206" s="11">
+        <v>0.87</v>
+      </c>
       <c r="G206" s="11">
-        <v>0.73</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M206" s="2"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="4" t="s">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>361</v>
+        <v>413</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D207" s="12">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="E207" s="11">
-        <v>0.91</v>
+        <v>0.98</v>
+      </c>
+      <c r="F207" s="11">
+        <v>0.98</v>
       </c>
       <c r="G207" s="11">
-        <v>0.82</v>
-      </c>
-      <c r="J207" s="11">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M207" s="2"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="4" t="s">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="C208" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D208" s="12">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="E208" s="11">
-        <v>1</v>
+        <v>0.91</v>
+      </c>
+      <c r="F208" s="11">
+        <v>0.82</v>
       </c>
       <c r="G208" s="11">
-        <v>0.64</v>
+        <v>0.82</v>
+      </c>
+      <c r="J208" s="11">
+        <v>0.8</v>
       </c>
       <c r="M208" s="2"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="4" t="s">
-        <v>366</v>
+        <v>424</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>367</v>
+        <v>425</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D209" s="12">
-        <v>0.81</v>
+        <v>0.92</v>
       </c>
       <c r="E209" s="11">
-        <v>0.88</v>
+        <v>1</v>
+      </c>
+      <c r="F209" s="11">
+        <v>0.93</v>
       </c>
       <c r="G209" s="11">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M209" s="2"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="4" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="C210" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D210" s="12">
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
       <c r="E210" s="11">
-        <v>0.98</v>
+        <v>0.88</v>
+      </c>
+      <c r="F210" s="11">
+        <v>0.87</v>
       </c>
       <c r="G210" s="11">
-        <v>0.56000000000000005</v>
+        <v>0.7</v>
       </c>
       <c r="M210" s="2"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="4" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="C211" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D211" s="12">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="E211" s="11">
-        <v>0.91</v>
+        <v>0.98</v>
+      </c>
+      <c r="F211" s="11">
+        <v>0.9</v>
       </c>
       <c r="G211" s="11">
-        <v>0.81</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M211" s="2"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="4" t="s">
-        <v>341</v>
+        <v>402</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>342</v>
+        <v>403</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D212" s="12">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="E212" s="11">
-        <v>0.88</v>
+        <v>0.91</v>
+      </c>
+      <c r="F212" s="11">
+        <v>0</v>
       </c>
       <c r="G212" s="11">
-        <v>0.71</v>
-      </c>
-      <c r="J212" s="11">
-        <v>0.83</v>
+        <v>0.81</v>
       </c>
       <c r="M212" s="2"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="4" t="s">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>407</v>
+        <v>342</v>
       </c>
       <c r="C213" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D213" s="12">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="E213" s="11">
-        <v>0.95</v>
+        <v>0.88</v>
+      </c>
+      <c r="F213" s="11">
+        <v>1</v>
       </c>
       <c r="G213" s="11">
-        <v>0.49</v>
+        <v>0.71</v>
+      </c>
+      <c r="J213" s="11">
+        <v>0.83</v>
       </c>
       <c r="M213" s="2"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="4" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C214" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D214" s="12">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="E214" s="11">
-        <v>0.91</v>
+        <v>0.95</v>
+      </c>
+      <c r="F214" s="11">
+        <v>0.94</v>
       </c>
       <c r="G214" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="J214" s="11">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="M214" s="2"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="4" t="s">
-        <v>446</v>
+        <v>370</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D215" s="12">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="E215" s="11">
-        <v>1</v>
+        <v>0.91</v>
+      </c>
+      <c r="F215" s="11">
+        <v>0.94</v>
       </c>
       <c r="G215" s="11">
-        <v>0.75</v>
+        <v>0.6</v>
+      </c>
+      <c r="J215" s="11">
+        <v>0.85</v>
       </c>
       <c r="M215" s="2"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="4" t="s">
-        <v>368</v>
+        <v>444</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>369</v>
+        <v>445</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D216" s="12">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="E216" s="11">
-        <v>0.98</v>
+        <v>1</v>
+      </c>
+      <c r="F216" s="11">
+        <v>0.95</v>
       </c>
       <c r="G216" s="11">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="M216" s="2"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="4" t="s">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D217" s="12">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="E217" s="11">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F217" s="11">
+        <v>0.98</v>
       </c>
       <c r="G217" s="11">
-        <v>0.73</v>
+        <v>0.69</v>
       </c>
       <c r="M217" s="2"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="4" t="s">
-        <v>344</v>
+        <v>408</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D218" s="12">
-        <v>0.81</v>
+        <v>0.96</v>
       </c>
       <c r="E218" s="11">
-        <v>0.95</v>
+        <v>1</v>
+      </c>
+      <c r="F218" s="11">
+        <v>0.92</v>
       </c>
       <c r="G218" s="11">
         <v>0.73</v>
       </c>
-      <c r="J218" s="11">
-        <v>0.79</v>
-      </c>
       <c r="M218" s="2"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="4" t="s">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="C219" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D219" s="12">
-        <v>0.96</v>
+        <v>0.81</v>
       </c>
       <c r="E219" s="11">
-        <v>0.98</v>
+        <v>0.95</v>
+      </c>
+      <c r="F219" s="11">
+        <v>0.93</v>
       </c>
       <c r="G219" s="11">
-        <v>0.69</v>
+        <v>0.73</v>
+      </c>
+      <c r="J219" s="11">
+        <v>0.79</v>
       </c>
       <c r="M219" s="2"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="4" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D220" s="12">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="E220" s="11">
-        <v>0.86</v>
+        <v>0.98</v>
+      </c>
+      <c r="F220" s="11">
+        <v>1</v>
       </c>
       <c r="G220" s="11">
-        <v>0.83</v>
+        <v>0.69</v>
       </c>
       <c r="M220" s="2"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="4" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D221" s="12">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="E221" s="11">
-        <v>0.98</v>
+        <v>0.86</v>
+      </c>
+      <c r="F221" s="11">
+        <v>0.86</v>
       </c>
       <c r="G221" s="11">
-        <v>0.56999999999999995</v>
+        <v>0.83</v>
       </c>
       <c r="M221" s="2"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="4" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D222" s="12">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="E222" s="11">
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="F222" s="11">
+        <v>0.8</v>
       </c>
       <c r="G222" s="11">
-        <v>0.77</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M222" s="2"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="4" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D223" s="12">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E223" s="11">
-        <v>0.88</v>
+        <v>1</v>
+      </c>
+      <c r="F223" s="11">
+        <v>0.95</v>
       </c>
       <c r="G223" s="11">
         <v>0.77</v>
       </c>
-      <c r="J223" s="11">
-        <v>0.93</v>
-      </c>
       <c r="M223" s="2"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="4" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D224" s="12">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="E224" s="11">
-        <v>0.98</v>
+        <v>0.88</v>
+      </c>
+      <c r="F224" s="11">
+        <v>0.94</v>
       </c>
       <c r="G224" s="11">
-        <v>0.74</v>
+        <v>0.77</v>
+      </c>
+      <c r="J224" s="11">
+        <v>0.93</v>
       </c>
       <c r="M224" s="2"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="4" t="s">
-        <v>356</v>
+        <v>430</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>357</v>
+        <v>431</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D225" s="12">
-        <v>0.55000000000000004</v>
+        <v>0.91</v>
       </c>
       <c r="E225" s="11">
-        <v>0</v>
+        <v>0.98</v>
+      </c>
+      <c r="F225" s="11">
+        <v>0.93</v>
       </c>
       <c r="G225" s="11">
-        <v>0.57999999999999996</v>
+        <v>0.74</v>
       </c>
       <c r="M225" s="2"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="4" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="C226" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D226" s="12">
-        <v>0.89</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E226" s="11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F226" s="11">
+        <v>0.78</v>
       </c>
       <c r="G226" s="11">
-        <v>0.35</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="4" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="C227" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D227" s="12">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="E227" s="11">
+        <v>1</v>
+      </c>
+      <c r="F227" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G227" s="11">
+        <v>0.35</v>
+      </c>
+      <c r="M227" s="2"/>
+    </row>
+    <row r="228" spans="1:13">
+      <c r="A228" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D228" s="12">
+        <v>0.98</v>
+      </c>
+      <c r="E228" s="11">
         <v>0</v>
       </c>
-      <c r="G227" s="11">
+      <c r="F228" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G228" s="11">
         <v>0.88</v>
       </c>
-      <c r="J227" s="11">
+      <c r="J228" s="11">
         <v>0.85</v>
       </c>
-      <c r="M227" s="2"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C228" s="13" t="s">
+      <c r="M228" s="2"/>
+    </row>
+    <row r="229" spans="1:13">
+      <c r="A229" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C229" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="D228" s="13">
+      <c r="D229" s="13">
         <v>0</v>
       </c>
-      <c r="E228" s="11">
-        <v>1</v>
-      </c>
-      <c r="G228" s="11">
+      <c r="E229" s="11">
+        <v>1</v>
+      </c>
+      <c r="F229" s="11">
+        <v>1</v>
+      </c>
+      <c r="G229" s="11">
         <v>0.6</v>
       </c>
-      <c r="J228" s="11">
+      <c r="J229" s="11">
         <v>0.93</v>
       </c>
-      <c r="M228" s="2"/>
-    </row>
-    <row r="229" spans="1:13">
-      <c r="A229" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="B229" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="C229" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D229" s="12">
-        <v>0.98</v>
-      </c>
-      <c r="E229" s="11">
-        <v>0.95</v>
-      </c>
-      <c r="G229" s="11">
-        <v>0.81</v>
-      </c>
-      <c r="M229" s="9"/>
+      <c r="M229" s="16"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="4" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="C230" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D230" s="12">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="E230" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="F230" s="11">
         <v>0.98</v>
       </c>
       <c r="G230" s="11">
-        <v>0.7</v>
-      </c>
-      <c r="M230" s="9"/>
+        <v>0.81</v>
+      </c>
+      <c r="M230" s="16"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="4" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="C231" s="12" t="s">
         <v>343</v>
@@ -7570,257 +7866,294 @@
         <v>0.96</v>
       </c>
       <c r="E231" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="F231" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G231" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="M231" s="16"/>
+    </row>
+    <row r="232" spans="1:13">
+      <c r="A232" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D232" s="12">
+        <v>0.96</v>
+      </c>
+      <c r="E232" s="11">
         <v>0.95</v>
       </c>
-      <c r="G231" s="11">
+      <c r="F232" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="G232" s="11">
         <v>0.77</v>
       </c>
-      <c r="M231" s="9"/>
-    </row>
-    <row r="232" spans="1:13">
-      <c r="A232" t="s">
-        <v>492</v>
-      </c>
-      <c r="B232" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="C232" s="11" t="s">
+      <c r="M232" s="16"/>
+    </row>
+    <row r="233" spans="1:13">
+      <c r="A233" t="s">
+        <v>490</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="C233" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D232" s="14">
+      <c r="D233" s="14">
+        <v>0.91</v>
+      </c>
+      <c r="E233" s="11">
         <v>0</v>
       </c>
-      <c r="E232" s="11">
-        <v>0</v>
-      </c>
-      <c r="G232" s="11">
+      <c r="F233" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="G233" s="11">
         <v>0.57999999999999996</v>
       </c>
-    </row>
-    <row r="233" spans="1:13">
-      <c r="A233" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="C233" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D233" s="12">
-        <v>0.42</v>
-      </c>
-      <c r="E233" s="11">
-        <v>0.77</v>
-      </c>
-      <c r="G233" s="11">
-        <v>0.53</v>
-      </c>
-      <c r="J233" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="M233" s="9"/>
+      <c r="M233" s="17"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="C234" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D234" s="12">
+        <v>0.42</v>
+      </c>
+      <c r="E234" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="F234" s="11">
         <v>0.88</v>
       </c>
-      <c r="E234" s="11">
-        <v>1</v>
-      </c>
       <c r="G234" s="11">
-        <v>0.69</v>
-      </c>
-      <c r="M234" s="9"/>
+        <v>0.53</v>
+      </c>
+      <c r="J234" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="M234" s="16"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="4" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C235" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D235" s="12">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="E235" s="11">
-        <v>0.95</v>
+        <v>1</v>
+      </c>
+      <c r="F235" s="11">
+        <v>0.98</v>
       </c>
       <c r="G235" s="11">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J235" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="M235" s="9"/>
+        <v>0.69</v>
+      </c>
+      <c r="M235" s="16"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="4" t="s">
-        <v>362</v>
+        <v>442</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>363</v>
+        <v>443</v>
       </c>
       <c r="C236" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D236" s="12">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="E236" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="F236" s="11">
+        <v>0.92</v>
+      </c>
+      <c r="G236" s="11">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J236" s="11">
         <v>0.93</v>
       </c>
-      <c r="G236" s="11">
-        <v>0.64</v>
-      </c>
-      <c r="M236" s="9"/>
+      <c r="M236" s="16"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="4" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C237" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D237" s="12">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="E237" s="11">
-        <v>1</v>
+        <v>0.93</v>
+      </c>
+      <c r="F237" s="11">
+        <v>0.95</v>
       </c>
       <c r="G237" s="11">
-        <v>0.82</v>
-      </c>
-      <c r="J237" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="M237" s="9"/>
+        <v>0.64</v>
+      </c>
+      <c r="M237" s="16"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="4" t="s">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="C238" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D238" s="12">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="E238" s="11">
+        <v>1</v>
+      </c>
+      <c r="F238" s="11">
         <v>0.98</v>
       </c>
       <c r="G238" s="11">
-        <v>0.68</v>
-      </c>
-      <c r="M238" s="9"/>
+        <v>0.82</v>
+      </c>
+      <c r="J238" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="M238" s="16"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="4" t="s">
-        <v>428</v>
+        <v>388</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>429</v>
+        <v>389</v>
       </c>
       <c r="C239" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D239" s="12">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="E239" s="11">
-        <v>0.63</v>
+        <v>0.98</v>
+      </c>
+      <c r="F239" s="11">
+        <v>0.93</v>
       </c>
       <c r="G239" s="11">
-        <v>0.43</v>
-      </c>
-      <c r="M239" s="9"/>
+        <v>0.68</v>
+      </c>
+      <c r="M239" s="16"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="4" t="s">
-        <v>346</v>
+        <v>426</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>347</v>
+        <v>427</v>
       </c>
       <c r="C240" s="12" t="s">
         <v>343</v>
       </c>
       <c r="D240" s="12">
+        <v>0.41</v>
+      </c>
+      <c r="E240" s="11">
+        <v>0.63</v>
+      </c>
+      <c r="F240" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="G240" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="M240" s="16"/>
+    </row>
+    <row r="241" spans="1:13">
+      <c r="A241" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="D241" s="12">
         <v>0.8</v>
       </c>
-      <c r="E240" s="11">
+      <c r="E241" s="11">
         <v>0.88</v>
       </c>
-      <c r="G240" s="11">
+      <c r="F241" s="11">
+        <v>0.92</v>
+      </c>
+      <c r="G241" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M240" s="9"/>
-    </row>
-    <row r="241" spans="1:13">
-      <c r="A241" t="s">
-        <v>494</v>
-      </c>
-      <c r="B241" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="C241" s="11" t="s">
+      <c r="M241" s="9"/>
+    </row>
+    <row r="242" spans="1:13">
+      <c r="A242" t="s">
+        <v>492</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="C242" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D241" s="14">
+      <c r="D242" s="14">
         <v>0</v>
-      </c>
-      <c r="E241" s="11">
-        <v>0</v>
-      </c>
-      <c r="G241" s="11">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="242" spans="1:13">
-      <c r="A242" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B242" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="C242" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="D242" s="12">
-        <v>0.91</v>
       </c>
       <c r="E242" s="11">
         <v>0</v>
       </c>
+      <c r="F242" s="11">
+        <v>0.81</v>
+      </c>
       <c r="G242" s="11">
-        <v>0</v>
-      </c>
-      <c r="M242" s="9"/>
+        <v>0.49</v>
+      </c>
     </row>
     <row r="243" spans="1:13">
       <c r="A243" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C243" s="12" t="s">
         <v>343</v>
@@ -7829,6 +8162,9 @@
         <v>0.91</v>
       </c>
       <c r="E243" s="11">
+        <v>0</v>
+      </c>
+      <c r="F243" s="11">
         <v>0</v>
       </c>
       <c r="G243" s="11">
@@ -7852,6 +8188,9 @@
       <c r="E244" s="11">
         <v>0.88</v>
       </c>
+      <c r="F244" s="11">
+        <v>1</v>
+      </c>
       <c r="G244" s="11">
         <v>0.51</v>
       </c>
@@ -7862,10 +8201,10 @@
     </row>
     <row r="245" spans="1:13">
       <c r="A245" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C245" s="12" t="s">
         <v>343</v>
@@ -7876,6 +8215,9 @@
       <c r="E245" s="11">
         <v>0.98</v>
       </c>
+      <c r="F245" s="11">
+        <v>0.87</v>
+      </c>
       <c r="G245" s="11">
         <v>0.78</v>
       </c>
@@ -7886,10 +8228,10 @@
     </row>
     <row r="246" spans="1:13">
       <c r="A246" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C246" s="11" t="s">
         <v>343</v>
@@ -7898,6 +8240,9 @@
         <v>0</v>
       </c>
       <c r="E246" s="11">
+        <v>0</v>
+      </c>
+      <c r="F246" s="11">
         <v>0</v>
       </c>
       <c r="G246" s="11">
@@ -7920,6 +8265,9 @@
       <c r="E247" s="11">
         <v>0.93</v>
       </c>
+      <c r="F247" s="11">
+        <v>0.86</v>
+      </c>
       <c r="G247" s="11">
         <v>0.65</v>
       </c>
@@ -7927,10 +8275,10 @@
     </row>
     <row r="248" spans="1:13">
       <c r="A248" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C248" s="12" t="s">
         <v>343</v>
@@ -7940,6 +8288,9 @@
       </c>
       <c r="E248" s="11">
         <v>0.95</v>
+      </c>
+      <c r="F248" s="11">
+        <v>1</v>
       </c>
       <c r="G248" s="11">
         <v>0.71</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30DE3FB-A1E7-FD40-9E52-FC57115828ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F98BE8-F766-3C49-8F27-47C51E577449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="620" windowWidth="30760" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="20380" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1688,10 +1688,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5428,6 +5424,9 @@
       <c r="G132" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H132" s="14">
+        <v>0.436</v>
+      </c>
       <c r="J132" s="11">
         <v>0.8</v>
       </c>
@@ -5455,6 +5454,9 @@
       <c r="G133" s="11">
         <v>0.62</v>
       </c>
+      <c r="H133" s="14">
+        <v>0.39300000000000002</v>
+      </c>
       <c r="J133" s="11">
         <v>0.83</v>
       </c>
@@ -5482,6 +5484,9 @@
       <c r="G134" s="11">
         <v>0.53</v>
       </c>
+      <c r="H134" s="14">
+        <v>0.32500000000000001</v>
+      </c>
       <c r="M134" s="2"/>
     </row>
     <row r="135" spans="1:13">
@@ -5506,6 +5511,9 @@
       <c r="G135" s="11">
         <v>0.52</v>
       </c>
+      <c r="H135" s="14">
+        <v>0.39300000000000002</v>
+      </c>
       <c r="M135" s="2"/>
     </row>
     <row r="136" spans="1:13">
@@ -5525,6 +5533,9 @@
         <v>0.89</v>
       </c>
       <c r="G136" s="11"/>
+      <c r="H136" s="14">
+        <v>7.6999999999999999E-2</v>
+      </c>
       <c r="M136" s="8"/>
     </row>
     <row r="137" spans="1:13">
@@ -5549,6 +5560,9 @@
       <c r="G137" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="H137" s="14">
+        <v>0.53</v>
+      </c>
       <c r="M137" s="2"/>
     </row>
     <row r="138" spans="1:13">
@@ -5573,6 +5587,9 @@
       <c r="G138" s="11">
         <v>0.47</v>
       </c>
+      <c r="H138" s="14">
+        <v>0.53800000000000003</v>
+      </c>
       <c r="M138" s="2"/>
     </row>
     <row r="139" spans="1:13">
@@ -5597,6 +5614,9 @@
       <c r="G139" s="11">
         <v>0.64</v>
       </c>
+      <c r="H139" s="14">
+        <v>0.56399999999999995</v>
+      </c>
       <c r="M139" s="2"/>
     </row>
     <row r="140" spans="1:13">
@@ -5621,6 +5641,9 @@
       <c r="G140" s="11">
         <v>0.42</v>
       </c>
+      <c r="H140" s="14">
+        <v>0.26500000000000001</v>
+      </c>
       <c r="M140" s="2"/>
     </row>
     <row r="141" spans="1:13">
@@ -5645,6 +5668,9 @@
       <c r="G141" s="11">
         <v>0.51</v>
       </c>
+      <c r="H141" s="14">
+        <v>0.29899999999999999</v>
+      </c>
       <c r="M141" s="2"/>
     </row>
     <row r="142" spans="1:13">
@@ -5669,6 +5695,9 @@
       <c r="G142" s="11">
         <v>0.66</v>
       </c>
+      <c r="H142" s="14">
+        <v>0.436</v>
+      </c>
       <c r="J142" s="11">
         <v>0.8</v>
       </c>
@@ -5696,6 +5725,9 @@
       <c r="G143" s="11">
         <v>0.6</v>
       </c>
+      <c r="H143" s="14">
+        <v>0.45300000000000001</v>
+      </c>
       <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13">
@@ -5720,6 +5752,9 @@
       <c r="G144" s="11">
         <v>0.25</v>
       </c>
+      <c r="H144" s="14">
+        <v>0.29899999999999999</v>
+      </c>
       <c r="M144" s="2"/>
     </row>
     <row r="145" spans="1:13">
@@ -5744,6 +5779,9 @@
       <c r="G145" s="11">
         <v>0.36</v>
       </c>
+      <c r="H145" s="14">
+        <v>0.23899999999999999</v>
+      </c>
       <c r="M145" s="2"/>
     </row>
     <row r="146" spans="1:13">
@@ -5768,6 +5806,9 @@
       <c r="G146" s="11">
         <v>0.47</v>
       </c>
+      <c r="H146" s="14">
+        <v>0.26500000000000001</v>
+      </c>
       <c r="M146" s="2"/>
     </row>
     <row r="147" spans="1:13">
@@ -5792,6 +5833,9 @@
       <c r="G147" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="H147" s="14">
+        <v>0.38500000000000001</v>
+      </c>
       <c r="J147" s="11">
         <v>0.83</v>
       </c>
@@ -5819,6 +5863,9 @@
       <c r="G148" s="11">
         <v>0.53</v>
       </c>
+      <c r="H148" s="14">
+        <v>0.188</v>
+      </c>
       <c r="J148" s="11">
         <v>0.83</v>
       </c>
@@ -5846,6 +5893,9 @@
       <c r="G149" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H149" s="14">
+        <v>0.36799999999999999</v>
+      </c>
       <c r="J149" s="11">
         <v>0.83</v>
       </c>
@@ -5873,6 +5923,9 @@
       <c r="G150" s="11">
         <v>0.61</v>
       </c>
+      <c r="H150" s="14">
+        <v>0.51300000000000001</v>
+      </c>
       <c r="M150" s="2"/>
     </row>
     <row r="151" spans="1:13">
@@ -5897,6 +5950,9 @@
       <c r="G151" s="11">
         <v>0.62</v>
       </c>
+      <c r="H151" s="14">
+        <v>0.46200000000000002</v>
+      </c>
       <c r="M151" s="2"/>
     </row>
     <row r="152" spans="1:13">
@@ -5921,6 +5977,9 @@
       <c r="G152" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H152" s="14">
+        <v>0.33300000000000002</v>
+      </c>
       <c r="M152" s="2"/>
     </row>
     <row r="153" spans="1:13">
@@ -5945,6 +6004,9 @@
       <c r="G153" s="11">
         <v>0.71</v>
       </c>
+      <c r="H153" s="14">
+        <v>0.40200000000000002</v>
+      </c>
       <c r="M153" s="2"/>
     </row>
     <row r="154" spans="1:13">
@@ -5969,6 +6031,9 @@
       <c r="G154" s="11">
         <v>0.45</v>
       </c>
+      <c r="H154" s="14">
+        <v>0.42699999999999999</v>
+      </c>
       <c r="J154" s="11">
         <v>0.83</v>
       </c>
@@ -5996,6 +6061,9 @@
       <c r="G155" s="11">
         <v>0.53</v>
       </c>
+      <c r="H155" s="14">
+        <v>0.47899999999999998</v>
+      </c>
       <c r="M155" s="2"/>
     </row>
     <row r="156" spans="1:13">
@@ -6020,6 +6088,9 @@
       <c r="G156" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H156" s="14">
+        <v>0.17100000000000001</v>
+      </c>
       <c r="M156" s="2"/>
     </row>
     <row r="157" spans="1:13">
@@ -6044,6 +6115,9 @@
       <c r="G157" s="11">
         <v>0.52</v>
       </c>
+      <c r="H157" s="14">
+        <v>0.35899999999999999</v>
+      </c>
       <c r="M157" s="8"/>
     </row>
     <row r="158" spans="1:13">
@@ -6068,6 +6142,9 @@
       <c r="G158" s="11">
         <v>0.47</v>
       </c>
+      <c r="H158" s="14">
+        <v>0.29099999999999998</v>
+      </c>
       <c r="M158" s="2"/>
     </row>
     <row r="159" spans="1:13">
@@ -6092,6 +6169,9 @@
       <c r="G159" s="11">
         <v>0.61</v>
       </c>
+      <c r="H159" s="14">
+        <v>0.23899999999999999</v>
+      </c>
       <c r="M159" s="2"/>
     </row>
     <row r="160" spans="1:13">
@@ -6116,6 +6196,9 @@
       <c r="G160" s="11">
         <v>0.39</v>
       </c>
+      <c r="H160" s="14">
+        <v>0.29099999999999998</v>
+      </c>
       <c r="M160" s="8"/>
     </row>
     <row r="161" spans="1:13">
@@ -6140,6 +6223,9 @@
       <c r="G161" s="11">
         <v>0.53</v>
       </c>
+      <c r="H161" s="14">
+        <v>0.41899999999999998</v>
+      </c>
       <c r="M161" s="2"/>
     </row>
     <row r="162" spans="1:13">
@@ -6164,6 +6250,9 @@
       <c r="G162" s="11">
         <v>0.45</v>
       </c>
+      <c r="H162" s="14">
+        <v>0.23899999999999999</v>
+      </c>
       <c r="M162" s="8"/>
     </row>
     <row r="163" spans="1:13">
@@ -6188,6 +6277,9 @@
       <c r="G163" s="11">
         <v>0.62</v>
       </c>
+      <c r="H163" s="14">
+        <v>0.35</v>
+      </c>
       <c r="M163" s="2"/>
     </row>
     <row r="164" spans="1:13">
@@ -6212,6 +6304,9 @@
       <c r="G164" s="11">
         <v>0.39</v>
       </c>
+      <c r="H164" s="14">
+        <v>0.42699999999999999</v>
+      </c>
       <c r="M164" s="2"/>
     </row>
     <row r="165" spans="1:13">
@@ -6236,6 +6331,9 @@
       <c r="G165" s="11">
         <v>0.75</v>
       </c>
+      <c r="H165" s="14">
+        <v>0.57299999999999995</v>
+      </c>
       <c r="J165" s="11">
         <v>0.83</v>
       </c>
@@ -6263,6 +6361,9 @@
       <c r="G166" s="11">
         <v>0.71</v>
       </c>
+      <c r="H166" s="14">
+        <v>0.57299999999999995</v>
+      </c>
       <c r="M166" s="2"/>
     </row>
     <row r="167" spans="1:13">
@@ -6287,6 +6388,9 @@
       <c r="G167" s="11">
         <v>0.81</v>
       </c>
+      <c r="H167" s="14">
+        <v>0.56399999999999995</v>
+      </c>
       <c r="M167" s="2"/>
     </row>
     <row r="168" spans="1:13">
@@ -6311,6 +6415,9 @@
       <c r="G168" s="11">
         <v>0.74</v>
       </c>
+      <c r="H168" s="14">
+        <v>0.67500000000000004</v>
+      </c>
       <c r="M168" s="2"/>
     </row>
     <row r="169" spans="1:13">
@@ -6335,6 +6442,9 @@
       <c r="G169" s="11">
         <v>0.71</v>
       </c>
+      <c r="H169" s="14">
+        <v>0.63200000000000001</v>
+      </c>
       <c r="M169" s="8"/>
     </row>
     <row r="170" spans="1:13">
@@ -6359,6 +6469,9 @@
       <c r="G170" s="11">
         <v>0.38</v>
       </c>
+      <c r="H170" s="14">
+        <v>0.20499999999999999</v>
+      </c>
       <c r="M170" s="8"/>
     </row>
     <row r="171" spans="1:13">
@@ -6383,6 +6496,9 @@
       <c r="G171" s="11">
         <v>0.44</v>
       </c>
+      <c r="H171" s="14">
+        <v>0.53</v>
+      </c>
       <c r="M171" s="2"/>
     </row>
     <row r="172" spans="1:13">
@@ -6407,6 +6523,9 @@
       <c r="G172" s="11">
         <v>0.51</v>
       </c>
+      <c r="H172" s="14">
+        <v>0.27400000000000002</v>
+      </c>
       <c r="M172" s="8"/>
     </row>
     <row r="173" spans="1:13">
@@ -6431,6 +6550,9 @@
       <c r="G173" s="11">
         <v>0.49</v>
       </c>
+      <c r="H173" s="14">
+        <v>0.44400000000000001</v>
+      </c>
       <c r="M173" s="2"/>
     </row>
     <row r="174" spans="1:13">
@@ -6455,6 +6577,9 @@
       <c r="G174" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="H174" s="14">
+        <v>0.376</v>
+      </c>
       <c r="J174" s="11">
         <v>0.83</v>
       </c>
@@ -6482,6 +6607,9 @@
       <c r="G175" s="11">
         <v>0.69</v>
       </c>
+      <c r="H175" s="14">
+        <v>0.51300000000000001</v>
+      </c>
       <c r="M175" s="2"/>
     </row>
     <row r="176" spans="1:13">
@@ -6506,6 +6634,9 @@
       <c r="G176" s="11">
         <v>0.65</v>
       </c>
+      <c r="H176" s="14">
+        <v>0.436</v>
+      </c>
       <c r="M176" s="2"/>
     </row>
     <row r="177" spans="1:13">
@@ -6530,6 +6661,9 @@
       <c r="G177" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H177" s="14">
+        <v>0.47899999999999998</v>
+      </c>
       <c r="M177" s="2"/>
     </row>
     <row r="178" spans="1:13">
@@ -6554,6 +6688,9 @@
       <c r="G178" s="11">
         <v>0.62</v>
       </c>
+      <c r="H178" s="14">
+        <v>0.36799999999999999</v>
+      </c>
       <c r="M178" s="2"/>
     </row>
     <row r="179" spans="1:13">
@@ -6578,6 +6715,9 @@
       <c r="G179" s="11">
         <v>0.48</v>
       </c>
+      <c r="H179" s="14">
+        <v>0.47899999999999998</v>
+      </c>
       <c r="M179" s="2"/>
     </row>
     <row r="180" spans="1:13">
@@ -6602,6 +6742,9 @@
       <c r="G180" s="11">
         <v>0.61</v>
       </c>
+      <c r="H180" s="14">
+        <v>0.23100000000000001</v>
+      </c>
       <c r="M180" s="2"/>
     </row>
     <row r="181" spans="1:13">
@@ -6626,6 +6769,9 @@
       <c r="G181" s="11">
         <v>0.36</v>
       </c>
+      <c r="H181" s="14">
+        <v>0.188</v>
+      </c>
       <c r="M181" s="2"/>
     </row>
     <row r="182" spans="1:13">
@@ -6650,6 +6796,9 @@
       <c r="G182" s="11">
         <v>0.68</v>
       </c>
+      <c r="H182" s="14">
+        <v>0</v>
+      </c>
       <c r="M182" s="8"/>
     </row>
     <row r="183" spans="1:13">
@@ -6674,6 +6823,9 @@
       <c r="G183" s="11">
         <v>0.4</v>
       </c>
+      <c r="H183" s="14">
+        <v>0.36799999999999999</v>
+      </c>
       <c r="M183" s="2"/>
     </row>
     <row r="184" spans="1:13">
@@ -6698,6 +6850,9 @@
       <c r="G184" s="11">
         <v>0.38</v>
       </c>
+      <c r="H184" s="14">
+        <v>0.17899999999999999</v>
+      </c>
       <c r="M184" s="2"/>
     </row>
     <row r="185" spans="1:13">
@@ -6722,6 +6877,9 @@
       <c r="G185" s="11">
         <v>0.66</v>
       </c>
+      <c r="H185" s="14">
+        <v>0.63200000000000001</v>
+      </c>
       <c r="M185" s="2"/>
     </row>
     <row r="186" spans="1:13">
@@ -6746,6 +6904,9 @@
       <c r="G186" s="11">
         <v>0.73</v>
       </c>
+      <c r="H186" s="14">
+        <v>0.70899999999999996</v>
+      </c>
       <c r="M186" s="2"/>
     </row>
     <row r="187" spans="1:13">
@@ -6770,6 +6931,9 @@
       <c r="G187" s="11">
         <v>0.53</v>
       </c>
+      <c r="H187" s="14">
+        <v>0.45300000000000001</v>
+      </c>
       <c r="J187" s="11">
         <v>0.8</v>
       </c>
@@ -6797,6 +6961,9 @@
       <c r="G188" s="11">
         <v>0.32</v>
       </c>
+      <c r="H188" s="14">
+        <v>0.38500000000000001</v>
+      </c>
       <c r="M188" s="2"/>
     </row>
     <row r="189" spans="1:13">
@@ -6821,6 +6988,9 @@
       <c r="G189" s="11">
         <v>0.82</v>
       </c>
+      <c r="H189" s="14">
+        <v>0.47</v>
+      </c>
       <c r="J189" s="11">
         <v>0.83</v>
       </c>
@@ -6848,6 +7018,9 @@
       <c r="G190" s="11">
         <v>0.73</v>
       </c>
+      <c r="H190" s="14">
+        <v>0.34200000000000003</v>
+      </c>
       <c r="M190" s="2"/>
     </row>
     <row r="191" spans="1:13">
@@ -6872,6 +7045,9 @@
       <c r="G191" s="11">
         <v>0.43</v>
       </c>
+      <c r="H191" s="14">
+        <v>0.436</v>
+      </c>
       <c r="M191" s="2"/>
     </row>
     <row r="192" spans="1:13">
@@ -6896,6 +7072,9 @@
       <c r="G192" s="11">
         <v>0.51</v>
       </c>
+      <c r="H192" s="14">
+        <v>0.35899999999999999</v>
+      </c>
       <c r="M192" s="2"/>
     </row>
     <row r="193" spans="1:13">
@@ -7826,7 +8005,7 @@
       <c r="J229" s="11">
         <v>0.93</v>
       </c>
-      <c r="M229" s="16"/>
+      <c r="M229" s="9"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="4" t="s">
@@ -7850,7 +8029,7 @@
       <c r="G230" s="11">
         <v>0.81</v>
       </c>
-      <c r="M230" s="16"/>
+      <c r="M230" s="9"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="4" t="s">
@@ -7874,7 +8053,7 @@
       <c r="G231" s="11">
         <v>0.7</v>
       </c>
-      <c r="M231" s="16"/>
+      <c r="M231" s="9"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="4" t="s">
@@ -7898,7 +8077,7 @@
       <c r="G232" s="11">
         <v>0.77</v>
       </c>
-      <c r="M232" s="16"/>
+      <c r="M232" s="9"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" t="s">
@@ -7922,7 +8101,6 @@
       <c r="G233" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M233" s="17"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
@@ -7949,7 +8127,7 @@
       <c r="J234" s="11">
         <v>0.93</v>
       </c>
-      <c r="M234" s="16"/>
+      <c r="M234" s="9"/>
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="4" t="s">
@@ -7973,7 +8151,7 @@
       <c r="G235" s="11">
         <v>0.69</v>
       </c>
-      <c r="M235" s="16"/>
+      <c r="M235" s="9"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="4" t="s">
@@ -8000,7 +8178,7 @@
       <c r="J236" s="11">
         <v>0.93</v>
       </c>
-      <c r="M236" s="16"/>
+      <c r="M236" s="9"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="4" t="s">
@@ -8024,7 +8202,7 @@
       <c r="G237" s="11">
         <v>0.64</v>
       </c>
-      <c r="M237" s="16"/>
+      <c r="M237" s="9"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="4" t="s">
@@ -8051,7 +8229,7 @@
       <c r="J238" s="11">
         <v>0.8</v>
       </c>
-      <c r="M238" s="16"/>
+      <c r="M238" s="9"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="4" t="s">
@@ -8075,7 +8253,7 @@
       <c r="G239" s="11">
         <v>0.68</v>
       </c>
-      <c r="M239" s="16"/>
+      <c r="M239" s="9"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="4" t="s">
@@ -8099,7 +8277,7 @@
       <c r="G240" s="11">
         <v>0.43</v>
       </c>
-      <c r="M240" s="16"/>
+      <c r="M240" s="9"/>
     </row>
     <row r="241" spans="1:13">
       <c r="A241" s="4" t="s">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F98BE8-F766-3C49-8F27-47C51E577449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1543F09F-7F1E-FF4A-B53D-054C6B644413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="20380" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="21960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2170,7 +2170,9 @@
       <c r="G2" s="11">
         <v>0.42</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="15">
+        <v>0.27350427350427353</v>
+      </c>
       <c r="J2" s="11">
         <v>0.72</v>
       </c>
@@ -2198,7 +2200,9 @@
       <c r="G3" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H3" s="15"/>
+      <c r="H3" s="15">
+        <v>0.30769230769230771</v>
+      </c>
       <c r="J3" s="11">
         <v>0.72</v>
       </c>
@@ -2226,6 +2230,9 @@
       <c r="G4" s="11">
         <v>0.75</v>
       </c>
+      <c r="H4" s="14">
+        <v>0.47863247863247865</v>
+      </c>
       <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
@@ -2250,7 +2257,9 @@
       <c r="G5" s="11">
         <v>0.77</v>
       </c>
-      <c r="H5" s="15"/>
+      <c r="H5" s="15">
+        <v>0.5213675213675214</v>
+      </c>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -2275,7 +2284,9 @@
       <c r="G6" s="11">
         <v>0.68</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="15">
+        <v>0.42735042735042733</v>
+      </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
@@ -2300,6 +2311,9 @@
       <c r="G7" s="11">
         <v>0.81</v>
       </c>
+      <c r="H7" s="14">
+        <v>0.20512820512820512</v>
+      </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
@@ -2324,7 +2338,9 @@
       <c r="G8" s="11">
         <v>0.6</v>
       </c>
-      <c r="H8" s="15"/>
+      <c r="H8" s="15">
+        <v>0.41025641025641024</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
@@ -2349,7 +2365,9 @@
       <c r="G9" s="11">
         <v>0.51</v>
       </c>
-      <c r="H9" s="15"/>
+      <c r="H9" s="15">
+        <v>0.54700854700854706</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
@@ -2374,7 +2392,9 @@
       <c r="G10" s="11">
         <v>0.53</v>
       </c>
-      <c r="H10" s="15"/>
+      <c r="H10" s="15">
+        <v>0.29914529914529914</v>
+      </c>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
@@ -2399,7 +2419,9 @@
       <c r="G11" s="11">
         <v>0.66</v>
       </c>
-      <c r="H11" s="15"/>
+      <c r="H11" s="15">
+        <v>0.35897435897435898</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13">
@@ -2424,7 +2446,9 @@
       <c r="G12" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="15">
+        <v>0.49572649572649574</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
@@ -2449,7 +2473,9 @@
       <c r="G13" s="11">
         <v>0.9</v>
       </c>
-      <c r="H13" s="15"/>
+      <c r="H13" s="15">
+        <v>0.6495726495726496</v>
+      </c>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
@@ -2474,7 +2500,9 @@
       <c r="G14" s="11">
         <v>0.51</v>
       </c>
-      <c r="H14" s="15"/>
+      <c r="H14" s="15">
+        <v>0.3504273504273504</v>
+      </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
@@ -2499,7 +2527,9 @@
       <c r="G15" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H15" s="15"/>
+      <c r="H15" s="15">
+        <v>0.50427350427350426</v>
+      </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
@@ -2524,7 +2554,9 @@
       <c r="G16" s="11">
         <v>0.52</v>
       </c>
-      <c r="H16" s="15"/>
+      <c r="H16" s="15">
+        <v>0.51282051282051277</v>
+      </c>
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13">
@@ -2549,7 +2581,9 @@
       <c r="G17" s="11">
         <v>0.47</v>
       </c>
-      <c r="H17" s="15"/>
+      <c r="H17" s="15">
+        <v>0.5213675213675214</v>
+      </c>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13">
@@ -2574,6 +2608,9 @@
       <c r="G18" s="11">
         <v>0.65</v>
       </c>
+      <c r="H18" s="14">
+        <v>0.51282051282051277</v>
+      </c>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13">
@@ -2598,7 +2635,9 @@
       <c r="G19" s="11">
         <v>0.73</v>
       </c>
-      <c r="H19" s="15"/>
+      <c r="H19" s="15">
+        <v>0.54700854700854706</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
@@ -2623,6 +2662,9 @@
       <c r="G20" s="11">
         <v>0.62</v>
       </c>
+      <c r="H20" s="14">
+        <v>0.47008547008547008</v>
+      </c>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
@@ -2647,7 +2689,9 @@
       <c r="G21" s="11">
         <v>0.66</v>
       </c>
-      <c r="H21" s="15"/>
+      <c r="H21" s="15">
+        <v>0.48717948717948717</v>
+      </c>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13">
@@ -2672,7 +2716,9 @@
       <c r="G22" s="11">
         <v>0.82</v>
       </c>
-      <c r="H22" s="15"/>
+      <c r="H22" s="15">
+        <v>0.75213675213675213</v>
+      </c>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13">
@@ -2697,6 +2743,9 @@
       <c r="G23" s="11">
         <v>0.38</v>
       </c>
+      <c r="H23" s="14">
+        <v>0.40170940170940173</v>
+      </c>
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
@@ -2721,6 +2770,9 @@
       <c r="G24" s="11">
         <v>0.74</v>
       </c>
+      <c r="H24" s="14">
+        <v>0.5641025641025641</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
@@ -2745,7 +2797,9 @@
       <c r="G25" s="11">
         <v>0.61</v>
       </c>
-      <c r="H25" s="15"/>
+      <c r="H25" s="15">
+        <v>0.45299145299145299</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13">
@@ -2770,7 +2824,9 @@
       <c r="G26" s="11">
         <v>0.4</v>
       </c>
-      <c r="H26" s="15"/>
+      <c r="H26" s="15">
+        <v>0.29059829059829062</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
@@ -2795,7 +2851,9 @@
       <c r="G27" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H27" s="15"/>
+      <c r="H27" s="15">
+        <v>0.53846153846153844</v>
+      </c>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13">
@@ -2820,6 +2878,9 @@
       <c r="G28" s="11">
         <v>0.78</v>
       </c>
+      <c r="H28" s="14">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13">
@@ -2844,7 +2905,9 @@
       <c r="G29" s="11">
         <v>0.34</v>
       </c>
-      <c r="H29" s="15"/>
+      <c r="H29" s="15">
+        <v>0.38461538461538464</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -2869,7 +2932,9 @@
       <c r="G30" s="11">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H30" s="15"/>
+      <c r="H30" s="15">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13">
@@ -2894,6 +2959,9 @@
       <c r="G31" s="11">
         <v>0.73</v>
       </c>
+      <c r="H31" s="14">
+        <v>0.57264957264957261</v>
+      </c>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13">
@@ -2918,7 +2986,9 @@
       <c r="G32" s="11">
         <v>0.4</v>
       </c>
-      <c r="H32" s="15"/>
+      <c r="H32" s="15">
+        <v>0.45299145299145299</v>
+      </c>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13">
@@ -2943,7 +3013,9 @@
       <c r="G33" s="11">
         <v>0.7</v>
       </c>
-      <c r="H33" s="15"/>
+      <c r="H33" s="15">
+        <v>0.50427350427350426</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
@@ -2968,6 +3040,9 @@
       <c r="G34" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="H34" s="14">
+        <v>0.45299145299145299</v>
+      </c>
       <c r="J34" s="11">
         <v>0.78</v>
       </c>
@@ -2995,7 +3070,9 @@
       <c r="G35" s="11">
         <v>0</v>
       </c>
-      <c r="H35" s="15"/>
+      <c r="H35" s="15">
+        <v>0</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -3020,7 +3097,9 @@
       <c r="G36" s="11">
         <v>0.27</v>
       </c>
-      <c r="H36" s="15"/>
+      <c r="H36" s="15">
+        <v>0.4358974358974359</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
@@ -3045,6 +3124,9 @@
       <c r="G37" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H37" s="14">
+        <v>0.34188034188034189</v>
+      </c>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13">
@@ -3069,7 +3151,9 @@
       <c r="G38" s="11">
         <v>0.65</v>
       </c>
-      <c r="H38" s="15"/>
+      <c r="H38" s="15">
+        <v>0.24786324786324787</v>
+      </c>
       <c r="J38" s="11">
         <v>0.7</v>
       </c>
@@ -3097,6 +3181,9 @@
       <c r="G39" s="11">
         <v>0.75</v>
       </c>
+      <c r="H39" s="14">
+        <v>0.63247863247863245</v>
+      </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13">
@@ -3121,7 +3208,9 @@
       <c r="G40" s="11">
         <v>0.48</v>
       </c>
-      <c r="H40" s="15"/>
+      <c r="H40" s="15">
+        <v>0.41880341880341881</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
@@ -3146,7 +3235,9 @@
       <c r="G41" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H41" s="15"/>
+      <c r="H41" s="15">
+        <v>0.50427350427350426</v>
+      </c>
       <c r="J41" s="11">
         <v>0.7</v>
       </c>
@@ -3174,7 +3265,9 @@
       <c r="G42" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H42" s="15"/>
+      <c r="H42" s="15">
+        <v>0.30769230769230771</v>
+      </c>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13">
@@ -3199,7 +3292,9 @@
       <c r="G43" s="11">
         <v>0.92</v>
       </c>
-      <c r="H43" s="15"/>
+      <c r="H43" s="15">
+        <v>0.67521367521367526</v>
+      </c>
       <c r="J43" s="11">
         <v>0.84</v>
       </c>
@@ -3227,6 +3322,9 @@
       <c r="G44" s="11">
         <v>0.77</v>
       </c>
+      <c r="H44" s="14">
+        <v>0.47863247863247865</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13">
@@ -3251,7 +3349,9 @@
       <c r="G45" s="11">
         <v>0</v>
       </c>
-      <c r="H45" s="15"/>
+      <c r="H45" s="15">
+        <v>0.21367521367521367</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -3276,7 +3376,9 @@
       <c r="G46" s="11">
         <v>0.66</v>
       </c>
-      <c r="H46" s="15"/>
+      <c r="H46" s="15">
+        <v>0.54700854700854706</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -3301,7 +3403,9 @@
       <c r="G47" s="11">
         <v>0.83</v>
       </c>
-      <c r="H47" s="15"/>
+      <c r="H47" s="15">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:13">
@@ -3326,7 +3430,9 @@
       <c r="G48" s="11">
         <v>0.18</v>
       </c>
-      <c r="H48" s="15"/>
+      <c r="H48" s="15">
+        <v>0.40170940170940173</v>
+      </c>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13">
@@ -3351,7 +3457,9 @@
       <c r="G49" s="11">
         <v>0.18</v>
       </c>
-      <c r="H49" s="15"/>
+      <c r="H49" s="15">
+        <v>0.29059829059829062</v>
+      </c>
       <c r="M49" s="2"/>
     </row>
     <row r="50" spans="1:13">
@@ -3376,6 +3484,9 @@
       <c r="G50" s="11">
         <v>0.52</v>
       </c>
+      <c r="H50" s="14">
+        <v>0.40170940170940173</v>
+      </c>
       <c r="J50" s="11">
         <v>0.84</v>
       </c>
@@ -3403,6 +3514,9 @@
       <c r="G51" s="11">
         <v>0.53</v>
       </c>
+      <c r="H51" s="14">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13">
@@ -3427,6 +3541,9 @@
       <c r="G52" s="11">
         <v>0.62</v>
       </c>
+      <c r="H52" s="14">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13">
@@ -3451,7 +3568,9 @@
       <c r="G53" s="11">
         <v>0.36</v>
       </c>
-      <c r="H53" s="15"/>
+      <c r="H53" s="15">
+        <v>0.31623931623931623</v>
+      </c>
       <c r="M53" s="2"/>
     </row>
     <row r="54" spans="1:13">
@@ -3476,7 +3595,9 @@
       <c r="G54" s="11">
         <v>0.65</v>
       </c>
-      <c r="H54" s="15"/>
+      <c r="H54" s="15">
+        <v>0.35897435897435898</v>
+      </c>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
@@ -3501,7 +3622,9 @@
       <c r="G55" s="11">
         <v>0.68</v>
       </c>
-      <c r="H55" s="15"/>
+      <c r="H55" s="15">
+        <v>0.31623931623931623</v>
+      </c>
       <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13">
@@ -3526,6 +3649,9 @@
       <c r="G56" s="11">
         <v>0.68</v>
       </c>
+      <c r="H56" s="14">
+        <v>0.58119658119658124</v>
+      </c>
       <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13">
@@ -3550,7 +3676,9 @@
       <c r="G57" s="11">
         <v>0.65</v>
       </c>
-      <c r="H57" s="15"/>
+      <c r="H57" s="15">
+        <v>0.52991452991452992</v>
+      </c>
       <c r="J57" s="11">
         <v>0.72</v>
       </c>
@@ -3578,6 +3706,9 @@
       <c r="G58" s="11">
         <v>0.34</v>
       </c>
+      <c r="H58" s="14">
+        <v>0.1623931623931624</v>
+      </c>
       <c r="J58" s="11">
         <v>0.84</v>
       </c>
@@ -3605,7 +3736,9 @@
       <c r="G59" s="11">
         <v>0.53</v>
       </c>
-      <c r="H59" s="15"/>
+      <c r="H59" s="15">
+        <v>0.39316239316239315</v>
+      </c>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:13">
@@ -3630,6 +3763,9 @@
       <c r="G60" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H60" s="14">
+        <v>0.42735042735042733</v>
+      </c>
       <c r="J60" s="11">
         <v>0.78</v>
       </c>
@@ -3657,7 +3793,9 @@
       <c r="G61" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H61" s="15"/>
+      <c r="H61" s="15">
+        <v>0.35897435897435898</v>
+      </c>
       <c r="J61" s="11">
         <v>0.7</v>
       </c>
@@ -3685,7 +3823,9 @@
       <c r="G62" s="11">
         <v>0.78</v>
       </c>
-      <c r="H62" s="15"/>
+      <c r="H62" s="15">
+        <v>0.63247863247863245</v>
+      </c>
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
@@ -3710,7 +3850,9 @@
       <c r="G63" s="11">
         <v>0.69</v>
       </c>
-      <c r="H63" s="15"/>
+      <c r="H63" s="15">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13">
@@ -3735,6 +3877,9 @@
       <c r="G64" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H64" s="14">
+        <v>0.22222222222222221</v>
+      </c>
       <c r="M64" s="2"/>
     </row>
     <row r="65" spans="1:13">
@@ -3759,7 +3904,9 @@
       <c r="G65" s="11">
         <v>0.6</v>
       </c>
-      <c r="H65" s="15"/>
+      <c r="H65" s="15">
+        <v>0.31623931623931623</v>
+      </c>
       <c r="M65" s="2"/>
     </row>
     <row r="66" spans="1:13">
@@ -3784,6 +3931,9 @@
       <c r="G66" s="11">
         <v>0.49</v>
       </c>
+      <c r="H66" s="14">
+        <v>0.51282051282051277</v>
+      </c>
       <c r="M66" s="2"/>
     </row>
     <row r="67" spans="1:13">
@@ -3808,6 +3958,9 @@
       <c r="G67" s="11">
         <v>0.7</v>
       </c>
+      <c r="H67" s="14">
+        <v>0.58974358974358976</v>
+      </c>
       <c r="J67" s="11">
         <v>0.78</v>
       </c>
@@ -3835,6 +3988,9 @@
       <c r="G68" s="11">
         <v>0.62</v>
       </c>
+      <c r="H68" s="14">
+        <v>0.52991452991452992</v>
+      </c>
       <c r="M68" s="2"/>
     </row>
     <row r="69" spans="1:13">
@@ -3859,7 +4015,9 @@
       <c r="G69" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H69" s="15"/>
+      <c r="H69" s="15">
+        <v>0.29914529914529914</v>
+      </c>
       <c r="J69" s="11">
         <v>0.72</v>
       </c>
@@ -3887,7 +4045,9 @@
       <c r="G70" s="11">
         <v>0.68</v>
       </c>
-      <c r="H70" s="15"/>
+      <c r="H70" s="15">
+        <v>0.48717948717948717</v>
+      </c>
       <c r="J70" s="11">
         <v>0.72</v>
       </c>
@@ -3915,7 +4075,9 @@
       <c r="G71" s="11">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H71" s="15"/>
+      <c r="H71" s="15">
+        <v>0.45299145299145299</v>
+      </c>
       <c r="J71" s="11">
         <v>0.78</v>
       </c>
@@ -3943,7 +4105,9 @@
       <c r="G72" s="11">
         <v>0</v>
       </c>
-      <c r="H72" s="15"/>
+      <c r="H72" s="15">
+        <v>0.28205128205128205</v>
+      </c>
       <c r="J72" s="11">
         <v>0.73</v>
       </c>
@@ -3971,6 +4135,9 @@
       <c r="G73" s="11">
         <v>0.66</v>
       </c>
+      <c r="H73" s="14">
+        <v>0.41025641025641024</v>
+      </c>
       <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:13">
@@ -3995,6 +4162,9 @@
       <c r="G74" s="11">
         <v>0.48</v>
       </c>
+      <c r="H74" s="14">
+        <v>0.28205128205128205</v>
+      </c>
       <c r="J74" s="11">
         <v>0.7</v>
       </c>
@@ -4022,6 +4192,9 @@
       <c r="G75" s="11">
         <v>0.62</v>
       </c>
+      <c r="H75" s="14">
+        <v>0.58119658119658124</v>
+      </c>
       <c r="J75" s="11">
         <v>0.78</v>
       </c>
@@ -4049,7 +4222,9 @@
       <c r="G76" s="11">
         <v>0.79</v>
       </c>
-      <c r="H76" s="15"/>
+      <c r="H76" s="15">
+        <v>0.55555555555555558</v>
+      </c>
       <c r="M76" s="2"/>
     </row>
     <row r="77" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1543F09F-7F1E-FF4A-B53D-054C6B644413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B9C37E-5F64-D34D-8210-C32302DCED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="21960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1487,9 +1487,6 @@
     <t>H264395O</t>
   </si>
   <si>
-    <t>Mapara</t>
-  </si>
-  <si>
     <t>H261856N</t>
   </si>
   <si>
@@ -1551,6 +1548,9 @@
   </si>
   <si>
     <t>H260915U</t>
+  </si>
+  <si>
+    <t>Maparara</t>
   </si>
 </sst>
 </file>
@@ -2095,11 +2095,11 @@
   <dimension ref="A1:M248"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="11"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" style="11" customWidth="1"/>
     <col min="6" max="6" width="7.42578125" style="11" customWidth="1"/>
     <col min="7" max="7" width="8.140625" customWidth="1"/>
     <col min="8" max="8" width="7.140625" style="14" customWidth="1"/>
@@ -2233,6 +2233,9 @@
       <c r="H4" s="14">
         <v>0.47863247863247865</v>
       </c>
+      <c r="J4" s="11">
+        <v>0.65</v>
+      </c>
       <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
@@ -2314,6 +2317,9 @@
       <c r="H7" s="14">
         <v>0.20512820512820512</v>
       </c>
+      <c r="J7" s="11">
+        <v>0.65</v>
+      </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
@@ -2476,6 +2482,9 @@
       <c r="H13" s="15">
         <v>0.6495726495726496</v>
       </c>
+      <c r="J13" s="11">
+        <v>0.65</v>
+      </c>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
@@ -3184,6 +3193,9 @@
       <c r="H39" s="14">
         <v>0.63247863247863245</v>
       </c>
+      <c r="J39" s="11">
+        <v>0.65</v>
+      </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13">
@@ -3325,6 +3337,9 @@
       <c r="H44" s="14">
         <v>0.47863247863247865</v>
       </c>
+      <c r="J44" s="11">
+        <v>0.65</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13">
@@ -4249,6 +4264,9 @@
       <c r="G77" s="11">
         <v>0.61</v>
       </c>
+      <c r="H77" s="14">
+        <v>0.5</v>
+      </c>
       <c r="J77" s="11">
         <v>0.78</v>
       </c>
@@ -4276,6 +4294,9 @@
       <c r="G78" s="11">
         <v>0.48</v>
       </c>
+      <c r="H78" s="14">
+        <v>0.62</v>
+      </c>
       <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13">
@@ -4300,6 +4321,9 @@
       <c r="G79" s="11">
         <v>0.52</v>
       </c>
+      <c r="H79" s="14">
+        <v>0.34</v>
+      </c>
       <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13">
@@ -4324,14 +4348,20 @@
       <c r="G80" s="11">
         <v>0.68</v>
       </c>
+      <c r="H80" s="14">
+        <v>0.33</v>
+      </c>
+      <c r="J80" s="11">
+        <v>0.72</v>
+      </c>
       <c r="M80" s="2"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
+        <v>494</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>495</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>496</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>159</v>
@@ -4347,6 +4377,12 @@
       </c>
       <c r="G81" s="11">
         <v>0.6</v>
+      </c>
+      <c r="H81" s="14">
+        <v>0.34</v>
+      </c>
+      <c r="I81" s="11">
+        <v>0.54</v>
       </c>
       <c r="M81" s="8"/>
     </row>
@@ -4372,6 +4408,9 @@
       <c r="G82" s="11">
         <v>0</v>
       </c>
+      <c r="H82" s="14">
+        <v>0.27</v>
+      </c>
       <c r="J82" s="11">
         <v>0.78</v>
       </c>
@@ -4399,14 +4438,20 @@
       <c r="G83" s="11">
         <v>0.78</v>
       </c>
+      <c r="H83" s="14">
+        <v>0.49</v>
+      </c>
+      <c r="I83" s="11">
+        <v>0.77</v>
+      </c>
       <c r="M83" s="2"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
+        <v>496</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>497</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>498</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>159</v>
@@ -4422,6 +4467,9 @@
       </c>
       <c r="G84" s="11">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="H84" s="14">
+        <v>0.43</v>
       </c>
       <c r="M84" s="8"/>
     </row>
@@ -4447,6 +4495,9 @@
       <c r="G85" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H85" s="14">
+        <v>0.65</v>
+      </c>
       <c r="M85" s="2"/>
     </row>
     <row r="86" spans="1:13">
@@ -4471,6 +4522,9 @@
       <c r="G86" s="11">
         <v>0.42</v>
       </c>
+      <c r="H86" s="14">
+        <v>0.15</v>
+      </c>
       <c r="J86" s="11">
         <v>0.78</v>
       </c>
@@ -4498,6 +4552,12 @@
       <c r="G87" s="11">
         <v>0.51</v>
       </c>
+      <c r="H87" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="I87" s="11">
+        <v>0.47</v>
+      </c>
       <c r="M87" s="2"/>
     </row>
     <row r="88" spans="1:13">
@@ -4505,7 +4565,7 @@
         <v>460</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>159</v>
@@ -4521,6 +4581,9 @@
       </c>
       <c r="G88" s="11">
         <v>0.53</v>
+      </c>
+      <c r="H88" s="14">
+        <v>0.44</v>
       </c>
       <c r="M88" s="8"/>
     </row>
@@ -4546,6 +4609,9 @@
       <c r="G89" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H89" s="14">
+        <v>0.4</v>
+      </c>
       <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:13">
@@ -4570,6 +4636,9 @@
       <c r="G90" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H90" s="14">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:13">
@@ -4594,6 +4663,9 @@
       <c r="G91" s="11">
         <v>0.62</v>
       </c>
+      <c r="H91" s="14">
+        <v>0.6</v>
+      </c>
       <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:13">
@@ -4618,6 +4690,12 @@
       <c r="G92" s="11">
         <v>0.61</v>
       </c>
+      <c r="H92" s="14">
+        <v>0.35</v>
+      </c>
+      <c r="I92" s="11">
+        <v>0.47</v>
+      </c>
       <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:13">
@@ -4642,6 +4720,9 @@
       <c r="G93" s="11">
         <v>0</v>
       </c>
+      <c r="H93" s="14">
+        <v>0</v>
+      </c>
       <c r="M93" s="2"/>
     </row>
     <row r="94" spans="1:13">
@@ -4666,6 +4747,9 @@
       <c r="G94" s="11">
         <v>0.65</v>
       </c>
+      <c r="H94" s="14">
+        <v>0.53</v>
+      </c>
       <c r="M94" s="2"/>
     </row>
     <row r="95" spans="1:13">
@@ -4690,14 +4774,17 @@
       <c r="G95" s="11">
         <v>0.52</v>
       </c>
+      <c r="H95" s="14">
+        <v>0.69</v>
+      </c>
       <c r="M95" s="2"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
+        <v>498</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>499</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>500</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>159</v>
@@ -4714,14 +4801,17 @@
       <c r="G96" s="11">
         <v>0.69</v>
       </c>
+      <c r="H96" s="14">
+        <v>0.62</v>
+      </c>
       <c r="M96" s="8"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
+        <v>500</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>501</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>502</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>159</v>
@@ -4737,6 +4827,9 @@
       </c>
       <c r="G97" s="11">
         <v>0.71</v>
+      </c>
+      <c r="H97" s="14">
+        <v>0.5</v>
       </c>
       <c r="M97" s="8"/>
     </row>
@@ -4762,6 +4855,9 @@
       <c r="G98" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H98" s="14">
+        <v>0.5</v>
+      </c>
       <c r="M98" s="2"/>
     </row>
     <row r="99" spans="1:13">
@@ -4786,6 +4882,12 @@
       <c r="G99" s="11">
         <v>0.77</v>
       </c>
+      <c r="H99" s="14">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I99" s="11">
+        <v>0.47</v>
+      </c>
       <c r="M99" s="2"/>
     </row>
     <row r="100" spans="1:13">
@@ -4810,6 +4912,9 @@
       <c r="G100" s="11">
         <v>0.73</v>
       </c>
+      <c r="H100" s="14">
+        <v>0.72</v>
+      </c>
       <c r="M100" s="2"/>
     </row>
     <row r="101" spans="1:13">
@@ -4834,6 +4939,12 @@
       <c r="G101" s="11">
         <v>0.52</v>
       </c>
+      <c r="H101" s="14">
+        <v>0.09</v>
+      </c>
+      <c r="I101" s="11">
+        <v>0.2</v>
+      </c>
       <c r="M101" s="2"/>
     </row>
     <row r="102" spans="1:13">
@@ -4858,14 +4969,23 @@
       <c r="G102" s="11">
         <v>0.65</v>
       </c>
+      <c r="H102" s="14">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I102" s="11">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J102" s="11">
+        <v>0.72</v>
+      </c>
       <c r="M102" s="2"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
+        <v>504</v>
+      </c>
+      <c r="B103" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>484</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>159</v>
@@ -4881,6 +5001,12 @@
       </c>
       <c r="G103" s="11">
         <v>0.6</v>
+      </c>
+      <c r="H103" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="I103" s="11">
+        <v>0.26</v>
       </c>
       <c r="M103" s="8"/>
     </row>
@@ -4906,6 +5032,9 @@
       <c r="G104" s="11">
         <v>0.64</v>
       </c>
+      <c r="H104" s="14">
+        <v>0.41</v>
+      </c>
       <c r="J104" s="11">
         <v>0.78</v>
       </c>
@@ -4913,10 +5042,10 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
+        <v>484</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>485</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>486</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>159</v>
@@ -4932,6 +5061,12 @@
       </c>
       <c r="G105" s="11">
         <v>0.85</v>
+      </c>
+      <c r="H105" s="14">
+        <v>0.77</v>
+      </c>
+      <c r="I105" s="11">
+        <v>0.64</v>
       </c>
       <c r="M105" s="8"/>
     </row>
@@ -4957,6 +5092,9 @@
       <c r="G106" s="11">
         <v>0</v>
       </c>
+      <c r="H106" s="14">
+        <v>0.17</v>
+      </c>
       <c r="M106" s="2"/>
     </row>
     <row r="107" spans="1:13">
@@ -4981,6 +5119,9 @@
       <c r="G107" s="11">
         <v>0.53</v>
       </c>
+      <c r="H107" s="14">
+        <v>0.53</v>
+      </c>
       <c r="M107" s="2"/>
     </row>
     <row r="108" spans="1:13">
@@ -5005,6 +5146,12 @@
       <c r="G108" s="11">
         <v>0.64</v>
       </c>
+      <c r="H108" s="14">
+        <v>0.53</v>
+      </c>
+      <c r="I108" s="11">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M108" s="2"/>
     </row>
     <row r="109" spans="1:13">
@@ -5029,6 +5176,12 @@
       <c r="G109" s="11">
         <v>0.51</v>
       </c>
+      <c r="H109" s="14">
+        <v>0.43</v>
+      </c>
+      <c r="I109" s="11">
+        <v>0.54</v>
+      </c>
       <c r="M109" s="2"/>
     </row>
     <row r="110" spans="1:13">
@@ -5053,6 +5206,9 @@
       <c r="G110" s="11">
         <v>0.61</v>
       </c>
+      <c r="H110" s="14">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="J110" s="11">
         <v>0.86</v>
       </c>
@@ -5080,14 +5236,20 @@
       <c r="G111" s="11">
         <v>0.36</v>
       </c>
+      <c r="H111" s="14">
+        <v>0.39</v>
+      </c>
+      <c r="J111" s="11">
+        <v>0.72</v>
+      </c>
       <c r="M111" s="2"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
+        <v>486</v>
+      </c>
+      <c r="B112" s="7" t="s">
         <v>487</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>488</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>159</v>
@@ -5103,6 +5265,12 @@
       </c>
       <c r="G112" s="11">
         <v>0.66</v>
+      </c>
+      <c r="H112" s="14">
+        <v>0.62</v>
+      </c>
+      <c r="I112" s="11">
+        <v>0.55000000000000004</v>
       </c>
       <c r="M112" s="8"/>
     </row>
@@ -5128,6 +5296,12 @@
       <c r="G113" s="11">
         <v>0.68</v>
       </c>
+      <c r="H113" s="14">
+        <v>0.66</v>
+      </c>
+      <c r="J113" s="11">
+        <v>0.72</v>
+      </c>
       <c r="M113" s="2"/>
     </row>
     <row r="114" spans="1:13">
@@ -5152,6 +5326,12 @@
       <c r="G114" s="11">
         <v>0.82</v>
       </c>
+      <c r="H114" s="14">
+        <v>0.52</v>
+      </c>
+      <c r="I114" s="11">
+        <v>0.75</v>
+      </c>
       <c r="M114" s="2"/>
     </row>
     <row r="115" spans="1:13">
@@ -5176,6 +5356,9 @@
       <c r="G115" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H115" s="14">
+        <v>0.48</v>
+      </c>
       <c r="M115" s="2"/>
     </row>
     <row r="116" spans="1:13">
@@ -5200,6 +5383,9 @@
       <c r="G116" s="11">
         <v>0.6</v>
       </c>
+      <c r="H116" s="14">
+        <v>0.54</v>
+      </c>
       <c r="J116" s="11">
         <v>0.86</v>
       </c>
@@ -5227,6 +5413,9 @@
       <c r="G117" s="11">
         <v>0.52</v>
       </c>
+      <c r="H117" s="14">
+        <v>0.34</v>
+      </c>
       <c r="M117" s="2"/>
     </row>
     <row r="118" spans="1:13">
@@ -5251,6 +5440,9 @@
       <c r="G118" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H118" s="14">
+        <v>0.4</v>
+      </c>
       <c r="M118" s="2"/>
     </row>
     <row r="119" spans="1:13">
@@ -5275,6 +5467,12 @@
       <c r="G119" s="11">
         <v>0.39</v>
       </c>
+      <c r="H119" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="I119" s="11">
+        <v>0.25</v>
+      </c>
       <c r="M119" s="2"/>
     </row>
     <row r="120" spans="1:13">
@@ -5299,6 +5497,15 @@
       <c r="G120" s="11">
         <v>0.71</v>
       </c>
+      <c r="H120" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="I120" s="11">
+        <v>0.52</v>
+      </c>
+      <c r="J120" s="11">
+        <v>0.72</v>
+      </c>
       <c r="M120" s="2"/>
     </row>
     <row r="121" spans="1:13">
@@ -5323,6 +5530,12 @@
       <c r="G121" s="11">
         <v>0.36</v>
       </c>
+      <c r="H121" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="I121" s="11">
+        <v>0.34</v>
+      </c>
       <c r="J121" s="11">
         <v>0.86</v>
       </c>
@@ -5350,6 +5563,9 @@
       <c r="G122" s="11">
         <v>0.42</v>
       </c>
+      <c r="H122" s="14">
+        <v>0.19</v>
+      </c>
       <c r="J122" s="11">
         <v>0.78</v>
       </c>
@@ -5377,6 +5593,12 @@
       <c r="G123" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H123" s="14">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I123" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M123" s="2"/>
     </row>
     <row r="124" spans="1:13">
@@ -5401,6 +5623,9 @@
       <c r="G124" s="11">
         <v>0</v>
       </c>
+      <c r="H124" s="14">
+        <v>0</v>
+      </c>
       <c r="M124" s="2"/>
     </row>
     <row r="125" spans="1:13">
@@ -5425,6 +5650,9 @@
       <c r="G125" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H125" s="14">
+        <v>0.31</v>
+      </c>
       <c r="M125" s="2"/>
     </row>
     <row r="126" spans="1:13">
@@ -5449,6 +5677,12 @@
       <c r="G126" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H126" s="14">
+        <v>0.44</v>
+      </c>
+      <c r="I126" s="11">
+        <v>0.49</v>
+      </c>
       <c r="M126" s="2"/>
     </row>
     <row r="127" spans="1:13">
@@ -5473,6 +5707,12 @@
       <c r="G127" s="11">
         <v>0.79</v>
       </c>
+      <c r="H127" s="14">
+        <v>0.43</v>
+      </c>
+      <c r="I127" s="11">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J127" s="11">
         <v>0.86</v>
       </c>
@@ -5500,6 +5740,9 @@
       <c r="G128" s="11">
         <v>0.28999999999999998</v>
       </c>
+      <c r="H128" s="14">
+        <v>0.19</v>
+      </c>
       <c r="M128" s="2"/>
     </row>
     <row r="129" spans="1:13">
@@ -5524,6 +5767,9 @@
       <c r="G129" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H129" s="14">
+        <v>0.74</v>
+      </c>
       <c r="M129" s="2"/>
     </row>
     <row r="130" spans="1:13">
@@ -5548,6 +5794,9 @@
       <c r="G130" s="11">
         <v>0.78</v>
       </c>
+      <c r="H130" s="14">
+        <v>0.59</v>
+      </c>
       <c r="M130" s="2"/>
     </row>
     <row r="131" spans="1:13">
@@ -5572,6 +5821,12 @@
       <c r="G131" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H131" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="I131" s="11">
+        <v>0.42</v>
+      </c>
       <c r="J131" s="11">
         <v>0.86</v>
       </c>
@@ -5662,6 +5917,9 @@
       <c r="H134" s="14">
         <v>0.32500000000000001</v>
       </c>
+      <c r="J134" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M134" s="2"/>
     </row>
     <row r="135" spans="1:13">
@@ -5689,14 +5947,17 @@
       <c r="H135" s="14">
         <v>0.39300000000000002</v>
       </c>
+      <c r="J135" s="11">
+        <v>0.73</v>
+      </c>
       <c r="M135" s="2"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" t="s">
+        <v>502</v>
+      </c>
+      <c r="B136" s="7" t="s">
         <v>503</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>504</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>245</v>
@@ -5738,6 +5999,9 @@
       <c r="H137" s="14">
         <v>0.53</v>
       </c>
+      <c r="J137" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M137" s="2"/>
     </row>
     <row r="138" spans="1:13">
@@ -6239,6 +6503,9 @@
       <c r="H155" s="14">
         <v>0.47899999999999998</v>
       </c>
+      <c r="J155" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M155" s="2"/>
     </row>
     <row r="156" spans="1:13">
@@ -6347,6 +6614,9 @@
       <c r="H159" s="14">
         <v>0.23899999999999999</v>
       </c>
+      <c r="J159" s="11">
+        <v>0.73</v>
+      </c>
       <c r="M159" s="2"/>
     </row>
     <row r="160" spans="1:13">
@@ -6620,6 +6890,9 @@
       <c r="H169" s="14">
         <v>0.63200000000000001</v>
       </c>
+      <c r="J169" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M169" s="8"/>
     </row>
     <row r="170" spans="1:13">
@@ -6647,6 +6920,9 @@
       <c r="H170" s="14">
         <v>0.20499999999999999</v>
       </c>
+      <c r="J170" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M170" s="8"/>
     </row>
     <row r="171" spans="1:13">
@@ -6701,6 +6977,9 @@
       <c r="H172" s="14">
         <v>0.27400000000000002</v>
       </c>
+      <c r="J172" s="11">
+        <v>0.73</v>
+      </c>
       <c r="M172" s="8"/>
     </row>
     <row r="173" spans="1:13">
@@ -6920,6 +7199,9 @@
       <c r="H180" s="14">
         <v>0.23100000000000001</v>
       </c>
+      <c r="J180" s="11">
+        <v>0.73</v>
+      </c>
       <c r="M180" s="2"/>
     </row>
     <row r="181" spans="1:13">
@@ -8256,10 +8538,10 @@
     </row>
     <row r="233" spans="1:13">
       <c r="A233" t="s">
+        <v>489</v>
+      </c>
+      <c r="B233" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>491</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>343</v>
@@ -8480,10 +8762,10 @@
     </row>
     <row r="242" spans="1:13">
       <c r="A242" t="s">
+        <v>491</v>
+      </c>
+      <c r="B242" s="7" t="s">
         <v>492</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>493</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>343</v>
@@ -8581,7 +8863,7 @@
     </row>
     <row r="246" spans="1:13">
       <c r="A246" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B246" s="7" t="s">
         <v>391</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B9C37E-5F64-D34D-8210-C32302DCED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D4E02B-B635-0C44-B3FE-1E04E78D1F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4351,6 +4351,9 @@
       <c r="H80" s="14">
         <v>0.33</v>
       </c>
+      <c r="I80" s="11">
+        <v>0.45</v>
+      </c>
       <c r="J80" s="11">
         <v>0.72</v>
       </c>
@@ -4525,6 +4528,9 @@
       <c r="H86" s="14">
         <v>0.15</v>
       </c>
+      <c r="I86" s="11">
+        <v>0.52</v>
+      </c>
       <c r="J86" s="11">
         <v>0.78</v>
       </c>
@@ -4585,6 +4591,9 @@
       <c r="H88" s="14">
         <v>0.44</v>
       </c>
+      <c r="I88" s="11">
+        <v>0.38</v>
+      </c>
       <c r="M88" s="8"/>
     </row>
     <row r="89" spans="1:13">
@@ -4612,6 +4621,9 @@
       <c r="H89" s="14">
         <v>0.4</v>
       </c>
+      <c r="I89" s="11">
+        <v>0.44</v>
+      </c>
       <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:13">
@@ -4777,6 +4789,9 @@
       <c r="H95" s="14">
         <v>0.69</v>
       </c>
+      <c r="I95" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M95" s="2"/>
     </row>
     <row r="96" spans="1:13">
@@ -4804,6 +4819,9 @@
       <c r="H96" s="14">
         <v>0.62</v>
       </c>
+      <c r="I96" s="11">
+        <v>0</v>
+      </c>
       <c r="M96" s="8"/>
     </row>
     <row r="97" spans="1:13">
@@ -4831,6 +4849,9 @@
       <c r="H97" s="14">
         <v>0.5</v>
       </c>
+      <c r="I97" s="11">
+        <v>0.73</v>
+      </c>
       <c r="M97" s="8"/>
     </row>
     <row r="98" spans="1:13">
@@ -4858,6 +4879,9 @@
       <c r="H98" s="14">
         <v>0.5</v>
       </c>
+      <c r="I98" s="11">
+        <v>0.44</v>
+      </c>
       <c r="M98" s="2"/>
     </row>
     <row r="99" spans="1:13">
@@ -4915,6 +4939,9 @@
       <c r="H100" s="14">
         <v>0.72</v>
       </c>
+      <c r="I100" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M100" s="2"/>
     </row>
     <row r="101" spans="1:13">
@@ -5035,6 +5062,9 @@
       <c r="H104" s="14">
         <v>0.41</v>
       </c>
+      <c r="I104" s="11">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="J104" s="11">
         <v>0.78</v>
       </c>
@@ -5122,6 +5152,9 @@
       <c r="H107" s="14">
         <v>0.53</v>
       </c>
+      <c r="I107" s="11">
+        <v>0.35</v>
+      </c>
       <c r="M107" s="2"/>
     </row>
     <row r="108" spans="1:13">
@@ -5299,6 +5332,9 @@
       <c r="H113" s="14">
         <v>0.66</v>
       </c>
+      <c r="I113" s="11">
+        <v>0</v>
+      </c>
       <c r="J113" s="11">
         <v>0.72</v>
       </c>
@@ -5386,6 +5422,9 @@
       <c r="H116" s="14">
         <v>0.54</v>
       </c>
+      <c r="I116" s="11">
+        <v>0</v>
+      </c>
       <c r="J116" s="11">
         <v>0.86</v>
       </c>
@@ -5416,6 +5455,9 @@
       <c r="H117" s="14">
         <v>0.34</v>
       </c>
+      <c r="I117" s="11">
+        <v>0.45</v>
+      </c>
       <c r="M117" s="2"/>
     </row>
     <row r="118" spans="1:13">
@@ -5624,6 +5666,9 @@
         <v>0</v>
       </c>
       <c r="H124" s="14">
+        <v>0</v>
+      </c>
+      <c r="I124" s="11">
         <v>0</v>
       </c>
       <c r="M124" s="2"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D4E02B-B635-0C44-B3FE-1E04E78D1F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DDEED2-D976-4346-8BC1-5190B766B3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="11">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="F97" s="11">
         <v>0.88</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DDEED2-D976-4346-8BC1-5190B766B3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EA6208-1B1D-E14A-BE07-22FFEE68726D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4267,6 +4267,9 @@
       <c r="H77" s="14">
         <v>0.5</v>
       </c>
+      <c r="I77" s="11">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J77" s="11">
         <v>0.78</v>
       </c>
@@ -4474,6 +4477,9 @@
       <c r="H84" s="14">
         <v>0.43</v>
       </c>
+      <c r="I84" s="11">
+        <v>0.38</v>
+      </c>
       <c r="M84" s="8"/>
     </row>
     <row r="85" spans="1:13">
@@ -5485,6 +5491,9 @@
       <c r="H118" s="14">
         <v>0.4</v>
       </c>
+      <c r="I118" s="11">
+        <v>0.15</v>
+      </c>
       <c r="M118" s="2"/>
     </row>
     <row r="119" spans="1:13">
@@ -5815,6 +5824,9 @@
       <c r="H129" s="14">
         <v>0.74</v>
       </c>
+      <c r="I129" s="11">
+        <v>0.77</v>
+      </c>
       <c r="M129" s="2"/>
     </row>
     <row r="130" spans="1:13">
@@ -5841,6 +5853,9 @@
       </c>
       <c r="H130" s="14">
         <v>0.59</v>
+      </c>
+      <c r="I130" s="11">
+        <v>0.72</v>
       </c>
       <c r="M130" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EA6208-1B1D-E14A-BE07-22FFEE68726D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B894C360-4AAE-1149-8E2F-496969E8F145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4417,6 +4417,9 @@
       <c r="H82" s="14">
         <v>0.27</v>
       </c>
+      <c r="I82" s="11">
+        <v>0.3</v>
+      </c>
       <c r="J82" s="11">
         <v>0.78</v>
       </c>
@@ -4768,6 +4771,9 @@
       <c r="H94" s="14">
         <v>0.53</v>
       </c>
+      <c r="I94" s="11">
+        <v>0.49</v>
+      </c>
       <c r="M94" s="2"/>
     </row>
     <row r="95" spans="1:13">
@@ -5131,6 +5137,9 @@
       <c r="H106" s="14">
         <v>0.17</v>
       </c>
+      <c r="I106" s="11">
+        <v>0.2</v>
+      </c>
       <c r="M106" s="2"/>
     </row>
     <row r="107" spans="1:13">
@@ -5248,6 +5257,9 @@
       <c r="H110" s="14">
         <v>0.56999999999999995</v>
       </c>
+      <c r="I110" s="11">
+        <v>0.45</v>
+      </c>
       <c r="J110" s="11">
         <v>0.86</v>
       </c>
@@ -5278,6 +5290,9 @@
       <c r="H111" s="14">
         <v>0.39</v>
       </c>
+      <c r="I111" s="11">
+        <v>0.24</v>
+      </c>
       <c r="J111" s="11">
         <v>0.72</v>
       </c>
@@ -5401,6 +5416,9 @@
       <c r="H115" s="14">
         <v>0.48</v>
       </c>
+      <c r="I115" s="11">
+        <v>0.43</v>
+      </c>
       <c r="M115" s="2"/>
     </row>
     <row r="116" spans="1:13">
@@ -5617,6 +5635,9 @@
       <c r="H122" s="14">
         <v>0.19</v>
       </c>
+      <c r="I122" s="11">
+        <v>0.3</v>
+      </c>
       <c r="J122" s="11">
         <v>0.78</v>
       </c>
@@ -5707,6 +5728,9 @@
       <c r="H125" s="14">
         <v>0.31</v>
       </c>
+      <c r="I125" s="11">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M125" s="2"/>
     </row>
     <row r="126" spans="1:13">
@@ -5796,6 +5820,9 @@
       </c>
       <c r="H128" s="14">
         <v>0.19</v>
+      </c>
+      <c r="I128" s="11">
+        <v>0.22</v>
       </c>
       <c r="M128" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B894C360-4AAE-1149-8E2F-496969E8F145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B716CD28-9720-764C-A0D3-57658063EF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4300,6 +4300,9 @@
       <c r="H78" s="14">
         <v>0.62</v>
       </c>
+      <c r="I78" s="11">
+        <v>0</v>
+      </c>
       <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13">
@@ -4327,6 +4330,9 @@
       <c r="H79" s="14">
         <v>0.34</v>
       </c>
+      <c r="I79" s="11">
+        <v>0.31</v>
+      </c>
       <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13">
@@ -4510,6 +4516,9 @@
       <c r="H85" s="14">
         <v>0.65</v>
       </c>
+      <c r="I85" s="11">
+        <v>0</v>
+      </c>
       <c r="M85" s="2"/>
     </row>
     <row r="86" spans="1:13">
@@ -4660,6 +4669,9 @@
       <c r="H90" s="14">
         <v>0.55000000000000004</v>
       </c>
+      <c r="I90" s="11">
+        <v>0</v>
+      </c>
       <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:13">
@@ -4687,6 +4699,9 @@
       <c r="H91" s="14">
         <v>0.6</v>
       </c>
+      <c r="I91" s="11">
+        <v>0.22</v>
+      </c>
       <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:13">
@@ -4742,6 +4757,9 @@
         <v>0</v>
       </c>
       <c r="H93" s="14">
+        <v>0</v>
+      </c>
+      <c r="I93" s="11">
         <v>0</v>
       </c>
       <c r="M93" s="2"/>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B716CD28-9720-764C-A0D3-57658063EF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E437EB84-3AC7-2C41-A1E8-568C461B3742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7661,6 +7661,9 @@
       <c r="G193" s="11">
         <v>0.75</v>
       </c>
+      <c r="H193" s="14">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="J193" s="11">
         <v>0.8</v>
       </c>
@@ -7688,6 +7691,12 @@
       <c r="G194" s="11">
         <v>0.64</v>
       </c>
+      <c r="H194" s="14">
+        <v>0.51</v>
+      </c>
+      <c r="I194" s="11">
+        <v>0.51</v>
+      </c>
       <c r="J194" s="11">
         <v>0.85</v>
       </c>
@@ -7715,6 +7724,12 @@
       <c r="G195" s="11">
         <v>0.45</v>
       </c>
+      <c r="H195" s="14">
+        <v>0.41</v>
+      </c>
+      <c r="I195" s="11">
+        <v>0.25</v>
+      </c>
       <c r="J195" s="11">
         <v>0.77</v>
       </c>
@@ -7742,6 +7757,9 @@
       <c r="G196" s="11">
         <v>0.61</v>
       </c>
+      <c r="H196" s="14">
+        <v>0.72</v>
+      </c>
       <c r="J196" s="11">
         <v>0.83</v>
       </c>
@@ -7769,6 +7787,12 @@
       <c r="G197" s="11">
         <v>0.7</v>
       </c>
+      <c r="H197" s="14">
+        <v>0.52</v>
+      </c>
+      <c r="I197" s="11">
+        <v>0.51</v>
+      </c>
       <c r="J197" s="11">
         <v>0.8</v>
       </c>
@@ -7796,6 +7820,12 @@
       <c r="G198" s="11">
         <v>0.64</v>
       </c>
+      <c r="H198" s="14">
+        <v>0.51</v>
+      </c>
+      <c r="I198" s="11">
+        <v>0.21</v>
+      </c>
       <c r="M198" s="2"/>
     </row>
     <row r="199" spans="1:13">
@@ -7820,6 +7850,9 @@
       <c r="G199" s="11">
         <v>0.64</v>
       </c>
+      <c r="H199" s="14">
+        <v>0.52</v>
+      </c>
       <c r="M199" s="2"/>
     </row>
     <row r="200" spans="1:13">
@@ -7844,6 +7877,9 @@
       <c r="G200" s="11">
         <v>0.65</v>
       </c>
+      <c r="H200" s="14">
+        <v>0.47</v>
+      </c>
       <c r="J200" s="11">
         <v>0.77</v>
       </c>
@@ -7871,6 +7907,12 @@
       <c r="G201" s="11">
         <v>0.69</v>
       </c>
+      <c r="H201" s="14">
+        <v>0.47</v>
+      </c>
+      <c r="I201" s="11">
+        <v>0.59</v>
+      </c>
       <c r="M201" s="2"/>
     </row>
     <row r="202" spans="1:13">
@@ -7895,6 +7937,9 @@
       <c r="G202" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H202" s="14">
+        <v>0.31</v>
+      </c>
       <c r="M202" s="2"/>
     </row>
     <row r="203" spans="1:13">
@@ -7919,6 +7964,9 @@
       <c r="G203" s="11">
         <v>0.78</v>
       </c>
+      <c r="H203" s="14">
+        <v>0.78</v>
+      </c>
       <c r="M203" s="2"/>
     </row>
     <row r="204" spans="1:13">
@@ -7943,6 +7991,9 @@
       <c r="G204" s="11">
         <v>0.64</v>
       </c>
+      <c r="H204" s="14">
+        <v>0.17</v>
+      </c>
       <c r="M204" s="2"/>
     </row>
     <row r="205" spans="1:13">
@@ -7967,6 +8018,12 @@
       <c r="G205" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H205" s="14">
+        <v>0.39</v>
+      </c>
+      <c r="I205" s="11">
+        <v>0.48</v>
+      </c>
       <c r="J205" s="11">
         <v>0.83</v>
       </c>
@@ -7994,6 +8051,9 @@
       <c r="G206" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="H206" s="14">
+        <v>0.37</v>
+      </c>
       <c r="M206" s="2"/>
     </row>
     <row r="207" spans="1:13">
@@ -8018,6 +8078,9 @@
       <c r="G207" s="11">
         <v>0.73</v>
       </c>
+      <c r="H207" s="14">
+        <v>0.48</v>
+      </c>
       <c r="M207" s="2"/>
     </row>
     <row r="208" spans="1:13">
@@ -8042,6 +8105,9 @@
       <c r="G208" s="11">
         <v>0.82</v>
       </c>
+      <c r="H208" s="14">
+        <v>0.59</v>
+      </c>
       <c r="J208" s="11">
         <v>0.8</v>
       </c>
@@ -8069,6 +8135,9 @@
       <c r="G209" s="11">
         <v>0.64</v>
       </c>
+      <c r="H209" s="14">
+        <v>0.59</v>
+      </c>
       <c r="M209" s="2"/>
     </row>
     <row r="210" spans="1:13">
@@ -8093,6 +8162,9 @@
       <c r="G210" s="11">
         <v>0.7</v>
       </c>
+      <c r="H210" s="14">
+        <v>0.61</v>
+      </c>
       <c r="M210" s="2"/>
     </row>
     <row r="211" spans="1:13">
@@ -8117,6 +8189,9 @@
       <c r="G211" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H211" s="14">
+        <v>0.51</v>
+      </c>
       <c r="M211" s="2"/>
     </row>
     <row r="212" spans="1:13">
@@ -8141,6 +8216,9 @@
       <c r="G212" s="11">
         <v>0.81</v>
       </c>
+      <c r="H212" s="14">
+        <v>0.72</v>
+      </c>
       <c r="M212" s="2"/>
     </row>
     <row r="213" spans="1:13">
@@ -8165,6 +8243,9 @@
       <c r="G213" s="11">
         <v>0.71</v>
       </c>
+      <c r="H213" s="14">
+        <v>0</v>
+      </c>
       <c r="J213" s="11">
         <v>0.83</v>
       </c>
@@ -8192,6 +8273,9 @@
       <c r="G214" s="11">
         <v>0.49</v>
       </c>
+      <c r="H214" s="14">
+        <v>0.5</v>
+      </c>
       <c r="M214" s="2"/>
     </row>
     <row r="215" spans="1:13">
@@ -8216,6 +8300,9 @@
       <c r="G215" s="11">
         <v>0.6</v>
       </c>
+      <c r="H215" s="14">
+        <v>0.31</v>
+      </c>
       <c r="J215" s="11">
         <v>0.85</v>
       </c>
@@ -8243,6 +8330,9 @@
       <c r="G216" s="11">
         <v>0.75</v>
       </c>
+      <c r="H216" s="14">
+        <v>0.5</v>
+      </c>
       <c r="M216" s="2"/>
     </row>
     <row r="217" spans="1:13">
@@ -8267,6 +8357,9 @@
       <c r="G217" s="11">
         <v>0.69</v>
       </c>
+      <c r="H217" s="14">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M217" s="2"/>
     </row>
     <row r="218" spans="1:13">
@@ -8291,6 +8384,12 @@
       <c r="G218" s="11">
         <v>0.73</v>
       </c>
+      <c r="H218" s="14">
+        <v>0.53</v>
+      </c>
+      <c r="I218" s="11">
+        <v>0.39</v>
+      </c>
       <c r="M218" s="2"/>
     </row>
     <row r="219" spans="1:13">
@@ -8315,6 +8414,12 @@
       <c r="G219" s="11">
         <v>0.73</v>
       </c>
+      <c r="H219" s="14">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I219" s="11">
+        <v>0.48</v>
+      </c>
       <c r="J219" s="11">
         <v>0.79</v>
       </c>
@@ -8342,6 +8447,9 @@
       <c r="G220" s="11">
         <v>0.69</v>
       </c>
+      <c r="H220" s="14">
+        <v>0.64</v>
+      </c>
       <c r="M220" s="2"/>
     </row>
     <row r="221" spans="1:13">
@@ -8366,6 +8474,9 @@
       <c r="G221" s="11">
         <v>0.83</v>
       </c>
+      <c r="H221" s="14">
+        <v>0.72</v>
+      </c>
       <c r="M221" s="2"/>
     </row>
     <row r="222" spans="1:13">
@@ -8390,6 +8501,9 @@
       <c r="G222" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="H222" s="14">
+        <v>0.54</v>
+      </c>
       <c r="M222" s="2"/>
     </row>
     <row r="223" spans="1:13">
@@ -8414,6 +8528,12 @@
       <c r="G223" s="11">
         <v>0.77</v>
       </c>
+      <c r="H223" s="14">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I223" s="11">
+        <v>0.37</v>
+      </c>
       <c r="M223" s="2"/>
     </row>
     <row r="224" spans="1:13">
@@ -8438,6 +8558,9 @@
       <c r="G224" s="11">
         <v>0.77</v>
       </c>
+      <c r="H224" s="14">
+        <v>0.71</v>
+      </c>
       <c r="J224" s="11">
         <v>0.93</v>
       </c>
@@ -8465,6 +8588,12 @@
       <c r="G225" s="11">
         <v>0.74</v>
       </c>
+      <c r="H225" s="14">
+        <v>0.6</v>
+      </c>
+      <c r="I225" s="11">
+        <v>0.31</v>
+      </c>
       <c r="M225" s="2"/>
     </row>
     <row r="226" spans="1:13">
@@ -8489,6 +8618,9 @@
       <c r="G226" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H226" s="14">
+        <v>0.43</v>
+      </c>
       <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13">
@@ -8513,6 +8645,9 @@
       <c r="G227" s="11">
         <v>0.35</v>
       </c>
+      <c r="H227" s="14">
+        <v>0.46</v>
+      </c>
       <c r="M227" s="2"/>
     </row>
     <row r="228" spans="1:13">
@@ -8537,6 +8672,9 @@
       <c r="G228" s="11">
         <v>0.88</v>
       </c>
+      <c r="H228" s="14">
+        <v>0.83</v>
+      </c>
       <c r="J228" s="11">
         <v>0.85</v>
       </c>
@@ -8564,6 +8702,9 @@
       <c r="G229" s="11">
         <v>0.6</v>
       </c>
+      <c r="H229" s="14">
+        <v>0.62</v>
+      </c>
       <c r="J229" s="11">
         <v>0.93</v>
       </c>
@@ -8591,6 +8732,9 @@
       <c r="G230" s="11">
         <v>0.81</v>
       </c>
+      <c r="H230" s="14">
+        <v>0.5</v>
+      </c>
       <c r="M230" s="9"/>
     </row>
     <row r="231" spans="1:13">
@@ -8615,6 +8759,9 @@
       <c r="G231" s="11">
         <v>0.7</v>
       </c>
+      <c r="H231" s="14">
+        <v>0.61</v>
+      </c>
       <c r="M231" s="9"/>
     </row>
     <row r="232" spans="1:13">
@@ -8639,6 +8786,9 @@
       <c r="G232" s="11">
         <v>0.77</v>
       </c>
+      <c r="H232" s="14">
+        <v>0.65</v>
+      </c>
       <c r="M232" s="9"/>
     </row>
     <row r="233" spans="1:13">
@@ -8663,6 +8813,9 @@
       <c r="G233" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H233" s="14">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
@@ -8686,6 +8839,9 @@
       <c r="G234" s="11">
         <v>0.53</v>
       </c>
+      <c r="H234" s="14">
+        <v>0.32</v>
+      </c>
       <c r="J234" s="11">
         <v>0.93</v>
       </c>
@@ -8713,6 +8869,12 @@
       <c r="G235" s="11">
         <v>0.69</v>
       </c>
+      <c r="H235" s="14">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I235" s="11">
+        <v>0.4</v>
+      </c>
       <c r="M235" s="9"/>
     </row>
     <row r="236" spans="1:13">
@@ -8737,6 +8899,9 @@
       <c r="G236" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H236" s="14">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J236" s="11">
         <v>0.93</v>
       </c>
@@ -8764,6 +8929,9 @@
       <c r="G237" s="11">
         <v>0.64</v>
       </c>
+      <c r="H237" s="14">
+        <v>0.51</v>
+      </c>
       <c r="M237" s="9"/>
     </row>
     <row r="238" spans="1:13">
@@ -8788,6 +8956,9 @@
       <c r="G238" s="11">
         <v>0.82</v>
       </c>
+      <c r="H238" s="14">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J238" s="11">
         <v>0.8</v>
       </c>
@@ -8815,6 +8986,9 @@
       <c r="G239" s="11">
         <v>0.68</v>
       </c>
+      <c r="H239" s="14">
+        <v>0.34</v>
+      </c>
       <c r="M239" s="9"/>
     </row>
     <row r="240" spans="1:13">
@@ -8839,6 +9013,9 @@
       <c r="G240" s="11">
         <v>0.43</v>
       </c>
+      <c r="H240" s="14">
+        <v>0.49</v>
+      </c>
       <c r="M240" s="9"/>
     </row>
     <row r="241" spans="1:13">
@@ -8863,6 +9040,9 @@
       <c r="G241" s="11">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H241" s="14">
+        <v>0.66</v>
+      </c>
       <c r="M241" s="9"/>
     </row>
     <row r="242" spans="1:13">
@@ -8887,6 +9067,9 @@
       <c r="G242" s="11">
         <v>0.49</v>
       </c>
+      <c r="H242" s="14">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="243" spans="1:13">
       <c r="A243" s="4" t="s">
@@ -8910,6 +9093,9 @@
       <c r="G243" s="11">
         <v>0.77</v>
       </c>
+      <c r="H243" s="14">
+        <v>0.53</v>
+      </c>
       <c r="M243" s="9"/>
     </row>
     <row r="244" spans="1:13">
@@ -8934,6 +9120,9 @@
       <c r="G244" s="11">
         <v>0.51</v>
       </c>
+      <c r="H244" s="14">
+        <v>0.64</v>
+      </c>
       <c r="J244" s="11">
         <v>0.83</v>
       </c>
@@ -8961,6 +9150,9 @@
       <c r="G245" s="11">
         <v>0.78</v>
       </c>
+      <c r="H245" s="14">
+        <v>0.47</v>
+      </c>
       <c r="J245" s="11">
         <v>0.8</v>
       </c>
@@ -8988,6 +9180,9 @@
       <c r="G246" s="11">
         <v>0.64</v>
       </c>
+      <c r="H246" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="247" spans="1:13">
       <c r="A247" s="4" t="s">
@@ -9011,6 +9206,9 @@
       <c r="G247" s="11">
         <v>0.65</v>
       </c>
+      <c r="H247" s="14">
+        <v>0.61</v>
+      </c>
       <c r="M247" s="9"/>
     </row>
     <row r="248" spans="1:13">
@@ -9034,6 +9232,9 @@
       </c>
       <c r="G248" s="11">
         <v>0.71</v>
+      </c>
+      <c r="H248" s="14">
+        <v>0.7</v>
       </c>
       <c r="J248" s="11">
         <v>0.93</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E437EB84-3AC7-2C41-A1E8-568C461B3742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0615AC21-4EDD-DA4C-9C05-292ED13012EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7760,6 +7760,9 @@
       <c r="H196" s="14">
         <v>0.72</v>
       </c>
+      <c r="I196" s="11">
+        <v>0.67</v>
+      </c>
       <c r="J196" s="11">
         <v>0.83</v>
       </c>
@@ -8108,6 +8111,9 @@
       <c r="H208" s="14">
         <v>0.59</v>
       </c>
+      <c r="I208" s="11">
+        <v>0.43</v>
+      </c>
       <c r="J208" s="11">
         <v>0.8</v>
       </c>
@@ -8303,6 +8309,9 @@
       <c r="H215" s="14">
         <v>0.31</v>
       </c>
+      <c r="I215" s="11">
+        <v>0.52</v>
+      </c>
       <c r="J215" s="11">
         <v>0.85</v>
       </c>
@@ -8621,6 +8630,9 @@
       <c r="H226" s="14">
         <v>0.43</v>
       </c>
+      <c r="I226" s="11">
+        <v>0.32</v>
+      </c>
       <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13">
@@ -8842,6 +8854,9 @@
       <c r="H234" s="14">
         <v>0.32</v>
       </c>
+      <c r="I234" s="11">
+        <v>0.39</v>
+      </c>
       <c r="J234" s="11">
         <v>0.93</v>
       </c>
@@ -8989,6 +9004,9 @@
       <c r="H239" s="14">
         <v>0.34</v>
       </c>
+      <c r="I239" s="11">
+        <v>0.3</v>
+      </c>
       <c r="M239" s="9"/>
     </row>
     <row r="240" spans="1:13">
@@ -9043,6 +9061,9 @@
       <c r="H241" s="14">
         <v>0.66</v>
       </c>
+      <c r="I241" s="11">
+        <v>0.44</v>
+      </c>
       <c r="M241" s="9"/>
     </row>
     <row r="242" spans="1:13">
@@ -9208,6 +9229,9 @@
       </c>
       <c r="H247" s="14">
         <v>0.61</v>
+      </c>
+      <c r="I247" s="11">
+        <v>0.45</v>
       </c>
       <c r="M247" s="9"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0615AC21-4EDD-DA4C-9C05-292ED13012EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0037DF8F-79DF-A441-A1F1-959B39EC634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7883,6 +7883,9 @@
       <c r="H200" s="14">
         <v>0.47</v>
       </c>
+      <c r="I200" s="11">
+        <v>0.44</v>
+      </c>
       <c r="J200" s="11">
         <v>0.77</v>
       </c>
@@ -7997,6 +8000,9 @@
       <c r="H204" s="14">
         <v>0.17</v>
       </c>
+      <c r="I204" s="11">
+        <v>0.6</v>
+      </c>
       <c r="M204" s="2"/>
     </row>
     <row r="205" spans="1:13">
@@ -8252,6 +8258,9 @@
       <c r="H213" s="14">
         <v>0</v>
       </c>
+      <c r="I213" s="11">
+        <v>0.71</v>
+      </c>
       <c r="J213" s="11">
         <v>0.83</v>
       </c>
@@ -8459,6 +8468,9 @@
       <c r="H220" s="14">
         <v>0.64</v>
       </c>
+      <c r="I220" s="11">
+        <v>0.61</v>
+      </c>
       <c r="M220" s="2"/>
     </row>
     <row r="221" spans="1:13">
@@ -8973,6 +8985,9 @@
       </c>
       <c r="H238" s="14">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="I238" s="11">
+        <v>0.44</v>
       </c>
       <c r="J238" s="11">
         <v>0.8</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0037DF8F-79DF-A441-A1F1-959B39EC634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4EF32A-5E40-1247-9BCF-23EF730D50E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7664,6 +7664,9 @@
       <c r="H193" s="14">
         <v>0.56999999999999995</v>
       </c>
+      <c r="I193" s="11">
+        <v>0.53</v>
+      </c>
       <c r="J193" s="11">
         <v>0.8</v>
       </c>
@@ -7856,6 +7859,9 @@
       <c r="H199" s="14">
         <v>0.52</v>
       </c>
+      <c r="I199" s="11">
+        <v>0.5</v>
+      </c>
       <c r="M199" s="2"/>
     </row>
     <row r="200" spans="1:13">
@@ -8672,6 +8678,9 @@
       <c r="H227" s="14">
         <v>0.46</v>
       </c>
+      <c r="I227" s="11">
+        <v>0.35</v>
+      </c>
       <c r="M227" s="2"/>
     </row>
     <row r="228" spans="1:13">
@@ -8840,6 +8849,9 @@
       <c r="H233" s="14">
         <v>0.46</v>
       </c>
+      <c r="I233" s="11">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
@@ -9048,6 +9060,9 @@
       </c>
       <c r="H240" s="14">
         <v>0.49</v>
+      </c>
+      <c r="I240" s="11">
+        <v>0.2</v>
       </c>
       <c r="M240" s="9"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4EF32A-5E40-1247-9BCF-23EF730D50E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D1B0A1-BD6B-314A-AE60-B920919C97C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7952,6 +7952,9 @@
       <c r="H202" s="14">
         <v>0.31</v>
       </c>
+      <c r="I202" s="11">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M202" s="2"/>
     </row>
     <row r="203" spans="1:13">
@@ -7979,6 +7982,9 @@
       <c r="H203" s="14">
         <v>0.78</v>
       </c>
+      <c r="I203" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M203" s="2"/>
     </row>
     <row r="204" spans="1:13">
@@ -8069,6 +8075,9 @@
       <c r="H206" s="14">
         <v>0.37</v>
       </c>
+      <c r="I206" s="11">
+        <v>0.61</v>
+      </c>
       <c r="M206" s="2"/>
     </row>
     <row r="207" spans="1:13">
@@ -8096,6 +8105,9 @@
       <c r="H207" s="14">
         <v>0.48</v>
       </c>
+      <c r="I207" s="11">
+        <v>0.42</v>
+      </c>
       <c r="M207" s="2"/>
     </row>
     <row r="208" spans="1:13">
@@ -8156,6 +8168,9 @@
       <c r="H209" s="14">
         <v>0.59</v>
       </c>
+      <c r="I209" s="11">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M209" s="2"/>
     </row>
     <row r="210" spans="1:13">
@@ -8183,6 +8198,9 @@
       <c r="H210" s="14">
         <v>0.61</v>
       </c>
+      <c r="I210" s="11">
+        <v>0</v>
+      </c>
       <c r="M210" s="2"/>
     </row>
     <row r="211" spans="1:13">
@@ -8210,6 +8228,9 @@
       <c r="H211" s="14">
         <v>0.51</v>
       </c>
+      <c r="I211" s="11">
+        <v>0</v>
+      </c>
       <c r="M211" s="2"/>
     </row>
     <row r="212" spans="1:13">
@@ -8237,6 +8258,9 @@
       <c r="H212" s="14">
         <v>0.72</v>
       </c>
+      <c r="I212" s="11">
+        <v>0</v>
+      </c>
       <c r="M212" s="2"/>
     </row>
     <row r="213" spans="1:13">
@@ -8297,6 +8321,9 @@
       <c r="H214" s="14">
         <v>0.5</v>
       </c>
+      <c r="I214" s="11">
+        <v>0.36</v>
+      </c>
       <c r="M214" s="2"/>
     </row>
     <row r="215" spans="1:13">
@@ -8357,6 +8384,9 @@
       <c r="H216" s="14">
         <v>0.5</v>
       </c>
+      <c r="I216" s="11">
+        <v>0</v>
+      </c>
       <c r="M216" s="2"/>
     </row>
     <row r="217" spans="1:13">
@@ -8384,6 +8414,9 @@
       <c r="H217" s="14">
         <v>0.57999999999999996</v>
       </c>
+      <c r="I217" s="11">
+        <v>0</v>
+      </c>
       <c r="M217" s="2"/>
     </row>
     <row r="218" spans="1:13">
@@ -8504,6 +8537,9 @@
       <c r="H221" s="14">
         <v>0.72</v>
       </c>
+      <c r="I221" s="11">
+        <v>0</v>
+      </c>
       <c r="M221" s="2"/>
     </row>
     <row r="222" spans="1:13">
@@ -8531,6 +8567,9 @@
       <c r="H222" s="14">
         <v>0.54</v>
       </c>
+      <c r="I222" s="11">
+        <v>0</v>
+      </c>
       <c r="M222" s="2"/>
     </row>
     <row r="223" spans="1:13">
@@ -8588,6 +8627,9 @@
       <c r="H224" s="14">
         <v>0.71</v>
       </c>
+      <c r="I224" s="11">
+        <v>0</v>
+      </c>
       <c r="J224" s="11">
         <v>0.93</v>
       </c>
@@ -8708,6 +8750,9 @@
       <c r="H228" s="14">
         <v>0.83</v>
       </c>
+      <c r="I228" s="11">
+        <v>0</v>
+      </c>
       <c r="J228" s="11">
         <v>0.85</v>
       </c>
@@ -8738,6 +8783,9 @@
       <c r="H229" s="14">
         <v>0.62</v>
       </c>
+      <c r="I229" s="11">
+        <v>0</v>
+      </c>
       <c r="J229" s="11">
         <v>0.93</v>
       </c>
@@ -8768,6 +8816,9 @@
       <c r="H230" s="14">
         <v>0.5</v>
       </c>
+      <c r="I230" s="11">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="M230" s="9"/>
     </row>
     <row r="231" spans="1:13">
@@ -8795,6 +8846,9 @@
       <c r="H231" s="14">
         <v>0.61</v>
       </c>
+      <c r="I231" s="11">
+        <v>0</v>
+      </c>
       <c r="M231" s="9"/>
     </row>
     <row r="232" spans="1:13">
@@ -8822,6 +8876,9 @@
       <c r="H232" s="14">
         <v>0.65</v>
       </c>
+      <c r="I232" s="11">
+        <v>0</v>
+      </c>
       <c r="M232" s="9"/>
     </row>
     <row r="233" spans="1:13">
@@ -8941,6 +8998,9 @@
       <c r="H236" s="14">
         <v>0.57999999999999996</v>
       </c>
+      <c r="I236" s="11">
+        <v>0</v>
+      </c>
       <c r="J236" s="11">
         <v>0.93</v>
       </c>
@@ -8971,6 +9031,9 @@
       <c r="H237" s="14">
         <v>0.51</v>
       </c>
+      <c r="I237" s="11">
+        <v>0</v>
+      </c>
       <c r="M237" s="9"/>
     </row>
     <row r="238" spans="1:13">
@@ -9121,6 +9184,9 @@
       <c r="H242" s="14">
         <v>0.37</v>
       </c>
+      <c r="I242" s="11">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="243" spans="1:13">
       <c r="A243" s="4" t="s">
@@ -9147,6 +9213,9 @@
       <c r="H243" s="14">
         <v>0.53</v>
       </c>
+      <c r="I243" s="11">
+        <v>0</v>
+      </c>
       <c r="M243" s="9"/>
     </row>
     <row r="244" spans="1:13">
@@ -9174,6 +9243,9 @@
       <c r="H244" s="14">
         <v>0.64</v>
       </c>
+      <c r="I244" s="11">
+        <v>0.72</v>
+      </c>
       <c r="J244" s="11">
         <v>0.83</v>
       </c>
@@ -9204,6 +9276,9 @@
       <c r="H245" s="14">
         <v>0.47</v>
       </c>
+      <c r="I245" s="11">
+        <v>0.41</v>
+      </c>
       <c r="J245" s="11">
         <v>0.8</v>
       </c>
@@ -9234,6 +9309,9 @@
       <c r="H246" s="14">
         <v>0</v>
       </c>
+      <c r="I246" s="11">
+        <v>0</v>
+      </c>
     </row>
     <row r="247" spans="1:13">
       <c r="A247" s="4" t="s">
@@ -9289,6 +9367,9 @@
       </c>
       <c r="H248" s="14">
         <v>0.7</v>
+      </c>
+      <c r="I248" s="11">
+        <v>0</v>
       </c>
       <c r="J248" s="11">
         <v>0.93</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D1B0A1-BD6B-314A-AE60-B920919C97C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00BBFC8-3438-814D-A358-F54561E70925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6272,6 +6272,9 @@
       <c r="H143" s="14">
         <v>0.45300000000000001</v>
       </c>
+      <c r="I143" s="11">
+        <v>0.37</v>
+      </c>
       <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13">
@@ -6299,6 +6302,9 @@
       <c r="H144" s="14">
         <v>0.29899999999999999</v>
       </c>
+      <c r="I144" s="11">
+        <v>0.21</v>
+      </c>
       <c r="M144" s="2"/>
     </row>
     <row r="145" spans="1:13">
@@ -6326,6 +6332,9 @@
       <c r="H145" s="14">
         <v>0.23899999999999999</v>
       </c>
+      <c r="I145" s="11">
+        <v>0.17</v>
+      </c>
       <c r="M145" s="2"/>
     </row>
     <row r="146" spans="1:13">
@@ -6776,6 +6785,9 @@
       <c r="H161" s="14">
         <v>0.41899999999999998</v>
       </c>
+      <c r="I161" s="11">
+        <v>0.19</v>
+      </c>
       <c r="M161" s="2"/>
     </row>
     <row r="162" spans="1:13">
@@ -7276,6 +7288,9 @@
       </c>
       <c r="H179" s="14">
         <v>0.47899999999999998</v>
+      </c>
+      <c r="I179" s="11">
+        <v>0.52</v>
       </c>
       <c r="M179" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00BBFC8-3438-814D-A358-F54561E70925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA02E64-E486-A04B-8118-DF8247FAD32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="18880" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -839,9 +839,6 @@
     <t>H260757R</t>
   </si>
   <si>
-    <t>MANJICHE</t>
-  </si>
-  <si>
     <t>H263158E</t>
   </si>
   <si>
@@ -1551,6 +1548,9 @@
   </si>
   <si>
     <t>Maparara</t>
+  </si>
+  <si>
+    <t>Manjiche</t>
   </si>
 </sst>
 </file>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>480</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>15</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
+        <v>480</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>481</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>482</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>15</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>15</v>
@@ -4370,10 +4370,10 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
+        <v>493</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>494</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>495</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>159</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>159</v>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
+        <v>495</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>496</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>497</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>159</v>
@@ -4586,10 +4586,10 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>159</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
+        <v>497</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>498</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>499</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>159</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
+        <v>499</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>500</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>501</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>159</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>159</v>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
+        <v>483</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>485</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>159</v>
@@ -5318,10 +5318,10 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
+        <v>485</v>
+      </c>
+      <c r="B112" s="7" t="s">
         <v>486</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>487</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>159</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>449</v>
       </c>
       <c r="C116" s="13" t="s">
         <v>159</v>
@@ -5783,10 +5783,10 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C127" s="13" t="s">
         <v>159</v>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="C131" s="13" t="s">
         <v>159</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B132" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>245</v>
@@ -5962,6 +5962,9 @@
       <c r="H132" s="14">
         <v>0.436</v>
       </c>
+      <c r="I132" s="11">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="J132" s="11">
         <v>0.8</v>
       </c>
@@ -5969,10 +5972,10 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>245</v>
@@ -5992,6 +5995,9 @@
       <c r="H133" s="14">
         <v>0.39300000000000002</v>
       </c>
+      <c r="I133" s="11">
+        <v>0.48</v>
+      </c>
       <c r="J133" s="11">
         <v>0.83</v>
       </c>
@@ -5999,10 +6005,10 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>312</v>
       </c>
       <c r="C134" s="12" t="s">
         <v>245</v>
@@ -6022,6 +6028,9 @@
       <c r="H134" s="14">
         <v>0.32500000000000001</v>
       </c>
+      <c r="I134" s="11">
+        <v>0.42</v>
+      </c>
       <c r="J134" s="11">
         <v>0.78</v>
       </c>
@@ -6029,10 +6038,10 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B135" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>334</v>
       </c>
       <c r="C135" s="12" t="s">
         <v>245</v>
@@ -6052,6 +6061,9 @@
       <c r="H135" s="14">
         <v>0.39300000000000002</v>
       </c>
+      <c r="I135" s="11">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="J135" s="11">
         <v>0.73</v>
       </c>
@@ -6059,10 +6071,10 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" t="s">
+        <v>501</v>
+      </c>
+      <c r="B136" s="7" t="s">
         <v>502</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>503</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>245</v>
@@ -6077,14 +6089,17 @@
       <c r="H136" s="14">
         <v>7.6999999999999999E-2</v>
       </c>
+      <c r="I136" s="11">
+        <v>0.24</v>
+      </c>
       <c r="M136" s="8"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B137" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>245</v>
@@ -6104,6 +6119,9 @@
       <c r="H137" s="14">
         <v>0.53</v>
       </c>
+      <c r="I137" s="11">
+        <v>0.59</v>
+      </c>
       <c r="J137" s="11">
         <v>0.78</v>
       </c>
@@ -6111,10 +6129,10 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>336</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>245</v>
@@ -6133,6 +6151,9 @@
       </c>
       <c r="H138" s="14">
         <v>0.53800000000000003</v>
+      </c>
+      <c r="I138" s="11">
+        <v>0.65</v>
       </c>
       <c r="M138" s="2"/>
     </row>
@@ -6161,6 +6182,9 @@
       <c r="H139" s="14">
         <v>0.56399999999999995</v>
       </c>
+      <c r="I139" s="11">
+        <v>0.46</v>
+      </c>
       <c r="M139" s="2"/>
     </row>
     <row r="140" spans="1:13">
@@ -6188,14 +6212,17 @@
       <c r="H140" s="14">
         <v>0.26500000000000001</v>
       </c>
+      <c r="I140" s="11">
+        <v>0.27</v>
+      </c>
       <c r="M140" s="2"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B141" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="C141" s="12" t="s">
         <v>245</v>
@@ -6215,14 +6242,17 @@
       <c r="H141" s="14">
         <v>0.29899999999999999</v>
       </c>
+      <c r="I141" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M141" s="2"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="C142" s="12" t="s">
         <v>245</v>
@@ -6242,6 +6272,9 @@
       <c r="H142" s="14">
         <v>0.436</v>
       </c>
+      <c r="I142" s="11">
+        <v>0.35</v>
+      </c>
       <c r="J142" s="11">
         <v>0.8</v>
       </c>
@@ -6249,10 +6282,10 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="C143" s="13" t="s">
         <v>245</v>
@@ -6279,10 +6312,10 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B144" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>245</v>
@@ -6309,10 +6342,10 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B145" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>245</v>
@@ -6339,10 +6372,10 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B146" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>245</v>
@@ -6361,6 +6394,9 @@
       </c>
       <c r="H146" s="14">
         <v>0.26500000000000001</v>
+      </c>
+      <c r="I146" s="11">
+        <v>0.23</v>
       </c>
       <c r="M146" s="2"/>
     </row>
@@ -6389,6 +6425,9 @@
       <c r="H147" s="14">
         <v>0.38500000000000001</v>
       </c>
+      <c r="I147" s="11">
+        <v>0.47</v>
+      </c>
       <c r="J147" s="11">
         <v>0.83</v>
       </c>
@@ -6396,10 +6435,10 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="C148" s="12" t="s">
         <v>245</v>
@@ -6419,6 +6458,9 @@
       <c r="H148" s="14">
         <v>0.188</v>
       </c>
+      <c r="I148" s="11">
+        <v>0.43</v>
+      </c>
       <c r="J148" s="11">
         <v>0.83</v>
       </c>
@@ -6426,10 +6468,10 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="C149" s="13" t="s">
         <v>245</v>
@@ -6449,6 +6491,9 @@
       <c r="H149" s="14">
         <v>0.36799999999999999</v>
       </c>
+      <c r="I149" s="11">
+        <v>0.52</v>
+      </c>
       <c r="J149" s="11">
         <v>0.83</v>
       </c>
@@ -6456,10 +6501,10 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B150" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="C150" s="12" t="s">
         <v>245</v>
@@ -6479,14 +6524,17 @@
       <c r="H150" s="14">
         <v>0.51300000000000001</v>
       </c>
+      <c r="I150" s="11">
+        <v>0.66</v>
+      </c>
       <c r="M150" s="2"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="C151" s="13" t="s">
         <v>245</v>
@@ -6506,14 +6554,17 @@
       <c r="H151" s="14">
         <v>0.46200000000000002</v>
       </c>
+      <c r="I151" s="11">
+        <v>0.48</v>
+      </c>
       <c r="M151" s="2"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="C152" s="12" t="s">
         <v>245</v>
@@ -6533,14 +6584,17 @@
       <c r="H152" s="14">
         <v>0.33300000000000002</v>
       </c>
+      <c r="I152" s="11">
+        <v>0.4</v>
+      </c>
       <c r="M152" s="2"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B153" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="C153" s="12" t="s">
         <v>245</v>
@@ -6560,14 +6614,17 @@
       <c r="H153" s="14">
         <v>0.40200000000000002</v>
       </c>
+      <c r="I153" s="11">
+        <v>0.41</v>
+      </c>
       <c r="M153" s="2"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B154" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="C154" s="12" t="s">
         <v>245</v>
@@ -6587,6 +6644,9 @@
       <c r="H154" s="14">
         <v>0.42699999999999999</v>
       </c>
+      <c r="I154" s="11">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="J154" s="11">
         <v>0.83</v>
       </c>
@@ -6594,10 +6654,10 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>465</v>
       </c>
       <c r="C155" s="13" t="s">
         <v>245</v>
@@ -6617,6 +6677,9 @@
       <c r="H155" s="14">
         <v>0.47899999999999998</v>
       </c>
+      <c r="I155" s="11">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="J155" s="11">
         <v>0.78</v>
       </c>
@@ -6624,10 +6687,10 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B156" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>308</v>
       </c>
       <c r="C156" s="12" t="s">
         <v>245</v>
@@ -6647,14 +6710,17 @@
       <c r="H156" s="14">
         <v>0.17100000000000001</v>
       </c>
+      <c r="I156" s="11">
+        <v>0.18</v>
+      </c>
       <c r="M156" s="2"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" t="s">
+        <v>476</v>
+      </c>
+      <c r="B157" s="7" t="s">
         <v>477</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>478</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>245</v>
@@ -6674,14 +6740,17 @@
       <c r="H157" s="14">
         <v>0.35899999999999999</v>
       </c>
+      <c r="I157" s="11">
+        <v>0.39</v>
+      </c>
       <c r="M157" s="8"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B158" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="C158" s="12" t="s">
         <v>245</v>
@@ -6700,6 +6769,9 @@
       </c>
       <c r="H158" s="14">
         <v>0.29099999999999998</v>
+      </c>
+      <c r="I158" s="11">
+        <v>0.37</v>
       </c>
       <c r="M158" s="2"/>
     </row>
@@ -6728,6 +6800,9 @@
       <c r="H159" s="14">
         <v>0.23899999999999999</v>
       </c>
+      <c r="I159" s="11">
+        <v>0.38</v>
+      </c>
       <c r="J159" s="11">
         <v>0.73</v>
       </c>
@@ -6735,10 +6810,10 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" t="s">
+        <v>465</v>
+      </c>
+      <c r="B160" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>467</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>245</v>
@@ -6758,14 +6833,17 @@
       <c r="H160" s="14">
         <v>0.29099999999999998</v>
       </c>
+      <c r="I160" s="11">
+        <v>0.66</v>
+      </c>
       <c r="M160" s="8"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B161" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="C161" s="12" t="s">
         <v>245</v>
@@ -6792,10 +6870,10 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" t="s">
+        <v>474</v>
+      </c>
+      <c r="B162" s="7" t="s">
         <v>475</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>476</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>245</v>
@@ -6814,6 +6892,9 @@
       </c>
       <c r="H162" s="14">
         <v>0.23899999999999999</v>
+      </c>
+      <c r="I162" s="11">
+        <v>0.46</v>
       </c>
       <c r="M162" s="8"/>
     </row>
@@ -6842,14 +6923,17 @@
       <c r="H163" s="14">
         <v>0.35</v>
       </c>
+      <c r="I163" s="11">
+        <v>0.49</v>
+      </c>
       <c r="M163" s="2"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B164" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="C164" s="12" t="s">
         <v>245</v>
@@ -6869,14 +6953,17 @@
       <c r="H164" s="14">
         <v>0.42699999999999999</v>
       </c>
+      <c r="I164" s="11">
+        <v>0.34</v>
+      </c>
       <c r="M164" s="2"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B165" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="C165" s="12" t="s">
         <v>245</v>
@@ -6896,6 +6983,9 @@
       <c r="H165" s="14">
         <v>0.57299999999999995</v>
       </c>
+      <c r="I165" s="11">
+        <v>0.6</v>
+      </c>
       <c r="J165" s="11">
         <v>0.83</v>
       </c>
@@ -6903,10 +6993,10 @@
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B166" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>294</v>
       </c>
       <c r="C166" s="12" t="s">
         <v>245</v>
@@ -6926,14 +7016,17 @@
       <c r="H166" s="14">
         <v>0.57299999999999995</v>
       </c>
+      <c r="I166" s="11">
+        <v>0.51</v>
+      </c>
       <c r="M166" s="2"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B167" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="C167" s="12" t="s">
         <v>245</v>
@@ -6953,14 +7046,17 @@
       <c r="H167" s="14">
         <v>0.56399999999999995</v>
       </c>
+      <c r="I167" s="11">
+        <v>0.71</v>
+      </c>
       <c r="M167" s="2"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B168" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>245</v>
@@ -6980,14 +7076,17 @@
       <c r="H168" s="14">
         <v>0.67500000000000004</v>
       </c>
+      <c r="I168" s="11">
+        <v>0.5</v>
+      </c>
       <c r="M168" s="2"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
+        <v>467</v>
+      </c>
+      <c r="B169" s="7" t="s">
         <v>468</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>469</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>245</v>
@@ -7007,6 +7106,9 @@
       <c r="H169" s="14">
         <v>0.63200000000000001</v>
       </c>
+      <c r="I169" s="11">
+        <v>0.59</v>
+      </c>
       <c r="J169" s="11">
         <v>0.78</v>
       </c>
@@ -7014,10 +7116,10 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" t="s">
+        <v>469</v>
+      </c>
+      <c r="B170" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>471</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>245</v>
@@ -7036,6 +7138,9 @@
       </c>
       <c r="H170" s="14">
         <v>0.20499999999999999</v>
+      </c>
+      <c r="I170" s="11">
+        <v>0.32</v>
       </c>
       <c r="J170" s="11">
         <v>0.78</v>
@@ -7067,14 +7172,17 @@
       <c r="H171" s="14">
         <v>0.53</v>
       </c>
+      <c r="I171" s="11">
+        <v>0.54</v>
+      </c>
       <c r="M171" s="2"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>245</v>
@@ -7093,6 +7201,9 @@
       </c>
       <c r="H172" s="14">
         <v>0.27400000000000002</v>
+      </c>
+      <c r="I172" s="11">
+        <v>0.57999999999999996</v>
       </c>
       <c r="J172" s="11">
         <v>0.73</v>
@@ -7124,14 +7235,17 @@
       <c r="H173" s="14">
         <v>0.44400000000000001</v>
       </c>
+      <c r="I173" s="11">
+        <v>0.34</v>
+      </c>
       <c r="M173" s="2"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B174" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="B174" s="4" t="s">
-        <v>286</v>
       </c>
       <c r="C174" s="12" t="s">
         <v>245</v>
@@ -7150,6 +7264,9 @@
       </c>
       <c r="H174" s="14">
         <v>0.376</v>
+      </c>
+      <c r="I174" s="11">
+        <v>0</v>
       </c>
       <c r="J174" s="11">
         <v>0.83</v>
@@ -7181,14 +7298,17 @@
       <c r="H175" s="14">
         <v>0.51300000000000001</v>
       </c>
+      <c r="I175" s="11">
+        <v>0.62</v>
+      </c>
       <c r="M175" s="2"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B176" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="C176" s="12" t="s">
         <v>245</v>
@@ -7208,14 +7328,17 @@
       <c r="H176" s="14">
         <v>0.436</v>
       </c>
+      <c r="I176" s="11">
+        <v>0.41</v>
+      </c>
       <c r="M176" s="2"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B177" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>296</v>
       </c>
       <c r="C177" s="12" t="s">
         <v>245</v>
@@ -7235,11 +7358,14 @@
       <c r="H177" s="14">
         <v>0.47899999999999998</v>
       </c>
+      <c r="I177" s="11">
+        <v>0.31</v>
+      </c>
       <c r="M177" s="2"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>250</v>
@@ -7262,14 +7388,17 @@
       <c r="H178" s="14">
         <v>0.36799999999999999</v>
       </c>
+      <c r="I178" s="11">
+        <v>0.5</v>
+      </c>
       <c r="M178" s="2"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B179" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="C179" s="12" t="s">
         <v>245</v>
@@ -7319,6 +7448,9 @@
       <c r="H180" s="14">
         <v>0.23100000000000001</v>
       </c>
+      <c r="I180" s="11">
+        <v>0.42</v>
+      </c>
       <c r="J180" s="11">
         <v>0.73</v>
       </c>
@@ -7326,10 +7458,10 @@
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B181" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="C181" s="12" t="s">
         <v>245</v>
@@ -7349,14 +7481,17 @@
       <c r="H181" s="14">
         <v>0.188</v>
       </c>
+      <c r="I181" s="11">
+        <v>0.25</v>
+      </c>
       <c r="M181" s="2"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" t="s">
+        <v>472</v>
+      </c>
+      <c r="B182" s="7" t="s">
         <v>473</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>474</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>245</v>
@@ -7375,6 +7510,9 @@
       </c>
       <c r="H182" s="14">
         <v>0</v>
+      </c>
+      <c r="I182" s="11">
+        <v>0.54</v>
       </c>
       <c r="M182" s="8"/>
     </row>
@@ -7403,14 +7541,17 @@
       <c r="H183" s="14">
         <v>0.36799999999999999</v>
       </c>
+      <c r="I183" s="11">
+        <v>0.45</v>
+      </c>
       <c r="M183" s="2"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B184" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="C184" s="12" t="s">
         <v>245</v>
@@ -7430,14 +7571,17 @@
       <c r="H184" s="14">
         <v>0.17899999999999999</v>
       </c>
+      <c r="I184" s="11">
+        <v>0.36</v>
+      </c>
       <c r="M184" s="2"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>292</v>
       </c>
       <c r="C185" s="12" t="s">
         <v>245</v>
@@ -7457,14 +7601,17 @@
       <c r="H185" s="14">
         <v>0.63200000000000001</v>
       </c>
+      <c r="I185" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M185" s="2"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B186" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="B186" s="4" t="s">
-        <v>278</v>
       </c>
       <c r="C186" s="12" t="s">
         <v>245</v>
@@ -7483,6 +7630,9 @@
       </c>
       <c r="H186" s="14">
         <v>0.70899999999999996</v>
+      </c>
+      <c r="I186" s="11">
+        <v>0.59</v>
       </c>
       <c r="M186" s="2"/>
     </row>
@@ -7511,6 +7661,9 @@
       <c r="H187" s="14">
         <v>0.45300000000000001</v>
       </c>
+      <c r="I187" s="11">
+        <v>0.36</v>
+      </c>
       <c r="J187" s="11">
         <v>0.8</v>
       </c>
@@ -7518,10 +7671,10 @@
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B188" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="B188" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="C188" s="12" t="s">
         <v>245</v>
@@ -7541,14 +7694,17 @@
       <c r="H188" s="14">
         <v>0.38500000000000001</v>
       </c>
+      <c r="I188" s="11">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="M188" s="2"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B189" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="B189" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="C189" s="12" t="s">
         <v>245</v>
@@ -7568,6 +7724,9 @@
       <c r="H189" s="14">
         <v>0.47</v>
       </c>
+      <c r="I189" s="11">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J189" s="11">
         <v>0.83</v>
       </c>
@@ -7575,10 +7734,10 @@
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B190" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B190" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="C190" s="12" t="s">
         <v>245</v>
@@ -7598,14 +7757,17 @@
       <c r="H190" s="14">
         <v>0.34200000000000003</v>
       </c>
+      <c r="I190" s="11">
+        <v>0.54</v>
+      </c>
       <c r="M190" s="2"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B191" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="B191" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>245</v>
@@ -7625,14 +7787,17 @@
       <c r="H191" s="14">
         <v>0.436</v>
       </c>
+      <c r="I191" s="11">
+        <v>0.38</v>
+      </c>
       <c r="M191" s="2"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B192" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="C192" s="12" t="s">
         <v>245</v>
@@ -7652,17 +7817,20 @@
       <c r="H192" s="14">
         <v>0.35899999999999999</v>
       </c>
+      <c r="I192" s="11">
+        <v>0.19</v>
+      </c>
       <c r="M192" s="2"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B193" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="B193" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="C193" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D193" s="12">
         <v>0.77</v>
@@ -7689,13 +7857,13 @@
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B194" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="B194" s="4" t="s">
-        <v>391</v>
-      </c>
       <c r="C194" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D194" s="12">
         <v>0.8</v>
@@ -7722,13 +7890,13 @@
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B195" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B195" s="4" t="s">
-        <v>429</v>
-      </c>
       <c r="C195" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D195" s="12">
         <v>0.74</v>
@@ -7755,13 +7923,13 @@
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B196" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="B196" s="4" t="s">
-        <v>365</v>
-      </c>
       <c r="C196" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D196" s="12">
         <v>0.82</v>
@@ -7788,13 +7956,13 @@
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B197" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="B197" s="4" t="s">
-        <v>351</v>
-      </c>
       <c r="C197" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D197" s="12">
         <v>0.85</v>
@@ -7821,13 +7989,13 @@
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="B198" s="4" t="s">
-        <v>373</v>
-      </c>
       <c r="C198" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D198" s="12">
         <v>0.98</v>
@@ -7851,13 +8019,13 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B199" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B199" s="4" t="s">
-        <v>433</v>
-      </c>
       <c r="C199" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D199" s="12">
         <v>0.93</v>
@@ -7881,13 +8049,13 @@
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B200" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="B200" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="C200" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D200" s="12">
         <v>0.67</v>
@@ -7914,13 +8082,13 @@
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B201" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="B201" s="4" t="s">
-        <v>417</v>
-      </c>
       <c r="C201" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D201" s="12">
         <v>0.96</v>
@@ -7944,13 +8112,13 @@
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B202" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B202" s="4" t="s">
-        <v>411</v>
-      </c>
       <c r="C202" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D202" s="12">
         <v>0.92</v>
@@ -7974,13 +8142,13 @@
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B203" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="B203" s="4" t="s">
-        <v>377</v>
-      </c>
       <c r="C203" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D203" s="12">
         <v>0.84</v>
@@ -8004,13 +8172,13 @@
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B204" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="B204" s="4" t="s">
-        <v>393</v>
-      </c>
       <c r="C204" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D204" s="12">
         <v>0.63</v>
@@ -8034,13 +8202,13 @@
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B205" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B205" s="4" t="s">
-        <v>399</v>
-      </c>
       <c r="C205" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D205" s="12">
         <v>0.82</v>
@@ -8067,13 +8235,13 @@
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B206" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B206" s="4" t="s">
-        <v>395</v>
-      </c>
       <c r="C206" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D206" s="12">
         <v>0.93</v>
@@ -8097,13 +8265,13 @@
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B207" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="B207" s="4" t="s">
-        <v>413</v>
-      </c>
       <c r="C207" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D207" s="12">
         <v>0.75</v>
@@ -8127,13 +8295,13 @@
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B208" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="B208" s="4" t="s">
-        <v>361</v>
-      </c>
       <c r="C208" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D208" s="12">
         <v>0.96</v>
@@ -8160,13 +8328,13 @@
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B209" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B209" s="4" t="s">
-        <v>425</v>
-      </c>
       <c r="C209" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D209" s="12">
         <v>0.92</v>
@@ -8190,13 +8358,13 @@
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B210" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="B210" s="4" t="s">
-        <v>367</v>
-      </c>
       <c r="C210" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D210" s="12">
         <v>0.81</v>
@@ -8220,13 +8388,13 @@
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B211" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B211" s="4" t="s">
-        <v>379</v>
-      </c>
       <c r="C211" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D211" s="12">
         <v>0.9</v>
@@ -8250,13 +8418,13 @@
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B212" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="B212" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="C212" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D212" s="12">
         <v>0.96</v>
@@ -8280,13 +8448,13 @@
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B213" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="C213" s="12" t="s">
         <v>342</v>
-      </c>
-      <c r="C213" s="12" t="s">
-        <v>343</v>
       </c>
       <c r="D213" s="12">
         <v>0.76</v>
@@ -8313,13 +8481,13 @@
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="B214" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="C214" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D214" s="12">
         <v>0.93</v>
@@ -8343,13 +8511,13 @@
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="B215" s="4" t="s">
-        <v>371</v>
-      </c>
       <c r="C215" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D215" s="12">
         <v>0.79</v>
@@ -8376,13 +8544,13 @@
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B216" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="B216" s="4" t="s">
-        <v>445</v>
-      </c>
       <c r="C216" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D216" s="12">
         <v>0.81</v>
@@ -8406,13 +8574,13 @@
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="B217" s="4" t="s">
-        <v>369</v>
-      </c>
       <c r="C217" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D217" s="12">
         <v>0.85</v>
@@ -8436,13 +8604,13 @@
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B218" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B218" s="4" t="s">
-        <v>409</v>
-      </c>
       <c r="C218" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D218" s="12">
         <v>0.96</v>
@@ -8466,13 +8634,13 @@
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B219" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="B219" s="4" t="s">
-        <v>345</v>
-      </c>
       <c r="C219" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D219" s="12">
         <v>0.81</v>
@@ -8499,13 +8667,13 @@
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B220" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="B220" s="4" t="s">
-        <v>397</v>
-      </c>
       <c r="C220" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D220" s="12">
         <v>0.96</v>
@@ -8529,13 +8697,13 @@
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B221" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="B221" s="4" t="s">
-        <v>375</v>
-      </c>
       <c r="C221" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D221" s="12">
         <v>0.85</v>
@@ -8559,13 +8727,13 @@
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B222" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="B222" s="4" t="s">
-        <v>387</v>
-      </c>
       <c r="C222" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D222" s="12">
         <v>0.77</v>
@@ -8589,13 +8757,13 @@
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B223" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B223" s="4" t="s">
-        <v>407</v>
-      </c>
       <c r="C223" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D223" s="12">
         <v>0.93</v>
@@ -8619,13 +8787,13 @@
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B224" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B224" s="4" t="s">
-        <v>419</v>
-      </c>
       <c r="C224" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D224" s="12">
         <v>1</v>
@@ -8652,13 +8820,13 @@
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="B225" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B225" s="4" t="s">
-        <v>431</v>
-      </c>
       <c r="C225" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D225" s="12">
         <v>0.91</v>
@@ -8682,13 +8850,13 @@
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B226" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="B226" s="4" t="s">
-        <v>357</v>
-      </c>
       <c r="C226" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D226" s="12">
         <v>0.55000000000000004</v>
@@ -8712,13 +8880,13 @@
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B227" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="B227" s="4" t="s">
-        <v>415</v>
-      </c>
       <c r="C227" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D227" s="12">
         <v>0.89</v>
@@ -8742,13 +8910,13 @@
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B228" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="B228" s="4" t="s">
-        <v>437</v>
-      </c>
       <c r="C228" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D228" s="12">
         <v>0.98</v>
@@ -8775,13 +8943,13 @@
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="B229" s="3" t="s">
-        <v>447</v>
-      </c>
       <c r="C229" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D229" s="13">
         <v>0</v>
@@ -8808,13 +8976,13 @@
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B230" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="B230" s="4" t="s">
-        <v>385</v>
-      </c>
       <c r="C230" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D230" s="12">
         <v>0.98</v>
@@ -8838,13 +9006,13 @@
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B231" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="B231" s="4" t="s">
-        <v>401</v>
-      </c>
       <c r="C231" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D231" s="12">
         <v>0.96</v>
@@ -8868,13 +9036,13 @@
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B232" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="B232" s="4" t="s">
-        <v>381</v>
-      </c>
       <c r="C232" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D232" s="12">
         <v>0.96</v>
@@ -8898,13 +9066,13 @@
     </row>
     <row r="233" spans="1:13">
       <c r="A233" t="s">
+        <v>488</v>
+      </c>
+      <c r="B233" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="B233" s="7" t="s">
-        <v>490</v>
-      </c>
       <c r="C233" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D233" s="14">
         <v>0.91</v>
@@ -8927,13 +9095,13 @@
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B234" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B234" s="4" t="s">
-        <v>423</v>
-      </c>
       <c r="C234" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D234" s="12">
         <v>0.42</v>
@@ -8960,13 +9128,13 @@
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="B235" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B235" s="4" t="s">
-        <v>439</v>
-      </c>
       <c r="C235" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D235" s="12">
         <v>0.88</v>
@@ -8990,13 +9158,13 @@
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B236" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="B236" s="4" t="s">
-        <v>443</v>
-      </c>
       <c r="C236" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D236" s="12">
         <v>0.78</v>
@@ -9023,13 +9191,13 @@
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B237" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="B237" s="4" t="s">
-        <v>363</v>
-      </c>
       <c r="C237" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D237" s="12">
         <v>0.96</v>
@@ -9053,13 +9221,13 @@
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B238" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B238" s="4" t="s">
-        <v>353</v>
-      </c>
       <c r="C238" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D238" s="12">
         <v>0.68</v>
@@ -9086,13 +9254,13 @@
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B239" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="B239" s="4" t="s">
-        <v>389</v>
-      </c>
       <c r="C239" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D239" s="12">
         <v>0.76</v>
@@ -9116,13 +9284,13 @@
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B240" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="B240" s="4" t="s">
-        <v>427</v>
-      </c>
       <c r="C240" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D240" s="12">
         <v>0.41</v>
@@ -9146,13 +9314,13 @@
     </row>
     <row r="241" spans="1:13">
       <c r="A241" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B241" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B241" s="4" t="s">
-        <v>347</v>
-      </c>
       <c r="C241" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D241" s="12">
         <v>0.8</v>
@@ -9176,13 +9344,13 @@
     </row>
     <row r="242" spans="1:13">
       <c r="A242" t="s">
+        <v>490</v>
+      </c>
+      <c r="B242" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B242" s="7" t="s">
-        <v>492</v>
-      </c>
       <c r="C242" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D242" s="14">
         <v>0</v>
@@ -9205,13 +9373,13 @@
     </row>
     <row r="243" spans="1:13">
       <c r="A243" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B243" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="B243" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="C243" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D243" s="12">
         <v>0.91</v>
@@ -9235,13 +9403,13 @@
     </row>
     <row r="244" spans="1:13">
       <c r="A244" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B244" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="B244" s="4" t="s">
-        <v>359</v>
-      </c>
       <c r="C244" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D244" s="12">
         <v>0.95</v>
@@ -9268,13 +9436,13 @@
     </row>
     <row r="245" spans="1:13">
       <c r="A245" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B245" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B245" s="4" t="s">
-        <v>383</v>
-      </c>
       <c r="C245" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D245" s="12">
         <v>0.97</v>
@@ -9301,13 +9469,13 @@
     </row>
     <row r="246" spans="1:13">
       <c r="A246" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D246" s="14">
         <v>0</v>
@@ -9330,13 +9498,13 @@
     </row>
     <row r="247" spans="1:13">
       <c r="A247" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B247" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B247" s="4" t="s">
-        <v>355</v>
-      </c>
       <c r="C247" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D247" s="12">
         <v>0.97</v>
@@ -9360,13 +9528,13 @@
     </row>
     <row r="248" spans="1:13">
       <c r="A248" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B248" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B248" s="4" t="s">
-        <v>441</v>
-      </c>
       <c r="C248" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D248" s="12">
         <v>0.88</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA02E64-E486-A04B-8118-DF8247FAD32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BABAED-70BF-D44F-AED8-C897FAA55D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2173,6 +2173,9 @@
       <c r="H2" s="15">
         <v>0.27350427350427353</v>
       </c>
+      <c r="I2" s="11">
+        <v>0.34</v>
+      </c>
       <c r="J2" s="11">
         <v>0.72</v>
       </c>
@@ -2203,6 +2206,9 @@
       <c r="H3" s="15">
         <v>0.30769230769230771</v>
       </c>
+      <c r="I3" s="11">
+        <v>0.43</v>
+      </c>
       <c r="J3" s="11">
         <v>0.72</v>
       </c>
@@ -2233,6 +2239,9 @@
       <c r="H4" s="14">
         <v>0.47863247863247865</v>
       </c>
+      <c r="I4" s="11">
+        <v>0.36</v>
+      </c>
       <c r="J4" s="11">
         <v>0.65</v>
       </c>
@@ -2263,6 +2272,9 @@
       <c r="H5" s="15">
         <v>0.5213675213675214</v>
       </c>
+      <c r="I5" s="11">
+        <v>0.67</v>
+      </c>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -2290,6 +2302,9 @@
       <c r="H6" s="15">
         <v>0.42735042735042733</v>
       </c>
+      <c r="I6" s="11">
+        <v>0.25</v>
+      </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
@@ -2317,6 +2332,9 @@
       <c r="H7" s="14">
         <v>0.20512820512820512</v>
       </c>
+      <c r="I7" s="11">
+        <v>0.51</v>
+      </c>
       <c r="J7" s="11">
         <v>0.65</v>
       </c>
@@ -2347,6 +2365,9 @@
       <c r="H8" s="15">
         <v>0.41025641025641024</v>
       </c>
+      <c r="I8" s="11">
+        <v>0.38</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
@@ -2374,6 +2395,9 @@
       <c r="H9" s="15">
         <v>0.54700854700854706</v>
       </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
@@ -2401,6 +2425,9 @@
       <c r="H10" s="15">
         <v>0.29914529914529914</v>
       </c>
+      <c r="I10" s="11">
+        <v>0.09</v>
+      </c>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
@@ -2428,6 +2455,9 @@
       <c r="H11" s="15">
         <v>0.35897435897435898</v>
       </c>
+      <c r="I11" s="11">
+        <v>0.33</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13">
@@ -2455,6 +2485,9 @@
       <c r="H12" s="15">
         <v>0.49572649572649574</v>
       </c>
+      <c r="I12" s="11">
+        <v>0.4</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
@@ -2482,6 +2515,9 @@
       <c r="H13" s="15">
         <v>0.6495726495726496</v>
       </c>
+      <c r="I13" s="11">
+        <v>0.23</v>
+      </c>
       <c r="J13" s="11">
         <v>0.65</v>
       </c>
@@ -2512,6 +2548,9 @@
       <c r="H14" s="15">
         <v>0.3504273504273504</v>
       </c>
+      <c r="I14" s="11">
+        <v>0.32</v>
+      </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
@@ -2539,6 +2578,9 @@
       <c r="H15" s="15">
         <v>0.50427350427350426</v>
       </c>
+      <c r="I15" s="11">
+        <v>0.42</v>
+      </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
@@ -2566,6 +2608,9 @@
       <c r="H16" s="15">
         <v>0.51282051282051277</v>
       </c>
+      <c r="I16" s="11">
+        <v>0.42</v>
+      </c>
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13">
@@ -2593,6 +2638,9 @@
       <c r="H17" s="15">
         <v>0.5213675213675214</v>
       </c>
+      <c r="I17" s="11">
+        <v>0.41</v>
+      </c>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13">
@@ -2620,6 +2668,9 @@
       <c r="H18" s="14">
         <v>0.51282051282051277</v>
       </c>
+      <c r="I18" s="11">
+        <v>0.52</v>
+      </c>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13">
@@ -2647,6 +2698,9 @@
       <c r="H19" s="15">
         <v>0.54700854700854706</v>
       </c>
+      <c r="I19" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
@@ -2674,6 +2728,9 @@
       <c r="H20" s="14">
         <v>0.47008547008547008</v>
       </c>
+      <c r="I20" s="11">
+        <v>0.46</v>
+      </c>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
@@ -2701,6 +2758,9 @@
       <c r="H21" s="15">
         <v>0.48717948717948717</v>
       </c>
+      <c r="I21" s="11">
+        <v>0</v>
+      </c>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13">
@@ -2728,6 +2788,9 @@
       <c r="H22" s="15">
         <v>0.75213675213675213</v>
       </c>
+      <c r="I22" s="11">
+        <v>0.71</v>
+      </c>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13">
@@ -2755,6 +2818,9 @@
       <c r="H23" s="14">
         <v>0.40170940170940173</v>
       </c>
+      <c r="I23" s="11">
+        <v>0.36</v>
+      </c>
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
@@ -2782,6 +2848,9 @@
       <c r="H24" s="14">
         <v>0.5641025641025641</v>
       </c>
+      <c r="I24" s="11">
+        <v>0.45</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
@@ -2809,6 +2878,9 @@
       <c r="H25" s="15">
         <v>0.45299145299145299</v>
       </c>
+      <c r="I25" s="11">
+        <v>0.43</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13">
@@ -2836,6 +2908,9 @@
       <c r="H26" s="15">
         <v>0.29059829059829062</v>
       </c>
+      <c r="I26" s="11">
+        <v>0.37</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
@@ -2863,6 +2938,9 @@
       <c r="H27" s="15">
         <v>0.53846153846153844</v>
       </c>
+      <c r="I27" s="11">
+        <v>0.51</v>
+      </c>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13">
@@ -2890,6 +2968,9 @@
       <c r="H28" s="14">
         <v>0.61538461538461542</v>
       </c>
+      <c r="I28" s="11">
+        <v>0.61</v>
+      </c>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13">
@@ -2917,6 +2998,9 @@
       <c r="H29" s="15">
         <v>0.38461538461538464</v>
       </c>
+      <c r="I29" s="11">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -2944,6 +3028,9 @@
       <c r="H30" s="15">
         <v>0.33333333333333331</v>
       </c>
+      <c r="I30" s="11">
+        <v>0.33</v>
+      </c>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13">
@@ -2971,6 +3058,9 @@
       <c r="H31" s="14">
         <v>0.57264957264957261</v>
       </c>
+      <c r="I31" s="11">
+        <v>0.62</v>
+      </c>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13">
@@ -2998,6 +3088,9 @@
       <c r="H32" s="15">
         <v>0.45299145299145299</v>
       </c>
+      <c r="I32" s="11">
+        <v>0.42</v>
+      </c>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13">
@@ -3025,6 +3118,9 @@
       <c r="H33" s="15">
         <v>0.50427350427350426</v>
       </c>
+      <c r="I33" s="11">
+        <v>0</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
@@ -3052,6 +3148,9 @@
       <c r="H34" s="14">
         <v>0.45299145299145299</v>
       </c>
+      <c r="I34" s="11">
+        <v>0.36</v>
+      </c>
       <c r="J34" s="11">
         <v>0.78</v>
       </c>
@@ -3082,6 +3181,9 @@
       <c r="H35" s="15">
         <v>0</v>
       </c>
+      <c r="I35" s="11">
+        <v>0.36</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -3109,6 +3211,9 @@
       <c r="H36" s="15">
         <v>0.4358974358974359</v>
       </c>
+      <c r="I36" s="11">
+        <v>0.38</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
@@ -3136,6 +3241,9 @@
       <c r="H37" s="14">
         <v>0.34188034188034189</v>
       </c>
+      <c r="I37" s="11">
+        <v>0.4</v>
+      </c>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13">
@@ -3163,6 +3271,9 @@
       <c r="H38" s="15">
         <v>0.24786324786324787</v>
       </c>
+      <c r="I38" s="11">
+        <v>0.15</v>
+      </c>
       <c r="J38" s="11">
         <v>0.7</v>
       </c>
@@ -3193,6 +3304,9 @@
       <c r="H39" s="14">
         <v>0.63247863247863245</v>
       </c>
+      <c r="I39" s="11">
+        <v>0.34</v>
+      </c>
       <c r="J39" s="11">
         <v>0.65</v>
       </c>
@@ -3223,6 +3337,9 @@
       <c r="H40" s="15">
         <v>0.41880341880341881</v>
       </c>
+      <c r="I40" s="11">
+        <v>0.24</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
@@ -3250,6 +3367,9 @@
       <c r="H41" s="15">
         <v>0.50427350427350426</v>
       </c>
+      <c r="I41" s="11">
+        <v>0</v>
+      </c>
       <c r="J41" s="11">
         <v>0.7</v>
       </c>
@@ -3280,6 +3400,9 @@
       <c r="H42" s="15">
         <v>0.30769230769230771</v>
       </c>
+      <c r="I42" s="11">
+        <v>0.54</v>
+      </c>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13">
@@ -3307,6 +3430,9 @@
       <c r="H43" s="15">
         <v>0.67521367521367526</v>
       </c>
+      <c r="I43" s="11">
+        <v>0</v>
+      </c>
       <c r="J43" s="11">
         <v>0.84</v>
       </c>
@@ -3337,6 +3463,9 @@
       <c r="H44" s="14">
         <v>0.47863247863247865</v>
       </c>
+      <c r="I44" s="11">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J44" s="11">
         <v>0.65</v>
       </c>
@@ -3367,6 +3496,9 @@
       <c r="H45" s="15">
         <v>0.21367521367521367</v>
       </c>
+      <c r="I45" s="11">
+        <v>0.25</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -3394,6 +3526,9 @@
       <c r="H46" s="15">
         <v>0.54700854700854706</v>
       </c>
+      <c r="I46" s="11">
+        <v>0</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -3421,6 +3556,9 @@
       <c r="H47" s="15">
         <v>0.77777777777777779</v>
       </c>
+      <c r="I47" s="11">
+        <v>0</v>
+      </c>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:13">
@@ -3448,6 +3586,9 @@
       <c r="H48" s="15">
         <v>0.40170940170940173</v>
       </c>
+      <c r="I48" s="11">
+        <v>0.2</v>
+      </c>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13">
@@ -3475,6 +3616,9 @@
       <c r="H49" s="15">
         <v>0.29059829059829062</v>
       </c>
+      <c r="I49" s="11">
+        <v>0.39</v>
+      </c>
       <c r="M49" s="2"/>
     </row>
     <row r="50" spans="1:13">
@@ -3502,6 +3646,9 @@
       <c r="H50" s="14">
         <v>0.40170940170940173</v>
       </c>
+      <c r="I50" s="11">
+        <v>0.46</v>
+      </c>
       <c r="J50" s="11">
         <v>0.84</v>
       </c>
@@ -3532,6 +3679,9 @@
       <c r="H51" s="14">
         <v>0.44444444444444442</v>
       </c>
+      <c r="I51" s="11">
+        <v>0.51</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13">
@@ -3559,6 +3709,9 @@
       <c r="H52" s="14">
         <v>0.44444444444444442</v>
       </c>
+      <c r="I52" s="11">
+        <v>0</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13">
@@ -3586,6 +3739,9 @@
       <c r="H53" s="15">
         <v>0.31623931623931623</v>
       </c>
+      <c r="I53" s="11">
+        <v>0.46</v>
+      </c>
       <c r="M53" s="2"/>
     </row>
     <row r="54" spans="1:13">
@@ -3613,6 +3769,9 @@
       <c r="H54" s="15">
         <v>0.35897435897435898</v>
       </c>
+      <c r="I54" s="11">
+        <v>0.39</v>
+      </c>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
@@ -3640,6 +3799,9 @@
       <c r="H55" s="15">
         <v>0.31623931623931623</v>
       </c>
+      <c r="I55" s="11">
+        <v>0.46</v>
+      </c>
       <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13">
@@ -3667,6 +3829,9 @@
       <c r="H56" s="14">
         <v>0.58119658119658124</v>
       </c>
+      <c r="I56" s="11">
+        <v>0</v>
+      </c>
       <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13">
@@ -3694,6 +3859,9 @@
       <c r="H57" s="15">
         <v>0.52991452991452992</v>
       </c>
+      <c r="I57" s="11">
+        <v>0.34</v>
+      </c>
       <c r="J57" s="11">
         <v>0.72</v>
       </c>
@@ -3724,6 +3892,9 @@
       <c r="H58" s="14">
         <v>0.1623931623931624</v>
       </c>
+      <c r="I58" s="11">
+        <v>0.03</v>
+      </c>
       <c r="J58" s="11">
         <v>0.84</v>
       </c>
@@ -3754,6 +3925,9 @@
       <c r="H59" s="15">
         <v>0.39316239316239315</v>
       </c>
+      <c r="I59" s="11">
+        <v>0.51</v>
+      </c>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:13">
@@ -3781,6 +3955,9 @@
       <c r="H60" s="14">
         <v>0.42735042735042733</v>
       </c>
+      <c r="I60" s="11">
+        <v>0.52</v>
+      </c>
       <c r="J60" s="11">
         <v>0.78</v>
       </c>
@@ -3811,6 +3988,9 @@
       <c r="H61" s="15">
         <v>0.35897435897435898</v>
       </c>
+      <c r="I61" s="11">
+        <v>0.38</v>
+      </c>
       <c r="J61" s="11">
         <v>0.7</v>
       </c>
@@ -3841,6 +4021,9 @@
       <c r="H62" s="15">
         <v>0.63247863247863245</v>
       </c>
+      <c r="I62" s="11">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
@@ -3868,6 +4051,9 @@
       <c r="H63" s="15">
         <v>0.66666666666666663</v>
       </c>
+      <c r="I63" s="11">
+        <v>0</v>
+      </c>
       <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13">
@@ -3895,6 +4081,9 @@
       <c r="H64" s="14">
         <v>0.22222222222222221</v>
       </c>
+      <c r="I64" s="11">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M64" s="2"/>
     </row>
     <row r="65" spans="1:13">
@@ -3922,6 +4111,9 @@
       <c r="H65" s="15">
         <v>0.31623931623931623</v>
       </c>
+      <c r="I65" s="11">
+        <v>0</v>
+      </c>
       <c r="M65" s="2"/>
     </row>
     <row r="66" spans="1:13">
@@ -3949,6 +4141,9 @@
       <c r="H66" s="14">
         <v>0.51282051282051277</v>
       </c>
+      <c r="I66" s="11">
+        <v>0.47</v>
+      </c>
       <c r="M66" s="2"/>
     </row>
     <row r="67" spans="1:13">
@@ -3976,6 +4171,9 @@
       <c r="H67" s="14">
         <v>0.58974358974358976</v>
       </c>
+      <c r="I67" s="11">
+        <v>0.26</v>
+      </c>
       <c r="J67" s="11">
         <v>0.78</v>
       </c>
@@ -4006,6 +4204,9 @@
       <c r="H68" s="14">
         <v>0.52991452991452992</v>
       </c>
+      <c r="I68" s="11">
+        <v>0.39</v>
+      </c>
       <c r="M68" s="2"/>
     </row>
     <row r="69" spans="1:13">
@@ -4033,6 +4234,9 @@
       <c r="H69" s="15">
         <v>0.29914529914529914</v>
       </c>
+      <c r="I69" s="11">
+        <v>0.38</v>
+      </c>
       <c r="J69" s="11">
         <v>0.72</v>
       </c>
@@ -4063,6 +4267,9 @@
       <c r="H70" s="15">
         <v>0.48717948717948717</v>
       </c>
+      <c r="I70" s="11">
+        <v>0.47</v>
+      </c>
       <c r="J70" s="11">
         <v>0.72</v>
       </c>
@@ -4093,6 +4300,9 @@
       <c r="H71" s="15">
         <v>0.45299145299145299</v>
       </c>
+      <c r="I71" s="11">
+        <v>0.39</v>
+      </c>
       <c r="J71" s="11">
         <v>0.78</v>
       </c>
@@ -4123,6 +4333,9 @@
       <c r="H72" s="15">
         <v>0.28205128205128205</v>
       </c>
+      <c r="I72" s="11">
+        <v>0.36</v>
+      </c>
       <c r="J72" s="11">
         <v>0.73</v>
       </c>
@@ -4153,6 +4366,9 @@
       <c r="H73" s="14">
         <v>0.41025641025641024</v>
       </c>
+      <c r="I73" s="11">
+        <v>0.38</v>
+      </c>
       <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:13">
@@ -4180,6 +4396,9 @@
       <c r="H74" s="14">
         <v>0.28205128205128205</v>
       </c>
+      <c r="I74" s="11">
+        <v>0.13</v>
+      </c>
       <c r="J74" s="11">
         <v>0.7</v>
       </c>
@@ -4210,6 +4429,9 @@
       <c r="H75" s="14">
         <v>0.58119658119658124</v>
       </c>
+      <c r="I75" s="11">
+        <v>0.47</v>
+      </c>
       <c r="J75" s="11">
         <v>0.78</v>
       </c>
@@ -4239,6 +4461,9 @@
       </c>
       <c r="H76" s="15">
         <v>0.55555555555555558</v>
+      </c>
+      <c r="I76" s="11">
+        <v>0.55000000000000004</v>
       </c>
       <c r="M76" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BABAED-70BF-D44F-AED8-C897FAA55D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB47A1BD-112B-5148-A322-0827433E4342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6380,6 +6380,9 @@
       <c r="I138" s="11">
         <v>0.65</v>
       </c>
+      <c r="J138" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M138" s="2"/>
     </row>
     <row r="139" spans="1:13">
@@ -6469,6 +6472,9 @@
       </c>
       <c r="I141" s="11">
         <v>0.53</v>
+      </c>
+      <c r="J141" s="11">
+        <v>0.7</v>
       </c>
       <c r="M141" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB47A1BD-112B-5148-A322-0827433E4342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FF55A8-2243-F042-A409-8E0230C45804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2237,7 +2237,7 @@
         <v>0.75</v>
       </c>
       <c r="H4" s="14">
-        <v>0.47863247863247865</v>
+        <v>0.49</v>
       </c>
       <c r="I4" s="11">
         <v>0.36</v>
@@ -2275,6 +2275,9 @@
       <c r="I5" s="11">
         <v>0.67</v>
       </c>
+      <c r="J5" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -2300,10 +2303,13 @@
         <v>0.68</v>
       </c>
       <c r="H6" s="15">
-        <v>0.42735042735042733</v>
+        <v>0.49</v>
       </c>
       <c r="I6" s="11">
         <v>0.25</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0.79</v>
       </c>
       <c r="M6" s="2"/>
     </row>
@@ -2333,7 +2339,7 @@
         <v>0.20512820512820512</v>
       </c>
       <c r="I7" s="11">
-        <v>0.51</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="J7" s="11">
         <v>0.65</v>
@@ -2363,10 +2369,13 @@
         <v>0.6</v>
       </c>
       <c r="H8" s="15">
-        <v>0.41025641025641024</v>
+        <v>0.45</v>
       </c>
       <c r="I8" s="11">
         <v>0.38</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.79</v>
       </c>
       <c r="M8" s="2"/>
     </row>
@@ -2398,6 +2407,9 @@
       <c r="I9" s="11">
         <v>0</v>
       </c>
+      <c r="J9" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
@@ -2428,6 +2440,9 @@
       <c r="I10" s="11">
         <v>0.09</v>
       </c>
+      <c r="J10" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
@@ -2458,6 +2473,9 @@
       <c r="I11" s="11">
         <v>0.33</v>
       </c>
+      <c r="J11" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13">
@@ -2488,6 +2506,9 @@
       <c r="I12" s="11">
         <v>0.4</v>
       </c>
+      <c r="J12" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
@@ -2513,7 +2534,7 @@
         <v>0.9</v>
       </c>
       <c r="H13" s="15">
-        <v>0.6495726495726496</v>
+        <v>0.7</v>
       </c>
       <c r="I13" s="11">
         <v>0.23</v>
@@ -2641,6 +2662,9 @@
       <c r="I17" s="11">
         <v>0.41</v>
       </c>
+      <c r="J17" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13">
@@ -2756,7 +2780,7 @@
         <v>0.66</v>
       </c>
       <c r="H21" s="15">
-        <v>0.48717948717948717</v>
+        <v>0.52</v>
       </c>
       <c r="I21" s="11">
         <v>0</v>
@@ -2789,7 +2813,7 @@
         <v>0.75213675213675213</v>
       </c>
       <c r="I22" s="11">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="M22" s="2"/>
     </row>
@@ -2876,7 +2900,7 @@
         <v>0.61</v>
       </c>
       <c r="H25" s="15">
-        <v>0.45299145299145299</v>
+        <v>0.49</v>
       </c>
       <c r="I25" s="11">
         <v>0.43</v>
@@ -2941,6 +2965,9 @@
       <c r="I27" s="11">
         <v>0.51</v>
       </c>
+      <c r="J27" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13">
@@ -3031,6 +3058,9 @@
       <c r="I30" s="11">
         <v>0.33</v>
       </c>
+      <c r="J30" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13">
@@ -3302,7 +3332,7 @@
         <v>0.75</v>
       </c>
       <c r="H39" s="14">
-        <v>0.63247863247863245</v>
+        <v>0.65</v>
       </c>
       <c r="I39" s="11">
         <v>0.34</v>
@@ -3335,7 +3365,7 @@
         <v>0.48</v>
       </c>
       <c r="H40" s="15">
-        <v>0.41880341880341881</v>
+        <v>0.43</v>
       </c>
       <c r="I40" s="11">
         <v>0.24</v>
@@ -3428,7 +3458,7 @@
         <v>0.92</v>
       </c>
       <c r="H43" s="15">
-        <v>0.67521367521367526</v>
+        <v>0.69</v>
       </c>
       <c r="I43" s="11">
         <v>0</v>
@@ -3461,7 +3491,7 @@
         <v>0.77</v>
       </c>
       <c r="H44" s="14">
-        <v>0.47863247863247865</v>
+        <v>0.72</v>
       </c>
       <c r="I44" s="11">
         <v>0.56000000000000005</v>
@@ -3499,6 +3529,9 @@
       <c r="I45" s="11">
         <v>0.25</v>
       </c>
+      <c r="J45" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -3554,10 +3587,13 @@
         <v>0.83</v>
       </c>
       <c r="H47" s="15">
-        <v>0.77777777777777779</v>
+        <v>0.79</v>
       </c>
       <c r="I47" s="11">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="J47" s="11">
+        <v>0.79</v>
       </c>
       <c r="M47" s="2"/>
     </row>
@@ -3589,6 +3625,9 @@
       <c r="I48" s="11">
         <v>0.2</v>
       </c>
+      <c r="J48" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13">
@@ -3619,6 +3658,9 @@
       <c r="I49" s="11">
         <v>0.39</v>
       </c>
+      <c r="J49" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M49" s="2"/>
     </row>
     <row r="50" spans="1:13">
@@ -3647,7 +3689,7 @@
         <v>0.40170940170940173</v>
       </c>
       <c r="I50" s="11">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="11">
         <v>0.84</v>
@@ -3712,6 +3754,9 @@
       <c r="I52" s="11">
         <v>0</v>
       </c>
+      <c r="J52" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13">
@@ -3742,6 +3787,9 @@
       <c r="I53" s="11">
         <v>0.46</v>
       </c>
+      <c r="J53" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M53" s="2"/>
     </row>
     <row r="54" spans="1:13">
@@ -3772,6 +3820,9 @@
       <c r="I54" s="11">
         <v>0.39</v>
       </c>
+      <c r="J54" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
@@ -4022,7 +4073,10 @@
         <v>0.63247863247863245</v>
       </c>
       <c r="I62" s="11">
-        <v>0.56999999999999995</v>
+        <v>0.65</v>
+      </c>
+      <c r="J62" s="11">
+        <v>0.79</v>
       </c>
       <c r="M62" s="2"/>
     </row>
@@ -4084,6 +4138,9 @@
       <c r="I64" s="11">
         <v>0.28999999999999998</v>
       </c>
+      <c r="J64" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M64" s="2"/>
     </row>
     <row r="65" spans="1:13">
@@ -4144,6 +4201,9 @@
       <c r="I66" s="11">
         <v>0.47</v>
       </c>
+      <c r="J66" s="11">
+        <v>0.76</v>
+      </c>
       <c r="M66" s="2"/>
     </row>
     <row r="67" spans="1:13">
@@ -4169,7 +4229,7 @@
         <v>0.7</v>
       </c>
       <c r="H67" s="14">
-        <v>0.58974358974358976</v>
+        <v>0.63</v>
       </c>
       <c r="I67" s="11">
         <v>0.26</v>
@@ -4298,7 +4358,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H71" s="15">
-        <v>0.45299145299145299</v>
+        <v>0.64</v>
       </c>
       <c r="I71" s="11">
         <v>0.39</v>
@@ -4427,7 +4487,7 @@
         <v>0.62</v>
       </c>
       <c r="H75" s="14">
-        <v>0.58119658119658124</v>
+        <v>0.6</v>
       </c>
       <c r="I75" s="11">
         <v>0.47</v>
@@ -4679,10 +4739,13 @@
         <v>0.78</v>
       </c>
       <c r="H83" s="14">
-        <v>0.49</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I83" s="11">
-        <v>0.77</v>
+        <v>0.78</v>
+      </c>
+      <c r="J83" s="11">
+        <v>0.78</v>
       </c>
       <c r="M83" s="2"/>
     </row>
@@ -4714,6 +4777,9 @@
       <c r="I84" s="11">
         <v>0.38</v>
       </c>
+      <c r="J84" s="11">
+        <v>0.88</v>
+      </c>
       <c r="M84" s="8"/>
     </row>
     <row r="85" spans="1:13">
@@ -4739,10 +4805,13 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H85" s="14">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="I85" s="11">
         <v>0</v>
+      </c>
+      <c r="J85" s="11">
+        <v>0.88</v>
       </c>
       <c r="M85" s="2"/>
     </row>
@@ -4802,10 +4871,13 @@
         <v>0.51</v>
       </c>
       <c r="H87" s="14">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="I87" s="11">
         <v>0.47</v>
+      </c>
+      <c r="J87" s="11">
+        <v>0.94</v>
       </c>
       <c r="M87" s="2"/>
     </row>
@@ -4927,6 +4999,9 @@
       <c r="I91" s="11">
         <v>0.22</v>
       </c>
+      <c r="J91" s="11">
+        <v>0.88</v>
+      </c>
       <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:13">
@@ -5012,7 +5087,7 @@
         <v>0.65</v>
       </c>
       <c r="H94" s="14">
-        <v>0.53</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I94" s="11">
         <v>0.49</v>
@@ -5077,6 +5152,9 @@
       <c r="I96" s="11">
         <v>0</v>
       </c>
+      <c r="J96" s="11">
+        <v>0.88</v>
+      </c>
       <c r="M96" s="8"/>
     </row>
     <row r="97" spans="1:13">
@@ -5348,10 +5426,13 @@
         <v>0.85</v>
       </c>
       <c r="H105" s="14">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I105" s="11">
-        <v>0.64</v>
+        <v>0.68</v>
+      </c>
+      <c r="J105" s="11">
+        <v>0.78</v>
       </c>
       <c r="M105" s="8"/>
     </row>
@@ -5443,6 +5524,9 @@
       <c r="I108" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J108" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M108" s="2"/>
     </row>
     <row r="109" spans="1:13">
@@ -5569,6 +5653,9 @@
       <c r="I112" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="J112" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M112" s="8"/>
     </row>
     <row r="113" spans="1:13">
@@ -5627,10 +5714,13 @@
         <v>0.82</v>
       </c>
       <c r="H114" s="14">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="I114" s="11">
-        <v>0.75</v>
+        <v>0.76</v>
+      </c>
+      <c r="J114" s="11">
+        <v>0.94</v>
       </c>
       <c r="M114" s="2"/>
     </row>
@@ -5662,6 +5752,9 @@
       <c r="I115" s="11">
         <v>0.43</v>
       </c>
+      <c r="J115" s="11">
+        <v>0.94</v>
+      </c>
       <c r="M115" s="2"/>
     </row>
     <row r="116" spans="1:13">
@@ -5725,6 +5818,9 @@
       <c r="I117" s="11">
         <v>0.45</v>
       </c>
+      <c r="J117" s="11">
+        <v>0.88</v>
+      </c>
       <c r="M117" s="2"/>
     </row>
     <row r="118" spans="1:13">
@@ -5999,10 +6095,13 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H126" s="14">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="I126" s="11">
         <v>0.49</v>
+      </c>
+      <c r="J126" s="11">
+        <v>0.94</v>
       </c>
       <c r="M126" s="2"/>
     </row>
@@ -6097,6 +6196,9 @@
       <c r="I129" s="11">
         <v>0.77</v>
       </c>
+      <c r="J129" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M129" s="2"/>
     </row>
     <row r="130" spans="1:13">
@@ -6127,6 +6229,9 @@
       <c r="I130" s="11">
         <v>0.72</v>
       </c>
+      <c r="J130" s="11">
+        <v>0.94</v>
+      </c>
       <c r="M130" s="2"/>
     </row>
     <row r="131" spans="1:13">
@@ -6284,7 +6389,7 @@
         <v>0.52</v>
       </c>
       <c r="H135" s="14">
-        <v>0.39300000000000002</v>
+        <v>0.44</v>
       </c>
       <c r="I135" s="11">
         <v>0.28000000000000003</v>
@@ -6345,7 +6450,7 @@
         <v>0.53</v>
       </c>
       <c r="I137" s="11">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="J137" s="11">
         <v>0.78</v>
@@ -6413,6 +6518,9 @@
       <c r="I139" s="11">
         <v>0.46</v>
       </c>
+      <c r="J139" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M139" s="2"/>
     </row>
     <row r="140" spans="1:13">
@@ -6443,6 +6551,9 @@
       <c r="I140" s="11">
         <v>0.27</v>
       </c>
+      <c r="J140" s="11">
+        <v>0.83</v>
+      </c>
       <c r="M140" s="2"/>
     </row>
     <row r="141" spans="1:13">
@@ -6539,6 +6650,9 @@
       <c r="I143" s="11">
         <v>0.37</v>
       </c>
+      <c r="J143" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13">
@@ -6569,6 +6683,9 @@
       <c r="I144" s="11">
         <v>0.21</v>
       </c>
+      <c r="J144" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M144" s="2"/>
     </row>
     <row r="145" spans="1:13">
@@ -6629,6 +6746,9 @@
       <c r="I146" s="11">
         <v>0.23</v>
       </c>
+      <c r="J146" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M146" s="2"/>
     </row>
     <row r="147" spans="1:13">
@@ -6786,7 +6906,7 @@
         <v>0.46200000000000002</v>
       </c>
       <c r="I151" s="11">
-        <v>0.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M151" s="2"/>
     </row>
@@ -6843,10 +6963,13 @@
         <v>0.71</v>
       </c>
       <c r="H153" s="14">
-        <v>0.40200000000000002</v>
+        <v>0.44</v>
       </c>
       <c r="I153" s="11">
-        <v>0.41</v>
+        <v>0.51</v>
+      </c>
+      <c r="J153" s="11">
+        <v>0.87</v>
       </c>
       <c r="M153" s="2"/>
     </row>
@@ -6944,6 +7067,9 @@
       <c r="I156" s="11">
         <v>0.18</v>
       </c>
+      <c r="J156" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M156" s="2"/>
     </row>
     <row r="157" spans="1:13">
@@ -7004,6 +7130,9 @@
       <c r="I158" s="11">
         <v>0.37</v>
       </c>
+      <c r="J158" s="11">
+        <v>0.83</v>
+      </c>
       <c r="M158" s="2"/>
     </row>
     <row r="159" spans="1:13">
@@ -7097,6 +7226,9 @@
       <c r="I161" s="11">
         <v>0.19</v>
       </c>
+      <c r="J161" s="11">
+        <v>0.83</v>
+      </c>
       <c r="M161" s="2"/>
     </row>
     <row r="162" spans="1:13">
@@ -7182,7 +7314,7 @@
         <v>0.39</v>
       </c>
       <c r="H164" s="14">
-        <v>0.42699999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="I164" s="11">
         <v>0.34</v>
@@ -7250,6 +7382,9 @@
       <c r="I166" s="11">
         <v>0.51</v>
       </c>
+      <c r="J166" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M166" s="2"/>
     </row>
     <row r="167" spans="1:13">
@@ -7275,10 +7410,13 @@
         <v>0.81</v>
       </c>
       <c r="H167" s="14">
-        <v>0.56399999999999995</v>
+        <v>0.6</v>
       </c>
       <c r="I167" s="11">
-        <v>0.71</v>
+        <v>0.76</v>
+      </c>
+      <c r="J167" s="11">
+        <v>0.87</v>
       </c>
       <c r="M167" s="2"/>
     </row>
@@ -7305,7 +7443,7 @@
         <v>0.74</v>
       </c>
       <c r="H168" s="14">
-        <v>0.67500000000000004</v>
+        <v>0.73</v>
       </c>
       <c r="I168" s="11">
         <v>0.5</v>
@@ -7371,7 +7509,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="I170" s="11">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="J170" s="11">
         <v>0.78</v>
@@ -7406,6 +7544,9 @@
       <c r="I171" s="11">
         <v>0.54</v>
       </c>
+      <c r="J171" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M171" s="2"/>
     </row>
     <row r="172" spans="1:13">
@@ -7532,6 +7673,9 @@
       <c r="I175" s="11">
         <v>0.62</v>
       </c>
+      <c r="J175" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M175" s="2"/>
     </row>
     <row r="176" spans="1:13">
@@ -7647,10 +7791,13 @@
         <v>0.48</v>
       </c>
       <c r="H179" s="14">
-        <v>0.47899999999999998</v>
+        <v>0.59</v>
       </c>
       <c r="I179" s="11">
         <v>0.52</v>
+      </c>
+      <c r="J179" s="11">
+        <v>0.83</v>
       </c>
       <c r="M179" s="2"/>
     </row>
@@ -7770,10 +7917,10 @@
         <v>0.4</v>
       </c>
       <c r="H183" s="14">
-        <v>0.36799999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="I183" s="11">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="M183" s="2"/>
     </row>
@@ -7803,7 +7950,10 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="I184" s="11">
-        <v>0.36</v>
+        <v>0.42</v>
+      </c>
+      <c r="J184" s="11">
+        <v>0.83</v>
       </c>
       <c r="M184" s="2"/>
     </row>
@@ -7830,7 +7980,7 @@
         <v>0.66</v>
       </c>
       <c r="H185" s="14">
-        <v>0.63200000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I185" s="11">
         <v>0.53</v>
@@ -7860,7 +8010,7 @@
         <v>0.73</v>
       </c>
       <c r="H186" s="14">
-        <v>0.70899999999999996</v>
+        <v>0.82</v>
       </c>
       <c r="I186" s="11">
         <v>0.59</v>
@@ -7923,7 +8073,7 @@
         <v>0.32</v>
       </c>
       <c r="H188" s="14">
-        <v>0.38500000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="I188" s="11">
         <v>0.55000000000000004</v>
@@ -8246,6 +8396,9 @@
       <c r="I198" s="11">
         <v>0.21</v>
       </c>
+      <c r="J198" s="11">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M198" s="2"/>
     </row>
     <row r="199" spans="1:13">
@@ -8276,6 +8429,9 @@
       <c r="I199" s="11">
         <v>0.5</v>
       </c>
+      <c r="J199" s="11">
+        <v>0.9</v>
+      </c>
       <c r="M199" s="2"/>
     </row>
     <row r="200" spans="1:13">
@@ -8339,6 +8495,9 @@
       <c r="I201" s="11">
         <v>0.59</v>
       </c>
+      <c r="J201" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M201" s="2"/>
     </row>
     <row r="202" spans="1:13">
@@ -8369,6 +8528,9 @@
       <c r="I202" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J202" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M202" s="2"/>
     </row>
     <row r="203" spans="1:13">
@@ -8394,10 +8556,13 @@
         <v>0.78</v>
       </c>
       <c r="H203" s="14">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="I203" s="11">
-        <v>0.86</v>
+        <v>0.89</v>
+      </c>
+      <c r="J203" s="11">
+        <v>0.88</v>
       </c>
       <c r="M203" s="2"/>
     </row>
@@ -8429,6 +8594,9 @@
       <c r="I204" s="11">
         <v>0.6</v>
       </c>
+      <c r="J204" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M204" s="2"/>
     </row>
     <row r="205" spans="1:13">
@@ -8492,6 +8660,9 @@
       <c r="I206" s="11">
         <v>0.61</v>
       </c>
+      <c r="J206" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M206" s="2"/>
     </row>
     <row r="207" spans="1:13">
@@ -8547,7 +8718,7 @@
         <v>0.82</v>
       </c>
       <c r="H208" s="14">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="I208" s="11">
         <v>0.43</v>
@@ -8585,6 +8756,9 @@
       <c r="I209" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J209" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M209" s="2"/>
     </row>
     <row r="210" spans="1:13">
@@ -8640,10 +8814,13 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H211" s="14">
-        <v>0.51</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I211" s="11">
         <v>0</v>
+      </c>
+      <c r="J211" s="11">
+        <v>0.56999999999999995</v>
       </c>
       <c r="M211" s="2"/>
     </row>
@@ -8675,6 +8852,9 @@
       <c r="I212" s="11">
         <v>0</v>
       </c>
+      <c r="J212" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M212" s="2"/>
     </row>
     <row r="213" spans="1:13">
@@ -8733,10 +8913,13 @@
         <v>0.49</v>
       </c>
       <c r="H214" s="14">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I214" s="11">
         <v>0.36</v>
+      </c>
+      <c r="J214" s="11">
+        <v>0.56999999999999995</v>
       </c>
       <c r="M214" s="2"/>
     </row>
@@ -8861,6 +9044,9 @@
       <c r="I218" s="11">
         <v>0.39</v>
       </c>
+      <c r="J218" s="11">
+        <v>0.9</v>
+      </c>
       <c r="M218" s="2"/>
     </row>
     <row r="219" spans="1:13">
@@ -8919,10 +9105,13 @@
         <v>0.69</v>
       </c>
       <c r="H220" s="14">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="I220" s="11">
         <v>0.61</v>
+      </c>
+      <c r="J220" s="11">
+        <v>0.8</v>
       </c>
       <c r="M220" s="2"/>
     </row>
@@ -8949,7 +9138,7 @@
         <v>0.83</v>
       </c>
       <c r="H221" s="14">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="I221" s="11">
         <v>0</v>
@@ -9014,6 +9203,9 @@
       <c r="I223" s="11">
         <v>0.37</v>
       </c>
+      <c r="J223" s="11">
+        <v>0.9</v>
+      </c>
       <c r="M223" s="2"/>
     </row>
     <row r="224" spans="1:13">
@@ -9072,10 +9264,13 @@
         <v>0.74</v>
       </c>
       <c r="H225" s="14">
-        <v>0.6</v>
+        <v>0.69</v>
       </c>
       <c r="I225" s="11">
         <v>0.31</v>
+      </c>
+      <c r="J225" s="11">
+        <v>0.9</v>
       </c>
       <c r="M225" s="2"/>
     </row>
@@ -9263,6 +9458,9 @@
       <c r="I231" s="11">
         <v>0</v>
       </c>
+      <c r="J231" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M231" s="9"/>
     </row>
     <row r="232" spans="1:13">
@@ -9318,10 +9516,13 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H233" s="14">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="I233" s="11">
-        <v>0.46</v>
+        <v>0.49</v>
+      </c>
+      <c r="J233" s="11">
+        <v>0.85</v>
       </c>
     </row>
     <row r="234" spans="1:13">
@@ -9380,7 +9581,7 @@
         <v>0.69</v>
       </c>
       <c r="H235" s="14">
-        <v>0.56999999999999995</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I235" s="11">
         <v>0.4</v>
@@ -9448,6 +9649,9 @@
       <c r="I237" s="11">
         <v>0</v>
       </c>
+      <c r="J237" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M237" s="9"/>
     </row>
     <row r="238" spans="1:13">
@@ -9571,6 +9775,9 @@
       <c r="I241" s="11">
         <v>0.44</v>
       </c>
+      <c r="J241" s="11">
+        <v>0.53</v>
+      </c>
       <c r="M241" s="9"/>
     </row>
     <row r="242" spans="1:13">
@@ -9601,6 +9808,9 @@
       <c r="I242" s="11">
         <v>0.33</v>
       </c>
+      <c r="J242" s="11">
+        <v>0.56999999999999995</v>
+      </c>
     </row>
     <row r="243" spans="1:13">
       <c r="A243" s="4" t="s">
@@ -9630,6 +9840,9 @@
       <c r="I243" s="11">
         <v>0</v>
       </c>
+      <c r="J243" s="11">
+        <v>0.9</v>
+      </c>
       <c r="M243" s="9"/>
     </row>
     <row r="244" spans="1:13">
@@ -9655,10 +9868,10 @@
         <v>0.51</v>
       </c>
       <c r="H244" s="14">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="I244" s="11">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="J244" s="11">
         <v>0.83</v>
@@ -9688,10 +9901,10 @@
         <v>0.78</v>
       </c>
       <c r="H245" s="14">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="I245" s="11">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="J245" s="11">
         <v>0.8</v>
@@ -9750,10 +9963,13 @@
         <v>0.65</v>
       </c>
       <c r="H247" s="14">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I247" s="11">
-        <v>0.45</v>
+        <v>0.53</v>
+      </c>
+      <c r="J247" s="11">
+        <v>0.53</v>
       </c>
       <c r="M247" s="9"/>
     </row>
@@ -9780,7 +9996,7 @@
         <v>0.71</v>
       </c>
       <c r="H248" s="14">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="I248" s="11">
         <v>0</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FF55A8-2243-F042-A409-8E0230C45804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70277E9-41EA-2444-BF13-F37649782C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2572,6 +2572,9 @@
       <c r="I14" s="11">
         <v>0.32</v>
       </c>
+      <c r="J14" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
@@ -2602,6 +2605,9 @@
       <c r="I15" s="11">
         <v>0.42</v>
       </c>
+      <c r="J15" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
@@ -2755,6 +2761,9 @@
       <c r="I20" s="11">
         <v>0.46</v>
       </c>
+      <c r="J20" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
@@ -2845,6 +2854,9 @@
       <c r="I23" s="11">
         <v>0.36</v>
       </c>
+      <c r="J23" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
@@ -3028,6 +3040,9 @@
       <c r="I29" s="11">
         <v>0.28999999999999998</v>
       </c>
+      <c r="J29" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -3244,6 +3259,9 @@
       <c r="I36" s="11">
         <v>0.38</v>
       </c>
+      <c r="J36" s="11">
+        <v>0.87</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
@@ -3562,6 +3580,9 @@
       <c r="I46" s="11">
         <v>0</v>
       </c>
+      <c r="J46" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -3724,6 +3745,9 @@
       <c r="I51" s="11">
         <v>0.51</v>
       </c>
+      <c r="J51" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13">
@@ -3883,6 +3907,9 @@
       <c r="I56" s="11">
         <v>0</v>
       </c>
+      <c r="J56" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13">
@@ -4429,6 +4456,9 @@
       <c r="I73" s="11">
         <v>0.38</v>
       </c>
+      <c r="J73" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:13">
@@ -4618,6 +4648,9 @@
       <c r="I79" s="11">
         <v>0.31</v>
       </c>
+      <c r="J79" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13">
@@ -4909,6 +4942,9 @@
       <c r="I88" s="11">
         <v>0.38</v>
       </c>
+      <c r="J88" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M88" s="8"/>
     </row>
     <row r="89" spans="1:13">
@@ -4969,6 +5005,9 @@
       <c r="I90" s="11">
         <v>0</v>
       </c>
+      <c r="J90" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:13">
@@ -5032,6 +5071,9 @@
       <c r="I92" s="11">
         <v>0.47</v>
       </c>
+      <c r="J92" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:13">
@@ -5092,6 +5134,9 @@
       <c r="I94" s="11">
         <v>0.49</v>
       </c>
+      <c r="J94" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M94" s="2"/>
     </row>
     <row r="95" spans="1:13">
@@ -5122,6 +5167,9 @@
       <c r="I95" s="11">
         <v>0.7</v>
       </c>
+      <c r="J95" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M95" s="2"/>
     </row>
     <row r="96" spans="1:13">
@@ -5215,6 +5263,9 @@
       <c r="I98" s="11">
         <v>0.44</v>
       </c>
+      <c r="J98" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M98" s="2"/>
     </row>
     <row r="99" spans="1:13">
@@ -5245,6 +5296,9 @@
       <c r="I99" s="11">
         <v>0.47</v>
       </c>
+      <c r="J99" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M99" s="2"/>
     </row>
     <row r="100" spans="1:13">
@@ -5305,6 +5359,9 @@
       <c r="I101" s="11">
         <v>0.2</v>
       </c>
+      <c r="J101" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M101" s="2"/>
     </row>
     <row r="102" spans="1:13">
@@ -5494,6 +5551,9 @@
       <c r="I107" s="11">
         <v>0.35</v>
       </c>
+      <c r="J107" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M107" s="2"/>
     </row>
     <row r="108" spans="1:13">
@@ -5881,6 +5941,9 @@
       <c r="I119" s="11">
         <v>0.25</v>
       </c>
+      <c r="J119" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M119" s="2"/>
     </row>
     <row r="120" spans="1:13">
@@ -6010,6 +6073,9 @@
       <c r="I123" s="11">
         <v>0.7</v>
       </c>
+      <c r="J123" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M123" s="2"/>
     </row>
     <row r="124" spans="1:13">
@@ -6040,6 +6106,9 @@
       <c r="I124" s="11">
         <v>0</v>
       </c>
+      <c r="J124" s="11">
+        <v>0.78</v>
+      </c>
       <c r="M124" s="2"/>
     </row>
     <row r="125" spans="1:13">
@@ -6166,6 +6235,9 @@
       <c r="I128" s="11">
         <v>0.22</v>
       </c>
+      <c r="J128" s="11">
+        <v>0.86</v>
+      </c>
       <c r="M128" s="2"/>
     </row>
     <row r="129" spans="1:13">
@@ -6716,6 +6788,9 @@
       <c r="I145" s="11">
         <v>0.17</v>
       </c>
+      <c r="J145" s="11">
+        <v>0.81</v>
+      </c>
       <c r="M145" s="2"/>
     </row>
     <row r="146" spans="1:13">
@@ -6878,6 +6953,9 @@
       <c r="I150" s="11">
         <v>0.66</v>
       </c>
+      <c r="J150" s="11">
+        <v>0.84</v>
+      </c>
       <c r="M150" s="2"/>
     </row>
     <row r="151" spans="1:13">
@@ -7289,6 +7367,9 @@
       <c r="I163" s="11">
         <v>0.49</v>
       </c>
+      <c r="J163" s="11">
+        <v>0.81</v>
+      </c>
       <c r="M163" s="2"/>
     </row>
     <row r="164" spans="1:13">
@@ -7610,6 +7691,9 @@
       <c r="I173" s="11">
         <v>0.34</v>
       </c>
+      <c r="J173" s="11">
+        <v>0.84</v>
+      </c>
       <c r="M173" s="2"/>
     </row>
     <row r="174" spans="1:13">
@@ -7862,6 +7946,9 @@
       <c r="I181" s="11">
         <v>0.25</v>
       </c>
+      <c r="J181" s="11">
+        <v>0.84</v>
+      </c>
       <c r="M181" s="2"/>
     </row>
     <row r="182" spans="1:13">
@@ -8015,6 +8102,9 @@
       <c r="I186" s="11">
         <v>0.59</v>
       </c>
+      <c r="J186" s="11">
+        <v>0.84</v>
+      </c>
       <c r="M186" s="2"/>
     </row>
     <row r="187" spans="1:13">
@@ -8692,6 +8782,9 @@
       </c>
       <c r="I207" s="11">
         <v>0.42</v>
+      </c>
+      <c r="J207" s="11">
+        <v>0.87</v>
       </c>
       <c r="M207" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70277E9-41EA-2444-BF13-F37649782C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A5DFDF-6F67-F847-B628-A4962843753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2638,6 +2638,9 @@
       <c r="I16" s="11">
         <v>0.42</v>
       </c>
+      <c r="J16" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13">
@@ -2701,6 +2704,9 @@
       <c r="I18" s="11">
         <v>0.52</v>
       </c>
+      <c r="J18" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13">
@@ -2731,6 +2737,9 @@
       <c r="I19" s="11">
         <v>0.53</v>
       </c>
+      <c r="J19" s="11">
+        <v>0.64</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
@@ -2794,6 +2803,9 @@
       <c r="I21" s="11">
         <v>0</v>
       </c>
+      <c r="J21" s="11">
+        <v>0.83</v>
+      </c>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13">
@@ -2887,6 +2899,9 @@
       <c r="I24" s="11">
         <v>0.45</v>
       </c>
+      <c r="J24" s="11">
+        <v>0.64</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
@@ -2917,6 +2932,9 @@
       <c r="I25" s="11">
         <v>0.43</v>
       </c>
+      <c r="J25" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13">
@@ -3010,6 +3028,9 @@
       <c r="I28" s="11">
         <v>0.61</v>
       </c>
+      <c r="J28" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13">
@@ -3106,6 +3127,9 @@
       <c r="I31" s="11">
         <v>0.62</v>
       </c>
+      <c r="J31" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13">
@@ -3136,6 +3160,9 @@
       <c r="I32" s="11">
         <v>0.42</v>
       </c>
+      <c r="J32" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13">
@@ -3166,6 +3193,9 @@
       <c r="I33" s="11">
         <v>0</v>
       </c>
+      <c r="J33" s="11">
+        <v>0.64</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
@@ -3229,6 +3259,9 @@
       <c r="I35" s="11">
         <v>0.36</v>
       </c>
+      <c r="J35" s="11">
+        <v>0.83</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -3292,6 +3325,9 @@
       <c r="I37" s="11">
         <v>0.4</v>
       </c>
+      <c r="J37" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13">
@@ -3451,6 +3487,9 @@
       <c r="I42" s="11">
         <v>0.54</v>
       </c>
+      <c r="J42" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13">
@@ -3641,7 +3680,7 @@
         <v>0.18</v>
       </c>
       <c r="H48" s="15">
-        <v>0.40170940170940173</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I48" s="11">
         <v>0.2</v>
@@ -3674,7 +3713,7 @@
         <v>0.18</v>
       </c>
       <c r="H49" s="15">
-        <v>0.29059829059829062</v>
+        <v>0.4</v>
       </c>
       <c r="I49" s="11">
         <v>0.39</v>
@@ -3866,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="11">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G55" s="11">
         <v>0.68</v>
@@ -3876,6 +3915,9 @@
       </c>
       <c r="I55" s="11">
         <v>0.46</v>
+      </c>
+      <c r="J55" s="11">
+        <v>0.7</v>
       </c>
       <c r="M55" s="2"/>
     </row>
@@ -4006,6 +4048,9 @@
       <c r="I59" s="11">
         <v>0.51</v>
       </c>
+      <c r="J59" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:13">
@@ -4135,6 +4180,9 @@
       <c r="I63" s="11">
         <v>0</v>
       </c>
+      <c r="J63" s="11">
+        <v>0.64</v>
+      </c>
       <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13">
@@ -4294,6 +4342,9 @@
       <c r="I68" s="11">
         <v>0.39</v>
       </c>
+      <c r="J68" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M68" s="2"/>
     </row>
     <row r="69" spans="1:13">
@@ -4555,6 +4606,9 @@
       <c r="I76" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="J76" s="11">
+        <v>0.83</v>
+      </c>
       <c r="M76" s="2"/>
     </row>
     <row r="77" spans="1:13">
@@ -4618,6 +4672,9 @@
       <c r="I78" s="11">
         <v>0</v>
       </c>
+      <c r="J78" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13">
@@ -4975,6 +5032,9 @@
       <c r="I89" s="11">
         <v>0.44</v>
       </c>
+      <c r="J89" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:13">
@@ -5233,6 +5293,9 @@
       <c r="I97" s="11">
         <v>0.73</v>
       </c>
+      <c r="J97" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M97" s="8"/>
     </row>
     <row r="98" spans="1:13">
@@ -5329,6 +5392,9 @@
       <c r="I100" s="11">
         <v>0.53</v>
       </c>
+      <c r="J100" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M100" s="2"/>
     </row>
     <row r="101" spans="1:13">
@@ -5425,6 +5491,9 @@
       <c r="I103" s="11">
         <v>0.26</v>
       </c>
+      <c r="J103" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M103" s="8"/>
     </row>
     <row r="104" spans="1:13">
@@ -5911,6 +5980,9 @@
       <c r="I118" s="11">
         <v>0.15</v>
       </c>
+      <c r="J118" s="11">
+        <v>0.7</v>
+      </c>
       <c r="M118" s="2"/>
     </row>
     <row r="119" spans="1:13">
@@ -6484,6 +6556,9 @@
       <c r="D136" s="14">
         <v>0</v>
       </c>
+      <c r="E136" s="11">
+        <v>0.98</v>
+      </c>
       <c r="F136" s="11">
         <v>0.89</v>
       </c>
@@ -6986,6 +7061,9 @@
       <c r="I151" s="11">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J151" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M151" s="2"/>
     </row>
     <row r="152" spans="1:13">
@@ -7016,6 +7094,9 @@
       <c r="I152" s="11">
         <v>0.4</v>
       </c>
+      <c r="J152" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M152" s="2"/>
     </row>
     <row r="153" spans="1:13">
@@ -7178,6 +7259,9 @@
       <c r="I157" s="11">
         <v>0.39</v>
       </c>
+      <c r="J157" s="11">
+        <v>0.74</v>
+      </c>
       <c r="M157" s="8"/>
     </row>
     <row r="158" spans="1:13">
@@ -7274,6 +7358,9 @@
       <c r="I160" s="11">
         <v>0.66</v>
       </c>
+      <c r="J160" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M160" s="8"/>
     </row>
     <row r="161" spans="1:13">
@@ -7400,6 +7487,9 @@
       <c r="I164" s="11">
         <v>0.34</v>
       </c>
+      <c r="J164" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M164" s="2"/>
     </row>
     <row r="165" spans="1:13">
@@ -7529,6 +7619,9 @@
       <c r="I168" s="11">
         <v>0.5</v>
       </c>
+      <c r="J168" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M168" s="2"/>
     </row>
     <row r="169" spans="1:13">
@@ -7790,6 +7883,9 @@
       <c r="I176" s="11">
         <v>0.41</v>
       </c>
+      <c r="J176" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M176" s="2"/>
     </row>
     <row r="177" spans="1:13">
@@ -7850,6 +7946,9 @@
       <c r="I178" s="11">
         <v>0.5</v>
       </c>
+      <c r="J178" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M178" s="2"/>
     </row>
     <row r="179" spans="1:13">
@@ -7979,6 +8078,9 @@
       <c r="I182" s="11">
         <v>0.54</v>
       </c>
+      <c r="J182" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M182" s="8"/>
     </row>
     <row r="183" spans="1:13">
@@ -8009,6 +8111,9 @@
       <c r="I183" s="11">
         <v>0.48</v>
       </c>
+      <c r="J183" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M183" s="2"/>
     </row>
     <row r="184" spans="1:13">
@@ -8072,6 +8177,9 @@
       <c r="I185" s="11">
         <v>0.53</v>
       </c>
+      <c r="J185" s="11">
+        <v>0.8</v>
+      </c>
       <c r="M185" s="2"/>
     </row>
     <row r="186" spans="1:13">
@@ -8168,6 +8276,9 @@
       <c r="I188" s="11">
         <v>0.55000000000000004</v>
       </c>
+      <c r="J188" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M188" s="2"/>
     </row>
     <row r="189" spans="1:13">
@@ -8231,6 +8342,9 @@
       <c r="I190" s="11">
         <v>0.54</v>
       </c>
+      <c r="J190" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M190" s="2"/>
     </row>
     <row r="191" spans="1:13">
@@ -8261,6 +8375,9 @@
       <c r="I191" s="11">
         <v>0.38</v>
       </c>
+      <c r="J191" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M191" s="2"/>
     </row>
     <row r="192" spans="1:13">
@@ -8291,6 +8408,9 @@
       <c r="I192" s="11">
         <v>0.19</v>
       </c>
+      <c r="J192" s="11">
+        <v>0.85</v>
+      </c>
       <c r="M192" s="2"/>
     </row>
     <row r="193" spans="1:13">
@@ -8882,6 +9002,9 @@
       <c r="I210" s="11">
         <v>0</v>
       </c>
+      <c r="J210" s="11">
+        <v>0.81</v>
+      </c>
       <c r="M210" s="2"/>
     </row>
     <row r="211" spans="1:13">
@@ -9077,6 +9200,9 @@
       <c r="I216" s="11">
         <v>0</v>
       </c>
+      <c r="J216" s="11">
+        <v>0.59</v>
+      </c>
       <c r="M216" s="2"/>
     </row>
     <row r="217" spans="1:13">
@@ -9107,6 +9233,9 @@
       <c r="I217" s="11">
         <v>0</v>
       </c>
+      <c r="J217" s="11">
+        <v>0.79</v>
+      </c>
       <c r="M217" s="2"/>
     </row>
     <row r="218" spans="1:13">
@@ -9395,6 +9524,9 @@
       <c r="I226" s="11">
         <v>0.32</v>
       </c>
+      <c r="J226" s="11">
+        <v>0.81</v>
+      </c>
       <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13">
@@ -9425,6 +9557,9 @@
       <c r="I227" s="11">
         <v>0.35</v>
       </c>
+      <c r="J227" s="11">
+        <v>0.59</v>
+      </c>
       <c r="M227" s="2"/>
     </row>
     <row r="228" spans="1:13">
@@ -9521,6 +9656,9 @@
       <c r="I230" s="11">
         <v>0.28000000000000003</v>
       </c>
+      <c r="J230" s="11">
+        <v>0.81</v>
+      </c>
       <c r="M230" s="9"/>
     </row>
     <row r="231" spans="1:13">
@@ -9584,6 +9722,9 @@
       <c r="I232" s="11">
         <v>0</v>
       </c>
+      <c r="J232" s="11">
+        <v>0.81</v>
+      </c>
       <c r="M232" s="9"/>
     </row>
     <row r="233" spans="1:13">
@@ -9678,6 +9819,9 @@
       </c>
       <c r="I235" s="11">
         <v>0.4</v>
+      </c>
+      <c r="J235" s="11">
+        <v>0.81</v>
       </c>
       <c r="M235" s="9"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A5DFDF-6F67-F847-B628-A4962843753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DFFFAF-3C5D-1C41-8000-B97AF310B2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1139,9 +1139,6 @@
     <t>H263985Z</t>
   </si>
   <si>
-    <t>Mangwanywa</t>
-  </si>
-  <si>
     <t>H267059G</t>
   </si>
   <si>
@@ -1551,6 +1548,9 @@
   </si>
   <si>
     <t>Manjiche</t>
+  </si>
+  <si>
+    <t>Mangwanya</t>
   </si>
 </sst>
 </file>
@@ -2216,10 +2216,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>478</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>479</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>15</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
+        <v>479</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>481</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>15</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>15</v>
@@ -4745,10 +4745,10 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
+        <v>492</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>493</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>494</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>159</v>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>159</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
+        <v>494</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>495</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>496</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>159</v>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>159</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
+        <v>496</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>497</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>498</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>159</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
+        <v>498</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>499</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>500</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>159</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>159</v>
@@ -5531,10 +5531,10 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
+        <v>482</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>484</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>159</v>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
+        <v>484</v>
+      </c>
+      <c r="B112" s="7" t="s">
         <v>485</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>486</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>159</v>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="C116" s="13" t="s">
         <v>159</v>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C127" s="13" t="s">
         <v>159</v>
@@ -6380,10 +6380,10 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="C131" s="13" t="s">
         <v>159</v>
@@ -6545,10 +6545,10 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" t="s">
+        <v>500</v>
+      </c>
+      <c r="B136" s="7" t="s">
         <v>501</v>
-      </c>
-      <c r="B136" s="7" t="s">
-        <v>502</v>
       </c>
       <c r="C136" s="11" t="s">
         <v>245</v>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>460</v>
       </c>
       <c r="C143" s="13" t="s">
         <v>245</v>
@@ -6969,10 +6969,10 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="C149" s="13" t="s">
         <v>245</v>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>462</v>
       </c>
       <c r="C151" s="13" t="s">
         <v>245</v>
@@ -7167,10 +7167,10 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="C155" s="13" t="s">
         <v>245</v>
@@ -7233,10 +7233,10 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" t="s">
+        <v>475</v>
+      </c>
+      <c r="B157" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>477</v>
       </c>
       <c r="C157" s="11" t="s">
         <v>245</v>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" t="s">
+        <v>464</v>
+      </c>
+      <c r="B160" s="7" t="s">
         <v>465</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>466</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>245</v>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" t="s">
+        <v>473</v>
+      </c>
+      <c r="B162" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>475</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>245</v>
@@ -7461,7 +7461,7 @@
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>267</v>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="169" spans="1:13">
       <c r="A169" t="s">
+        <v>466</v>
+      </c>
+      <c r="B169" s="7" t="s">
         <v>467</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>468</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>245</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" t="s">
+        <v>468</v>
+      </c>
+      <c r="B170" s="7" t="s">
         <v>469</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>470</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>245</v>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="172" spans="1:13">
       <c r="A172" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C172" s="11" t="s">
         <v>245</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B178" s="4" t="s">
         <v>250</v>
@@ -8052,10 +8052,10 @@
     </row>
     <row r="182" spans="1:13">
       <c r="A182" t="s">
+        <v>471</v>
+      </c>
+      <c r="B182" s="7" t="s">
         <v>472</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>473</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>245</v>
@@ -8444,14 +8444,17 @@
       <c r="J193" s="11">
         <v>0.8</v>
       </c>
+      <c r="K193">
+        <v>0.85</v>
+      </c>
       <c r="M193" s="2"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B194" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>390</v>
       </c>
       <c r="C194" s="12" t="s">
         <v>342</v>
@@ -8481,10 +8484,10 @@
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B195" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>428</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>342</v>
@@ -8576,14 +8579,17 @@
       <c r="J197" s="11">
         <v>0.8</v>
       </c>
+      <c r="K197">
+        <v>0.85</v>
+      </c>
       <c r="M197" s="2"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="C198" s="12" t="s">
         <v>342</v>
@@ -8609,14 +8615,17 @@
       <c r="J198" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K198">
+        <v>0.81</v>
+      </c>
       <c r="M198" s="2"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B199" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>432</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>342</v>
@@ -8646,10 +8655,10 @@
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B200" s="4" t="s">
         <v>433</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>434</v>
       </c>
       <c r="C200" s="12" t="s">
         <v>342</v>
@@ -8679,10 +8688,10 @@
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B201" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>416</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>342</v>
@@ -8708,14 +8717,17 @@
       <c r="J201" s="11">
         <v>0.8</v>
       </c>
+      <c r="K201">
+        <v>0.44</v>
+      </c>
       <c r="M201" s="2"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B202" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>342</v>
@@ -8745,10 +8757,10 @@
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B203" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>376</v>
       </c>
       <c r="C203" s="12" t="s">
         <v>342</v>
@@ -8778,10 +8790,10 @@
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B204" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>342</v>
@@ -8811,10 +8823,10 @@
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B205" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="B205" s="4" t="s">
-        <v>398</v>
       </c>
       <c r="C205" s="12" t="s">
         <v>342</v>
@@ -8844,10 +8856,10 @@
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B206" s="4" t="s">
         <v>393</v>
-      </c>
-      <c r="B206" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>342</v>
@@ -8873,14 +8885,17 @@
       <c r="J206" s="11">
         <v>0.8</v>
       </c>
+      <c r="K206">
+        <v>0.44</v>
+      </c>
       <c r="M206" s="2"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B207" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="C207" s="12" t="s">
         <v>342</v>
@@ -8905,6 +8920,9 @@
       </c>
       <c r="J207" s="11">
         <v>0.87</v>
+      </c>
+      <c r="K207">
+        <v>0.85</v>
       </c>
       <c r="M207" s="2"/>
     </row>
@@ -8939,14 +8957,17 @@
       <c r="J208" s="11">
         <v>0.8</v>
       </c>
+      <c r="K208">
+        <v>0.85</v>
+      </c>
       <c r="M208" s="2"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B209" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="B209" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="C209" s="12" t="s">
         <v>342</v>
@@ -9009,10 +9030,10 @@
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B211" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="B211" s="4" t="s">
-        <v>378</v>
       </c>
       <c r="C211" s="12" t="s">
         <v>342</v>
@@ -9038,14 +9059,17 @@
       <c r="J211" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K211">
+        <v>0.81</v>
+      </c>
       <c r="M211" s="2"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B212" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="B212" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="C212" s="12" t="s">
         <v>342</v>
@@ -9108,10 +9132,10 @@
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="C214" s="12" t="s">
         <v>342</v>
@@ -9137,14 +9161,17 @@
       <c r="J214" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K214">
+        <v>0.81</v>
+      </c>
       <c r="M214" s="2"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>370</v>
       </c>
       <c r="C215" s="12" t="s">
         <v>342</v>
@@ -9174,10 +9201,10 @@
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B216" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="C216" s="12" t="s">
         <v>342</v>
@@ -9207,10 +9234,10 @@
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>368</v>
       </c>
       <c r="C217" s="12" t="s">
         <v>342</v>
@@ -9236,14 +9263,17 @@
       <c r="J217" s="11">
         <v>0.79</v>
       </c>
+      <c r="K217">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M217" s="2"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B218" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>408</v>
       </c>
       <c r="C218" s="12" t="s">
         <v>342</v>
@@ -9302,14 +9332,17 @@
       <c r="J219" s="11">
         <v>0.79</v>
       </c>
+      <c r="K219">
+        <v>0.64</v>
+      </c>
       <c r="M219" s="2"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B220" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="B220" s="4" t="s">
-        <v>396</v>
       </c>
       <c r="C220" s="12" t="s">
         <v>342</v>
@@ -9335,14 +9368,17 @@
       <c r="J220" s="11">
         <v>0.8</v>
       </c>
+      <c r="K220">
+        <v>0.44</v>
+      </c>
       <c r="M220" s="2"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B221" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>374</v>
       </c>
       <c r="C221" s="12" t="s">
         <v>342</v>
@@ -9365,14 +9401,17 @@
       <c r="I221" s="11">
         <v>0</v>
       </c>
+      <c r="K221">
+        <v>0.25</v>
+      </c>
       <c r="M221" s="2"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B222" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>386</v>
       </c>
       <c r="C222" s="12" t="s">
         <v>342</v>
@@ -9395,14 +9434,20 @@
       <c r="I222" s="11">
         <v>0</v>
       </c>
+      <c r="J222" s="11">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0.25</v>
+      </c>
       <c r="M222" s="2"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B223" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="B223" s="4" t="s">
-        <v>406</v>
       </c>
       <c r="C223" s="12" t="s">
         <v>342</v>
@@ -9432,10 +9477,10 @@
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B224" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="B224" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="C224" s="12" t="s">
         <v>342</v>
@@ -9465,10 +9510,10 @@
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="B225" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="B225" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>342</v>
@@ -9531,10 +9576,10 @@
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B227" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="C227" s="12" t="s">
         <v>342</v>
@@ -9564,10 +9609,10 @@
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B228" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="C228" s="12" t="s">
         <v>342</v>
@@ -9597,10 +9642,10 @@
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="C229" s="13" t="s">
         <v>342</v>
@@ -9626,14 +9671,17 @@
       <c r="J229" s="11">
         <v>0.93</v>
       </c>
+      <c r="K229">
+        <v>0.71</v>
+      </c>
       <c r="M229" s="9"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B230" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="B230" s="4" t="s">
-        <v>384</v>
       </c>
       <c r="C230" s="12" t="s">
         <v>342</v>
@@ -9663,10 +9711,10 @@
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B231" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="C231" s="12" t="s">
         <v>342</v>
@@ -9692,14 +9740,17 @@
       <c r="J231" s="11">
         <v>0.8</v>
       </c>
+      <c r="K231">
+        <v>0.44</v>
+      </c>
       <c r="M231" s="9"/>
     </row>
     <row r="232" spans="1:13">
       <c r="A232" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B232" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="B232" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>342</v>
@@ -9729,10 +9780,10 @@
     </row>
     <row r="233" spans="1:13">
       <c r="A233" t="s">
+        <v>487</v>
+      </c>
+      <c r="B233" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="C233" s="11" t="s">
         <v>342</v>
@@ -9761,10 +9812,10 @@
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B234" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="B234" s="4" t="s">
-        <v>422</v>
       </c>
       <c r="C234" s="12" t="s">
         <v>342</v>
@@ -9794,10 +9845,10 @@
     </row>
     <row r="235" spans="1:13">
       <c r="A235" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B235" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="B235" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="C235" s="12" t="s">
         <v>342</v>
@@ -9827,10 +9878,10 @@
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B236" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="B236" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="C236" s="12" t="s">
         <v>342</v>
@@ -9922,14 +9973,17 @@
       <c r="J238" s="11">
         <v>0.8</v>
       </c>
+      <c r="K238">
+        <v>0.85</v>
+      </c>
       <c r="M238" s="9"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B239" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="B239" s="4" t="s">
-        <v>388</v>
       </c>
       <c r="C239" s="12" t="s">
         <v>342</v>
@@ -9952,14 +10006,20 @@
       <c r="I239" s="11">
         <v>0.3</v>
       </c>
+      <c r="J239" s="11">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>0.25</v>
+      </c>
       <c r="M239" s="9"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B240" s="4" t="s">
         <v>425</v>
-      </c>
-      <c r="B240" s="4" t="s">
-        <v>426</v>
       </c>
       <c r="C240" s="12" t="s">
         <v>342</v>
@@ -10019,10 +10079,10 @@
     </row>
     <row r="242" spans="1:13">
       <c r="A242" t="s">
+        <v>489</v>
+      </c>
+      <c r="B242" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>491</v>
       </c>
       <c r="C242" s="11" t="s">
         <v>342</v>
@@ -10048,13 +10108,16 @@
       <c r="J242" s="11">
         <v>0.56999999999999995</v>
       </c>
+      <c r="K242">
+        <v>0.81</v>
+      </c>
     </row>
     <row r="243" spans="1:13">
       <c r="A243" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B243" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>420</v>
       </c>
       <c r="C243" s="12" t="s">
         <v>342</v>
@@ -10117,10 +10180,10 @@
     </row>
     <row r="245" spans="1:13">
       <c r="A245" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B245" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="B245" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="C245" s="12" t="s">
         <v>342</v>
@@ -10146,14 +10209,17 @@
       <c r="J245" s="11">
         <v>0.8</v>
       </c>
+      <c r="K245">
+        <v>0.85</v>
+      </c>
       <c r="M245" s="9"/>
     </row>
     <row r="246" spans="1:13">
       <c r="A246" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C246" s="11" t="s">
         <v>342</v>
@@ -10212,10 +10278,10 @@
     </row>
     <row r="248" spans="1:13">
       <c r="A248" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B248" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="B248" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="C248" s="12" t="s">
         <v>342</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DFFFAF-3C5D-1C41-8000-B97AF310B2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2536E0-8FA2-184B-B56A-9507798503BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="30960" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2245,6 +2245,9 @@
       <c r="J4" s="11">
         <v>0.65</v>
       </c>
+      <c r="K4">
+        <v>0.75</v>
+      </c>
       <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
@@ -2344,6 +2347,9 @@
       <c r="J7" s="11">
         <v>0.65</v>
       </c>
+      <c r="K7">
+        <v>0.75</v>
+      </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
@@ -2542,6 +2548,9 @@
       <c r="J13" s="11">
         <v>0.65</v>
       </c>
+      <c r="K13">
+        <v>0.75</v>
+      </c>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
@@ -2641,6 +2650,9 @@
       <c r="J16" s="11">
         <v>0.8</v>
       </c>
+      <c r="K16">
+        <v>0.67</v>
+      </c>
       <c r="M16" s="2"/>
     </row>
     <row r="17" spans="1:13">
@@ -2836,6 +2848,9 @@
       <c r="I22" s="11">
         <v>0.74</v>
       </c>
+      <c r="K22">
+        <v>0.67</v>
+      </c>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13">
@@ -2935,6 +2950,9 @@
       <c r="J25" s="11">
         <v>0.8</v>
       </c>
+      <c r="K25">
+        <v>0.67</v>
+      </c>
       <c r="M25" s="2"/>
     </row>
     <row r="26" spans="1:13">
@@ -2965,6 +2983,9 @@
       <c r="I26" s="11">
         <v>0.37</v>
       </c>
+      <c r="J26" s="11">
+        <v>0</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
@@ -3394,6 +3415,9 @@
       <c r="J39" s="11">
         <v>0.65</v>
       </c>
+      <c r="K39">
+        <v>0.75</v>
+      </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13">
@@ -3424,6 +3448,9 @@
       <c r="I40" s="11">
         <v>0.24</v>
       </c>
+      <c r="J40" s="11">
+        <v>0</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
@@ -3490,6 +3517,9 @@
       <c r="J42" s="11">
         <v>0.8</v>
       </c>
+      <c r="K42">
+        <v>0.67</v>
+      </c>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13">
@@ -3523,6 +3553,9 @@
       <c r="J43" s="11">
         <v>0.84</v>
       </c>
+      <c r="K43">
+        <v>0.81</v>
+      </c>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13">
@@ -3556,6 +3589,9 @@
       <c r="J44" s="11">
         <v>0.65</v>
       </c>
+      <c r="K44">
+        <v>0.75</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13">
@@ -3754,6 +3790,9 @@
       <c r="J50" s="11">
         <v>0.84</v>
       </c>
+      <c r="K50">
+        <v>0.81</v>
+      </c>
       <c r="M50" s="2"/>
     </row>
     <row r="51" spans="1:13">
@@ -4018,6 +4057,9 @@
       <c r="J58" s="11">
         <v>0.84</v>
       </c>
+      <c r="K58">
+        <v>0.81</v>
+      </c>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:13">
@@ -5395,6 +5437,9 @@
       <c r="J100" s="11">
         <v>0.8</v>
       </c>
+      <c r="K100">
+        <v>0.67</v>
+      </c>
       <c r="M100" s="2"/>
     </row>
     <row r="101" spans="1:13">
@@ -8480,6 +8525,9 @@
       <c r="J194" s="11">
         <v>0.85</v>
       </c>
+      <c r="K194">
+        <v>0.81</v>
+      </c>
       <c r="M194" s="2"/>
     </row>
     <row r="195" spans="1:13">
@@ -8513,6 +8561,9 @@
       <c r="J195" s="11">
         <v>0.77</v>
       </c>
+      <c r="K195">
+        <v>0.65</v>
+      </c>
       <c r="M195" s="2"/>
     </row>
     <row r="196" spans="1:13">
@@ -8546,6 +8597,9 @@
       <c r="J196" s="11">
         <v>0.83</v>
       </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
       <c r="M196" s="2"/>
     </row>
     <row r="197" spans="1:13">
@@ -8651,6 +8705,9 @@
       <c r="J199" s="11">
         <v>0.9</v>
       </c>
+      <c r="K199">
+        <v>0.69</v>
+      </c>
       <c r="M199" s="2"/>
     </row>
     <row r="200" spans="1:13">
@@ -8684,6 +8741,9 @@
       <c r="J200" s="11">
         <v>0.77</v>
       </c>
+      <c r="K200">
+        <v>0.65</v>
+      </c>
       <c r="M200" s="2"/>
     </row>
     <row r="201" spans="1:13">
@@ -8753,6 +8813,9 @@
       <c r="J202" s="11">
         <v>0.85</v>
       </c>
+      <c r="K202">
+        <v>0.87</v>
+      </c>
       <c r="M202" s="2"/>
     </row>
     <row r="203" spans="1:13">
@@ -8786,6 +8849,9 @@
       <c r="J203" s="11">
         <v>0.88</v>
       </c>
+      <c r="K203">
+        <v>0.88</v>
+      </c>
       <c r="M203" s="2"/>
     </row>
     <row r="204" spans="1:13">
@@ -8819,6 +8885,9 @@
       <c r="J204" s="11">
         <v>0.53</v>
       </c>
+      <c r="K204">
+        <v>0.75</v>
+      </c>
       <c r="M204" s="2"/>
     </row>
     <row r="205" spans="1:13">
@@ -8852,6 +8921,9 @@
       <c r="J205" s="11">
         <v>0.83</v>
       </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
       <c r="M205" s="2"/>
     </row>
     <row r="206" spans="1:13">
@@ -8993,6 +9065,9 @@
       <c r="J209" s="11">
         <v>0.85</v>
       </c>
+      <c r="K209">
+        <v>0.87</v>
+      </c>
       <c r="M209" s="2"/>
     </row>
     <row r="210" spans="1:13">
@@ -9026,6 +9101,9 @@
       <c r="J210" s="11">
         <v>0.81</v>
       </c>
+      <c r="K210">
+        <v>0.65</v>
+      </c>
       <c r="M210" s="2"/>
     </row>
     <row r="211" spans="1:13">
@@ -9095,6 +9173,9 @@
       <c r="J212" s="11">
         <v>0.53</v>
       </c>
+      <c r="K212">
+        <v>0.75</v>
+      </c>
       <c r="M212" s="2"/>
     </row>
     <row r="213" spans="1:13">
@@ -9128,6 +9209,9 @@
       <c r="J213" s="11">
         <v>0.83</v>
       </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
       <c r="M213" s="2"/>
     </row>
     <row r="214" spans="1:13">
@@ -9197,6 +9281,9 @@
       <c r="J215" s="11">
         <v>0.85</v>
       </c>
+      <c r="K215">
+        <v>0.81</v>
+      </c>
       <c r="M215" s="2"/>
     </row>
     <row r="216" spans="1:13">
@@ -9230,6 +9317,9 @@
       <c r="J216" s="11">
         <v>0.59</v>
       </c>
+      <c r="K216">
+        <v>0.85</v>
+      </c>
       <c r="M216" s="2"/>
     </row>
     <row r="217" spans="1:13">
@@ -9299,6 +9389,9 @@
       <c r="J218" s="11">
         <v>0.9</v>
       </c>
+      <c r="K218">
+        <v>0.69</v>
+      </c>
       <c r="M218" s="2"/>
     </row>
     <row r="219" spans="1:13">
@@ -9473,6 +9566,9 @@
       <c r="J223" s="11">
         <v>0.9</v>
       </c>
+      <c r="K223">
+        <v>0.69</v>
+      </c>
       <c r="M223" s="2"/>
     </row>
     <row r="224" spans="1:13">
@@ -9506,6 +9602,9 @@
       <c r="J224" s="11">
         <v>0.93</v>
       </c>
+      <c r="K224">
+        <v>0.77</v>
+      </c>
       <c r="M224" s="2"/>
     </row>
     <row r="225" spans="1:13">
@@ -9539,6 +9638,9 @@
       <c r="J225" s="11">
         <v>0.9</v>
       </c>
+      <c r="K225">
+        <v>0.69</v>
+      </c>
       <c r="M225" s="2"/>
     </row>
     <row r="226" spans="1:13">
@@ -9572,6 +9674,9 @@
       <c r="J226" s="11">
         <v>0.81</v>
       </c>
+      <c r="K226">
+        <v>0.65</v>
+      </c>
       <c r="M226" s="2"/>
     </row>
     <row r="227" spans="1:13">
@@ -9605,6 +9710,9 @@
       <c r="J227" s="11">
         <v>0.59</v>
       </c>
+      <c r="K227">
+        <v>0.85</v>
+      </c>
       <c r="M227" s="2"/>
     </row>
     <row r="228" spans="1:13">
@@ -9638,6 +9746,9 @@
       <c r="J228" s="11">
         <v>0.85</v>
       </c>
+      <c r="K228">
+        <v>0.81</v>
+      </c>
       <c r="M228" s="2"/>
     </row>
     <row r="229" spans="1:13">
@@ -9707,6 +9818,9 @@
       <c r="J230" s="11">
         <v>0.81</v>
       </c>
+      <c r="K230">
+        <v>0.65</v>
+      </c>
       <c r="M230" s="9"/>
     </row>
     <row r="231" spans="1:13">
@@ -9776,6 +9890,9 @@
       <c r="J232" s="11">
         <v>0.81</v>
       </c>
+      <c r="K232">
+        <v>0.65</v>
+      </c>
       <c r="M232" s="9"/>
     </row>
     <row r="233" spans="1:13">
@@ -9809,6 +9926,9 @@
       <c r="J233" s="11">
         <v>0.85</v>
       </c>
+      <c r="K233">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="4" t="s">
@@ -9841,6 +9961,9 @@
       <c r="J234" s="11">
         <v>0.93</v>
       </c>
+      <c r="K234">
+        <v>0.77</v>
+      </c>
       <c r="M234" s="9"/>
     </row>
     <row r="235" spans="1:13">
@@ -9874,6 +9997,9 @@
       <c r="J235" s="11">
         <v>0.81</v>
       </c>
+      <c r="K235">
+        <v>0.65</v>
+      </c>
       <c r="M235" s="9"/>
     </row>
     <row r="236" spans="1:13">
@@ -9907,6 +10033,9 @@
       <c r="J236" s="11">
         <v>0.93</v>
       </c>
+      <c r="K236">
+        <v>0.77</v>
+      </c>
       <c r="M236" s="9"/>
     </row>
     <row r="237" spans="1:13">
@@ -9940,6 +10069,9 @@
       <c r="J237" s="11">
         <v>0.53</v>
       </c>
+      <c r="K237">
+        <v>0.75</v>
+      </c>
       <c r="M237" s="9"/>
     </row>
     <row r="238" spans="1:13">
@@ -10042,6 +10174,9 @@
       <c r="I240" s="11">
         <v>0.2</v>
       </c>
+      <c r="K240">
+        <v>0.77</v>
+      </c>
       <c r="M240" s="9"/>
     </row>
     <row r="241" spans="1:13">
@@ -10075,6 +10210,9 @@
       <c r="J241" s="11">
         <v>0.53</v>
       </c>
+      <c r="K241">
+        <v>0.75</v>
+      </c>
       <c r="M241" s="9"/>
     </row>
     <row r="242" spans="1:13">
@@ -10143,6 +10281,9 @@
       <c r="J243" s="11">
         <v>0.9</v>
       </c>
+      <c r="K243">
+        <v>0.69</v>
+      </c>
       <c r="M243" s="9"/>
     </row>
     <row r="244" spans="1:13">
@@ -10176,6 +10317,9 @@
       <c r="J244" s="11">
         <v>0.83</v>
       </c>
+      <c r="K244">
+        <v>0.65</v>
+      </c>
       <c r="M244" s="9"/>
     </row>
     <row r="245" spans="1:13">
@@ -10242,6 +10386,12 @@
       <c r="I246" s="11">
         <v>0</v>
       </c>
+      <c r="J246" s="11">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>0</v>
+      </c>
     </row>
     <row r="247" spans="1:13">
       <c r="A247" s="4" t="s">
@@ -10274,6 +10424,9 @@
       <c r="J247" s="11">
         <v>0.53</v>
       </c>
+      <c r="K247">
+        <v>0.75</v>
+      </c>
       <c r="M247" s="9"/>
     </row>
     <row r="248" spans="1:13">
@@ -10306,6 +10459,9 @@
       </c>
       <c r="J248" s="11">
         <v>0.93</v>
+      </c>
+      <c r="K248">
+        <v>0.77</v>
       </c>
       <c r="M248" s="9"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A31804-CBF5-5D49-994F-EB4340CAA981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C8D6A-6C9A-3945-B6D0-0D5EF64076EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2848,6 +2848,9 @@
       <c r="I22" s="10">
         <v>0.74</v>
       </c>
+      <c r="J22" s="10">
+        <v>0.8</v>
+      </c>
       <c r="K22">
         <v>0.67</v>
       </c>
@@ -5176,6 +5179,9 @@
       <c r="J92" s="10">
         <v>0.78</v>
       </c>
+      <c r="L92">
+        <v>0.44</v>
+      </c>
       <c r="M92" s="2"/>
     </row>
     <row r="93" spans="1:13">
@@ -5371,6 +5377,9 @@
       <c r="J98" s="10">
         <v>0.78</v>
       </c>
+      <c r="L98">
+        <v>0.44</v>
+      </c>
       <c r="M98" s="2"/>
     </row>
     <row r="99" spans="1:13">
@@ -5668,6 +5677,9 @@
       <c r="J107" s="10">
         <v>0.78</v>
       </c>
+      <c r="L107">
+        <v>0.44</v>
+      </c>
       <c r="M107" s="2"/>
     </row>
     <row r="108" spans="1:13">
@@ -5731,6 +5743,9 @@
       <c r="I109" s="10">
         <v>0.54</v>
       </c>
+      <c r="K109">
+        <v>0.6</v>
+      </c>
       <c r="M109" s="2"/>
     </row>
     <row r="110" spans="1:13">
@@ -6061,6 +6076,9 @@
       <c r="J119" s="10">
         <v>0.78</v>
       </c>
+      <c r="L119">
+        <v>0.44</v>
+      </c>
       <c r="M119" s="2"/>
     </row>
     <row r="120" spans="1:13">
@@ -6226,6 +6244,9 @@
       <c r="J124" s="10">
         <v>0.78</v>
       </c>
+      <c r="L124">
+        <v>0.44</v>
+      </c>
       <c r="M124" s="2"/>
     </row>
     <row r="125" spans="1:13">
@@ -7109,6 +7130,9 @@
       <c r="J151" s="10">
         <v>0.79</v>
       </c>
+      <c r="L151">
+        <v>0.81</v>
+      </c>
       <c r="M151" s="2"/>
     </row>
     <row r="152" spans="1:13">
@@ -7406,6 +7430,9 @@
       <c r="J160" s="10">
         <v>0.79</v>
       </c>
+      <c r="L160">
+        <v>0.81</v>
+      </c>
       <c r="M160" s="8"/>
     </row>
     <row r="161" spans="1:13">
@@ -7535,6 +7562,9 @@
       <c r="J164" s="10">
         <v>0.8</v>
       </c>
+      <c r="K164">
+        <v>0.6</v>
+      </c>
       <c r="M164" s="2"/>
     </row>
     <row r="165" spans="1:13">
@@ -7667,6 +7697,9 @@
       <c r="J168" s="10">
         <v>0.8</v>
       </c>
+      <c r="K168">
+        <v>0.6</v>
+      </c>
       <c r="M168" s="2"/>
     </row>
     <row r="169" spans="1:13">
@@ -7931,6 +7964,9 @@
       <c r="J176" s="10">
         <v>0.79</v>
       </c>
+      <c r="L176">
+        <v>0.81</v>
+      </c>
       <c r="M176" s="2"/>
     </row>
     <row r="177" spans="1:13">
@@ -7997,6 +8033,9 @@
       <c r="J178" s="10">
         <v>0.8</v>
       </c>
+      <c r="K178">
+        <v>0.6</v>
+      </c>
       <c r="M178" s="2"/>
     </row>
     <row r="179" spans="1:13">
@@ -8129,6 +8168,9 @@
       <c r="J182" s="10">
         <v>0.79</v>
       </c>
+      <c r="L182">
+        <v>0.81</v>
+      </c>
       <c r="M182" s="8"/>
     </row>
     <row r="183" spans="1:13">
@@ -8228,6 +8270,9 @@
       <c r="J185" s="10">
         <v>0.8</v>
       </c>
+      <c r="K185">
+        <v>0.6</v>
+      </c>
       <c r="M185" s="2"/>
     </row>
     <row r="186" spans="1:13">
@@ -8326,6 +8371,9 @@
       </c>
       <c r="J188" s="10">
         <v>0.79</v>
+      </c>
+      <c r="L188">
+        <v>0.81</v>
       </c>
       <c r="M188" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1C8D6A-6C9A-3945-B6D0-0D5EF64076EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B5CB37-F8A7-5D40-97B6-3846F4AEDF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2179,6 +2179,9 @@
       <c r="J2" s="10">
         <v>0.72</v>
       </c>
+      <c r="K2">
+        <v>0.5</v>
+      </c>
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:13">
@@ -2212,6 +2215,9 @@
       <c r="J3" s="10">
         <v>0.72</v>
       </c>
+      <c r="K3">
+        <v>0.5</v>
+      </c>
       <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13">
@@ -2281,6 +2287,9 @@
       <c r="J5" s="10">
         <v>0.79</v>
       </c>
+      <c r="K5">
+        <v>0.77</v>
+      </c>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -2314,6 +2323,9 @@
       <c r="J6" s="10">
         <v>0.79</v>
       </c>
+      <c r="K6">
+        <v>0.9</v>
+      </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13">
@@ -2383,6 +2395,9 @@
       <c r="J8" s="10">
         <v>0.79</v>
       </c>
+      <c r="K8">
+        <v>0.9</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13">
@@ -2416,6 +2431,9 @@
       <c r="J9" s="10">
         <v>0.79</v>
       </c>
+      <c r="K9">
+        <v>0.77</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
@@ -2449,6 +2467,9 @@
       <c r="J10" s="10">
         <v>0.79</v>
       </c>
+      <c r="K10">
+        <v>0.9</v>
+      </c>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13">
@@ -2584,6 +2605,9 @@
       <c r="J14" s="10">
         <v>0.86</v>
       </c>
+      <c r="K14">
+        <v>0.79</v>
+      </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
@@ -2617,6 +2641,9 @@
       <c r="J15" s="10">
         <v>0.87</v>
       </c>
+      <c r="K15">
+        <v>0.81</v>
+      </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
@@ -2752,6 +2779,9 @@
       <c r="J19" s="10">
         <v>0.64</v>
       </c>
+      <c r="K19">
+        <v>0.83</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
@@ -2785,6 +2815,9 @@
       <c r="J20" s="10">
         <v>0.87</v>
       </c>
+      <c r="K20">
+        <v>0.81</v>
+      </c>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
@@ -2818,6 +2851,9 @@
       <c r="J21" s="10">
         <v>0.83</v>
       </c>
+      <c r="K21">
+        <v>0.71</v>
+      </c>
       <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13">
@@ -2887,6 +2923,9 @@
       <c r="J23" s="10">
         <v>0.87</v>
       </c>
+      <c r="K23">
+        <v>0.81</v>
+      </c>
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
@@ -2920,6 +2959,9 @@
       <c r="J24" s="10">
         <v>0.64</v>
       </c>
+      <c r="K24">
+        <v>0.83</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
@@ -3022,6 +3064,9 @@
       <c r="J27" s="10">
         <v>0.79</v>
       </c>
+      <c r="K27">
+        <v>0.9</v>
+      </c>
       <c r="M27" s="2"/>
     </row>
     <row r="28" spans="1:13">
@@ -3088,6 +3133,9 @@
       <c r="J29" s="10">
         <v>0.87</v>
       </c>
+      <c r="K29">
+        <v>0.81</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -3220,6 +3268,9 @@
       <c r="J33" s="10">
         <v>0.64</v>
       </c>
+      <c r="K33">
+        <v>0.83</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
@@ -3253,6 +3304,9 @@
       <c r="J34" s="10">
         <v>0.78</v>
       </c>
+      <c r="K34">
+        <v>0.62</v>
+      </c>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="1:13">
@@ -3286,6 +3340,9 @@
       <c r="J35" s="10">
         <v>0.83</v>
       </c>
+      <c r="K35">
+        <v>0.71</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -3319,6 +3376,9 @@
       <c r="J36" s="10">
         <v>0.87</v>
       </c>
+      <c r="K36">
+        <v>0.81</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
@@ -3385,6 +3445,9 @@
       <c r="J38" s="10">
         <v>0.7</v>
       </c>
+      <c r="K38">
+        <v>0.67</v>
+      </c>
       <c r="M38" s="2"/>
     </row>
     <row r="39" spans="1:13">
@@ -3487,6 +3550,9 @@
       <c r="J41" s="10">
         <v>0.7</v>
       </c>
+      <c r="K41">
+        <v>0.67</v>
+      </c>
       <c r="M41" s="2"/>
     </row>
     <row r="42" spans="1:13">
@@ -3628,6 +3694,9 @@
       <c r="J45" s="10">
         <v>0.79</v>
       </c>
+      <c r="K45">
+        <v>0.9</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -3661,6 +3730,9 @@
       <c r="J46" s="10">
         <v>0.86</v>
       </c>
+      <c r="K46">
+        <v>0.79</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -3694,6 +3766,9 @@
       <c r="J47" s="10">
         <v>0.79</v>
       </c>
+      <c r="K47">
+        <v>0.77</v>
+      </c>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:13">
@@ -3829,6 +3904,9 @@
       <c r="J51" s="10">
         <v>0.86</v>
       </c>
+      <c r="K51">
+        <v>0.79</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13">
@@ -3862,6 +3940,9 @@
       <c r="J52" s="10">
         <v>0.79</v>
       </c>
+      <c r="K52">
+        <v>0.77</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13">
@@ -3994,6 +4075,9 @@
       <c r="J56" s="10">
         <v>0.86</v>
       </c>
+      <c r="K56">
+        <v>0.79</v>
+      </c>
       <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13">
@@ -4027,6 +4111,9 @@
       <c r="J57" s="10">
         <v>0.72</v>
       </c>
+      <c r="K57">
+        <v>0.5</v>
+      </c>
       <c r="M57" s="2"/>
     </row>
     <row r="58" spans="1:13">
@@ -4129,6 +4216,9 @@
       <c r="J60" s="10">
         <v>0.78</v>
       </c>
+      <c r="K60">
+        <v>0.62</v>
+      </c>
       <c r="M60" s="2"/>
     </row>
     <row r="61" spans="1:13">
@@ -4162,6 +4252,9 @@
       <c r="J61" s="10">
         <v>0.7</v>
       </c>
+      <c r="K61">
+        <v>0.67</v>
+      </c>
       <c r="M61" s="2"/>
     </row>
     <row r="62" spans="1:13">
@@ -4195,6 +4288,9 @@
       <c r="J62" s="10">
         <v>0.79</v>
       </c>
+      <c r="K62">
+        <v>0.77</v>
+      </c>
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
@@ -4228,6 +4324,9 @@
       <c r="J63" s="10">
         <v>0.64</v>
       </c>
+      <c r="K63">
+        <v>0.83</v>
+      </c>
       <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13">
@@ -4291,6 +4390,9 @@
       <c r="I65" s="10">
         <v>0</v>
       </c>
+      <c r="K65">
+        <v>0.83</v>
+      </c>
       <c r="M65" s="2"/>
     </row>
     <row r="66" spans="1:13">
@@ -4357,6 +4459,9 @@
       <c r="J67" s="10">
         <v>0.78</v>
       </c>
+      <c r="K67">
+        <v>0.62</v>
+      </c>
       <c r="M67" s="2"/>
     </row>
     <row r="68" spans="1:13">
@@ -4423,6 +4528,9 @@
       <c r="J69" s="10">
         <v>0.72</v>
       </c>
+      <c r="K69">
+        <v>0.5</v>
+      </c>
       <c r="M69" s="2"/>
     </row>
     <row r="70" spans="1:13">
@@ -4489,6 +4597,9 @@
       <c r="J71" s="10">
         <v>0.78</v>
       </c>
+      <c r="K71">
+        <v>0.62</v>
+      </c>
       <c r="M71" s="2"/>
     </row>
     <row r="72" spans="1:13">
@@ -4522,6 +4633,9 @@
       <c r="J72" s="10">
         <v>0.73</v>
       </c>
+      <c r="K72">
+        <v>0.79</v>
+      </c>
       <c r="M72" s="2"/>
     </row>
     <row r="73" spans="1:13">
@@ -4555,6 +4669,9 @@
       <c r="J73" s="10">
         <v>0.86</v>
       </c>
+      <c r="K73">
+        <v>0.79</v>
+      </c>
       <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:13">
@@ -4588,6 +4705,9 @@
       <c r="J74" s="10">
         <v>0.7</v>
       </c>
+      <c r="K74">
+        <v>0.67</v>
+      </c>
       <c r="M74" s="2"/>
     </row>
     <row r="75" spans="1:13">
@@ -4621,6 +4741,9 @@
       <c r="J75" s="10">
         <v>0.78</v>
       </c>
+      <c r="K75">
+        <v>0.62</v>
+      </c>
       <c r="M75" s="2"/>
     </row>
     <row r="76" spans="1:13">
@@ -4653,6 +4776,9 @@
       </c>
       <c r="J76" s="10">
         <v>0.83</v>
+      </c>
+      <c r="K76">
+        <v>0.71</v>
       </c>
       <c r="M76" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B5CB37-F8A7-5D40-97B6-3846F4AEDF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C2E83F-CF5D-2140-B331-1A7F177EEC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2503,6 +2503,9 @@
       <c r="J11" s="10">
         <v>0.76</v>
       </c>
+      <c r="K11">
+        <v>0.77</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13">
@@ -2536,6 +2539,9 @@
       <c r="J12" s="10">
         <v>0.76</v>
       </c>
+      <c r="K12">
+        <v>0.46</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13">
@@ -2713,6 +2719,9 @@
       <c r="J17" s="10">
         <v>0.76</v>
       </c>
+      <c r="K17">
+        <v>0.77</v>
+      </c>
       <c r="M17" s="2"/>
     </row>
     <row r="18" spans="1:13">
@@ -2746,6 +2755,9 @@
       <c r="J18" s="10">
         <v>0.8</v>
       </c>
+      <c r="K18">
+        <v>0.79</v>
+      </c>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13">
@@ -3031,6 +3043,9 @@
       <c r="J26" s="10">
         <v>0</v>
       </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
@@ -3100,6 +3115,9 @@
       <c r="J28" s="10">
         <v>0.8</v>
       </c>
+      <c r="K28">
+        <v>0.79</v>
+      </c>
       <c r="M28" s="2"/>
     </row>
     <row r="29" spans="1:13">
@@ -3169,6 +3187,9 @@
       <c r="J30" s="10">
         <v>0.76</v>
       </c>
+      <c r="K30">
+        <v>0.46</v>
+      </c>
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13">
@@ -3235,6 +3256,9 @@
       <c r="J32" s="10">
         <v>0.7</v>
       </c>
+      <c r="K32">
+        <v>0.5</v>
+      </c>
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13">
@@ -3412,6 +3436,9 @@
       <c r="J37" s="10">
         <v>0.8</v>
       </c>
+      <c r="K37">
+        <v>0.79</v>
+      </c>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13">
@@ -3802,6 +3829,9 @@
       <c r="J48" s="10">
         <v>0.76</v>
       </c>
+      <c r="K48">
+        <v>0.46</v>
+      </c>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13">
@@ -3835,6 +3865,9 @@
       <c r="J49" s="10">
         <v>0.76</v>
       </c>
+      <c r="K49">
+        <v>0.46</v>
+      </c>
       <c r="M49" s="2"/>
     </row>
     <row r="50" spans="1:13">
@@ -3976,6 +4009,9 @@
       <c r="J53" s="10">
         <v>0.76</v>
       </c>
+      <c r="K53">
+        <v>0.77</v>
+      </c>
       <c r="M53" s="2"/>
     </row>
     <row r="54" spans="1:13">
@@ -4009,6 +4045,9 @@
       <c r="J54" s="10">
         <v>0.76</v>
       </c>
+      <c r="K54">
+        <v>0.77</v>
+      </c>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13">
@@ -4042,6 +4081,9 @@
       <c r="J55" s="10">
         <v>0.7</v>
       </c>
+      <c r="K55">
+        <v>0.5</v>
+      </c>
       <c r="M55" s="2"/>
     </row>
     <row r="56" spans="1:13">
@@ -4183,6 +4225,9 @@
       <c r="J59" s="10">
         <v>0.7</v>
       </c>
+      <c r="K59">
+        <v>0.5</v>
+      </c>
       <c r="M59" s="2"/>
     </row>
     <row r="60" spans="1:13">
@@ -4360,6 +4405,9 @@
       <c r="J64" s="10">
         <v>0.76</v>
       </c>
+      <c r="K64">
+        <v>0.46</v>
+      </c>
       <c r="M64" s="2"/>
     </row>
     <row r="65" spans="1:13">
@@ -4390,6 +4438,9 @@
       <c r="I65" s="10">
         <v>0</v>
       </c>
+      <c r="J65" s="10">
+        <v>0.64</v>
+      </c>
       <c r="K65">
         <v>0.83</v>
       </c>
@@ -4426,6 +4477,9 @@
       <c r="J66" s="10">
         <v>0.76</v>
       </c>
+      <c r="K66">
+        <v>0.77</v>
+      </c>
       <c r="M66" s="2"/>
     </row>
     <row r="67" spans="1:13">
@@ -4495,6 +4549,9 @@
       <c r="J68" s="10">
         <v>0.8</v>
       </c>
+      <c r="K68">
+        <v>0.79</v>
+      </c>
       <c r="M68" s="2"/>
     </row>
     <row r="69" spans="1:13">
@@ -5470,6 +5527,9 @@
       <c r="J97" s="10">
         <v>0.7</v>
       </c>
+      <c r="K97">
+        <v>0.5</v>
+      </c>
       <c r="M97" s="8"/>
     </row>
     <row r="98" spans="1:13">
@@ -6403,6 +6463,12 @@
       <c r="I125" s="10">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J125" s="10">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0.5</v>
+      </c>
       <c r="M125" s="2"/>
     </row>
     <row r="126" spans="1:13">
@@ -6700,6 +6766,9 @@
       <c r="J134" s="10">
         <v>0.78</v>
       </c>
+      <c r="K134">
+        <v>0.85</v>
+      </c>
       <c r="M134" s="2"/>
     </row>
     <row r="135" spans="1:13">
@@ -6794,6 +6863,9 @@
       <c r="J137" s="10">
         <v>0.78</v>
       </c>
+      <c r="K137">
+        <v>0.85</v>
+      </c>
       <c r="M137" s="2"/>
     </row>
     <row r="138" spans="1:13">
@@ -6860,6 +6932,9 @@
       <c r="J139" s="10">
         <v>0.87</v>
       </c>
+      <c r="K139">
+        <v>0.83</v>
+      </c>
       <c r="M139" s="2"/>
     </row>
     <row r="140" spans="1:13">
@@ -7058,6 +7133,9 @@
       <c r="J145" s="10">
         <v>0.81</v>
       </c>
+      <c r="K145">
+        <v>0.63</v>
+      </c>
       <c r="M145" s="2"/>
     </row>
     <row r="146" spans="1:13">
@@ -7223,6 +7301,9 @@
       <c r="J150" s="10">
         <v>0.84</v>
       </c>
+      <c r="K150">
+        <v>0.83</v>
+      </c>
       <c r="M150" s="2"/>
     </row>
     <row r="151" spans="1:13">
@@ -7292,6 +7373,9 @@
       <c r="J152" s="10">
         <v>0.85</v>
       </c>
+      <c r="K152">
+        <v>0.79</v>
+      </c>
       <c r="M152" s="2"/>
     </row>
     <row r="153" spans="1:13">
@@ -7325,6 +7409,9 @@
       <c r="J153" s="10">
         <v>0.87</v>
       </c>
+      <c r="K153">
+        <v>0.83</v>
+      </c>
       <c r="M153" s="2"/>
     </row>
     <row r="154" spans="1:13">
@@ -7391,6 +7478,9 @@
       <c r="J155" s="10">
         <v>0.78</v>
       </c>
+      <c r="K155">
+        <v>0.85</v>
+      </c>
       <c r="M155" s="2"/>
     </row>
     <row r="156" spans="1:13">
@@ -7457,6 +7547,9 @@
       <c r="J157" s="10">
         <v>0.74</v>
       </c>
+      <c r="K157">
+        <v>0.73</v>
+      </c>
       <c r="M157" s="8"/>
     </row>
     <row r="158" spans="1:13">
@@ -7655,6 +7748,9 @@
       <c r="J163" s="10">
         <v>0.81</v>
       </c>
+      <c r="K163">
+        <v>0.63</v>
+      </c>
       <c r="M163" s="2"/>
     </row>
     <row r="164" spans="1:13">
@@ -7757,6 +7853,9 @@
       <c r="J166" s="10">
         <v>0.87</v>
       </c>
+      <c r="K166">
+        <v>0.83</v>
+      </c>
       <c r="M166" s="2"/>
     </row>
     <row r="167" spans="1:13">
@@ -7790,6 +7889,9 @@
       <c r="J167" s="10">
         <v>0.87</v>
       </c>
+      <c r="K167">
+        <v>0.83</v>
+      </c>
       <c r="M167" s="2"/>
     </row>
     <row r="168" spans="1:13">
@@ -7859,6 +7961,9 @@
       <c r="J169" s="10">
         <v>0.78</v>
       </c>
+      <c r="K169">
+        <v>0.85</v>
+      </c>
       <c r="M169" s="8"/>
     </row>
     <row r="170" spans="1:13">
@@ -7892,6 +7997,9 @@
       <c r="J170" s="10">
         <v>0.78</v>
       </c>
+      <c r="K170">
+        <v>0.85</v>
+      </c>
       <c r="M170" s="8"/>
     </row>
     <row r="171" spans="1:13">
@@ -7991,6 +8099,9 @@
       <c r="J173" s="10">
         <v>0.84</v>
       </c>
+      <c r="K173">
+        <v>0.83</v>
+      </c>
       <c r="M173" s="2"/>
     </row>
     <row r="174" spans="1:13">
@@ -8057,6 +8168,9 @@
       <c r="J175" s="10">
         <v>0.87</v>
       </c>
+      <c r="K175">
+        <v>0.83</v>
+      </c>
       <c r="M175" s="2"/>
     </row>
     <row r="176" spans="1:13">
@@ -8126,6 +8240,9 @@
       <c r="J177" s="10">
         <v>0</v>
       </c>
+      <c r="K177">
+        <v>0.83</v>
+      </c>
       <c r="M177" s="2"/>
     </row>
     <row r="178" spans="1:13">
@@ -8261,6 +8378,9 @@
       <c r="J181" s="10">
         <v>0.84</v>
       </c>
+      <c r="K181">
+        <v>0.83</v>
+      </c>
       <c r="M181" s="2"/>
     </row>
     <row r="182" spans="1:13">
@@ -8330,6 +8450,9 @@
       <c r="J183" s="10">
         <v>0.85</v>
       </c>
+      <c r="K183">
+        <v>0.79</v>
+      </c>
       <c r="M183" s="2"/>
     </row>
     <row r="184" spans="1:13">
@@ -8432,6 +8555,9 @@
       <c r="J186" s="10">
         <v>0.84</v>
       </c>
+      <c r="K186">
+        <v>0.83</v>
+      </c>
       <c r="M186" s="2"/>
     </row>
     <row r="187" spans="1:13">
@@ -8567,6 +8693,9 @@
       <c r="J190" s="10">
         <v>0.85</v>
       </c>
+      <c r="K190">
+        <v>0.79</v>
+      </c>
       <c r="M190" s="2"/>
     </row>
     <row r="191" spans="1:13">
@@ -8600,6 +8729,9 @@
       <c r="J191" s="10">
         <v>0.85</v>
       </c>
+      <c r="K191">
+        <v>0.79</v>
+      </c>
       <c r="M191" s="2"/>
     </row>
     <row r="192" spans="1:13">
@@ -8632,6 +8764,9 @@
       </c>
       <c r="J192" s="10">
         <v>0.85</v>
+      </c>
+      <c r="K192">
+        <v>0.79</v>
       </c>
       <c r="M192" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C2E83F-CF5D-2140-B331-1A7F177EEC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5E6B15-C56E-A742-8ED2-320A60591EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -6700,6 +6700,9 @@
       <c r="J132" s="10">
         <v>0.8</v>
       </c>
+      <c r="K132">
+        <v>0.77</v>
+      </c>
       <c r="M132" s="2"/>
     </row>
     <row r="133" spans="1:13">
@@ -6733,6 +6736,9 @@
       <c r="J133" s="10">
         <v>0.83</v>
       </c>
+      <c r="K133">
+        <v>0.85</v>
+      </c>
       <c r="M133" s="2"/>
     </row>
     <row r="134" spans="1:13">
@@ -6968,6 +6974,9 @@
       <c r="J140" s="10">
         <v>0.83</v>
       </c>
+      <c r="K140">
+        <v>0.87</v>
+      </c>
       <c r="M140" s="2"/>
     </row>
     <row r="141" spans="1:13">
@@ -7034,6 +7043,9 @@
       <c r="J142" s="10">
         <v>0.8</v>
       </c>
+      <c r="K142">
+        <v>0.77</v>
+      </c>
       <c r="M142" s="2"/>
     </row>
     <row r="143" spans="1:13">
@@ -7067,6 +7079,9 @@
       <c r="J143" s="10">
         <v>0.8</v>
       </c>
+      <c r="K143">
+        <v>0.5</v>
+      </c>
       <c r="M143" s="2"/>
     </row>
     <row r="144" spans="1:13">
@@ -7100,6 +7115,9 @@
       <c r="J144" s="10">
         <v>0.8</v>
       </c>
+      <c r="K144">
+        <v>0.5</v>
+      </c>
       <c r="M144" s="2"/>
     </row>
     <row r="145" spans="1:13">
@@ -7169,6 +7187,9 @@
       <c r="J146" s="10">
         <v>0.8</v>
       </c>
+      <c r="K146">
+        <v>0.5</v>
+      </c>
       <c r="M146" s="2"/>
     </row>
     <row r="147" spans="1:13">
@@ -7202,6 +7223,9 @@
       <c r="J147" s="10">
         <v>0.83</v>
       </c>
+      <c r="K147">
+        <v>0.85</v>
+      </c>
       <c r="M147" s="2"/>
     </row>
     <row r="148" spans="1:13">
@@ -7235,6 +7259,9 @@
       <c r="J148" s="10">
         <v>0.83</v>
       </c>
+      <c r="K148">
+        <v>0.85</v>
+      </c>
       <c r="M148" s="2"/>
     </row>
     <row r="149" spans="1:13">
@@ -7337,6 +7364,9 @@
       <c r="J151" s="10">
         <v>0.79</v>
       </c>
+      <c r="K151">
+        <v>0.73</v>
+      </c>
       <c r="L151">
         <v>0.81</v>
       </c>
@@ -7445,6 +7475,9 @@
       <c r="J154" s="10">
         <v>0.83</v>
       </c>
+      <c r="K154">
+        <v>0.85</v>
+      </c>
       <c r="M154" s="2"/>
     </row>
     <row r="155" spans="1:13">
@@ -7514,6 +7547,9 @@
       <c r="J156" s="10">
         <v>0.8</v>
       </c>
+      <c r="K156">
+        <v>0.5</v>
+      </c>
       <c r="M156" s="2"/>
     </row>
     <row r="157" spans="1:13">
@@ -7583,6 +7619,9 @@
       <c r="J158" s="10">
         <v>0.83</v>
       </c>
+      <c r="K158">
+        <v>0.87</v>
+      </c>
       <c r="M158" s="2"/>
     </row>
     <row r="159" spans="1:13">
@@ -7649,6 +7688,9 @@
       <c r="J160" s="10">
         <v>0.79</v>
       </c>
+      <c r="K160">
+        <v>0.73</v>
+      </c>
       <c r="L160">
         <v>0.81</v>
       </c>
@@ -7685,6 +7727,9 @@
       <c r="J161" s="10">
         <v>0.83</v>
       </c>
+      <c r="K161">
+        <v>0.87</v>
+      </c>
       <c r="M161" s="2"/>
     </row>
     <row r="162" spans="1:13">
@@ -8204,6 +8249,9 @@
       <c r="J176" s="10">
         <v>0.79</v>
       </c>
+      <c r="K176">
+        <v>0.73</v>
+      </c>
       <c r="L176">
         <v>0.81</v>
       </c>
@@ -8312,6 +8360,9 @@
       <c r="J179" s="10">
         <v>0.83</v>
       </c>
+      <c r="K179">
+        <v>0.87</v>
+      </c>
       <c r="M179" s="2"/>
     </row>
     <row r="180" spans="1:13">
@@ -8414,6 +8465,9 @@
       <c r="J182" s="10">
         <v>0.79</v>
       </c>
+      <c r="K182">
+        <v>0.73</v>
+      </c>
       <c r="L182">
         <v>0.81</v>
       </c>
@@ -8486,6 +8540,9 @@
       <c r="J184" s="10">
         <v>0.83</v>
       </c>
+      <c r="K184">
+        <v>0.87</v>
+      </c>
       <c r="M184" s="2"/>
     </row>
     <row r="185" spans="1:13">
@@ -8591,6 +8648,9 @@
       <c r="J187" s="10">
         <v>0.8</v>
       </c>
+      <c r="K187">
+        <v>0.77</v>
+      </c>
       <c r="M187" s="2"/>
     </row>
     <row r="188" spans="1:13">
@@ -8623,6 +8683,9 @@
       </c>
       <c r="J188" s="10">
         <v>0.79</v>
+      </c>
+      <c r="K188">
+        <v>0.73</v>
       </c>
       <c r="L188">
         <v>0.81</v>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5E6B15-C56E-A742-8ED2-320A60591EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6A8858-B498-384A-96A5-A0EDED76CE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3223,6 +3223,9 @@
       <c r="J31" s="10">
         <v>0.8</v>
       </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13">
@@ -3544,6 +3547,9 @@
       <c r="J40" s="10">
         <v>0</v>
       </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
@@ -4621,6 +4627,9 @@
       <c r="J70" s="10">
         <v>0.72</v>
       </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
       <c r="M70" s="2"/>
     </row>
     <row r="71" spans="1:13">
@@ -4870,6 +4879,9 @@
       <c r="J77" s="10">
         <v>0.78</v>
       </c>
+      <c r="K77">
+        <v>0.6</v>
+      </c>
       <c r="M77" s="2"/>
     </row>
     <row r="78" spans="1:13">
@@ -4903,6 +4915,9 @@
       <c r="J78" s="10">
         <v>0.7</v>
       </c>
+      <c r="K78">
+        <v>0.33</v>
+      </c>
       <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13">
@@ -4936,6 +4951,9 @@
       <c r="J79" s="10">
         <v>0.86</v>
       </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
       <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13">
@@ -4969,6 +4987,9 @@
       <c r="J80" s="10">
         <v>0.72</v>
       </c>
+      <c r="K80">
+        <v>0.79</v>
+      </c>
       <c r="M80" s="2"/>
     </row>
     <row r="81" spans="1:13">
@@ -4999,6 +5020,9 @@
       <c r="I81" s="10">
         <v>0.54</v>
       </c>
+      <c r="K81">
+        <v>0.52</v>
+      </c>
       <c r="M81" s="8"/>
     </row>
     <row r="82" spans="1:13">
@@ -5032,6 +5056,9 @@
       <c r="J82" s="10">
         <v>0.78</v>
       </c>
+      <c r="K82">
+        <v>0.6</v>
+      </c>
       <c r="M82" s="2"/>
     </row>
     <row r="83" spans="1:13">
@@ -5065,6 +5092,9 @@
       <c r="J83" s="10">
         <v>0.78</v>
       </c>
+      <c r="K83">
+        <v>0.83</v>
+      </c>
       <c r="M83" s="2"/>
     </row>
     <row r="84" spans="1:13">
@@ -5098,6 +5128,9 @@
       <c r="J84" s="10">
         <v>0.88</v>
       </c>
+      <c r="K84">
+        <v>0.44</v>
+      </c>
       <c r="M84" s="8"/>
     </row>
     <row r="85" spans="1:13">
@@ -5131,6 +5164,9 @@
       <c r="J85" s="10">
         <v>0.88</v>
       </c>
+      <c r="K85">
+        <v>0.44</v>
+      </c>
       <c r="M85" s="2"/>
     </row>
     <row r="86" spans="1:13">
@@ -5164,6 +5200,9 @@
       <c r="J86" s="10">
         <v>0.78</v>
       </c>
+      <c r="K86">
+        <v>0.6</v>
+      </c>
       <c r="M86" s="2"/>
     </row>
     <row r="87" spans="1:13">
@@ -5197,6 +5236,9 @@
       <c r="J87" s="10">
         <v>0.94</v>
       </c>
+      <c r="K87">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M87" s="2"/>
     </row>
     <row r="88" spans="1:13">
@@ -5230,6 +5272,9 @@
       <c r="J88" s="10">
         <v>0.86</v>
       </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
       <c r="M88" s="8"/>
     </row>
     <row r="89" spans="1:13">
@@ -5263,6 +5308,9 @@
       <c r="J89" s="10">
         <v>0.7</v>
       </c>
+      <c r="K89">
+        <v>0.33</v>
+      </c>
       <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:13">
@@ -5296,6 +5344,9 @@
       <c r="J90" s="10">
         <v>0.86</v>
       </c>
+      <c r="K90">
+        <v>0.77</v>
+      </c>
       <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:13">
@@ -5329,6 +5380,9 @@
       <c r="J91" s="10">
         <v>0.88</v>
       </c>
+      <c r="K91">
+        <v>0.44</v>
+      </c>
       <c r="M91" s="2"/>
     </row>
     <row r="92" spans="1:13">
@@ -5362,6 +5416,9 @@
       <c r="J92" s="10">
         <v>0.78</v>
       </c>
+      <c r="K92">
+        <v>0.5</v>
+      </c>
       <c r="L92">
         <v>0.44</v>
       </c>
@@ -5395,6 +5452,12 @@
       <c r="I93" s="10">
         <v>0</v>
       </c>
+      <c r="J93" s="10">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
       <c r="M93" s="2"/>
     </row>
     <row r="94" spans="1:13">
@@ -5428,6 +5491,9 @@
       <c r="J94" s="10">
         <v>0.86</v>
       </c>
+      <c r="K94">
+        <v>0.77</v>
+      </c>
       <c r="M94" s="2"/>
     </row>
     <row r="95" spans="1:13">
@@ -5461,6 +5527,9 @@
       <c r="J95" s="10">
         <v>0.86</v>
       </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
       <c r="M95" s="2"/>
     </row>
     <row r="96" spans="1:13">
@@ -5494,6 +5563,9 @@
       <c r="J96" s="10">
         <v>0.88</v>
       </c>
+      <c r="K96">
+        <v>0.44</v>
+      </c>
       <c r="M96" s="8"/>
     </row>
     <row r="97" spans="1:13">
@@ -5563,6 +5635,9 @@
       <c r="J98" s="10">
         <v>0.78</v>
       </c>
+      <c r="K98">
+        <v>0.5</v>
+      </c>
       <c r="L98">
         <v>0.44</v>
       </c>
@@ -5599,6 +5674,9 @@
       <c r="J99" s="10">
         <v>0.86</v>
       </c>
+      <c r="K99">
+        <v>0.77</v>
+      </c>
       <c r="M99" s="2"/>
     </row>
     <row r="100" spans="1:13">
@@ -5668,6 +5746,9 @@
       <c r="J101" s="10">
         <v>0.86</v>
       </c>
+      <c r="K101">
+        <v>0.77</v>
+      </c>
       <c r="M101" s="2"/>
     </row>
     <row r="102" spans="1:13">
@@ -5701,6 +5782,9 @@
       <c r="J102" s="10">
         <v>0.72</v>
       </c>
+      <c r="K102">
+        <v>0.79</v>
+      </c>
       <c r="M102" s="2"/>
     </row>
     <row r="103" spans="1:13">
@@ -5734,6 +5818,9 @@
       <c r="J103" s="10">
         <v>0.7</v>
       </c>
+      <c r="K103">
+        <v>0.33</v>
+      </c>
       <c r="M103" s="8"/>
     </row>
     <row r="104" spans="1:13">
@@ -5767,6 +5854,9 @@
       <c r="J104" s="10">
         <v>0.78</v>
       </c>
+      <c r="K104">
+        <v>0.6</v>
+      </c>
       <c r="M104" s="2"/>
     </row>
     <row r="105" spans="1:13">
@@ -5800,6 +5890,9 @@
       <c r="J105" s="10">
         <v>0.78</v>
       </c>
+      <c r="K105">
+        <v>0.83</v>
+      </c>
       <c r="M105" s="8"/>
     </row>
     <row r="106" spans="1:13">
@@ -5830,6 +5923,12 @@
       <c r="I106" s="10">
         <v>0.2</v>
       </c>
+      <c r="J106" s="10">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0.52</v>
+      </c>
       <c r="M106" s="2"/>
     </row>
     <row r="107" spans="1:13">
@@ -5863,6 +5962,9 @@
       <c r="J107" s="10">
         <v>0.78</v>
       </c>
+      <c r="K107">
+        <v>0.5</v>
+      </c>
       <c r="L107">
         <v>0.44</v>
       </c>
@@ -5899,6 +6001,9 @@
       <c r="J108" s="10">
         <v>0.78</v>
       </c>
+      <c r="K108">
+        <v>0.83</v>
+      </c>
       <c r="M108" s="2"/>
     </row>
     <row r="109" spans="1:13">
@@ -5965,6 +6070,9 @@
       <c r="J110" s="10">
         <v>0.86</v>
       </c>
+      <c r="K110">
+        <v>0.85</v>
+      </c>
       <c r="M110" s="2"/>
     </row>
     <row r="111" spans="1:13">
@@ -5998,6 +6106,9 @@
       <c r="J111" s="10">
         <v>0.72</v>
       </c>
+      <c r="K111">
+        <v>0.79</v>
+      </c>
       <c r="M111" s="2"/>
     </row>
     <row r="112" spans="1:13">
@@ -6031,6 +6142,9 @@
       <c r="J112" s="10">
         <v>0.78</v>
       </c>
+      <c r="K112">
+        <v>0.83</v>
+      </c>
       <c r="M112" s="8"/>
     </row>
     <row r="113" spans="1:13">
@@ -6064,6 +6178,9 @@
       <c r="J113" s="10">
         <v>0.72</v>
       </c>
+      <c r="K113">
+        <v>0.79</v>
+      </c>
       <c r="M113" s="2"/>
     </row>
     <row r="114" spans="1:13">
@@ -6097,6 +6214,9 @@
       <c r="J114" s="10">
         <v>0.94</v>
       </c>
+      <c r="K114">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M114" s="2"/>
     </row>
     <row r="115" spans="1:13">
@@ -6130,6 +6250,9 @@
       <c r="J115" s="10">
         <v>0.94</v>
       </c>
+      <c r="K115">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M115" s="2"/>
     </row>
     <row r="116" spans="1:13">
@@ -6163,6 +6286,9 @@
       <c r="J116" s="10">
         <v>0.86</v>
       </c>
+      <c r="K116">
+        <v>0.85</v>
+      </c>
       <c r="M116" s="2"/>
     </row>
     <row r="117" spans="1:13">
@@ -6196,6 +6322,9 @@
       <c r="J117" s="10">
         <v>0.88</v>
       </c>
+      <c r="K117">
+        <v>0.44</v>
+      </c>
       <c r="M117" s="2"/>
     </row>
     <row r="118" spans="1:13">
@@ -6229,6 +6358,9 @@
       <c r="J118" s="10">
         <v>0.7</v>
       </c>
+      <c r="K118">
+        <v>0.33</v>
+      </c>
       <c r="M118" s="2"/>
     </row>
     <row r="119" spans="1:13">
@@ -6262,6 +6394,9 @@
       <c r="J119" s="10">
         <v>0.78</v>
       </c>
+      <c r="K119">
+        <v>0.5</v>
+      </c>
       <c r="L119">
         <v>0.44</v>
       </c>
@@ -6298,6 +6433,9 @@
       <c r="J120" s="10">
         <v>0.72</v>
       </c>
+      <c r="K120">
+        <v>0.79</v>
+      </c>
       <c r="M120" s="2"/>
     </row>
     <row r="121" spans="1:13">
@@ -6331,6 +6469,9 @@
       <c r="J121" s="10">
         <v>0.86</v>
       </c>
+      <c r="K121">
+        <v>0.85</v>
+      </c>
       <c r="M121" s="2"/>
     </row>
     <row r="122" spans="1:13">
@@ -6364,6 +6505,9 @@
       <c r="J122" s="10">
         <v>0.78</v>
       </c>
+      <c r="K122">
+        <v>0.6</v>
+      </c>
       <c r="M122" s="2"/>
     </row>
     <row r="123" spans="1:13">
@@ -6397,6 +6541,9 @@
       <c r="J123" s="10">
         <v>0.86</v>
       </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
       <c r="M123" s="2"/>
     </row>
     <row r="124" spans="1:13">
@@ -6430,6 +6577,9 @@
       <c r="J124" s="10">
         <v>0.78</v>
       </c>
+      <c r="K124">
+        <v>0.5</v>
+      </c>
       <c r="L124">
         <v>0.44</v>
       </c>
@@ -6502,6 +6652,9 @@
       <c r="J126" s="10">
         <v>0.94</v>
       </c>
+      <c r="K126">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M126" s="2"/>
     </row>
     <row r="127" spans="1:13">
@@ -6535,6 +6688,9 @@
       <c r="J127" s="10">
         <v>0.86</v>
       </c>
+      <c r="K127">
+        <v>0.85</v>
+      </c>
       <c r="M127" s="2"/>
     </row>
     <row r="128" spans="1:13">
@@ -6568,6 +6724,9 @@
       <c r="J128" s="10">
         <v>0.86</v>
       </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
       <c r="M128" s="2"/>
     </row>
     <row r="129" spans="1:13">
@@ -6601,6 +6760,9 @@
       <c r="J129" s="10">
         <v>0.78</v>
       </c>
+      <c r="K129">
+        <v>0.83</v>
+      </c>
       <c r="M129" s="2"/>
     </row>
     <row r="130" spans="1:13">
@@ -6634,6 +6796,9 @@
       <c r="J130" s="10">
         <v>0.94</v>
       </c>
+      <c r="K130">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M130" s="2"/>
     </row>
     <row r="131" spans="1:13">
@@ -6667,6 +6832,9 @@
       <c r="J131" s="10">
         <v>0.86</v>
       </c>
+      <c r="K131">
+        <v>0.85</v>
+      </c>
       <c r="M131" s="2"/>
     </row>
     <row r="132" spans="1:13">
@@ -6808,6 +6976,9 @@
       <c r="J135" s="10">
         <v>0.73</v>
       </c>
+      <c r="K135">
+        <v>0.85</v>
+      </c>
       <c r="M135" s="2"/>
     </row>
     <row r="136" spans="1:13">
@@ -6836,6 +7007,12 @@
       <c r="I136" s="10">
         <v>0.24</v>
       </c>
+      <c r="J136" s="10">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0.79</v>
+      </c>
       <c r="M136" s="8"/>
     </row>
     <row r="137" spans="1:13">
@@ -6905,6 +7082,9 @@
       <c r="J138" s="10">
         <v>0.7</v>
       </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
       <c r="M138" s="2"/>
     </row>
     <row r="139" spans="1:13">
@@ -7010,6 +7190,9 @@
       <c r="J141" s="10">
         <v>0.7</v>
       </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
       <c r="M141" s="2"/>
     </row>
     <row r="142" spans="1:13">
@@ -7295,6 +7478,9 @@
       <c r="J149" s="10">
         <v>0.83</v>
       </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
       <c r="M149" s="2"/>
     </row>
     <row r="150" spans="1:13">
@@ -7655,6 +7841,9 @@
       <c r="J159" s="10">
         <v>0.73</v>
       </c>
+      <c r="K159">
+        <v>0.85</v>
+      </c>
       <c r="M159" s="2"/>
     </row>
     <row r="160" spans="1:13">
@@ -7760,6 +7949,12 @@
       <c r="I162" s="10">
         <v>0.46</v>
       </c>
+      <c r="J162" s="10">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
       <c r="M162" s="8"/>
     </row>
     <row r="163" spans="1:13">
@@ -8111,6 +8306,9 @@
       <c r="J172" s="10">
         <v>0.73</v>
       </c>
+      <c r="K172">
+        <v>0.85</v>
+      </c>
       <c r="M172" s="8"/>
     </row>
     <row r="173" spans="1:13">
@@ -8396,6 +8594,9 @@
       <c r="J180" s="10">
         <v>0.73</v>
       </c>
+      <c r="K180">
+        <v>0.85</v>
+      </c>
       <c r="M180" s="2"/>
     </row>
     <row r="181" spans="1:13">
@@ -8991,14 +9192,14 @@
         <v>0.83</v>
       </c>
       <c r="K196">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L196">
         <v>0</v>
       </c>
       <c r="M196" s="15">
         <f t="shared" si="0"/>
-        <v>0.67</v>
+        <v>0.7945000000000001</v>
       </c>
     </row>
     <row r="197" spans="1:13">
@@ -9369,14 +9570,14 @@
         <v>0.83</v>
       </c>
       <c r="K205">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L205">
         <v>0</v>
       </c>
       <c r="M205" s="15">
         <f t="shared" si="0"/>
-        <v>0.57999999999999996</v>
+        <v>0.7044999999999999</v>
       </c>
     </row>
     <row r="206" spans="1:13">
@@ -9705,14 +9906,14 @@
         <v>0.83</v>
       </c>
       <c r="K213">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L213">
         <v>0</v>
       </c>
       <c r="M213" s="15">
         <f t="shared" si="0"/>
-        <v>0.66749999999999987</v>
+        <v>0.79199999999999993</v>
       </c>
     </row>
     <row r="214" spans="1:13">
@@ -10035,6 +10236,9 @@
         <v>0.75</v>
       </c>
       <c r="I221" s="10">
+        <v>0</v>
+      </c>
+      <c r="J221" s="10">
         <v>0</v>
       </c>
       <c r="K221">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6A8858-B498-384A-96A5-A0EDED76CE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCFB8DF5-D7FA-9D4B-8415-BFD9FEFE287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2254,6 +2254,9 @@
       <c r="K4">
         <v>0.75</v>
       </c>
+      <c r="L4">
+        <v>0.68</v>
+      </c>
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:13">
@@ -2290,6 +2293,9 @@
       <c r="K5">
         <v>0.77</v>
       </c>
+      <c r="L5">
+        <v>0.45</v>
+      </c>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -2362,6 +2368,9 @@
       <c r="K7">
         <v>0.75</v>
       </c>
+      <c r="L7">
+        <v>0.68</v>
+      </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13">
@@ -2434,6 +2443,9 @@
       <c r="K9">
         <v>0.77</v>
       </c>
+      <c r="L9">
+        <v>0.45</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10" spans="1:13">
@@ -2578,6 +2590,9 @@
       <c r="K13">
         <v>0.75</v>
       </c>
+      <c r="L13">
+        <v>0.68</v>
+      </c>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13">
@@ -2614,6 +2629,9 @@
       <c r="K14">
         <v>0.79</v>
       </c>
+      <c r="L14">
+        <v>0.6</v>
+      </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13">
@@ -2650,6 +2668,9 @@
       <c r="K15">
         <v>0.81</v>
       </c>
+      <c r="L15">
+        <v>0.61</v>
+      </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13">
@@ -2794,6 +2815,9 @@
       <c r="K19">
         <v>0.83</v>
       </c>
+      <c r="L19">
+        <v>0.49</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13">
@@ -2830,6 +2854,9 @@
       <c r="K20">
         <v>0.81</v>
       </c>
+      <c r="L20">
+        <v>0.61</v>
+      </c>
       <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13">
@@ -2938,6 +2965,9 @@
       <c r="K23">
         <v>0.81</v>
       </c>
+      <c r="L23">
+        <v>0.61</v>
+      </c>
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
@@ -2974,6 +3004,9 @@
       <c r="K24">
         <v>0.83</v>
       </c>
+      <c r="L24">
+        <v>0.49</v>
+      </c>
       <c r="M24" s="2"/>
     </row>
     <row r="25" spans="1:13">
@@ -3046,6 +3079,9 @@
       <c r="K26">
         <v>0</v>
       </c>
+      <c r="L26">
+        <v>0.63</v>
+      </c>
       <c r="M26" s="2"/>
     </row>
     <row r="27" spans="1:13">
@@ -3154,6 +3190,9 @@
       <c r="K29">
         <v>0.81</v>
       </c>
+      <c r="L29">
+        <v>0.61</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -3298,6 +3337,9 @@
       <c r="K33">
         <v>0.83</v>
       </c>
+      <c r="L33">
+        <v>0.49</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13">
@@ -3334,6 +3376,9 @@
       <c r="K34">
         <v>0.62</v>
       </c>
+      <c r="L34">
+        <v>0.41</v>
+      </c>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="1:13">
@@ -3406,6 +3451,9 @@
       <c r="K36">
         <v>0.81</v>
       </c>
+      <c r="L36">
+        <v>0.61</v>
+      </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13">
@@ -3514,6 +3562,9 @@
       <c r="K39">
         <v>0.75</v>
       </c>
+      <c r="L39">
+        <v>0.68</v>
+      </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13">
@@ -3550,6 +3601,9 @@
       <c r="K40">
         <v>0</v>
       </c>
+      <c r="L40">
+        <v>0.63</v>
+      </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" spans="1:13">
@@ -3658,6 +3712,9 @@
       <c r="K43">
         <v>0.81</v>
       </c>
+      <c r="L43">
+        <v>0.45</v>
+      </c>
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13">
@@ -3694,6 +3751,9 @@
       <c r="K44">
         <v>0.75</v>
       </c>
+      <c r="L44">
+        <v>0.68</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13">
@@ -3766,6 +3826,9 @@
       <c r="K46">
         <v>0.79</v>
       </c>
+      <c r="L46">
+        <v>0.6</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -3802,6 +3865,9 @@
       <c r="K47">
         <v>0.77</v>
       </c>
+      <c r="L47">
+        <v>0.45</v>
+      </c>
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:13">
@@ -3910,6 +3976,9 @@
       <c r="K50">
         <v>0.81</v>
       </c>
+      <c r="L50">
+        <v>0.45</v>
+      </c>
       <c r="M50" s="2"/>
     </row>
     <row r="51" spans="1:13">
@@ -3946,6 +4015,9 @@
       <c r="K51">
         <v>0.79</v>
       </c>
+      <c r="L51">
+        <v>0.6</v>
+      </c>
       <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13">
@@ -3982,6 +4054,9 @@
       <c r="K52">
         <v>0.77</v>
       </c>
+      <c r="L52">
+        <v>0.45</v>
+      </c>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13">
@@ -4126,6 +4201,9 @@
       <c r="K56">
         <v>0.79</v>
       </c>
+      <c r="L56">
+        <v>0.6</v>
+      </c>
       <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13">
@@ -4198,6 +4276,9 @@
       <c r="K58">
         <v>0.81</v>
       </c>
+      <c r="L58">
+        <v>0.45</v>
+      </c>
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:13">
@@ -4270,6 +4351,9 @@
       <c r="K60">
         <v>0.62</v>
       </c>
+      <c r="L60">
+        <v>0.41</v>
+      </c>
       <c r="M60" s="2"/>
     </row>
     <row r="61" spans="1:13">
@@ -4342,6 +4426,9 @@
       <c r="K62">
         <v>0.77</v>
       </c>
+      <c r="L62">
+        <v>0.45</v>
+      </c>
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13">
@@ -4378,6 +4465,9 @@
       <c r="K63">
         <v>0.83</v>
       </c>
+      <c r="L63">
+        <v>0.49</v>
+      </c>
       <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13">
@@ -4450,6 +4540,9 @@
       <c r="K65">
         <v>0.83</v>
       </c>
+      <c r="L65">
+        <v>0.49</v>
+      </c>
       <c r="M65" s="2"/>
     </row>
     <row r="66" spans="1:13">
@@ -4522,6 +4615,9 @@
       <c r="K67">
         <v>0.62</v>
       </c>
+      <c r="L67">
+        <v>0.41</v>
+      </c>
       <c r="M67" s="2"/>
     </row>
     <row r="68" spans="1:13">
@@ -4666,6 +4762,9 @@
       <c r="K71">
         <v>0.62</v>
       </c>
+      <c r="L71">
+        <v>0.41</v>
+      </c>
       <c r="M71" s="2"/>
     </row>
     <row r="72" spans="1:13">
@@ -4702,6 +4801,9 @@
       <c r="K72">
         <v>0.79</v>
       </c>
+      <c r="L72">
+        <v>0.68</v>
+      </c>
       <c r="M72" s="2"/>
     </row>
     <row r="73" spans="1:13">
@@ -4738,6 +4840,9 @@
       <c r="K73">
         <v>0.79</v>
       </c>
+      <c r="L73">
+        <v>0.6</v>
+      </c>
       <c r="M73" s="2"/>
     </row>
     <row r="74" spans="1:13">
@@ -4809,6 +4914,9 @@
       </c>
       <c r="K75">
         <v>0.62</v>
+      </c>
+      <c r="L75">
+        <v>0.41</v>
       </c>
       <c r="M75" s="2"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345B322C-BEDA-1C47-880A-E617F80D5FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899B870C-DA03-EB42-BFA0-13A34DD2FB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4867,7 +4867,7 @@
         <v>0.03</v>
       </c>
       <c r="M66" s="12">
-        <f t="shared" ref="M66:M76" si="1">(((LARGE(D66:F66,1)+LARGE(D66:F66,2))*0.2/2+(LARGE(G66:I66,1)+LARGE(G66:I66,2))*0.5/2+(LARGE(J66:L66,1)+LARGE(J66:L66,2))*0.3/2))</f>
+        <f t="shared" ref="M66:M129" si="1">(((LARGE(D66:F66,1)+LARGE(D66:F66,2))*0.2/2+(LARGE(G66:I66,1)+LARGE(G66:I66,2))*0.5/2+(LARGE(J66:L66,1)+LARGE(J66:L66,2))*0.3/2))</f>
         <v>0.67620512820512824</v>
       </c>
     </row>
@@ -5325,7 +5325,13 @@
       <c r="K77">
         <v>0.6</v>
       </c>
-      <c r="M77" s="2"/>
+      <c r="L77">
+        <v>0.73</v>
+      </c>
+      <c r="M77" s="12">
+        <f t="shared" si="1"/>
+        <v>0.72399999999999998</v>
+      </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="4" t="s">
@@ -5361,7 +5367,13 @@
       <c r="K78">
         <v>0.33</v>
       </c>
-      <c r="M78" s="2"/>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" s="12">
+        <f t="shared" si="1"/>
+        <v>0.62750000000000006</v>
+      </c>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="4" t="s">
@@ -5397,7 +5409,13 @@
       <c r="K79">
         <v>0</v>
       </c>
-      <c r="M79" s="2"/>
+      <c r="L79">
+        <v>0.68</v>
+      </c>
+      <c r="M79" s="12">
+        <f t="shared" si="1"/>
+        <v>0.64400000000000002</v>
+      </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="4" t="s">
@@ -5433,7 +5451,13 @@
       <c r="K80">
         <v>0.79</v>
       </c>
-      <c r="M80" s="2"/>
+      <c r="L80">
+        <v>0.44</v>
+      </c>
+      <c r="M80" s="12">
+        <f t="shared" si="1"/>
+        <v>0.69700000000000006</v>
+      </c>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
@@ -5466,7 +5490,13 @@
       <c r="K81">
         <v>0.52</v>
       </c>
-      <c r="M81" s="6"/>
+      <c r="L81">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M81" s="12">
+        <f t="shared" si="1"/>
+        <v>0.54500000000000004</v>
+      </c>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="3" t="s">
@@ -5502,7 +5532,13 @@
       <c r="K82">
         <v>0.6</v>
       </c>
-      <c r="M82" s="2"/>
+      <c r="L82">
+        <v>0.73</v>
+      </c>
+      <c r="M82" s="12">
+        <f t="shared" si="1"/>
+        <v>0.53400000000000003</v>
+      </c>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="4" t="s">
@@ -5538,7 +5574,13 @@
       <c r="K83">
         <v>0.83</v>
       </c>
-      <c r="M83" s="2"/>
+      <c r="L83">
+        <v>0.68</v>
+      </c>
+      <c r="M83" s="12">
+        <f t="shared" si="1"/>
+        <v>0.8155</v>
+      </c>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" t="s">
@@ -5574,7 +5616,13 @@
       <c r="K84">
         <v>0.44</v>
       </c>
-      <c r="M84" s="6"/>
+      <c r="L84">
+        <v>0.44</v>
+      </c>
+      <c r="M84" s="12">
+        <f t="shared" si="1"/>
+        <v>0.45050000000000001</v>
+      </c>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="4" t="s">
@@ -5610,7 +5658,13 @@
       <c r="K85">
         <v>0.44</v>
       </c>
-      <c r="M85" s="2"/>
+      <c r="L85">
+        <v>0.44</v>
+      </c>
+      <c r="M85" s="12">
+        <f t="shared" si="1"/>
+        <v>0.71199999999999997</v>
+      </c>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="4" t="s">
@@ -5646,7 +5700,13 @@
       <c r="K86">
         <v>0.6</v>
       </c>
-      <c r="M86" s="2"/>
+      <c r="L86">
+        <v>0.73</v>
+      </c>
+      <c r="M86" s="12">
+        <f t="shared" si="1"/>
+        <v>0.64349999999999996</v>
+      </c>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="4" t="s">
@@ -5682,7 +5742,13 @@
       <c r="K87">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M87" s="2"/>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87" s="12">
+        <f t="shared" si="1"/>
+        <v>0.65949999999999998</v>
+      </c>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" t="s">
@@ -5718,7 +5784,13 @@
       <c r="K88">
         <v>0</v>
       </c>
-      <c r="M88" s="6"/>
+      <c r="L88">
+        <v>0.68</v>
+      </c>
+      <c r="M88" s="12">
+        <f t="shared" si="1"/>
+        <v>0.64949999999999997</v>
+      </c>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="4" t="s">
@@ -5754,7 +5826,13 @@
       <c r="K89">
         <v>0.33</v>
       </c>
-      <c r="M89" s="2"/>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" s="12">
+        <f t="shared" si="1"/>
+        <v>0.60499999999999998</v>
+      </c>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="4" t="s">
@@ -5790,7 +5868,13 @@
       <c r="K90">
         <v>0.77</v>
       </c>
-      <c r="M90" s="2"/>
+      <c r="L90">
+        <v>0.41</v>
+      </c>
+      <c r="M90" s="12">
+        <f t="shared" si="1"/>
+        <v>0.69799999999999995</v>
+      </c>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="4" t="s">
@@ -5826,7 +5910,13 @@
       <c r="K91">
         <v>0.44</v>
       </c>
-      <c r="M91" s="2"/>
+      <c r="L91">
+        <v>0.44</v>
+      </c>
+      <c r="M91" s="12">
+        <f t="shared" si="1"/>
+        <v>0.69799999999999995</v>
+      </c>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="4" t="s">
@@ -5865,7 +5955,10 @@
       <c r="L92">
         <v>0.44</v>
       </c>
-      <c r="M92" s="2"/>
+      <c r="M92" s="12">
+        <f t="shared" si="1"/>
+        <v>0.65100000000000002</v>
+      </c>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="4" t="s">
@@ -5901,7 +5994,13 @@
       <c r="K93">
         <v>0</v>
       </c>
-      <c r="M93" s="2"/>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93" s="12">
+        <f t="shared" si="1"/>
+        <v>8.1000000000000016E-2</v>
+      </c>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="4" t="s">
@@ -5937,7 +6036,13 @@
       <c r="K94">
         <v>0.77</v>
       </c>
-      <c r="M94" s="2"/>
+      <c r="L94">
+        <v>0.41</v>
+      </c>
+      <c r="M94" s="12">
+        <f t="shared" si="1"/>
+        <v>0.73499999999999999</v>
+      </c>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="4" t="s">
@@ -5973,7 +6078,13 @@
       <c r="K95">
         <v>0</v>
       </c>
-      <c r="M95" s="2"/>
+      <c r="L95">
+        <v>0.68</v>
+      </c>
+      <c r="M95" s="12">
+        <f t="shared" si="1"/>
+        <v>0.75449999999999995</v>
+      </c>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" t="s">
@@ -6009,7 +6120,13 @@
       <c r="K96">
         <v>0.44</v>
       </c>
-      <c r="M96" s="6"/>
+      <c r="L96">
+        <v>0.44</v>
+      </c>
+      <c r="M96" s="12">
+        <f t="shared" si="1"/>
+        <v>0.60550000000000004</v>
+      </c>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" t="s">
@@ -6048,7 +6165,10 @@
       <c r="L97">
         <v>0.47</v>
       </c>
-      <c r="M97" s="6"/>
+      <c r="M97" s="12">
+        <f t="shared" si="1"/>
+        <v>0.71399999999999997</v>
+      </c>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="4" t="s">
@@ -6087,7 +6207,10 @@
       <c r="L98">
         <v>0.44</v>
       </c>
-      <c r="M98" s="2"/>
+      <c r="M98" s="12">
+        <f t="shared" si="1"/>
+        <v>0.65500000000000003</v>
+      </c>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="4" t="s">
@@ -6123,7 +6246,13 @@
       <c r="K99">
         <v>0.77</v>
       </c>
-      <c r="M99" s="2"/>
+      <c r="L99">
+        <v>0.41</v>
+      </c>
+      <c r="M99" s="12">
+        <f t="shared" si="1"/>
+        <v>0.75449999999999995</v>
+      </c>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="4" t="s">
@@ -6159,7 +6288,13 @@
       <c r="K100">
         <v>0.67</v>
       </c>
-      <c r="M100" s="2"/>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100" s="12">
+        <f t="shared" si="1"/>
+        <v>0.77300000000000002</v>
+      </c>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="4" t="s">
@@ -6195,7 +6330,13 @@
       <c r="K101">
         <v>0.77</v>
       </c>
-      <c r="M101" s="2"/>
+      <c r="L101">
+        <v>0.41</v>
+      </c>
+      <c r="M101" s="12">
+        <f t="shared" si="1"/>
+        <v>0.60649999999999993</v>
+      </c>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="4" t="s">
@@ -6231,7 +6372,13 @@
       <c r="K102">
         <v>0.79</v>
       </c>
-      <c r="M102" s="2"/>
+      <c r="L102">
+        <v>0.44</v>
+      </c>
+      <c r="M102" s="12">
+        <f t="shared" si="1"/>
+        <v>0.71449999999999991</v>
+      </c>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" t="s">
@@ -6267,7 +6414,13 @@
       <c r="K103">
         <v>0.33</v>
       </c>
-      <c r="M103" s="6"/>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103" s="12">
+        <f t="shared" si="1"/>
+        <v>0.55549999999999999</v>
+      </c>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="4" t="s">
@@ -6303,7 +6456,13 @@
       <c r="K104">
         <v>0.6</v>
       </c>
-      <c r="M104" s="2"/>
+      <c r="L104">
+        <v>0.73</v>
+      </c>
+      <c r="M104" s="12">
+        <f t="shared" si="1"/>
+        <v>0.72399999999999998</v>
+      </c>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" t="s">
@@ -6339,7 +6498,13 @@
       <c r="K105">
         <v>0.83</v>
       </c>
-      <c r="M105" s="6"/>
+      <c r="L105">
+        <v>0.68</v>
+      </c>
+      <c r="M105" s="12">
+        <f t="shared" si="1"/>
+        <v>0.84499999999999986</v>
+      </c>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="4" t="s">
@@ -6375,7 +6540,13 @@
       <c r="K106">
         <v>0.52</v>
       </c>
-      <c r="M106" s="2"/>
+      <c r="L106">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M106" s="12">
+        <f t="shared" si="1"/>
+        <v>0.4375</v>
+      </c>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="4" t="s">
@@ -6414,7 +6585,10 @@
       <c r="L107">
         <v>0.44</v>
       </c>
-      <c r="M107" s="2"/>
+      <c r="M107" s="12">
+        <f t="shared" si="1"/>
+        <v>0.64500000000000002</v>
+      </c>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="4" t="s">
@@ -6450,7 +6624,13 @@
       <c r="K108">
         <v>0.83</v>
       </c>
-      <c r="M108" s="2"/>
+      <c r="L108">
+        <v>0.68</v>
+      </c>
+      <c r="M108" s="12">
+        <f t="shared" si="1"/>
+        <v>0.74399999999999988</v>
+      </c>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="4" t="s">
@@ -6483,7 +6663,13 @@
       <c r="K109">
         <v>0.6</v>
       </c>
-      <c r="M109" s="2"/>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109" s="12">
+        <f t="shared" si="1"/>
+        <v>0.53149999999999997</v>
+      </c>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="4" t="s">
@@ -6519,7 +6705,13 @@
       <c r="K110">
         <v>0.85</v>
       </c>
-      <c r="M110" s="2"/>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" s="12">
+        <f t="shared" si="1"/>
+        <v>0.73849999999999993</v>
+      </c>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="4" t="s">
@@ -6555,7 +6747,13 @@
       <c r="K111">
         <v>0.79</v>
       </c>
-      <c r="M111" s="2"/>
+      <c r="L111">
+        <v>0.44</v>
+      </c>
+      <c r="M111" s="12">
+        <f t="shared" si="1"/>
+        <v>0.59899999999999998</v>
+      </c>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" t="s">
@@ -6591,7 +6789,13 @@
       <c r="K112">
         <v>0.83</v>
       </c>
-      <c r="M112" s="6"/>
+      <c r="L112">
+        <v>0.68</v>
+      </c>
+      <c r="M112" s="12">
+        <f t="shared" si="1"/>
+        <v>0.74349999999999994</v>
+      </c>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="4" t="s">
@@ -6627,7 +6831,13 @@
       <c r="K113">
         <v>0.79</v>
       </c>
-      <c r="M113" s="2"/>
+      <c r="L113">
+        <v>0.44</v>
+      </c>
+      <c r="M113" s="12">
+        <f t="shared" si="1"/>
+        <v>0.75950000000000006</v>
+      </c>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="4" t="s">
@@ -6663,7 +6873,13 @@
       <c r="K114">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M114" s="2"/>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114" s="12">
+        <f t="shared" si="1"/>
+        <v>0.81799999999999995</v>
+      </c>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="4" t="s">
@@ -6699,7 +6915,13 @@
       <c r="K115">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M115" s="2"/>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115" s="12">
+        <f t="shared" si="1"/>
+        <v>0.67649999999999999</v>
+      </c>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="3" t="s">
@@ -6735,7 +6957,13 @@
       <c r="K116">
         <v>0.85</v>
       </c>
-      <c r="M116" s="2"/>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116" s="12">
+        <f t="shared" si="1"/>
+        <v>0.71550000000000002</v>
+      </c>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="4" t="s">
@@ -6771,7 +6999,13 @@
       <c r="K117">
         <v>0.44</v>
       </c>
-      <c r="M117" s="2"/>
+      <c r="L117">
+        <v>0.44</v>
+      </c>
+      <c r="M117" s="12">
+        <f t="shared" si="1"/>
+        <v>0.62450000000000006</v>
+      </c>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="4" t="s">
@@ -6807,7 +7041,13 @@
       <c r="K118">
         <v>0.33</v>
       </c>
-      <c r="M118" s="2"/>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118" s="12">
+        <f t="shared" si="1"/>
+        <v>0.57799999999999996</v>
+      </c>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="4" t="s">
@@ -6846,7 +7086,10 @@
       <c r="L119">
         <v>0.44</v>
       </c>
-      <c r="M119" s="2"/>
+      <c r="M119" s="12">
+        <f t="shared" si="1"/>
+        <v>0.5515000000000001</v>
+      </c>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="4" t="s">
@@ -6882,7 +7125,13 @@
       <c r="K120">
         <v>0.79</v>
       </c>
-      <c r="M120" s="2"/>
+      <c r="L120">
+        <v>0.44</v>
+      </c>
+      <c r="M120" s="12">
+        <f t="shared" si="1"/>
+        <v>0.72599999999999998</v>
+      </c>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="4" t="s">
@@ -6918,7 +7167,13 @@
       <c r="K121">
         <v>0.85</v>
       </c>
-      <c r="M121" s="2"/>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121" s="12">
+        <f t="shared" si="1"/>
+        <v>0.62349999999999994</v>
+      </c>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="4" t="s">
@@ -6954,7 +7209,13 @@
       <c r="K122">
         <v>0.6</v>
       </c>
-      <c r="M122" s="2"/>
+      <c r="L122">
+        <v>0.73</v>
+      </c>
+      <c r="M122" s="12">
+        <f t="shared" si="1"/>
+        <v>0.58749999999999991</v>
+      </c>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="4" t="s">
@@ -6990,7 +7251,13 @@
       <c r="K123">
         <v>0</v>
       </c>
-      <c r="M123" s="2"/>
+      <c r="L123">
+        <v>0.68</v>
+      </c>
+      <c r="M123" s="12">
+        <f t="shared" si="1"/>
+        <v>0.74199999999999999</v>
+      </c>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="4" t="s">
@@ -7029,7 +7296,10 @@
       <c r="L124">
         <v>0.44</v>
       </c>
-      <c r="M124" s="2"/>
+      <c r="M124" s="12">
+        <f t="shared" si="1"/>
+        <v>0.28800000000000003</v>
+      </c>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="4" t="s">
@@ -7068,7 +7338,10 @@
       <c r="L125">
         <v>0.47</v>
       </c>
-      <c r="M125" s="2"/>
+      <c r="M125" s="12">
+        <f t="shared" si="1"/>
+        <v>0.63049999999999995</v>
+      </c>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="4" t="s">
@@ -7104,7 +7377,13 @@
       <c r="K126">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M126" s="2"/>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" s="12">
+        <f t="shared" si="1"/>
+        <v>0.68049999999999999</v>
+      </c>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="3" t="s">
@@ -7140,7 +7419,13 @@
       <c r="K127">
         <v>0.85</v>
       </c>
-      <c r="M127" s="2"/>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" s="12">
+        <f t="shared" si="1"/>
+        <v>0.78</v>
+      </c>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="4" t="s">
@@ -7176,7 +7461,13 @@
       <c r="K128">
         <v>0</v>
       </c>
-      <c r="M128" s="2"/>
+      <c r="L128">
+        <v>0.68</v>
+      </c>
+      <c r="M128" s="12">
+        <f t="shared" si="1"/>
+        <v>0.54349999999999998</v>
+      </c>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="4" t="s">
@@ -7212,7 +7503,13 @@
       <c r="K129">
         <v>0.83</v>
       </c>
-      <c r="M129" s="2"/>
+      <c r="L129">
+        <v>0.68</v>
+      </c>
+      <c r="M129" s="12">
+        <f t="shared" si="1"/>
+        <v>0.81499999999999995</v>
+      </c>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="4" t="s">
@@ -7248,7 +7545,13 @@
       <c r="K130">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M130" s="2"/>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130" s="12">
+        <f t="shared" ref="M130" si="2">(((LARGE(D130:F130,1)+LARGE(D130:F130,2))*0.2/2+(LARGE(G130:I130,1)+LARGE(G130:I130,2))*0.5/2+(LARGE(J130:L130,1)+LARGE(J130:L130,2))*0.3/2))</f>
+        <v>0.78300000000000003</v>
+      </c>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="3" t="s">
@@ -7284,6 +7587,9 @@
       <c r="K131">
         <v>0.85</v>
       </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
       <c r="M131" s="2"/>
     </row>
     <row r="132" spans="1:13">
@@ -9521,7 +9827,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="M193" s="12">
-        <f t="shared" ref="M193:M248" si="2">(((LARGE(D193:F193,1)+LARGE(D193:F193,2))*0.2/2+(LARGE(G193:I193,1)+LARGE(G193:I193,2))*0.5/2+(LARGE(J193:L193,1)+LARGE(J193:L193,2))*0.3/2))</f>
+        <f t="shared" ref="M193:M248" si="3">(((LARGE(D193:F193,1)+LARGE(D193:F193,2))*0.2/2+(LARGE(G193:I193,1)+LARGE(G193:I193,2))*0.5/2+(LARGE(J193:L193,1)+LARGE(J193:L193,2))*0.3/2))</f>
         <v>0.76649999999999996</v>
       </c>
     </row>
@@ -9563,7 +9869,7 @@
         <v>0.41</v>
       </c>
       <c r="M194" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.72449999999999992</v>
       </c>
     </row>
@@ -9605,7 +9911,7 @@
         <v>0.53</v>
       </c>
       <c r="M195" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.61199999999999999</v>
       </c>
     </row>
@@ -9647,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.7945000000000001</v>
       </c>
     </row>
@@ -9689,7 +9995,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="M197" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.74749999999999994</v>
       </c>
     </row>
@@ -9731,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="M198" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.6925</v>
       </c>
     </row>
@@ -9773,7 +10079,7 @@
         <v>0.31</v>
       </c>
       <c r="M199" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.71450000000000002</v>
       </c>
     </row>
@@ -9815,7 +10121,7 @@
         <v>0.53</v>
       </c>
       <c r="M200" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.68400000000000005</v>
       </c>
     </row>
@@ -9857,7 +10163,7 @@
         <v>0.44</v>
       </c>
       <c r="M201" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.69300000000000006</v>
       </c>
     </row>
@@ -9899,7 +10205,7 @@
         <v>0</v>
       </c>
       <c r="M202" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.73049999999999993</v>
       </c>
     </row>
@@ -9941,7 +10247,7 @@
         <v>0.59</v>
       </c>
       <c r="M203" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.89400000000000002</v>
       </c>
     </row>
@@ -9983,7 +10289,7 @@
         <v>0.23</v>
       </c>
       <c r="M204" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.6080000000000001</v>
       </c>
     </row>
@@ -10025,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="M205" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.7044999999999999</v>
       </c>
     </row>
@@ -10067,7 +10373,7 @@
         <v>0.44</v>
       </c>
       <c r="M206" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.66700000000000004</v>
       </c>
     </row>
@@ -10109,7 +10415,7 @@
         <v>0.52</v>
       </c>
       <c r="M207" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.75649999999999995</v>
       </c>
     </row>
@@ -10151,7 +10457,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="M208" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.83450000000000002</v>
       </c>
     </row>
@@ -10193,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="M209" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.75850000000000006</v>
       </c>
     </row>
@@ -10235,7 +10541,7 @@
         <v>0.27</v>
       </c>
       <c r="M210" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.72150000000000003</v>
       </c>
     </row>
@@ -10277,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="M211" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.67249999999999999</v>
       </c>
     </row>
@@ -10319,7 +10625,7 @@
         <v>0.23</v>
       </c>
       <c r="M212" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76150000000000007</v>
       </c>
     </row>
@@ -10361,7 +10667,7 @@
         <v>0</v>
       </c>
       <c r="M213" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.79199999999999993</v>
       </c>
     </row>
@@ -10403,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="M214" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.65600000000000003</v>
       </c>
     </row>
@@ -10445,7 +10751,7 @@
         <v>0.41</v>
       </c>
       <c r="M215" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.71400000000000008</v>
       </c>
     </row>
@@ -10487,7 +10793,7 @@
         <v>0.51</v>
       </c>
       <c r="M216" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.72350000000000003</v>
       </c>
     </row>
@@ -10529,7 +10835,7 @@
         <v>0.48</v>
       </c>
       <c r="M217" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.71600000000000008</v>
       </c>
     </row>
@@ -10571,7 +10877,7 @@
         <v>0.31</v>
       </c>
       <c r="M218" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.74949999999999994</v>
       </c>
     </row>
@@ -10613,7 +10919,7 @@
         <v>0.33</v>
       </c>
       <c r="M219" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.72749999999999992</v>
       </c>
     </row>
@@ -10655,7 +10961,7 @@
         <v>0.44</v>
       </c>
       <c r="M220" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.73399999999999999</v>
       </c>
     </row>
@@ -10697,7 +11003,7 @@
         <v>0.44</v>
       </c>
       <c r="M221" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.6705000000000001</v>
       </c>
     </row>
@@ -10739,7 +11045,7 @@
         <v>0.44</v>
       </c>
       <c r="M222" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.55900000000000005</v>
       </c>
     </row>
@@ -10781,7 +11087,7 @@
         <v>0.31</v>
       </c>
       <c r="M223" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76600000000000001</v>
       </c>
     </row>
@@ -10823,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="M224" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.81900000000000006</v>
       </c>
     </row>
@@ -10865,7 +11171,7 @@
         <v>0.31</v>
       </c>
       <c r="M225" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.78699999999999992</v>
       </c>
     </row>
@@ -10907,7 +11213,7 @@
         <v>0.27</v>
       </c>
       <c r="M226" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.60450000000000004</v>
       </c>
     </row>
@@ -10949,7 +11255,7 @@
         <v>0.51</v>
       </c>
       <c r="M227" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.61650000000000005</v>
       </c>
     </row>
@@ -10991,7 +11297,7 @@
         <v>0.41</v>
       </c>
       <c r="M228" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.86950000000000005</v>
       </c>
     </row>
@@ -11033,7 +11339,7 @@
         <v>0</v>
       </c>
       <c r="M229" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.751</v>
       </c>
     </row>
@@ -11075,7 +11381,7 @@
         <v>0.27</v>
       </c>
       <c r="M230" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.74250000000000005</v>
       </c>
     </row>
@@ -11117,7 +11423,7 @@
         <v>0.44</v>
       </c>
       <c r="M231" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.70950000000000002</v>
       </c>
     </row>
@@ -11159,7 +11465,7 @@
         <v>0.27</v>
       </c>
       <c r="M232" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76500000000000001</v>
       </c>
     </row>
@@ -11201,7 +11507,7 @@
         <v>0</v>
       </c>
       <c r="M233" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.70950000000000002</v>
       </c>
     </row>
@@ -11243,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="M234" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
     </row>
@@ -11285,7 +11591,7 @@
         <v>0.27</v>
       </c>
       <c r="M235" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.73450000000000004</v>
       </c>
     </row>
@@ -11327,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="M236" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.73199999999999998</v>
       </c>
     </row>
@@ -11369,7 +11675,7 @@
         <v>0.23</v>
       </c>
       <c r="M237" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.67049999999999998</v>
       </c>
     </row>
@@ -11411,7 +11717,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="M238" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.79049999999999987</v>
       </c>
     </row>
@@ -11453,7 +11759,7 @@
         <v>0.44</v>
       </c>
       <c r="M239" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.5495000000000001</v>
       </c>
     </row>
@@ -11495,7 +11801,7 @@
         <v>0</v>
       </c>
       <c r="M240" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.50249999999999995</v>
       </c>
     </row>
@@ -11537,7 +11843,7 @@
         <v>0.23</v>
       </c>
       <c r="M241" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.68199999999999994</v>
       </c>
     </row>
@@ -11579,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="M242" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.503</v>
       </c>
     </row>
@@ -11621,7 +11927,7 @@
         <v>0.31</v>
       </c>
       <c r="M243" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.65449999999999997</v>
       </c>
     </row>
@@ -11663,7 +11969,7 @@
         <v>0.53</v>
       </c>
       <c r="M244" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.77950000000000008</v>
       </c>
     </row>
@@ -11705,7 +12011,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="M245" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.76500000000000001</v>
       </c>
     </row>
@@ -11747,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="M246" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
     </row>
@@ -11789,7 +12095,7 @@
         <v>0.23</v>
       </c>
       <c r="M247" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.69950000000000001</v>
       </c>
     </row>
@@ -11831,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="M248" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.81500000000000006</v>
       </c>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899B870C-DA03-EB42-BFA0-13A34DD2FB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96529D69-80F4-6B4E-87A8-C1E2225EB6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7549,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="12">
-        <f t="shared" ref="M130" si="2">(((LARGE(D130:F130,1)+LARGE(D130:F130,2))*0.2/2+(LARGE(G130:I130,1)+LARGE(G130:I130,2))*0.5/2+(LARGE(J130:L130,1)+LARGE(J130:L130,2))*0.3/2))</f>
+        <f t="shared" ref="M130:M131" si="2">(((LARGE(D130:F130,1)+LARGE(D130:F130,2))*0.2/2+(LARGE(G130:I130,1)+LARGE(G130:I130,2))*0.5/2+(LARGE(J130:L130,1)+LARGE(J130:L130,2))*0.3/2))</f>
         <v>0.78300000000000003</v>
       </c>
     </row>
@@ -7590,7 +7590,10 @@
       <c r="L131">
         <v>0</v>
       </c>
-      <c r="M131" s="2"/>
+      <c r="M131" s="12">
+        <f t="shared" si="2"/>
+        <v>0.747</v>
+      </c>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="4" t="s">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49547B-9E8F-0D42-9F99-81E32B55DEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8380905D-70C6-AA44-BF93-EBC79D3008C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7756,7 +7756,9 @@
       <c r="F136" s="5">
         <v>0.89</v>
       </c>
-      <c r="G136" s="5"/>
+      <c r="G136" s="5">
+        <v>0.62</v>
+      </c>
       <c r="H136" s="8">
         <v>7.6999999999999999E-2</v>
       </c>
@@ -7769,7 +7771,10 @@
       <c r="K136">
         <v>0.79</v>
       </c>
-      <c r="M136" s="10"/>
+      <c r="M136" s="10">
+        <f t="shared" si="2"/>
+        <v>0.52049999999999996</v>
+      </c>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="3" t="s">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8380905D-70C6-AA44-BF93-EBC79D3008C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1152A0-6113-5349-BB22-66ABDEC9D7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2070,8 +2070,10 @@
     <col min="6" max="6" width="7.42578125" style="5" customWidth="1"/>
     <col min="7" max="7" width="8.140625" customWidth="1"/>
     <col min="8" max="8" width="7.140625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="5"/>
-    <col min="10" max="10" width="7" style="5" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="5" customWidth="1"/>
+    <col min="11" max="12" width="5.85546875" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -5447,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5">
         <v>0.98</v>
@@ -5469,7 +5471,7 @@
       </c>
       <c r="M81" s="10">
         <f t="shared" si="1"/>
-        <v>0.54500000000000004</v>
+        <v>0.64500000000000002</v>
       </c>
     </row>
     <row r="82" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1152A0-6113-5349-BB22-66ABDEC9D7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C683884-0E9E-5F4A-BEF8-D91D767BA242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -9463,7 +9463,7 @@
         <v>0.31</v>
       </c>
       <c r="J177" s="5">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="K177">
         <v>0.83</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="M177" s="10">
         <f t="shared" si="2"/>
-        <v>0.64675000000000005</v>
+        <v>0.67825000000000002</v>
       </c>
     </row>
     <row r="178" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C683884-0E9E-5F4A-BEF8-D91D767BA242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1255A21-6706-E349-8642-4975BC7C5A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -7306,7 +7306,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="J125" s="5">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K125">
         <v>0.5</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="M125" s="10">
         <f t="shared" si="1"/>
-        <v>0.63049999999999995</v>
+        <v>0.66500000000000004</v>
       </c>
     </row>
     <row r="126" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1255A21-6706-E349-8642-4975BC7C5A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3639595-5453-1144-9565-2437182C658E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -5719,11 +5719,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M87" s="10">
         <f t="shared" si="1"/>
-        <v>0.65949999999999998</v>
+        <v>0.70599999999999996</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -6850,11 +6850,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M114" s="10">
         <f t="shared" si="1"/>
-        <v>0.81799999999999995</v>
+        <v>0.86450000000000005</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -6892,11 +6892,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M115" s="10">
         <f t="shared" si="1"/>
-        <v>0.67649999999999999</v>
+        <v>0.72300000000000009</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -7354,11 +7354,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L126">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M126" s="10">
         <f t="shared" si="1"/>
-        <v>0.68049999999999999</v>
+        <v>0.72700000000000009</v>
       </c>
     </row>
     <row r="127" spans="1:13">
@@ -7522,11 +7522,11 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M130" s="10">
         <f t="shared" ref="M130:M192" si="2">(((LARGE(D130:F130,1)+LARGE(D130:F130,2))*0.2/2+(LARGE(G130:I130,1)+LARGE(G130:I130,2))*0.5/2+(LARGE(J130:L130,1)+LARGE(J130:L130,2))*0.3/2))</f>
-        <v>0.78300000000000003</v>
+        <v>0.82950000000000013</v>
       </c>
     </row>
     <row r="131" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3639595-5453-1144-9565-2437182C658E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D26FFFD-0DFD-9D4B-B211-1181069CB2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -8302,14 +8302,14 @@
         <v>0.83</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="L149">
         <v>0.41</v>
       </c>
       <c r="M149" s="10">
         <f t="shared" si="2"/>
-        <v>0.63000000000000012</v>
+        <v>0.69600000000000006</v>
       </c>
     </row>
     <row r="150" spans="1:13">
